--- a/costs.xlsx
+++ b/costs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\recipe-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Servando\Zambales\Dong\recipe-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3489B810-B562-4B9F-9FD1-514CD85452B6}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26157C97-8872-41E0-8EC8-D26C6E81B830}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="552">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -1683,6 +1683,9 @@
   </si>
   <si>
     <t>Lime - Dried, Sliced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water </t>
   </si>
 </sst>
 </file>
@@ -1690,9 +1693,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1842,48 +1845,48 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2200,7 +2203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D529"/>
+  <dimension ref="A1:D530"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -9604,6 +9607,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="530" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A530" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="B530" s="5">
+        <v>0</v>
+      </c>
+      <c r="C530" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D530" s="17" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Servando\Zambales\Dong\recipe-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26157C97-8872-41E0-8EC8-D26C6E81B830}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE52D5FE-C054-4553-AB5D-EEAED7B15BF8}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="692">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -1686,6 +1686,426 @@
   </si>
   <si>
     <t xml:space="preserve">Water </t>
+  </si>
+  <si>
+    <t>Baggoong Alamang - Production</t>
+  </si>
+  <si>
+    <t>Cream Dory 200grams Sweet and Sour</t>
+  </si>
+  <si>
+    <t>Garlic Ginger Paste</t>
+  </si>
+  <si>
+    <t>portion</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>grams</t>
+  </si>
+  <si>
+    <t>pieces</t>
+  </si>
+  <si>
+    <t>Annatto Oil - Production</t>
+  </si>
+  <si>
+    <t>Atsara - Production</t>
+  </si>
+  <si>
+    <t>scoop</t>
+  </si>
+  <si>
+    <t>Tinapa Flakes - Production</t>
+  </si>
+  <si>
+    <t>Soy Sesame Oil - Production</t>
+  </si>
+  <si>
+    <t>BBQ Sauce - Production</t>
+  </si>
+  <si>
+    <t>Bechamel - Production</t>
+  </si>
+  <si>
+    <t>Beef Kaldereta Meat - Production</t>
+  </si>
+  <si>
+    <t>Beef Kaldereta Vegetables -Production</t>
+  </si>
+  <si>
+    <t>Beef Kare Kare Meat - Production</t>
+  </si>
+  <si>
+    <t>Beef Kare Kare Sauce - Production</t>
+  </si>
+  <si>
+    <t>Beef Patty - Production</t>
+  </si>
+  <si>
+    <t>Atay for Lomi - Production</t>
+  </si>
+  <si>
+    <t>Baked Bangus - Production</t>
+  </si>
+  <si>
+    <t>Baked Salmon - Production</t>
+  </si>
+  <si>
+    <t>Baked Salmon Vegetables - Production</t>
+  </si>
+  <si>
+    <t>Beef Bulalo - Production</t>
+  </si>
+  <si>
+    <t>Beef Callos - Production</t>
+  </si>
+  <si>
+    <t>Beef Skin - Production</t>
+  </si>
+  <si>
+    <t>Beef Tapa - Production</t>
+  </si>
+  <si>
+    <t>Beef Tuwalya - Production</t>
+  </si>
+  <si>
+    <t>Belgian Waffle - Production</t>
+  </si>
+  <si>
+    <t>Bingsu - Production</t>
+  </si>
+  <si>
+    <t>Bistek Tagalog - Production</t>
+  </si>
+  <si>
+    <t>Brioche Buns - Production</t>
+  </si>
+  <si>
+    <t>Brioche Loaf - Production</t>
+  </si>
+  <si>
+    <t>Burger Dressing - Production</t>
+  </si>
+  <si>
+    <t>Caramelized Onion - Production</t>
+  </si>
+  <si>
+    <t>Cheese Mix - Production</t>
+  </si>
+  <si>
+    <t>Cheese Sauce - Production</t>
+  </si>
+  <si>
+    <t>Cheesy Beef Fries Meat - Production</t>
+  </si>
+  <si>
+    <t>Chicharon Bulaklak - Production</t>
+  </si>
+  <si>
+    <t>Chicken for Bicol - Production</t>
+  </si>
+  <si>
+    <t>Chicken Inasal - Production</t>
+  </si>
+  <si>
+    <t>Chicken Oil - Production</t>
+  </si>
+  <si>
+    <t>Chicken Satay (3 pieces) - Production</t>
+  </si>
+  <si>
+    <t>Chicken Strips - Production</t>
+  </si>
+  <si>
+    <t>Chicken Surol - Production</t>
+  </si>
+  <si>
+    <t>Chocolate Royale - Production</t>
+  </si>
+  <si>
+    <t>Cilantro Cream - Production</t>
+  </si>
+  <si>
+    <t>Cilantro Soy Sauce - Production</t>
+  </si>
+  <si>
+    <t>Coconut Cream - Production</t>
+  </si>
+  <si>
+    <t>Coral Tuile - Production</t>
+  </si>
+  <si>
+    <t>Corn for Bulalo - Production</t>
+  </si>
+  <si>
+    <t>Crab Meat 50grams - Production</t>
+  </si>
+  <si>
+    <t>Creamy Longganisa Meat - Production</t>
+  </si>
+  <si>
+    <t>Crispy Danggit 25grams - Production</t>
+  </si>
+  <si>
+    <t>Crispy Pata Meat - Production</t>
+  </si>
+  <si>
+    <t>Daing Bangus 1pc - Production</t>
+  </si>
+  <si>
+    <t>Dessicated Coconut Mix - Production</t>
+  </si>
+  <si>
+    <t>Flour Mix for Breading - Production</t>
+  </si>
+  <si>
+    <t>Focaccia 2pcs - Production</t>
+  </si>
+  <si>
+    <t>French Toast 1pc - Production</t>
+  </si>
+  <si>
+    <t>Fried Basil - Production</t>
+  </si>
+  <si>
+    <t>Fried Chicken 450grams - Production</t>
+  </si>
+  <si>
+    <t>Fried Ginger - Production</t>
+  </si>
+  <si>
+    <t>Ground Fried Peanut - Production</t>
+  </si>
+  <si>
+    <t>Toasted Sesame Seeds - Production</t>
+  </si>
+  <si>
+    <t>Garlic Aioli - Production</t>
+  </si>
+  <si>
+    <t>Garlic Butter - Production</t>
+  </si>
+  <si>
+    <t>Garlic Chips - Production</t>
+  </si>
+  <si>
+    <t>Garlic Longganisa 3pcs - Production</t>
+  </si>
+  <si>
+    <t>Garlic Oil - Production</t>
+  </si>
+  <si>
+    <t>Ginger Oil - Production</t>
+  </si>
+  <si>
+    <t>Ginisang Munggo 450grams - Production</t>
+  </si>
+  <si>
+    <t>Gravy Mix - Production</t>
+  </si>
+  <si>
+    <t>Grilled Liempo 250grams - Production</t>
+  </si>
+  <si>
+    <t>Hungarian Sausage 2pcs - Production</t>
+  </si>
+  <si>
+    <t>Inutak Rolls 6pcs - Production</t>
+  </si>
+  <si>
+    <t>Kanto Sauce - Production</t>
+  </si>
+  <si>
+    <t>Lava Cake 1pc - Production</t>
+  </si>
+  <si>
+    <t>Leche Flan 55grams - Production</t>
+  </si>
+  <si>
+    <t>Lechon Kawali 400grams - Production</t>
+  </si>
+  <si>
+    <t>Chasu Roll - 400 grams - Production</t>
+  </si>
+  <si>
+    <t>Lechon Kawali for Munggo - Production</t>
+  </si>
+  <si>
+    <t>Linguine 120grams - Production</t>
+  </si>
+  <si>
+    <t>Lumpia Crepe 1pc - Production</t>
+  </si>
+  <si>
+    <t>Lumpia Vegetable Sauce - Production</t>
+  </si>
+  <si>
+    <t>Lumpiang Sariwa Vegetables - Production</t>
+  </si>
+  <si>
+    <t>Lumpiang Shanghai 6pcs - Production</t>
+  </si>
+  <si>
+    <t>Lumpiang Siomai 6pcs - Production</t>
+  </si>
+  <si>
+    <t>Mahiwagang Kamote 1pc - Production</t>
+  </si>
+  <si>
+    <t>Miki Sariwa 200grams - Production</t>
+  </si>
+  <si>
+    <t>Fried Minced Garlic - Production</t>
+  </si>
+  <si>
+    <t>Okoy Vegetables - Production</t>
+  </si>
+  <si>
+    <t>Palabok Sauce 320grams - Production</t>
+  </si>
+  <si>
+    <t>Pastry Cream - Production</t>
+  </si>
+  <si>
+    <t>Pata Tim 1pc - Production</t>
+  </si>
+  <si>
+    <t>Pata Tim Sauce 600ml - Production</t>
+  </si>
+  <si>
+    <t>Peanut Sauce - Production</t>
+  </si>
+  <si>
+    <t>Penne Pasta 120grams - Production</t>
+  </si>
+  <si>
+    <t>Pinakurat - Production</t>
+  </si>
+  <si>
+    <t>Pizza Dough - Production</t>
+  </si>
+  <si>
+    <t>Pomodoro Sauce - Production</t>
+  </si>
+  <si>
+    <t>Pork Asado - Production</t>
+  </si>
+  <si>
+    <t>Pork Sisig 300grams - Production</t>
+  </si>
+  <si>
+    <t>Pulled Pork BBQ Meat - Production</t>
+  </si>
+  <si>
+    <t>Roasted Garlic 50grams - Production</t>
+  </si>
+  <si>
+    <t>Salmon Cubes 200grams - Production</t>
+  </si>
+  <si>
+    <t>Shoestring Fries 100grams - Production</t>
+  </si>
+  <si>
+    <t>Shrimp 50 grams - Production</t>
+  </si>
+  <si>
+    <t>Sinigang Baboy Meat - Production</t>
+  </si>
+  <si>
+    <t>Sisig Sauce - Production</t>
+  </si>
+  <si>
+    <t>Sliced Cheese - Production</t>
+  </si>
+  <si>
+    <t>Smoked Bacon 60grams - Production</t>
+  </si>
+  <si>
+    <t>Spam 120grams - Production</t>
+  </si>
+  <si>
+    <t>Squid Ball 50grams - Production</t>
+  </si>
+  <si>
+    <t>Steamed Pampano 1pc - Production</t>
+  </si>
+  <si>
+    <t>Sweet &amp; Sour Sauce - Production</t>
+  </si>
+  <si>
+    <t>Thick Bacon 50grams - Production</t>
+  </si>
+  <si>
+    <t>Tinapa Roll 3pcs - Production</t>
+  </si>
+  <si>
+    <t>Tiramisu - Production</t>
+  </si>
+  <si>
+    <t>Tocino 200grams - Production</t>
+  </si>
+  <si>
+    <t>Tokwa Sauce - Production</t>
+  </si>
+  <si>
+    <t>Tomato Salsa - Production</t>
+  </si>
+  <si>
+    <t>Tortilla - Production</t>
+  </si>
+  <si>
+    <t>Tuna Belly 350grams - Production</t>
+  </si>
+  <si>
+    <t>Twister Fries 100grams - Production</t>
+  </si>
+  <si>
+    <t>Ube Champurado - Production</t>
+  </si>
+  <si>
+    <t>Ube Coconut Cream - Production</t>
+  </si>
+  <si>
+    <t>Ube Pudding Mixture - Production</t>
+  </si>
+  <si>
+    <t>Vanilla Cream Puffs 1pc - Production</t>
+  </si>
+  <si>
+    <t>Vanilla Ice Cream 1pc - Production</t>
+  </si>
+  <si>
+    <t>Vanilla Tuile - Production</t>
+  </si>
+  <si>
+    <t>Waffle Cream - Production</t>
+  </si>
+  <si>
+    <t>Chicken Cubes 100 grms - Production</t>
+  </si>
+  <si>
+    <t>Liempo Sharing 450 grams - Production</t>
+  </si>
+  <si>
+    <t>Okoy Mixture - Production</t>
+  </si>
+  <si>
+    <t>Baked Salmon Mixture - Production</t>
+  </si>
+  <si>
+    <t>Boiled Egg - Production</t>
+  </si>
+  <si>
+    <t>Choux Pastry per pc - Production</t>
+  </si>
+  <si>
+    <t>Chocolate Soil per grams - Production</t>
+  </si>
+  <si>
+    <t>Chocolate Ganache - Production</t>
   </si>
 </sst>
 </file>
@@ -1697,7 +2117,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1722,8 +2142,19 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Century Gothic"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1742,8 +2173,86 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFB4C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFA8D08D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFC5E0B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFCCFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1836,11 +2345,107 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1887,6 +2492,78 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2203,19 +2880,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D530"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D665"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2229,7 +2906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -2243,7 +2920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2257,7 +2934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2271,7 +2948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -2285,7 +2962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -2299,7 +2976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -2313,7 +2990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -2327,7 +3004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -2341,7 +3018,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -2355,7 +3032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
@@ -2369,7 +3046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -2383,7 +3060,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
@@ -2397,7 +3074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -2411,7 +3088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
@@ -2425,7 +3102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
@@ -2439,7 +3116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -2453,7 +3130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
@@ -2467,7 +3144,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>24</v>
       </c>
@@ -2481,7 +3158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>26</v>
       </c>
@@ -2495,7 +3172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>27</v>
       </c>
@@ -2509,7 +3186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>28</v>
       </c>
@@ -2523,7 +3200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>29</v>
       </c>
@@ -2537,7 +3214,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -2551,7 +3228,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>32</v>
       </c>
@@ -2565,7 +3242,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
@@ -2579,7 +3256,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>35</v>
       </c>
@@ -2593,7 +3270,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>36</v>
       </c>
@@ -2607,7 +3284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>37</v>
       </c>
@@ -2621,7 +3298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>38</v>
       </c>
@@ -2635,7 +3312,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>40</v>
       </c>
@@ -2649,7 +3326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>41</v>
       </c>
@@ -2663,7 +3340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>42</v>
       </c>
@@ -2677,7 +3354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
@@ -2691,7 +3368,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>45</v>
       </c>
@@ -2705,7 +3382,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>46</v>
       </c>
@@ -2719,7 +3396,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>47</v>
       </c>
@@ -2733,7 +3410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>48</v>
       </c>
@@ -2747,7 +3424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -2761,7 +3438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>50</v>
       </c>
@@ -2775,7 +3452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>51</v>
       </c>
@@ -2789,7 +3466,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>52</v>
       </c>
@@ -2803,7 +3480,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>54</v>
       </c>
@@ -2817,7 +3494,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>55</v>
       </c>
@@ -2831,7 +3508,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>56</v>
       </c>
@@ -2845,7 +3522,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>57</v>
       </c>
@@ -2859,7 +3536,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>58</v>
       </c>
@@ -2873,7 +3550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>59</v>
       </c>
@@ -2887,7 +3564,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>60</v>
       </c>
@@ -2901,7 +3578,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>61</v>
       </c>
@@ -2915,7 +3592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>62</v>
       </c>
@@ -2929,7 +3606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>63</v>
       </c>
@@ -2943,7 +3620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>64</v>
       </c>
@@ -2957,7 +3634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>65</v>
       </c>
@@ -2971,7 +3648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>66</v>
       </c>
@@ -2985,7 +3662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>67</v>
       </c>
@@ -2999,7 +3676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>68</v>
       </c>
@@ -3013,7 +3690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>69</v>
       </c>
@@ -3027,7 +3704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>70</v>
       </c>
@@ -3041,7 +3718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>71</v>
       </c>
@@ -3055,7 +3732,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>72</v>
       </c>
@@ -3069,7 +3746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>73</v>
       </c>
@@ -3083,7 +3760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>74</v>
       </c>
@@ -3097,7 +3774,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>75</v>
       </c>
@@ -3111,7 +3788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>76</v>
       </c>
@@ -3125,7 +3802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>77</v>
       </c>
@@ -3139,7 +3816,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>78</v>
       </c>
@@ -3153,7 +3830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>79</v>
       </c>
@@ -3167,7 +3844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>80</v>
       </c>
@@ -3181,7 +3858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>81</v>
       </c>
@@ -3195,7 +3872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>82</v>
       </c>
@@ -3209,7 +3886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>83</v>
       </c>
@@ -3223,7 +3900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>85</v>
       </c>
@@ -3237,7 +3914,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>86</v>
       </c>
@@ -3251,7 +3928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>87</v>
       </c>
@@ -3265,7 +3942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>88</v>
       </c>
@@ -3279,7 +3956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>89</v>
       </c>
@@ -3293,7 +3970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>90</v>
       </c>
@@ -3307,7 +3984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>91</v>
       </c>
@@ -3321,7 +3998,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>92</v>
       </c>
@@ -3335,7 +4012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>93</v>
       </c>
@@ -3349,7 +4026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>94</v>
       </c>
@@ -3363,7 +4040,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>95</v>
       </c>
@@ -3377,7 +4054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>96</v>
       </c>
@@ -3391,7 +4068,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>97</v>
       </c>
@@ -3405,7 +4082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>98</v>
       </c>
@@ -3419,7 +4096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>99</v>
       </c>
@@ -3433,7 +4110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>100</v>
       </c>
@@ -3447,7 +4124,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>101</v>
       </c>
@@ -3461,7 +4138,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>103</v>
       </c>
@@ -3475,7 +4152,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>104</v>
       </c>
@@ -3489,7 +4166,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>105</v>
       </c>
@@ -3503,7 +4180,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>106</v>
       </c>
@@ -3517,7 +4194,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>107</v>
       </c>
@@ -3531,7 +4208,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>108</v>
       </c>
@@ -3545,7 +4222,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>109</v>
       </c>
@@ -3559,7 +4236,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>110</v>
       </c>
@@ -3573,7 +4250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>111</v>
       </c>
@@ -3587,7 +4264,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>112</v>
       </c>
@@ -3601,7 +4278,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>113</v>
       </c>
@@ -3615,7 +4292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>114</v>
       </c>
@@ -3629,7 +4306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>115</v>
       </c>
@@ -3643,7 +4320,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>117</v>
       </c>
@@ -3657,7 +4334,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>118</v>
       </c>
@@ -3671,7 +4348,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>119</v>
       </c>
@@ -3685,7 +4362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>120</v>
       </c>
@@ -3699,7 +4376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>121</v>
       </c>
@@ -3713,7 +4390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>122</v>
       </c>
@@ -3727,7 +4404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>123</v>
       </c>
@@ -3741,7 +4418,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>124</v>
       </c>
@@ -3755,7 +4432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>125</v>
       </c>
@@ -3769,7 +4446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>126</v>
       </c>
@@ -3783,7 +4460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>127</v>
       </c>
@@ -3797,7 +4474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>128</v>
       </c>
@@ -3811,7 +4488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>129</v>
       </c>
@@ -3825,7 +4502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>130</v>
       </c>
@@ -3839,7 +4516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>131</v>
       </c>
@@ -3853,7 +4530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>132</v>
       </c>
@@ -3867,7 +4544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>133</v>
       </c>
@@ -3881,7 +4558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>134</v>
       </c>
@@ -3895,7 +4572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>135</v>
       </c>
@@ -3909,7 +4586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>136</v>
       </c>
@@ -3923,7 +4600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>137</v>
       </c>
@@ -3937,7 +4614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>138</v>
       </c>
@@ -3951,7 +4628,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>139</v>
       </c>
@@ -3965,7 +4642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>140</v>
       </c>
@@ -3979,7 +4656,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>141</v>
       </c>
@@ -3993,7 +4670,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>142</v>
       </c>
@@ -4007,7 +4684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>143</v>
       </c>
@@ -4021,7 +4698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>144</v>
       </c>
@@ -4035,7 +4712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>146</v>
       </c>
@@ -4049,7 +4726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>147</v>
       </c>
@@ -4063,7 +4740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>148</v>
       </c>
@@ -4077,7 +4754,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>149</v>
       </c>
@@ -4091,7 +4768,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>150</v>
       </c>
@@ -4105,7 +4782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>151</v>
       </c>
@@ -4119,7 +4796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>152</v>
       </c>
@@ -4133,7 +4810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>153</v>
       </c>
@@ -4147,7 +4824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>154</v>
       </c>
@@ -4161,7 +4838,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>155</v>
       </c>
@@ -4175,7 +4852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>156</v>
       </c>
@@ -4189,7 +4866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>157</v>
       </c>
@@ -4203,7 +4880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>158</v>
       </c>
@@ -4217,7 +4894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>159</v>
       </c>
@@ -4231,7 +4908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>160</v>
       </c>
@@ -4245,7 +4922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>161</v>
       </c>
@@ -4259,7 +4936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>162</v>
       </c>
@@ -4273,7 +4950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>163</v>
       </c>
@@ -4287,7 +4964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>164</v>
       </c>
@@ -4301,7 +4978,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>165</v>
       </c>
@@ -4315,7 +4992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>166</v>
       </c>
@@ -4329,7 +5006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>167</v>
       </c>
@@ -4343,7 +5020,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>168</v>
       </c>
@@ -4357,7 +5034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>169</v>
       </c>
@@ -4371,7 +5048,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>170</v>
       </c>
@@ -4385,7 +5062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>171</v>
       </c>
@@ -4399,7 +5076,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>172</v>
       </c>
@@ -4413,7 +5090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>173</v>
       </c>
@@ -4427,7 +5104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>174</v>
       </c>
@@ -4441,7 +5118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>175</v>
       </c>
@@ -4455,7 +5132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>176</v>
       </c>
@@ -4469,7 +5146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>177</v>
       </c>
@@ -4483,7 +5160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>178</v>
       </c>
@@ -4497,7 +5174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>179</v>
       </c>
@@ -4511,7 +5188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>180</v>
       </c>
@@ -4525,7 +5202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>181</v>
       </c>
@@ -4539,7 +5216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>182</v>
       </c>
@@ -4553,7 +5230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>183</v>
       </c>
@@ -4567,7 +5244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>184</v>
       </c>
@@ -4581,7 +5258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>185</v>
       </c>
@@ -4595,7 +5272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>186</v>
       </c>
@@ -4609,7 +5286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>187</v>
       </c>
@@ -4623,7 +5300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>188</v>
       </c>
@@ -4637,7 +5314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>189</v>
       </c>
@@ -4651,7 +5328,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>190</v>
       </c>
@@ -4665,7 +5342,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>191</v>
       </c>
@@ -4679,7 +5356,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>192</v>
       </c>
@@ -4693,7 +5370,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>193</v>
       </c>
@@ -4707,7 +5384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>194</v>
       </c>
@@ -4721,7 +5398,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>195</v>
       </c>
@@ -4735,7 +5412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>196</v>
       </c>
@@ -4749,7 +5426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>197</v>
       </c>
@@ -4763,7 +5440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>198</v>
       </c>
@@ -4777,7 +5454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>199</v>
       </c>
@@ -4791,7 +5468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>200</v>
       </c>
@@ -4805,7 +5482,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>202</v>
       </c>
@@ -4819,7 +5496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>203</v>
       </c>
@@ -4833,7 +5510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>204</v>
       </c>
@@ -4847,7 +5524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>205</v>
       </c>
@@ -4861,7 +5538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>206</v>
       </c>
@@ -4875,7 +5552,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>207</v>
       </c>
@@ -4889,7 +5566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>208</v>
       </c>
@@ -4903,7 +5580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>209</v>
       </c>
@@ -4917,7 +5594,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>210</v>
       </c>
@@ -4931,7 +5608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>211</v>
       </c>
@@ -4945,7 +5622,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>212</v>
       </c>
@@ -4959,7 +5636,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>213</v>
       </c>
@@ -4973,7 +5650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>214</v>
       </c>
@@ -4987,7 +5664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>215</v>
       </c>
@@ -5001,7 +5678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>216</v>
       </c>
@@ -5015,7 +5692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>217</v>
       </c>
@@ -5029,7 +5706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>218</v>
       </c>
@@ -5043,7 +5720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>219</v>
       </c>
@@ -5057,7 +5734,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>220</v>
       </c>
@@ -5071,7 +5748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>221</v>
       </c>
@@ -5085,7 +5762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>222</v>
       </c>
@@ -5099,7 +5776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>223</v>
       </c>
@@ -5113,7 +5790,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>225</v>
       </c>
@@ -5127,7 +5804,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>227</v>
       </c>
@@ -5141,7 +5818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>228</v>
       </c>
@@ -5155,7 +5832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>229</v>
       </c>
@@ -5169,7 +5846,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>230</v>
       </c>
@@ -5183,7 +5860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>231</v>
       </c>
@@ -5197,7 +5874,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>232</v>
       </c>
@@ -5211,7 +5888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>233</v>
       </c>
@@ -5225,7 +5902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>234</v>
       </c>
@@ -5239,7 +5916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>235</v>
       </c>
@@ -5253,7 +5930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>236</v>
       </c>
@@ -5267,7 +5944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>237</v>
       </c>
@@ -5281,7 +5958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>238</v>
       </c>
@@ -5295,7 +5972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>239</v>
       </c>
@@ -5309,7 +5986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>240</v>
       </c>
@@ -5323,7 +6000,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
         <v>241</v>
       </c>
@@ -5337,7 +6014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>242</v>
       </c>
@@ -5351,7 +6028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>243</v>
       </c>
@@ -5365,7 +6042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>244</v>
       </c>
@@ -5379,7 +6056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>245</v>
       </c>
@@ -5393,7 +6070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>246</v>
       </c>
@@ -5407,7 +6084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>247</v>
       </c>
@@ -5421,7 +6098,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>248</v>
       </c>
@@ -5435,7 +6112,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>249</v>
       </c>
@@ -5449,7 +6126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>250</v>
       </c>
@@ -5463,7 +6140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>251</v>
       </c>
@@ -5477,7 +6154,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>252</v>
       </c>
@@ -5491,7 +6168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>253</v>
       </c>
@@ -5505,7 +6182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>254</v>
       </c>
@@ -5519,7 +6196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>255</v>
       </c>
@@ -5533,7 +6210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>256</v>
       </c>
@@ -5547,7 +6224,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>257</v>
       </c>
@@ -5561,7 +6238,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>258</v>
       </c>
@@ -5575,7 +6252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>259</v>
       </c>
@@ -5589,7 +6266,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>260</v>
       </c>
@@ -5603,7 +6280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>261</v>
       </c>
@@ -5617,7 +6294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>262</v>
       </c>
@@ -5631,7 +6308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>263</v>
       </c>
@@ -5645,7 +6322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>264</v>
       </c>
@@ -5659,7 +6336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>265</v>
       </c>
@@ -5673,7 +6350,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>266</v>
       </c>
@@ -5687,7 +6364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>267</v>
       </c>
@@ -5701,7 +6378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>268</v>
       </c>
@@ -5715,7 +6392,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>269</v>
       </c>
@@ -5729,7 +6406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>270</v>
       </c>
@@ -5743,7 +6420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>271</v>
       </c>
@@ -5757,7 +6434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>272</v>
       </c>
@@ -5771,7 +6448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>273</v>
       </c>
@@ -5785,7 +6462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>274</v>
       </c>
@@ -5799,7 +6476,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>275</v>
       </c>
@@ -5813,7 +6490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>276</v>
       </c>
@@ -5827,7 +6504,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>277</v>
       </c>
@@ -5841,7 +6518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>278</v>
       </c>
@@ -5855,7 +6532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>279</v>
       </c>
@@ -5869,7 +6546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>280</v>
       </c>
@@ -5883,7 +6560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>281</v>
       </c>
@@ -5897,7 +6574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>282</v>
       </c>
@@ -5911,7 +6588,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>283</v>
       </c>
@@ -5925,7 +6602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>284</v>
       </c>
@@ -5939,7 +6616,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>285</v>
       </c>
@@ -5953,7 +6630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>286</v>
       </c>
@@ -5967,7 +6644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>287</v>
       </c>
@@ -5981,7 +6658,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>288</v>
       </c>
@@ -5995,7 +6672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>289</v>
       </c>
@@ -6009,7 +6686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>290</v>
       </c>
@@ -6023,7 +6700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>291</v>
       </c>
@@ -6037,7 +6714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>292</v>
       </c>
@@ -6051,7 +6728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>293</v>
       </c>
@@ -6065,7 +6742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>294</v>
       </c>
@@ -6079,7 +6756,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>296</v>
       </c>
@@ -6093,7 +6770,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>297</v>
       </c>
@@ -6107,7 +6784,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>298</v>
       </c>
@@ -6121,7 +6798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>299</v>
       </c>
@@ -6135,7 +6812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>300</v>
       </c>
@@ -6149,7 +6826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>301</v>
       </c>
@@ -6163,7 +6840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>302</v>
       </c>
@@ -6177,7 +6854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>303</v>
       </c>
@@ -6191,7 +6868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>304</v>
       </c>
@@ -6205,7 +6882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>305</v>
       </c>
@@ -6219,7 +6896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>306</v>
       </c>
@@ -6233,7 +6910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>307</v>
       </c>
@@ -6247,7 +6924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>308</v>
       </c>
@@ -6261,7 +6938,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>309</v>
       </c>
@@ -6275,7 +6952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>310</v>
       </c>
@@ -6289,7 +6966,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>311</v>
       </c>
@@ -6303,7 +6980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>312</v>
       </c>
@@ -6317,7 +6994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>313</v>
       </c>
@@ -6331,7 +7008,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>314</v>
       </c>
@@ -6345,7 +7022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>315</v>
       </c>
@@ -6359,7 +7036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>316</v>
       </c>
@@ -6373,7 +7050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>317</v>
       </c>
@@ -6387,7 +7064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>318</v>
       </c>
@@ -6401,7 +7078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>319</v>
       </c>
@@ -6415,7 +7092,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>320</v>
       </c>
@@ -6429,7 +7106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>321</v>
       </c>
@@ -6443,7 +7120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>322</v>
       </c>
@@ -6457,7 +7134,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>323</v>
       </c>
@@ -6471,7 +7148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>324</v>
       </c>
@@ -6485,7 +7162,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>325</v>
       </c>
@@ -6499,7 +7176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>326</v>
       </c>
@@ -6513,7 +7190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>327</v>
       </c>
@@ -6527,7 +7204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>328</v>
       </c>
@@ -6541,7 +7218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>329</v>
       </c>
@@ -6555,7 +7232,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>330</v>
       </c>
@@ -6569,7 +7246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>331</v>
       </c>
@@ -6583,7 +7260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>332</v>
       </c>
@@ -6597,7 +7274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>333</v>
       </c>
@@ -6611,7 +7288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>334</v>
       </c>
@@ -6625,7 +7302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>335</v>
       </c>
@@ -6639,7 +7316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>336</v>
       </c>
@@ -6653,7 +7330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>337</v>
       </c>
@@ -6667,7 +7344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>338</v>
       </c>
@@ -6681,7 +7358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>339</v>
       </c>
@@ -6695,7 +7372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>340</v>
       </c>
@@ -6709,7 +7386,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>341</v>
       </c>
@@ -6723,7 +7400,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>343</v>
       </c>
@@ -6737,7 +7414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>344</v>
       </c>
@@ -6751,7 +7428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>345</v>
       </c>
@@ -6765,7 +7442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>346</v>
       </c>
@@ -6779,7 +7456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>347</v>
       </c>
@@ -6793,7 +7470,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>348</v>
       </c>
@@ -6807,7 +7484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>349</v>
       </c>
@@ -6821,7 +7498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>350</v>
       </c>
@@ -6835,7 +7512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>351</v>
       </c>
@@ -6849,7 +7526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>352</v>
       </c>
@@ -6863,7 +7540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>353</v>
       </c>
@@ -6877,7 +7554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>354</v>
       </c>
@@ -6891,7 +7568,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>355</v>
       </c>
@@ -6905,7 +7582,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>356</v>
       </c>
@@ -6919,7 +7596,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>357</v>
       </c>
@@ -6933,7 +7610,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>358</v>
       </c>
@@ -6947,7 +7624,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>359</v>
       </c>
@@ -6961,7 +7638,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>360</v>
       </c>
@@ -6975,7 +7652,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>361</v>
       </c>
@@ -6989,7 +7666,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>362</v>
       </c>
@@ -7003,7 +7680,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>363</v>
       </c>
@@ -7017,7 +7694,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>364</v>
       </c>
@@ -7031,7 +7708,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>365</v>
       </c>
@@ -7045,7 +7722,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>366</v>
       </c>
@@ -7059,7 +7736,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>367</v>
       </c>
@@ -7073,7 +7750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>368</v>
       </c>
@@ -7087,7 +7764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>369</v>
       </c>
@@ -7101,7 +7778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>370</v>
       </c>
@@ -7115,7 +7792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>371</v>
       </c>
@@ -7129,7 +7806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>372</v>
       </c>
@@ -7143,7 +7820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>373</v>
       </c>
@@ -7157,7 +7834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>374</v>
       </c>
@@ -7171,7 +7848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>375</v>
       </c>
@@ -7185,7 +7862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>376</v>
       </c>
@@ -7199,7 +7876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>377</v>
       </c>
@@ -7213,7 +7890,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>378</v>
       </c>
@@ -7227,7 +7904,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>379</v>
       </c>
@@ -7241,7 +7918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>380</v>
       </c>
@@ -7255,7 +7932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>381</v>
       </c>
@@ -7269,7 +7946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>382</v>
       </c>
@@ -7283,7 +7960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>383</v>
       </c>
@@ -7297,7 +7974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>384</v>
       </c>
@@ -7311,7 +7988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>385</v>
       </c>
@@ -7325,7 +8002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>386</v>
       </c>
@@ -7339,7 +8016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>387</v>
       </c>
@@ -7353,7 +8030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>388</v>
       </c>
@@ -7367,7 +8044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>389</v>
       </c>
@@ -7381,7 +8058,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>390</v>
       </c>
@@ -7395,7 +8072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>391</v>
       </c>
@@ -7409,7 +8086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>392</v>
       </c>
@@ -7423,7 +8100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>393</v>
       </c>
@@ -7437,7 +8114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>394</v>
       </c>
@@ -7451,7 +8128,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>395</v>
       </c>
@@ -7465,7 +8142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>396</v>
       </c>
@@ -7479,7 +8156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>397</v>
       </c>
@@ -7493,7 +8170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>398</v>
       </c>
@@ -7507,7 +8184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>399</v>
       </c>
@@ -7521,7 +8198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>400</v>
       </c>
@@ -7535,7 +8212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>401</v>
       </c>
@@ -7549,7 +8226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>402</v>
       </c>
@@ -7563,7 +8240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>403</v>
       </c>
@@ -7577,7 +8254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>404</v>
       </c>
@@ -7591,7 +8268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>405</v>
       </c>
@@ -7605,7 +8282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>406</v>
       </c>
@@ -7619,7 +8296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>407</v>
       </c>
@@ -7633,7 +8310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>408</v>
       </c>
@@ -7647,7 +8324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>409</v>
       </c>
@@ -7661,7 +8338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>410</v>
       </c>
@@ -7675,7 +8352,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>411</v>
       </c>
@@ -7689,7 +8366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>412</v>
       </c>
@@ -7703,7 +8380,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>413</v>
       </c>
@@ -7717,7 +8394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>414</v>
       </c>
@@ -7731,7 +8408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>415</v>
       </c>
@@ -7745,7 +8422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>416</v>
       </c>
@@ -7759,7 +8436,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>417</v>
       </c>
@@ -7773,7 +8450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>418</v>
       </c>
@@ -7787,7 +8464,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>419</v>
       </c>
@@ -7801,7 +8478,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>420</v>
       </c>
@@ -7815,7 +8492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>421</v>
       </c>
@@ -7829,7 +8506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>422</v>
       </c>
@@ -7843,7 +8520,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>423</v>
       </c>
@@ -7857,7 +8534,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>424</v>
       </c>
@@ -7871,7 +8548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
         <v>425</v>
       </c>
@@ -7885,7 +8562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>426</v>
       </c>
@@ -7899,7 +8576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>427</v>
       </c>
@@ -7913,7 +8590,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>428</v>
       </c>
@@ -7927,7 +8604,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="410" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>429</v>
       </c>
@@ -7941,7 +8618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>430</v>
       </c>
@@ -7955,7 +8632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>431</v>
       </c>
@@ -7969,7 +8646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>432</v>
       </c>
@@ -7983,7 +8660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>433</v>
       </c>
@@ -7997,7 +8674,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>434</v>
       </c>
@@ -8011,7 +8688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>435</v>
       </c>
@@ -8025,7 +8702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>436</v>
       </c>
@@ -8039,7 +8716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>437</v>
       </c>
@@ -8053,7 +8730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>438</v>
       </c>
@@ -8067,7 +8744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="420" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>439</v>
       </c>
@@ -8081,7 +8758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>440</v>
       </c>
@@ -8095,7 +8772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>441</v>
       </c>
@@ -8109,7 +8786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>442</v>
       </c>
@@ -8123,7 +8800,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="424" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>443</v>
       </c>
@@ -8137,7 +8814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="425" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>444</v>
       </c>
@@ -8151,7 +8828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="426" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>445</v>
       </c>
@@ -8165,7 +8842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>446</v>
       </c>
@@ -8179,7 +8856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>447</v>
       </c>
@@ -8193,7 +8870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>448</v>
       </c>
@@ -8207,7 +8884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>449</v>
       </c>
@@ -8221,7 +8898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>450</v>
       </c>
@@ -8235,7 +8912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>451</v>
       </c>
@@ -8249,7 +8926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>452</v>
       </c>
@@ -8263,7 +8940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>453</v>
       </c>
@@ -8277,7 +8954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>454</v>
       </c>
@@ -8291,7 +8968,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>455</v>
       </c>
@@ -8305,7 +8982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>456</v>
       </c>
@@ -8319,7 +8996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>457</v>
       </c>
@@ -8333,7 +9010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>458</v>
       </c>
@@ -8347,7 +9024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>459</v>
       </c>
@@ -8361,7 +9038,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>460</v>
       </c>
@@ -8375,7 +9052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>461</v>
       </c>
@@ -8389,7 +9066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>462</v>
       </c>
@@ -8403,7 +9080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>463</v>
       </c>
@@ -8417,7 +9094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>464</v>
       </c>
@@ -8431,7 +9108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>465</v>
       </c>
@@ -8445,7 +9122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>466</v>
       </c>
@@ -8459,7 +9136,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>467</v>
       </c>
@@ -8473,7 +9150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>468</v>
       </c>
@@ -8487,7 +9164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>469</v>
       </c>
@@ -8501,7 +9178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>470</v>
       </c>
@@ -8515,7 +9192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
         <v>471</v>
       </c>
@@ -8529,7 +9206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="453" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>472</v>
       </c>
@@ -8543,7 +9220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>473</v>
       </c>
@@ -8557,7 +9234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:4" ht="27" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>474</v>
       </c>
@@ -8571,7 +9248,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>475</v>
       </c>
@@ -8585,7 +9262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>476</v>
       </c>
@@ -8599,7 +9276,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="458" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>477</v>
       </c>
@@ -8613,7 +9290,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>478</v>
       </c>
@@ -8627,7 +9304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="460" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>479</v>
       </c>
@@ -8641,7 +9318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>480</v>
       </c>
@@ -8655,7 +9332,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>481</v>
       </c>
@@ -8669,7 +9346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>482</v>
       </c>
@@ -8683,7 +9360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>483</v>
       </c>
@@ -8697,7 +9374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="465" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>484</v>
       </c>
@@ -8711,7 +9388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>485</v>
       </c>
@@ -8725,7 +9402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>486</v>
       </c>
@@ -8739,7 +9416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
         <v>487</v>
       </c>
@@ -8753,7 +9430,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="469" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>488</v>
       </c>
@@ -8767,7 +9444,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>489</v>
       </c>
@@ -8781,7 +9458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>490</v>
       </c>
@@ -8795,7 +9472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>491</v>
       </c>
@@ -8809,7 +9486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="473" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>492</v>
       </c>
@@ -8823,7 +9500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="474" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>493</v>
       </c>
@@ -8837,7 +9514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="475" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
         <v>494</v>
       </c>
@@ -8851,7 +9528,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="476" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
         <v>495</v>
       </c>
@@ -8865,7 +9542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="477" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>496</v>
       </c>
@@ -8879,7 +9556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="478" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>497</v>
       </c>
@@ -8893,7 +9570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
         <v>498</v>
       </c>
@@ -8907,7 +9584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="480" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>499</v>
       </c>
@@ -8921,7 +9598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>500</v>
       </c>
@@ -8935,7 +9612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>501</v>
       </c>
@@ -8949,7 +9626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>502</v>
       </c>
@@ -8963,7 +9640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>503</v>
       </c>
@@ -8977,7 +9654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>504</v>
       </c>
@@ -8991,7 +9668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>505</v>
       </c>
@@ -9005,7 +9682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>506</v>
       </c>
@@ -9019,7 +9696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>507</v>
       </c>
@@ -9033,7 +9710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>508</v>
       </c>
@@ -9047,7 +9724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>509</v>
       </c>
@@ -9061,7 +9738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>510</v>
       </c>
@@ -9075,7 +9752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>511</v>
       </c>
@@ -9089,7 +9766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>512</v>
       </c>
@@ -9103,7 +9780,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>514</v>
       </c>
@@ -9117,7 +9794,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>516</v>
       </c>
@@ -9131,7 +9808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>517</v>
       </c>
@@ -9145,7 +9822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A497" s="4" t="s">
         <v>518</v>
       </c>
@@ -9159,7 +9836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
         <v>519</v>
       </c>
@@ -9173,7 +9850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="499" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" s="4" t="s">
         <v>520</v>
       </c>
@@ -9187,7 +9864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
         <v>521</v>
       </c>
@@ -9201,7 +9878,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="501" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" s="4" t="s">
         <v>522</v>
       </c>
@@ -9215,7 +9892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
         <v>523</v>
       </c>
@@ -9229,7 +9906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>524</v>
       </c>
@@ -9243,7 +9920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="504" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>525</v>
       </c>
@@ -9257,7 +9934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="505" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>526</v>
       </c>
@@ -9271,7 +9948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>527</v>
       </c>
@@ -9285,7 +9962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="507" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>528</v>
       </c>
@@ -9299,7 +9976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>529</v>
       </c>
@@ -9313,7 +9990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>530</v>
       </c>
@@ -9327,7 +10004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="510" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>531</v>
       </c>
@@ -9341,7 +10018,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="511" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
         <v>532</v>
       </c>
@@ -9355,7 +10032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
         <v>533</v>
       </c>
@@ -9369,7 +10046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>534</v>
       </c>
@@ -9383,7 +10060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
         <v>535</v>
       </c>
@@ -9397,7 +10074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A515" s="8" t="s">
         <v>536</v>
       </c>
@@ -9411,7 +10088,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A516" s="8" t="s">
         <v>537</v>
       </c>
@@ -9425,7 +10102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A517" s="9" t="s">
         <v>538</v>
       </c>
@@ -9439,7 +10116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A518" s="12" t="s">
         <v>539</v>
       </c>
@@ -9453,7 +10130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" s="12" t="s">
         <v>540</v>
       </c>
@@ -9467,7 +10144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" s="12" t="s">
         <v>541</v>
       </c>
@@ -9481,7 +10158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="521" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>542</v>
       </c>
@@ -9495,7 +10172,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A522" s="12" t="s">
         <v>543</v>
       </c>
@@ -9509,7 +10186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A523" s="12" t="s">
         <v>544</v>
       </c>
@@ -9523,7 +10200,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="524" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
         <v>545</v>
       </c>
@@ -9537,7 +10214,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="525" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
         <v>546</v>
       </c>
@@ -9551,7 +10228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="526" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
         <v>547</v>
       </c>
@@ -9565,7 +10242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A527" s="12" t="s">
         <v>548</v>
       </c>
@@ -9579,7 +10256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="528" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A528" s="12" t="s">
         <v>549</v>
       </c>
@@ -9593,7 +10270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="529" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
         <v>550</v>
       </c>
@@ -9607,7 +10284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="530" spans="1:4" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
         <v>551</v>
       </c>
@@ -9617,8 +10294,1898 @@
       <c r="C530" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D530" s="17" t="s">
-        <v>5</v>
+      <c r="D530" s="50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A531" s="19" t="s">
+        <v>559</v>
+      </c>
+      <c r="B531" s="38">
+        <v>0.19</v>
+      </c>
+      <c r="C531" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D531" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A532" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="B532" s="39">
+        <v>12.63</v>
+      </c>
+      <c r="C532" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D532" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A533" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="B533" s="38">
+        <v>0.13</v>
+      </c>
+      <c r="C533" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D533" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A534" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="B534" s="38">
+        <v>0.36</v>
+      </c>
+      <c r="C534" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D534" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A535" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="B535" s="39">
+        <v>270</v>
+      </c>
+      <c r="C535" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D535" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A536" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="B536" s="39">
+        <v>350</v>
+      </c>
+      <c r="C536" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D536" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A537" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="B537" s="39">
+        <v>36.5</v>
+      </c>
+      <c r="C537" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D537" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A538" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="B538" s="40">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="C538" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D538" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A539" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="B539" s="40">
+        <v>0.111</v>
+      </c>
+      <c r="C539" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D539" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A540" s="22" t="s">
+        <v>575</v>
+      </c>
+      <c r="B540" s="39">
+        <v>261.39999999999998</v>
+      </c>
+      <c r="C540" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D540" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A541" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="B541" s="39">
+        <v>153.33000000000001</v>
+      </c>
+      <c r="C541" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D541" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A542" s="23" t="s">
+        <v>566</v>
+      </c>
+      <c r="B542" s="40">
+        <v>219.96</v>
+      </c>
+      <c r="C542" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D542" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A543" s="23" t="s">
+        <v>567</v>
+      </c>
+      <c r="B543" s="40">
+        <v>24.75</v>
+      </c>
+      <c r="C543" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D543" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A544" s="22" t="s">
+        <v>568</v>
+      </c>
+      <c r="B544" s="39">
+        <v>85</v>
+      </c>
+      <c r="C544" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D544" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A545" s="22" t="s">
+        <v>569</v>
+      </c>
+      <c r="B545" s="39">
+        <v>73.12</v>
+      </c>
+      <c r="C545" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D545" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A546" s="22" t="s">
+        <v>570</v>
+      </c>
+      <c r="B546" s="42">
+        <v>72.010000000000005</v>
+      </c>
+      <c r="C546" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D546" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A547" s="22" t="s">
+        <v>577</v>
+      </c>
+      <c r="B547" s="43">
+        <v>8</v>
+      </c>
+      <c r="C547" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D547" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A548" s="19" t="s">
+        <v>578</v>
+      </c>
+      <c r="B548" s="43">
+        <v>72.91</v>
+      </c>
+      <c r="C548" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D548" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A549" s="22" t="s">
+        <v>579</v>
+      </c>
+      <c r="B549" s="43">
+        <v>10</v>
+      </c>
+      <c r="C549" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D549" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A550" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="B550" s="44">
+        <v>18.5</v>
+      </c>
+      <c r="C550" s="41" t="s">
+        <v>558</v>
+      </c>
+      <c r="D550" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A551" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="B551" s="40">
+        <v>23.66</v>
+      </c>
+      <c r="C551" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D551" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A552" s="19" t="s">
+        <v>582</v>
+      </c>
+      <c r="B552" s="40">
+        <v>196.62</v>
+      </c>
+      <c r="C552" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D552" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A553" s="22" t="s">
+        <v>583</v>
+      </c>
+      <c r="B553" s="40">
+        <v>11.02</v>
+      </c>
+      <c r="C553" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D553" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A554" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="B554" s="40">
+        <v>8.65</v>
+      </c>
+      <c r="C554" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="D554" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A555" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="B555" s="40">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="C555" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D555" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A556" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="B556" s="36">
+        <v>0.53</v>
+      </c>
+      <c r="C556" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D556" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A557" s="19" t="s">
+        <v>587</v>
+      </c>
+      <c r="B557" s="40">
+        <v>36.03</v>
+      </c>
+      <c r="C557" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D557" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A558" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="B558" s="38">
+        <v>0.31</v>
+      </c>
+      <c r="C558" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D558" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A559" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="B559" s="39">
+        <v>25.39</v>
+      </c>
+      <c r="C559" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D559" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A560" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="B560" s="39">
+        <v>80.88</v>
+      </c>
+      <c r="C560" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D560" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A561" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="B561" s="43">
+        <v>179.51</v>
+      </c>
+      <c r="C561" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D561" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A562" s="25" t="s">
+        <v>592</v>
+      </c>
+      <c r="B562" s="39">
+        <v>77.59</v>
+      </c>
+      <c r="C562" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D562" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A563" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="B563" s="40">
+        <v>0.312</v>
+      </c>
+      <c r="C563" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D563" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A564" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="B564" s="40">
+        <v>124.44</v>
+      </c>
+      <c r="C564" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D564" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A565" s="26" t="s">
+        <v>595</v>
+      </c>
+      <c r="B565" s="39">
+        <v>18</v>
+      </c>
+      <c r="C565" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D565" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A566" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="B566" s="39">
+        <v>193.88</v>
+      </c>
+      <c r="C566" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D566" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A567" s="25" t="s">
+        <v>597</v>
+      </c>
+      <c r="B567" s="40">
+        <v>86.83</v>
+      </c>
+      <c r="C567" s="37" t="s">
+        <v>555</v>
+      </c>
+      <c r="D567" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A568" s="28" t="s">
+        <v>598</v>
+      </c>
+      <c r="B568" s="45">
+        <v>0.6</v>
+      </c>
+      <c r="C568" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D568" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A569" s="27" t="s">
+        <v>599</v>
+      </c>
+      <c r="B569" s="46">
+        <v>0.379</v>
+      </c>
+      <c r="C569" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D569" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A570" s="27" t="s">
+        <v>600</v>
+      </c>
+      <c r="B570" s="46">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="C570" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D570" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A571" s="25" t="s">
+        <v>601</v>
+      </c>
+      <c r="B571" s="46">
+        <v>0.46</v>
+      </c>
+      <c r="C571" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D571" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A572" s="26" t="s">
+        <v>602</v>
+      </c>
+      <c r="B572" s="47">
+        <v>7</v>
+      </c>
+      <c r="C572" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D572" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A573" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="B573" s="43">
+        <v>39</v>
+      </c>
+      <c r="C573" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D573" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A574" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="B574" s="39">
+        <v>30</v>
+      </c>
+      <c r="C574" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D574" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A575" s="30" t="s">
+        <v>604</v>
+      </c>
+      <c r="B575" s="39">
+        <v>72.87</v>
+      </c>
+      <c r="C575" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D575" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A576" s="25" t="s">
+        <v>605</v>
+      </c>
+      <c r="B576" s="39">
+        <v>30</v>
+      </c>
+      <c r="C576" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D576" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A577" s="31" t="s">
+        <v>606</v>
+      </c>
+      <c r="B577" s="39">
+        <v>317.8</v>
+      </c>
+      <c r="C577" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D577" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A578" s="25" t="s">
+        <v>607</v>
+      </c>
+      <c r="B578" s="39">
+        <v>70</v>
+      </c>
+      <c r="C578" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D578" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A579" s="27" t="s">
+        <v>608</v>
+      </c>
+      <c r="B579" s="40">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="C579" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D579" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A580" s="25" t="s">
+        <v>609</v>
+      </c>
+      <c r="B580" s="40">
+        <v>0.128</v>
+      </c>
+      <c r="C580" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D580" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A581" s="30" t="s">
+        <v>610</v>
+      </c>
+      <c r="B581" s="39">
+        <v>14.92</v>
+      </c>
+      <c r="C581" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D581" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A582" s="25" t="s">
+        <v>611</v>
+      </c>
+      <c r="B582" s="39">
+        <v>17.3</v>
+      </c>
+      <c r="C582" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D582" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A583" s="25" t="s">
+        <v>612</v>
+      </c>
+      <c r="B583" s="40">
+        <v>1</v>
+      </c>
+      <c r="C583" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D583" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A584" s="30" t="s">
+        <v>613</v>
+      </c>
+      <c r="B584" s="39">
+        <v>112.14</v>
+      </c>
+      <c r="C584" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D584" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A585" s="25" t="s">
+        <v>614</v>
+      </c>
+      <c r="B585" s="40">
+        <v>0.71</v>
+      </c>
+      <c r="C585" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D585" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A586" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="B586" s="40">
+        <v>0.18</v>
+      </c>
+      <c r="C586" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D586" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A587" s="25" t="s">
+        <v>616</v>
+      </c>
+      <c r="B587" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="C587" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D587" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A588" s="25" t="s">
+        <v>617</v>
+      </c>
+      <c r="B588" s="38">
+        <v>0.46</v>
+      </c>
+      <c r="C588" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D588" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A589" s="25" t="s">
+        <v>618</v>
+      </c>
+      <c r="B589" s="40">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="C589" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D589" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A590" s="25" t="s">
+        <v>619</v>
+      </c>
+      <c r="B590" s="40">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="C590" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D590" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A591" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="B591" s="40">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="C591" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D591" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A592" s="25" t="s">
+        <v>620</v>
+      </c>
+      <c r="B592" s="39">
+        <v>63.92</v>
+      </c>
+      <c r="C592" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D592" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A593" s="25" t="s">
+        <v>621</v>
+      </c>
+      <c r="B593" s="48">
+        <v>0.54</v>
+      </c>
+      <c r="C593" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D593" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A594" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="B594" s="36">
+        <v>0.71</v>
+      </c>
+      <c r="C594" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D594" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A595" s="25" t="s">
+        <v>623</v>
+      </c>
+      <c r="B595" s="39">
+        <v>43.56</v>
+      </c>
+      <c r="C595" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D595" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A596" s="25" t="s">
+        <v>624</v>
+      </c>
+      <c r="B596" s="36">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="C596" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D596" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A597" s="30" t="s">
+        <v>625</v>
+      </c>
+      <c r="B597" s="36">
+        <v>118.91</v>
+      </c>
+      <c r="C597" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D597" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A598" s="26" t="s">
+        <v>626</v>
+      </c>
+      <c r="B598" s="39">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="C598" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D598" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A599" s="25" t="s">
+        <v>627</v>
+      </c>
+      <c r="B599" s="40">
+        <v>17.5</v>
+      </c>
+      <c r="C599" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D599" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A600" s="25" t="s">
+        <v>628</v>
+      </c>
+      <c r="B600" s="38">
+        <v>0.153</v>
+      </c>
+      <c r="C600" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D600" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A601" s="25" t="s">
+        <v>629</v>
+      </c>
+      <c r="B601" s="40">
+        <v>37.444000000000003</v>
+      </c>
+      <c r="C601" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D601" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A602" s="25" t="s">
+        <v>630</v>
+      </c>
+      <c r="B602" s="40">
+        <v>15.24</v>
+      </c>
+      <c r="C602" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D602" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A603" s="32" t="s">
+        <v>632</v>
+      </c>
+      <c r="B603" s="39">
+        <v>208.78</v>
+      </c>
+      <c r="C603" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D603" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A604" s="25" t="s">
+        <v>631</v>
+      </c>
+      <c r="B604" s="39">
+        <v>203.77</v>
+      </c>
+      <c r="C604" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D604" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A605" s="25" t="s">
+        <v>633</v>
+      </c>
+      <c r="B605" s="39">
+        <v>102</v>
+      </c>
+      <c r="C605" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D605" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A606" s="30" t="s">
+        <v>634</v>
+      </c>
+      <c r="B606" s="39">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="C606" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D606" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A607" s="33" t="s">
+        <v>635</v>
+      </c>
+      <c r="B607" s="39">
+        <v>11.73</v>
+      </c>
+      <c r="C607" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D607" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A608" s="25" t="s">
+        <v>636</v>
+      </c>
+      <c r="B608" s="40">
+        <v>3.1E-2</v>
+      </c>
+      <c r="C608" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D608" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A609" s="33" t="s">
+        <v>637</v>
+      </c>
+      <c r="B609" s="40">
+        <v>23.2</v>
+      </c>
+      <c r="C609" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D609" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A610" s="25" t="s">
+        <v>638</v>
+      </c>
+      <c r="B610" s="39">
+        <v>75</v>
+      </c>
+      <c r="C610" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D610" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A611" s="25" t="s">
+        <v>639</v>
+      </c>
+      <c r="B611" s="39">
+        <v>75</v>
+      </c>
+      <c r="C611" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D611" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A612" s="25" t="s">
+        <v>640</v>
+      </c>
+      <c r="B612" s="40">
+        <v>46.36</v>
+      </c>
+      <c r="C612" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D612" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A613" s="34" t="s">
+        <v>641</v>
+      </c>
+      <c r="B613" s="39">
+        <v>20</v>
+      </c>
+      <c r="C613" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D613" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A614" s="25" t="s">
+        <v>642</v>
+      </c>
+      <c r="B614" s="36">
+        <v>0.18</v>
+      </c>
+      <c r="C614" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D614" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A615" s="25" t="s">
+        <v>643</v>
+      </c>
+      <c r="B615" s="40">
+        <v>47.7</v>
+      </c>
+      <c r="C615" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D615" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A616" s="25" t="s">
+        <v>644</v>
+      </c>
+      <c r="B616" s="39">
+        <v>43.28</v>
+      </c>
+      <c r="C616" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D616" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A617" s="27" t="s">
+        <v>645</v>
+      </c>
+      <c r="B617" s="40">
+        <v>0.223</v>
+      </c>
+      <c r="C617" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D617" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A618" s="18" t="s">
+        <v>646</v>
+      </c>
+      <c r="B618" s="39">
+        <v>255.59</v>
+      </c>
+      <c r="C618" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D618" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A619" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="B619" s="39">
+        <v>38.03</v>
+      </c>
+      <c r="C619" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D619" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A620" s="25" t="s">
+        <v>648</v>
+      </c>
+      <c r="B620" s="40">
+        <v>0.26</v>
+      </c>
+      <c r="C620" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D620" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A621" s="30" t="s">
+        <v>649</v>
+      </c>
+      <c r="B621" s="39">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="C621" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D621" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A622" s="25" t="s">
+        <v>650</v>
+      </c>
+      <c r="B622" s="38">
+        <v>0.11</v>
+      </c>
+      <c r="C622" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D622" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A623" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="B623" s="40">
+        <v>34.24</v>
+      </c>
+      <c r="C623" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D623" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A624" s="25" t="s">
+        <v>652</v>
+      </c>
+      <c r="B624" s="39">
+        <v>77</v>
+      </c>
+      <c r="C624" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D624" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A625" s="25" t="s">
+        <v>653</v>
+      </c>
+      <c r="B625" s="39">
+        <v>130.91</v>
+      </c>
+      <c r="C625" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D625" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A626" s="25" t="s">
+        <v>654</v>
+      </c>
+      <c r="B626" s="36">
+        <v>118.01</v>
+      </c>
+      <c r="C626" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D626" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A627" s="25" t="s">
+        <v>655</v>
+      </c>
+      <c r="B627" s="40">
+        <v>43.75</v>
+      </c>
+      <c r="C627" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D627" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A628" s="30" t="s">
+        <v>656</v>
+      </c>
+      <c r="B628" s="39">
+        <v>25.55</v>
+      </c>
+      <c r="C628" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D628" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A629" s="25" t="s">
+        <v>657</v>
+      </c>
+      <c r="B629" s="39">
+        <v>200</v>
+      </c>
+      <c r="C629" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D629" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A630" s="30" t="s">
+        <v>658</v>
+      </c>
+      <c r="B630" s="39">
+        <v>30</v>
+      </c>
+      <c r="C630" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D630" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A631" s="26" t="s">
+        <v>659</v>
+      </c>
+      <c r="B631" s="39">
+        <v>22.25</v>
+      </c>
+      <c r="C631" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D631" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A632" s="26" t="s">
+        <v>660</v>
+      </c>
+      <c r="B632" s="39">
+        <v>155.62</v>
+      </c>
+      <c r="C632" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D632" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A633" s="25" t="s">
+        <v>661</v>
+      </c>
+      <c r="B633" s="40">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="C633" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D633" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A634" s="25" t="s">
+        <v>662</v>
+      </c>
+      <c r="B634" s="40">
+        <v>66</v>
+      </c>
+      <c r="C634" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D634" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A635" s="26" t="s">
+        <v>663</v>
+      </c>
+      <c r="B635" s="39">
+        <v>36</v>
+      </c>
+      <c r="C635" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D635" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A636" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="B636" s="36">
+        <v>0.42</v>
+      </c>
+      <c r="C636" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D636" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A637" s="25" t="s">
+        <v>664</v>
+      </c>
+      <c r="B637" s="39">
+        <v>74.78</v>
+      </c>
+      <c r="C637" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D637" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A638" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="B638" s="39">
+        <v>8</v>
+      </c>
+      <c r="C638" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D638" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A639" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="B639" s="39">
+        <v>125</v>
+      </c>
+      <c r="C639" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D639" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A640" s="25" t="s">
+        <v>667</v>
+      </c>
+      <c r="B640" s="40">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="C640" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D640" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A641" s="30" t="s">
+        <v>668</v>
+      </c>
+      <c r="B641" s="39">
+        <v>49.5</v>
+      </c>
+      <c r="C641" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D641" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A642" s="25" t="s">
+        <v>562</v>
+      </c>
+      <c r="B642" s="40">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="C642" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D642" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A643" s="25" t="s">
+        <v>669</v>
+      </c>
+      <c r="B643" s="39">
+        <v>86.22</v>
+      </c>
+      <c r="C643" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D643" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A644" s="25" t="s">
+        <v>670</v>
+      </c>
+      <c r="B644" s="40">
+        <v>175</v>
+      </c>
+      <c r="C644" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D644" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A645" s="25" t="s">
+        <v>671</v>
+      </c>
+      <c r="B645" s="39">
+        <v>57.15</v>
+      </c>
+      <c r="C645" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D645" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A646" s="25" t="s">
+        <v>672</v>
+      </c>
+      <c r="B646" s="40">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="C646" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D646" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A647" s="25" t="s">
+        <v>673</v>
+      </c>
+      <c r="B647" s="38">
+        <v>0.12</v>
+      </c>
+      <c r="C647" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D647" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A648" s="25" t="s">
+        <v>674</v>
+      </c>
+      <c r="B648" s="40">
+        <v>14.35</v>
+      </c>
+      <c r="C648" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D648" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A649" s="25" t="s">
+        <v>675</v>
+      </c>
+      <c r="B649" s="39">
+        <v>117.25</v>
+      </c>
+      <c r="C649" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D649" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A650" s="25" t="s">
+        <v>676</v>
+      </c>
+      <c r="B650" s="39">
+        <v>38</v>
+      </c>
+      <c r="C650" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D650" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A651" s="25" t="s">
+        <v>677</v>
+      </c>
+      <c r="B651" s="40">
+        <v>37.33</v>
+      </c>
+      <c r="C651" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D651" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A652" s="27" t="s">
+        <v>678</v>
+      </c>
+      <c r="B652" s="40">
+        <v>0.222</v>
+      </c>
+      <c r="C652" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D652" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A653" s="25" t="s">
+        <v>679</v>
+      </c>
+      <c r="B653" s="40">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="C653" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D653" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A654" s="25" t="s">
+        <v>680</v>
+      </c>
+      <c r="B654" s="40">
+        <v>33</v>
+      </c>
+      <c r="C654" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D654" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A655" s="25" t="s">
+        <v>681</v>
+      </c>
+      <c r="B655" s="40">
+        <v>29.5</v>
+      </c>
+      <c r="C655" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="D655" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A656" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="B656" s="45">
+        <v>0.24</v>
+      </c>
+      <c r="C656" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D656" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A657" s="35" t="s">
+        <v>683</v>
+      </c>
+      <c r="B657" s="46">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="C657" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D657" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A658" s="35" t="s">
+        <v>684</v>
+      </c>
+      <c r="B658" s="45">
+        <v>34</v>
+      </c>
+      <c r="C658" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D658" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A659" s="35" t="s">
+        <v>685</v>
+      </c>
+      <c r="B659" s="45">
+        <v>209.55</v>
+      </c>
+      <c r="C659" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D659" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A660" s="28" t="s">
+        <v>686</v>
+      </c>
+      <c r="B660" s="45">
+        <v>0.05</v>
+      </c>
+      <c r="C660" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D660" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A661" s="28" t="s">
+        <v>687</v>
+      </c>
+      <c r="B661" s="45">
+        <v>0.81</v>
+      </c>
+      <c r="C661" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D661" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A662" s="28" t="s">
+        <v>688</v>
+      </c>
+      <c r="B662" s="45">
+        <v>10</v>
+      </c>
+      <c r="C662" s="49" t="s">
+        <v>558</v>
+      </c>
+      <c r="D662" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A663" s="28" t="s">
+        <v>689</v>
+      </c>
+      <c r="B663" s="40">
+        <v>8.5</v>
+      </c>
+      <c r="C663" s="49" t="s">
+        <v>558</v>
+      </c>
+      <c r="D663" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A664" s="28" t="s">
+        <v>690</v>
+      </c>
+      <c r="B664" s="40">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="C664" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D664" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A665" s="28" t="s">
+        <v>691</v>
+      </c>
+      <c r="B665" s="40">
+        <v>0.35</v>
+      </c>
+      <c r="C665" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D665" s="51" t="s">
+        <v>556</v>
       </c>
     </row>
   </sheetData>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE52D5FE-C054-4553-AB5D-EEAED7B15BF8}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F1230-7FC5-4E0C-A60E-1E929CB57F29}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="693">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2106,6 +2106,9 @@
   </si>
   <si>
     <t>Chocolate Ganache - Production</t>
+  </si>
+  <si>
+    <t>Sugar Syrup - Production</t>
   </si>
 </sst>
 </file>
@@ -2880,19 +2883,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D665"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D666"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2906,7 +2909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -2920,7 +2923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2934,7 +2937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -2948,7 +2951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -2962,7 +2965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -2976,7 +2979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -2990,7 +2993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -3004,7 +3007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -3018,7 +3021,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -3032,7 +3035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
@@ -3046,7 +3049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -3060,7 +3063,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
@@ -3074,7 +3077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -3088,7 +3091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
@@ -3102,7 +3105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
@@ -3116,7 +3119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
@@ -3130,7 +3133,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>23</v>
       </c>
@@ -3144,7 +3147,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>24</v>
       </c>
@@ -3158,7 +3161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>26</v>
       </c>
@@ -3172,7 +3175,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>27</v>
       </c>
@@ -3186,7 +3189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>28</v>
       </c>
@@ -3200,7 +3203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>29</v>
       </c>
@@ -3214,7 +3217,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -3228,7 +3231,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>32</v>
       </c>
@@ -3242,7 +3245,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>33</v>
       </c>
@@ -3256,7 +3259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>35</v>
       </c>
@@ -3270,7 +3273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>36</v>
       </c>
@@ -3284,7 +3287,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>37</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>38</v>
       </c>
@@ -3312,7 +3315,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>40</v>
       </c>
@@ -3326,7 +3329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>41</v>
       </c>
@@ -3340,7 +3343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>42</v>
       </c>
@@ -3354,7 +3357,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>43</v>
       </c>
@@ -3368,7 +3371,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>45</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>46</v>
       </c>
@@ -3396,7 +3399,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>47</v>
       </c>
@@ -3410,7 +3413,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>48</v>
       </c>
@@ -3424,7 +3427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -3438,7 +3441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>50</v>
       </c>
@@ -3452,7 +3455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>51</v>
       </c>
@@ -3466,7 +3469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>52</v>
       </c>
@@ -3480,7 +3483,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>54</v>
       </c>
@@ -3494,7 +3497,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>55</v>
       </c>
@@ -3508,7 +3511,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>56</v>
       </c>
@@ -3522,7 +3525,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>57</v>
       </c>
@@ -3536,7 +3539,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>58</v>
       </c>
@@ -3550,7 +3553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>59</v>
       </c>
@@ -3564,7 +3567,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>60</v>
       </c>
@@ -3578,7 +3581,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>61</v>
       </c>
@@ -3592,7 +3595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>62</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>63</v>
       </c>
@@ -3620,7 +3623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>64</v>
       </c>
@@ -3634,7 +3637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>65</v>
       </c>
@@ -3648,7 +3651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>66</v>
       </c>
@@ -3662,7 +3665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>67</v>
       </c>
@@ -3676,7 +3679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>68</v>
       </c>
@@ -3690,7 +3693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>69</v>
       </c>
@@ -3704,7 +3707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>70</v>
       </c>
@@ -3718,7 +3721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>71</v>
       </c>
@@ -3732,7 +3735,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>72</v>
       </c>
@@ -3746,7 +3749,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>73</v>
       </c>
@@ -3760,7 +3763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>74</v>
       </c>
@@ -3774,7 +3777,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>75</v>
       </c>
@@ -3788,7 +3791,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>76</v>
       </c>
@@ -3802,7 +3805,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>77</v>
       </c>
@@ -3816,7 +3819,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>78</v>
       </c>
@@ -3830,7 +3833,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>79</v>
       </c>
@@ -3844,7 +3847,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>80</v>
       </c>
@@ -3858,7 +3861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>81</v>
       </c>
@@ -3872,7 +3875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>82</v>
       </c>
@@ -3886,7 +3889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>83</v>
       </c>
@@ -3900,7 +3903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>85</v>
       </c>
@@ -3914,7 +3917,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>86</v>
       </c>
@@ -3928,7 +3931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>87</v>
       </c>
@@ -3942,7 +3945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>88</v>
       </c>
@@ -3956,7 +3959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>89</v>
       </c>
@@ -3970,7 +3973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>90</v>
       </c>
@@ -3984,7 +3987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>91</v>
       </c>
@@ -3998,7 +4001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>92</v>
       </c>
@@ -4012,7 +4015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>93</v>
       </c>
@@ -4026,7 +4029,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>94</v>
       </c>
@@ -4040,7 +4043,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>95</v>
       </c>
@@ -4054,7 +4057,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>96</v>
       </c>
@@ -4068,7 +4071,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>97</v>
       </c>
@@ -4082,7 +4085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>98</v>
       </c>
@@ -4096,7 +4099,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>99</v>
       </c>
@@ -4110,7 +4113,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>100</v>
       </c>
@@ -4124,7 +4127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>101</v>
       </c>
@@ -4138,7 +4141,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>103</v>
       </c>
@@ -4152,7 +4155,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>104</v>
       </c>
@@ -4166,7 +4169,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>105</v>
       </c>
@@ -4180,7 +4183,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>106</v>
       </c>
@@ -4194,7 +4197,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>107</v>
       </c>
@@ -4208,7 +4211,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>108</v>
       </c>
@@ -4222,7 +4225,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>109</v>
       </c>
@@ -4236,7 +4239,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>110</v>
       </c>
@@ -4250,7 +4253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>111</v>
       </c>
@@ -4264,7 +4267,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>112</v>
       </c>
@@ -4278,7 +4281,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>113</v>
       </c>
@@ -4292,7 +4295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>114</v>
       </c>
@@ -4306,7 +4309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>115</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>117</v>
       </c>
@@ -4334,7 +4337,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>118</v>
       </c>
@@ -4348,7 +4351,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>119</v>
       </c>
@@ -4362,7 +4365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>120</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>121</v>
       </c>
@@ -4390,7 +4393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>122</v>
       </c>
@@ -4404,7 +4407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>123</v>
       </c>
@@ -4418,7 +4421,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>124</v>
       </c>
@@ -4432,7 +4435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>125</v>
       </c>
@@ -4446,7 +4449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>126</v>
       </c>
@@ -4460,7 +4463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>127</v>
       </c>
@@ -4474,7 +4477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>128</v>
       </c>
@@ -4488,7 +4491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>129</v>
       </c>
@@ -4502,7 +4505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>130</v>
       </c>
@@ -4516,7 +4519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>131</v>
       </c>
@@ -4530,7 +4533,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>132</v>
       </c>
@@ -4544,7 +4547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>133</v>
       </c>
@@ -4558,7 +4561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>134</v>
       </c>
@@ -4572,7 +4575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>135</v>
       </c>
@@ -4586,7 +4589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>136</v>
       </c>
@@ -4600,7 +4603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>137</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>138</v>
       </c>
@@ -4628,7 +4631,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>139</v>
       </c>
@@ -4642,7 +4645,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>140</v>
       </c>
@@ -4656,7 +4659,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>141</v>
       </c>
@@ -4670,7 +4673,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>142</v>
       </c>
@@ -4684,7 +4687,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>143</v>
       </c>
@@ -4698,7 +4701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>144</v>
       </c>
@@ -4712,7 +4715,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>146</v>
       </c>
@@ -4726,7 +4729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>147</v>
       </c>
@@ -4740,7 +4743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>148</v>
       </c>
@@ -4754,7 +4757,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>149</v>
       </c>
@@ -4768,7 +4771,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>150</v>
       </c>
@@ -4782,7 +4785,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>151</v>
       </c>
@@ -4796,7 +4799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>152</v>
       </c>
@@ -4810,7 +4813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>153</v>
       </c>
@@ -4824,7 +4827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>154</v>
       </c>
@@ -4838,7 +4841,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>155</v>
       </c>
@@ -4852,7 +4855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>156</v>
       </c>
@@ -4866,7 +4869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>157</v>
       </c>
@@ -4880,7 +4883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>158</v>
       </c>
@@ -4894,7 +4897,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>159</v>
       </c>
@@ -4908,7 +4911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>160</v>
       </c>
@@ -4922,7 +4925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>161</v>
       </c>
@@ -4936,7 +4939,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>162</v>
       </c>
@@ -4950,7 +4953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>163</v>
       </c>
@@ -4964,7 +4967,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>164</v>
       </c>
@@ -4978,7 +4981,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>165</v>
       </c>
@@ -4992,7 +4995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>166</v>
       </c>
@@ -5006,7 +5009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>167</v>
       </c>
@@ -5020,7 +5023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>168</v>
       </c>
@@ -5034,7 +5037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>169</v>
       </c>
@@ -5048,7 +5051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>170</v>
       </c>
@@ -5062,7 +5065,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>171</v>
       </c>
@@ -5076,7 +5079,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>172</v>
       </c>
@@ -5090,7 +5093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>173</v>
       </c>
@@ -5104,7 +5107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>174</v>
       </c>
@@ -5118,7 +5121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>175</v>
       </c>
@@ -5132,7 +5135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>176</v>
       </c>
@@ -5146,7 +5149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>177</v>
       </c>
@@ -5160,7 +5163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>178</v>
       </c>
@@ -5174,7 +5177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>179</v>
       </c>
@@ -5188,7 +5191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>180</v>
       </c>
@@ -5202,7 +5205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>181</v>
       </c>
@@ -5216,7 +5219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>182</v>
       </c>
@@ -5230,7 +5233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>183</v>
       </c>
@@ -5244,7 +5247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>184</v>
       </c>
@@ -5258,7 +5261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>185</v>
       </c>
@@ -5272,7 +5275,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>186</v>
       </c>
@@ -5286,7 +5289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>187</v>
       </c>
@@ -5300,7 +5303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>188</v>
       </c>
@@ -5314,7 +5317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>189</v>
       </c>
@@ -5328,7 +5331,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>190</v>
       </c>
@@ -5342,7 +5345,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>191</v>
       </c>
@@ -5356,7 +5359,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>192</v>
       </c>
@@ -5370,7 +5373,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>193</v>
       </c>
@@ -5384,7 +5387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>194</v>
       </c>
@@ -5398,7 +5401,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>195</v>
       </c>
@@ -5412,7 +5415,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>196</v>
       </c>
@@ -5426,7 +5429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>197</v>
       </c>
@@ -5440,7 +5443,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>198</v>
       </c>
@@ -5454,7 +5457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>199</v>
       </c>
@@ -5468,7 +5471,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>200</v>
       </c>
@@ -5482,7 +5485,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>202</v>
       </c>
@@ -5496,7 +5499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>203</v>
       </c>
@@ -5510,7 +5513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>204</v>
       </c>
@@ -5524,7 +5527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>205</v>
       </c>
@@ -5538,7 +5541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>206</v>
       </c>
@@ -5552,7 +5555,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>207</v>
       </c>
@@ -5566,7 +5569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>208</v>
       </c>
@@ -5580,7 +5583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>209</v>
       </c>
@@ -5594,7 +5597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>210</v>
       </c>
@@ -5608,7 +5611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>211</v>
       </c>
@@ -5622,7 +5625,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>212</v>
       </c>
@@ -5636,7 +5639,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>213</v>
       </c>
@@ -5650,7 +5653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>214</v>
       </c>
@@ -5664,7 +5667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>215</v>
       </c>
@@ -5678,7 +5681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>216</v>
       </c>
@@ -5692,7 +5695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>217</v>
       </c>
@@ -5706,7 +5709,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>218</v>
       </c>
@@ -5720,7 +5723,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>219</v>
       </c>
@@ -5734,7 +5737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>220</v>
       </c>
@@ -5748,7 +5751,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>221</v>
       </c>
@@ -5762,7 +5765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>222</v>
       </c>
@@ -5776,7 +5779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>223</v>
       </c>
@@ -5790,7 +5793,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>225</v>
       </c>
@@ -5804,7 +5807,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>227</v>
       </c>
@@ -5818,7 +5821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>228</v>
       </c>
@@ -5832,7 +5835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>229</v>
       </c>
@@ -5846,7 +5849,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>230</v>
       </c>
@@ -5860,7 +5863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>231</v>
       </c>
@@ -5874,7 +5877,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>232</v>
       </c>
@@ -5888,7 +5891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>233</v>
       </c>
@@ -5902,7 +5905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>234</v>
       </c>
@@ -5916,7 +5919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>235</v>
       </c>
@@ -5930,7 +5933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>236</v>
       </c>
@@ -5944,7 +5947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>237</v>
       </c>
@@ -5958,7 +5961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>238</v>
       </c>
@@ -5972,7 +5975,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>239</v>
       </c>
@@ -5986,7 +5989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>240</v>
       </c>
@@ -6000,7 +6003,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
         <v>241</v>
       </c>
@@ -6014,7 +6017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>242</v>
       </c>
@@ -6028,7 +6031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>243</v>
       </c>
@@ -6042,7 +6045,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>244</v>
       </c>
@@ -6056,7 +6059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>245</v>
       </c>
@@ -6070,7 +6073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>246</v>
       </c>
@@ -6084,7 +6087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>247</v>
       </c>
@@ -6098,7 +6101,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>248</v>
       </c>
@@ -6112,7 +6115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>249</v>
       </c>
@@ -6126,7 +6129,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>250</v>
       </c>
@@ -6140,7 +6143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>251</v>
       </c>
@@ -6154,7 +6157,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>252</v>
       </c>
@@ -6168,7 +6171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>253</v>
       </c>
@@ -6182,7 +6185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>254</v>
       </c>
@@ -6196,7 +6199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>255</v>
       </c>
@@ -6210,7 +6213,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>256</v>
       </c>
@@ -6224,7 +6227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>257</v>
       </c>
@@ -6238,7 +6241,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>258</v>
       </c>
@@ -6252,7 +6255,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>259</v>
       </c>
@@ -6266,7 +6269,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>260</v>
       </c>
@@ -6280,7 +6283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>261</v>
       </c>
@@ -6294,7 +6297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>262</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>263</v>
       </c>
@@ -6322,7 +6325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>264</v>
       </c>
@@ -6336,7 +6339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>265</v>
       </c>
@@ -6350,7 +6353,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>266</v>
       </c>
@@ -6364,7 +6367,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>267</v>
       </c>
@@ -6378,7 +6381,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>268</v>
       </c>
@@ -6392,7 +6395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>269</v>
       </c>
@@ -6406,7 +6409,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>270</v>
       </c>
@@ -6420,7 +6423,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>271</v>
       </c>
@@ -6434,7 +6437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>272</v>
       </c>
@@ -6448,7 +6451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>273</v>
       </c>
@@ -6462,7 +6465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>274</v>
       </c>
@@ -6476,7 +6479,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>275</v>
       </c>
@@ -6490,7 +6493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>276</v>
       </c>
@@ -6504,7 +6507,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>277</v>
       </c>
@@ -6518,7 +6521,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>278</v>
       </c>
@@ -6532,7 +6535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>279</v>
       </c>
@@ -6546,7 +6549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>280</v>
       </c>
@@ -6560,7 +6563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>281</v>
       </c>
@@ -6574,7 +6577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>282</v>
       </c>
@@ -6588,7 +6591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>283</v>
       </c>
@@ -6602,7 +6605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>284</v>
       </c>
@@ -6616,7 +6619,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>285</v>
       </c>
@@ -6630,7 +6633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>286</v>
       </c>
@@ -6644,7 +6647,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>287</v>
       </c>
@@ -6658,7 +6661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>288</v>
       </c>
@@ -6672,7 +6675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>289</v>
       </c>
@@ -6686,7 +6689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>290</v>
       </c>
@@ -6700,7 +6703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>291</v>
       </c>
@@ -6714,7 +6717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>292</v>
       </c>
@@ -6728,7 +6731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>293</v>
       </c>
@@ -6742,7 +6745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>294</v>
       </c>
@@ -6756,7 +6759,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>296</v>
       </c>
@@ -6770,7 +6773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>297</v>
       </c>
@@ -6784,7 +6787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>298</v>
       </c>
@@ -6798,7 +6801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>299</v>
       </c>
@@ -6812,7 +6815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>300</v>
       </c>
@@ -6826,7 +6829,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>301</v>
       </c>
@@ -6840,7 +6843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>302</v>
       </c>
@@ -6854,7 +6857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>303</v>
       </c>
@@ -6868,7 +6871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>304</v>
       </c>
@@ -6882,7 +6885,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>305</v>
       </c>
@@ -6896,7 +6899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>306</v>
       </c>
@@ -6910,7 +6913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>307</v>
       </c>
@@ -6924,7 +6927,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>308</v>
       </c>
@@ -6938,7 +6941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>309</v>
       </c>
@@ -6952,7 +6955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>310</v>
       </c>
@@ -6966,7 +6969,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>311</v>
       </c>
@@ -6980,7 +6983,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>312</v>
       </c>
@@ -6994,7 +6997,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>313</v>
       </c>
@@ -7008,7 +7011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>314</v>
       </c>
@@ -7022,7 +7025,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>315</v>
       </c>
@@ -7036,7 +7039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>316</v>
       </c>
@@ -7050,7 +7053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>317</v>
       </c>
@@ -7064,7 +7067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>318</v>
       </c>
@@ -7078,7 +7081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>319</v>
       </c>
@@ -7092,7 +7095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>320</v>
       </c>
@@ -7106,7 +7109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>321</v>
       </c>
@@ -7120,7 +7123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>322</v>
       </c>
@@ -7134,7 +7137,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>323</v>
       </c>
@@ -7148,7 +7151,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>324</v>
       </c>
@@ -7162,7 +7165,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>325</v>
       </c>
@@ -7176,7 +7179,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>326</v>
       </c>
@@ -7190,7 +7193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>327</v>
       </c>
@@ -7204,7 +7207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>328</v>
       </c>
@@ -7218,7 +7221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>329</v>
       </c>
@@ -7232,7 +7235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>330</v>
       </c>
@@ -7246,7 +7249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>331</v>
       </c>
@@ -7260,7 +7263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>332</v>
       </c>
@@ -7274,7 +7277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>333</v>
       </c>
@@ -7288,7 +7291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>334</v>
       </c>
@@ -7302,7 +7305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>335</v>
       </c>
@@ -7316,7 +7319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>336</v>
       </c>
@@ -7330,7 +7333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>337</v>
       </c>
@@ -7344,7 +7347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>338</v>
       </c>
@@ -7358,7 +7361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>339</v>
       </c>
@@ -7372,7 +7375,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>340</v>
       </c>
@@ -7386,7 +7389,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>341</v>
       </c>
@@ -7400,7 +7403,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>343</v>
       </c>
@@ -7414,7 +7417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>344</v>
       </c>
@@ -7428,7 +7431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>345</v>
       </c>
@@ -7442,7 +7445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>346</v>
       </c>
@@ -7456,7 +7459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>347</v>
       </c>
@@ -7470,7 +7473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>348</v>
       </c>
@@ -7484,7 +7487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>349</v>
       </c>
@@ -7498,7 +7501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>350</v>
       </c>
@@ -7512,7 +7515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>351</v>
       </c>
@@ -7526,7 +7529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>352</v>
       </c>
@@ -7540,7 +7543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>353</v>
       </c>
@@ -7554,7 +7557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>354</v>
       </c>
@@ -7568,7 +7571,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>355</v>
       </c>
@@ -7582,7 +7585,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>356</v>
       </c>
@@ -7596,7 +7599,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>357</v>
       </c>
@@ -7610,7 +7613,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>358</v>
       </c>
@@ -7624,7 +7627,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>359</v>
       </c>
@@ -7638,7 +7641,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>360</v>
       </c>
@@ -7652,7 +7655,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>361</v>
       </c>
@@ -7666,7 +7669,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>362</v>
       </c>
@@ -7680,7 +7683,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>363</v>
       </c>
@@ -7694,7 +7697,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>364</v>
       </c>
@@ -7708,7 +7711,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>365</v>
       </c>
@@ -7722,7 +7725,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>366</v>
       </c>
@@ -7736,7 +7739,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>367</v>
       </c>
@@ -7750,7 +7753,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>368</v>
       </c>
@@ -7764,7 +7767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>369</v>
       </c>
@@ -7778,7 +7781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>370</v>
       </c>
@@ -7792,7 +7795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>371</v>
       </c>
@@ -7806,7 +7809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>372</v>
       </c>
@@ -7820,7 +7823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>373</v>
       </c>
@@ -7834,7 +7837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>374</v>
       </c>
@@ -7848,7 +7851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>375</v>
       </c>
@@ -7862,7 +7865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>376</v>
       </c>
@@ -7876,7 +7879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>377</v>
       </c>
@@ -7890,7 +7893,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>378</v>
       </c>
@@ -7904,7 +7907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>379</v>
       </c>
@@ -7918,7 +7921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>380</v>
       </c>
@@ -7932,7 +7935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>381</v>
       </c>
@@ -7946,7 +7949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>382</v>
       </c>
@@ -7960,7 +7963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>383</v>
       </c>
@@ -7974,7 +7977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>384</v>
       </c>
@@ -7988,7 +7991,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>385</v>
       </c>
@@ -8002,7 +8005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>386</v>
       </c>
@@ -8016,7 +8019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>387</v>
       </c>
@@ -8030,7 +8033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>388</v>
       </c>
@@ -8044,7 +8047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>389</v>
       </c>
@@ -8058,7 +8061,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>390</v>
       </c>
@@ -8072,7 +8075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>391</v>
       </c>
@@ -8086,7 +8089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>392</v>
       </c>
@@ -8100,7 +8103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>393</v>
       </c>
@@ -8114,7 +8117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>394</v>
       </c>
@@ -8128,7 +8131,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>395</v>
       </c>
@@ -8142,7 +8145,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>396</v>
       </c>
@@ -8156,7 +8159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>397</v>
       </c>
@@ -8170,7 +8173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>398</v>
       </c>
@@ -8184,7 +8187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>399</v>
       </c>
@@ -8198,7 +8201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>400</v>
       </c>
@@ -8212,7 +8215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>401</v>
       </c>
@@ -8226,7 +8229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>402</v>
       </c>
@@ -8240,7 +8243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>403</v>
       </c>
@@ -8254,7 +8257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>404</v>
       </c>
@@ -8268,7 +8271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>405</v>
       </c>
@@ -8282,7 +8285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>406</v>
       </c>
@@ -8296,7 +8299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>407</v>
       </c>
@@ -8310,7 +8313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>408</v>
       </c>
@@ -8324,7 +8327,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>409</v>
       </c>
@@ -8338,7 +8341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>410</v>
       </c>
@@ -8352,7 +8355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>411</v>
       </c>
@@ -8366,7 +8369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>412</v>
       </c>
@@ -8380,7 +8383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>413</v>
       </c>
@@ -8394,7 +8397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>414</v>
       </c>
@@ -8408,7 +8411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>415</v>
       </c>
@@ -8422,7 +8425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>416</v>
       </c>
@@ -8436,7 +8439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>417</v>
       </c>
@@ -8450,7 +8453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>418</v>
       </c>
@@ -8464,7 +8467,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>419</v>
       </c>
@@ -8478,7 +8481,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>420</v>
       </c>
@@ -8492,7 +8495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>421</v>
       </c>
@@ -8506,7 +8509,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>422</v>
       </c>
@@ -8520,7 +8523,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>423</v>
       </c>
@@ -8534,7 +8537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>424</v>
       </c>
@@ -8548,7 +8551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
         <v>425</v>
       </c>
@@ -8562,7 +8565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>426</v>
       </c>
@@ -8576,7 +8579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>427</v>
       </c>
@@ -8590,7 +8593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>428</v>
       </c>
@@ -8604,7 +8607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>429</v>
       </c>
@@ -8618,7 +8621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>430</v>
       </c>
@@ -8632,7 +8635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>431</v>
       </c>
@@ -8646,7 +8649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>432</v>
       </c>
@@ -8660,7 +8663,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>433</v>
       </c>
@@ -8674,7 +8677,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>434</v>
       </c>
@@ -8688,7 +8691,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>435</v>
       </c>
@@ -8702,7 +8705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>436</v>
       </c>
@@ -8716,7 +8719,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>437</v>
       </c>
@@ -8730,7 +8733,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>438</v>
       </c>
@@ -8744,7 +8747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>439</v>
       </c>
@@ -8758,7 +8761,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>440</v>
       </c>
@@ -8772,7 +8775,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>441</v>
       </c>
@@ -8786,7 +8789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>442</v>
       </c>
@@ -8800,7 +8803,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>443</v>
       </c>
@@ -8814,7 +8817,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>444</v>
       </c>
@@ -8828,7 +8831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>445</v>
       </c>
@@ -8842,7 +8845,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>446</v>
       </c>
@@ -8856,7 +8859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>447</v>
       </c>
@@ -8870,7 +8873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>448</v>
       </c>
@@ -8884,7 +8887,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>449</v>
       </c>
@@ -8898,7 +8901,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>450</v>
       </c>
@@ -8912,7 +8915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>451</v>
       </c>
@@ -8926,7 +8929,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>452</v>
       </c>
@@ -8940,7 +8943,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>453</v>
       </c>
@@ -8954,7 +8957,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>454</v>
       </c>
@@ -8968,7 +8971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>455</v>
       </c>
@@ -8982,7 +8985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>456</v>
       </c>
@@ -8996,7 +8999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>457</v>
       </c>
@@ -9010,7 +9013,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>458</v>
       </c>
@@ -9024,7 +9027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>459</v>
       </c>
@@ -9038,7 +9041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>460</v>
       </c>
@@ -9052,7 +9055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>461</v>
       </c>
@@ -9066,7 +9069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>462</v>
       </c>
@@ -9080,7 +9083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>463</v>
       </c>
@@ -9094,7 +9097,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>464</v>
       </c>
@@ -9108,7 +9111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>465</v>
       </c>
@@ -9122,7 +9125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>466</v>
       </c>
@@ -9136,7 +9139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>467</v>
       </c>
@@ -9150,7 +9153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>468</v>
       </c>
@@ -9164,7 +9167,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>469</v>
       </c>
@@ -9178,7 +9181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>470</v>
       </c>
@@ -9192,7 +9195,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
         <v>471</v>
       </c>
@@ -9206,7 +9209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>472</v>
       </c>
@@ -9220,7 +9223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>473</v>
       </c>
@@ -9234,7 +9237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>474</v>
       </c>
@@ -9248,7 +9251,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>475</v>
       </c>
@@ -9262,7 +9265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>476</v>
       </c>
@@ -9276,7 +9279,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>477</v>
       </c>
@@ -9290,7 +9293,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>478</v>
       </c>
@@ -9304,7 +9307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>479</v>
       </c>
@@ -9318,7 +9321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>480</v>
       </c>
@@ -9332,7 +9335,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>481</v>
       </c>
@@ -9346,7 +9349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>482</v>
       </c>
@@ -9360,7 +9363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>483</v>
       </c>
@@ -9374,7 +9377,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>484</v>
       </c>
@@ -9388,7 +9391,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>485</v>
       </c>
@@ -9402,7 +9405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>486</v>
       </c>
@@ -9416,7 +9419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
         <v>487</v>
       </c>
@@ -9430,7 +9433,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>488</v>
       </c>
@@ -9444,7 +9447,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>489</v>
       </c>
@@ -9458,7 +9461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>490</v>
       </c>
@@ -9472,7 +9475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>491</v>
       </c>
@@ -9486,7 +9489,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>492</v>
       </c>
@@ -9500,7 +9503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>493</v>
       </c>
@@ -9514,7 +9517,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
         <v>494</v>
       </c>
@@ -9528,7 +9531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
         <v>495</v>
       </c>
@@ -9542,7 +9545,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>496</v>
       </c>
@@ -9556,7 +9559,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>497</v>
       </c>
@@ -9570,7 +9573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
         <v>498</v>
       </c>
@@ -9584,7 +9587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>499</v>
       </c>
@@ -9598,7 +9601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>500</v>
       </c>
@@ -9612,7 +9615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>501</v>
       </c>
@@ -9626,7 +9629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>502</v>
       </c>
@@ -9640,7 +9643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>503</v>
       </c>
@@ -9654,7 +9657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>504</v>
       </c>
@@ -9668,7 +9671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>505</v>
       </c>
@@ -9682,7 +9685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>506</v>
       </c>
@@ -9696,7 +9699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>507</v>
       </c>
@@ -9710,7 +9713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>508</v>
       </c>
@@ -9724,7 +9727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>509</v>
       </c>
@@ -9738,7 +9741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>510</v>
       </c>
@@ -9752,7 +9755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>511</v>
       </c>
@@ -9766,7 +9769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>512</v>
       </c>
@@ -9780,7 +9783,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>514</v>
       </c>
@@ -9794,7 +9797,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>516</v>
       </c>
@@ -9808,7 +9811,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>517</v>
       </c>
@@ -9822,7 +9825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="4" t="s">
         <v>518</v>
       </c>
@@ -9836,7 +9839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
         <v>519</v>
       </c>
@@ -9850,7 +9853,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="4" t="s">
         <v>520</v>
       </c>
@@ -9864,7 +9867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
         <v>521</v>
       </c>
@@ -9878,7 +9881,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="4" t="s">
         <v>522</v>
       </c>
@@ -9892,7 +9895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
         <v>523</v>
       </c>
@@ -9906,7 +9909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>524</v>
       </c>
@@ -9920,7 +9923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>525</v>
       </c>
@@ -9934,7 +9937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>526</v>
       </c>
@@ -9948,7 +9951,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>527</v>
       </c>
@@ -9962,7 +9965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>528</v>
       </c>
@@ -9976,7 +9979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>529</v>
       </c>
@@ -9990,7 +9993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>530</v>
       </c>
@@ -10004,7 +10007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>531</v>
       </c>
@@ -10018,7 +10021,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
         <v>532</v>
       </c>
@@ -10032,7 +10035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
         <v>533</v>
       </c>
@@ -10046,7 +10049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>534</v>
       </c>
@@ -10060,7 +10063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
         <v>535</v>
       </c>
@@ -10074,7 +10077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="8" t="s">
         <v>536</v>
       </c>
@@ -10088,7 +10091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="8" t="s">
         <v>537</v>
       </c>
@@ -10102,7 +10105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="9" t="s">
         <v>538</v>
       </c>
@@ -10116,7 +10119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="12" t="s">
         <v>539</v>
       </c>
@@ -10130,7 +10133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="12" t="s">
         <v>540</v>
       </c>
@@ -10144,7 +10147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="12" t="s">
         <v>541</v>
       </c>
@@ -10158,7 +10161,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>542</v>
       </c>
@@ -10172,7 +10175,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="12" t="s">
         <v>543</v>
       </c>
@@ -10186,7 +10189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="12" t="s">
         <v>544</v>
       </c>
@@ -10200,7 +10203,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
         <v>545</v>
       </c>
@@ -10214,7 +10217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
         <v>546</v>
       </c>
@@ -10228,7 +10231,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
         <v>547</v>
       </c>
@@ -10242,7 +10245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="12" t="s">
         <v>548</v>
       </c>
@@ -10256,7 +10259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="12" t="s">
         <v>549</v>
       </c>
@@ -10270,7 +10273,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
         <v>550</v>
       </c>
@@ -10284,7 +10287,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
         <v>551</v>
       </c>
@@ -10298,7 +10301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="19" t="s">
         <v>559</v>
       </c>
@@ -10312,7 +10315,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="20" t="s">
         <v>571</v>
       </c>
@@ -10326,7 +10329,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="19" t="s">
         <v>560</v>
       </c>
@@ -10340,7 +10343,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="19" t="s">
         <v>552</v>
       </c>
@@ -10354,7 +10357,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="19" t="s">
         <v>572</v>
       </c>
@@ -10368,7 +10371,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="21" t="s">
         <v>573</v>
       </c>
@@ -10382,7 +10385,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="21" t="s">
         <v>574</v>
       </c>
@@ -10396,7 +10399,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="19" t="s">
         <v>564</v>
       </c>
@@ -10410,7 +10413,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="19" t="s">
         <v>565</v>
       </c>
@@ -10424,7 +10427,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="22" t="s">
         <v>575</v>
       </c>
@@ -10438,7 +10441,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="21" t="s">
         <v>576</v>
       </c>
@@ -10452,7 +10455,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="23" t="s">
         <v>566</v>
       </c>
@@ -10466,7 +10469,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="23" t="s">
         <v>567</v>
       </c>
@@ -10480,7 +10483,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="22" t="s">
         <v>568</v>
       </c>
@@ -10494,7 +10497,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="22" t="s">
         <v>569</v>
       </c>
@@ -10508,7 +10511,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="22" t="s">
         <v>570</v>
       </c>
@@ -10522,7 +10525,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="22" t="s">
         <v>577</v>
       </c>
@@ -10536,7 +10539,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="19" t="s">
         <v>578</v>
       </c>
@@ -10550,7 +10553,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="22" t="s">
         <v>579</v>
       </c>
@@ -10564,7 +10567,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="24" t="s">
         <v>580</v>
       </c>
@@ -10578,7 +10581,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="19" t="s">
         <v>581</v>
       </c>
@@ -10592,7 +10595,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="19" t="s">
         <v>582</v>
       </c>
@@ -10606,7 +10609,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="22" t="s">
         <v>583</v>
       </c>
@@ -10620,7 +10623,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="19" t="s">
         <v>584</v>
       </c>
@@ -10634,7 +10637,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="19" t="s">
         <v>585</v>
       </c>
@@ -10648,7 +10651,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="19" t="s">
         <v>586</v>
       </c>
@@ -10662,7 +10665,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="19" t="s">
         <v>587</v>
       </c>
@@ -10676,7 +10679,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="19" t="s">
         <v>588</v>
       </c>
@@ -10690,7 +10693,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="19" t="s">
         <v>589</v>
       </c>
@@ -10704,7 +10707,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="19" t="s">
         <v>590</v>
       </c>
@@ -10718,7 +10721,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="19" t="s">
         <v>591</v>
       </c>
@@ -10732,7 +10735,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="25" t="s">
         <v>592</v>
       </c>
@@ -10746,7 +10749,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="19" t="s">
         <v>593</v>
       </c>
@@ -10760,7 +10763,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="25" t="s">
         <v>594</v>
       </c>
@@ -10774,7 +10777,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="26" t="s">
         <v>595</v>
       </c>
@@ -10788,7 +10791,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="19" t="s">
         <v>596</v>
       </c>
@@ -10802,7 +10805,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="25" t="s">
         <v>597</v>
       </c>
@@ -10816,7 +10819,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="28" t="s">
         <v>598</v>
       </c>
@@ -10830,7 +10833,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="27" t="s">
         <v>599</v>
       </c>
@@ -10844,7 +10847,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="27" t="s">
         <v>600</v>
       </c>
@@ -10858,7 +10861,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="25" t="s">
         <v>601</v>
       </c>
@@ -10872,7 +10875,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="26" t="s">
         <v>602</v>
       </c>
@@ -10886,7 +10889,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="29" t="s">
         <v>603</v>
       </c>
@@ -10900,7 +10903,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="25" t="s">
         <v>553</v>
       </c>
@@ -10914,7 +10917,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="30" t="s">
         <v>604</v>
       </c>
@@ -10928,7 +10931,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="25" t="s">
         <v>605</v>
       </c>
@@ -10942,7 +10945,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="31" t="s">
         <v>606</v>
       </c>
@@ -10956,7 +10959,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="25" t="s">
         <v>607</v>
       </c>
@@ -10970,7 +10973,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="27" t="s">
         <v>608</v>
       </c>
@@ -10984,7 +10987,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="25" t="s">
         <v>609</v>
       </c>
@@ -10998,7 +11001,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="30" t="s">
         <v>610</v>
       </c>
@@ -11012,7 +11015,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="25" t="s">
         <v>611</v>
       </c>
@@ -11026,7 +11029,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="25" t="s">
         <v>612</v>
       </c>
@@ -11040,7 +11043,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="30" t="s">
         <v>613</v>
       </c>
@@ -11054,7 +11057,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="25" t="s">
         <v>614</v>
       </c>
@@ -11068,7 +11071,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="25" t="s">
         <v>615</v>
       </c>
@@ -11082,7 +11085,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="25" t="s">
         <v>616</v>
       </c>
@@ -11096,7 +11099,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="25" t="s">
         <v>617</v>
       </c>
@@ -11110,7 +11113,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="25" t="s">
         <v>618</v>
       </c>
@@ -11124,7 +11127,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="25" t="s">
         <v>619</v>
       </c>
@@ -11138,7 +11141,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="19" t="s">
         <v>554</v>
       </c>
@@ -11152,7 +11155,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="25" t="s">
         <v>620</v>
       </c>
@@ -11166,7 +11169,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="25" t="s">
         <v>621</v>
       </c>
@@ -11180,7 +11183,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="25" t="s">
         <v>622</v>
       </c>
@@ -11194,7 +11197,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="25" t="s">
         <v>623</v>
       </c>
@@ -11208,7 +11211,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="25" t="s">
         <v>624</v>
       </c>
@@ -11222,7 +11225,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="30" t="s">
         <v>625</v>
       </c>
@@ -11236,7 +11239,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="26" t="s">
         <v>626</v>
       </c>
@@ -11250,7 +11253,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="25" t="s">
         <v>627</v>
       </c>
@@ -11264,7 +11267,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="25" t="s">
         <v>628</v>
       </c>
@@ -11278,7 +11281,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="25" t="s">
         <v>629</v>
       </c>
@@ -11292,7 +11295,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="25" t="s">
         <v>630</v>
       </c>
@@ -11306,7 +11309,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="32" t="s">
         <v>632</v>
       </c>
@@ -11320,7 +11323,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="25" t="s">
         <v>631</v>
       </c>
@@ -11334,7 +11337,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="25" t="s">
         <v>633</v>
       </c>
@@ -11348,7 +11351,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="30" t="s">
         <v>634</v>
       </c>
@@ -11362,7 +11365,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="33" t="s">
         <v>635</v>
       </c>
@@ -11376,7 +11379,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="25" t="s">
         <v>636</v>
       </c>
@@ -11390,7 +11393,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="33" t="s">
         <v>637</v>
       </c>
@@ -11404,7 +11407,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="25" t="s">
         <v>638</v>
       </c>
@@ -11418,7 +11421,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="25" t="s">
         <v>639</v>
       </c>
@@ -11432,7 +11435,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="25" t="s">
         <v>640</v>
       </c>
@@ -11446,7 +11449,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="34" t="s">
         <v>641</v>
       </c>
@@ -11460,7 +11463,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="25" t="s">
         <v>642</v>
       </c>
@@ -11474,7 +11477,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="25" t="s">
         <v>643</v>
       </c>
@@ -11488,7 +11491,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="25" t="s">
         <v>644</v>
       </c>
@@ -11502,7 +11505,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="27" t="s">
         <v>645</v>
       </c>
@@ -11516,7 +11519,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="18" t="s">
         <v>646</v>
       </c>
@@ -11530,7 +11533,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="18" t="s">
         <v>647</v>
       </c>
@@ -11544,7 +11547,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="25" t="s">
         <v>648</v>
       </c>
@@ -11558,7 +11561,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="30" t="s">
         <v>649</v>
       </c>
@@ -11572,7 +11575,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="25" t="s">
         <v>650</v>
       </c>
@@ -11586,7 +11589,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="25" t="s">
         <v>651</v>
       </c>
@@ -11600,7 +11603,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="25" t="s">
         <v>652</v>
       </c>
@@ -11614,7 +11617,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="25" t="s">
         <v>653</v>
       </c>
@@ -11628,7 +11631,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="25" t="s">
         <v>654</v>
       </c>
@@ -11642,7 +11645,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="25" t="s">
         <v>655</v>
       </c>
@@ -11656,7 +11659,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="30" t="s">
         <v>656</v>
       </c>
@@ -11670,7 +11673,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="25" t="s">
         <v>657</v>
       </c>
@@ -11684,7 +11687,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="30" t="s">
         <v>658</v>
       </c>
@@ -11698,7 +11701,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="26" t="s">
         <v>659</v>
       </c>
@@ -11712,7 +11715,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="26" t="s">
         <v>660</v>
       </c>
@@ -11726,7 +11729,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="25" t="s">
         <v>661</v>
       </c>
@@ -11740,7 +11743,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="25" t="s">
         <v>662</v>
       </c>
@@ -11754,7 +11757,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="26" t="s">
         <v>663</v>
       </c>
@@ -11768,7 +11771,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="25" t="s">
         <v>563</v>
       </c>
@@ -11782,7 +11785,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="25" t="s">
         <v>664</v>
       </c>
@@ -11796,7 +11799,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="26" t="s">
         <v>665</v>
       </c>
@@ -11810,7 +11813,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="25" t="s">
         <v>666</v>
       </c>
@@ -11824,7 +11827,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="25" t="s">
         <v>667</v>
       </c>
@@ -11838,7 +11841,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="30" t="s">
         <v>668</v>
       </c>
@@ -11852,7 +11855,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="25" t="s">
         <v>562</v>
       </c>
@@ -11866,7 +11869,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="25" t="s">
         <v>669</v>
       </c>
@@ -11880,7 +11883,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="25" t="s">
         <v>670</v>
       </c>
@@ -11894,7 +11897,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="25" t="s">
         <v>671</v>
       </c>
@@ -11908,7 +11911,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="25" t="s">
         <v>672</v>
       </c>
@@ -11922,7 +11925,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="25" t="s">
         <v>673</v>
       </c>
@@ -11936,7 +11939,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="25" t="s">
         <v>674</v>
       </c>
@@ -11950,7 +11953,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="25" t="s">
         <v>675</v>
       </c>
@@ -11964,7 +11967,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="25" t="s">
         <v>676</v>
       </c>
@@ -11978,7 +11981,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="25" t="s">
         <v>677</v>
       </c>
@@ -11992,7 +11995,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="27" t="s">
         <v>678</v>
       </c>
@@ -12006,7 +12009,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="25" t="s">
         <v>679</v>
       </c>
@@ -12020,7 +12023,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="25" t="s">
         <v>680</v>
       </c>
@@ -12034,7 +12037,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="25" t="s">
         <v>681</v>
       </c>
@@ -12048,7 +12051,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="28" t="s">
         <v>682</v>
       </c>
@@ -12062,7 +12065,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="35" t="s">
         <v>683</v>
       </c>
@@ -12076,7 +12079,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="35" t="s">
         <v>684</v>
       </c>
@@ -12090,7 +12093,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="35" t="s">
         <v>685</v>
       </c>
@@ -12104,7 +12107,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="28" t="s">
         <v>686</v>
       </c>
@@ -12118,7 +12121,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="28" t="s">
         <v>687</v>
       </c>
@@ -12132,7 +12135,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="28" t="s">
         <v>688</v>
       </c>
@@ -12146,7 +12149,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="28" t="s">
         <v>689</v>
       </c>
@@ -12160,7 +12163,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="28" t="s">
         <v>690</v>
       </c>
@@ -12174,7 +12177,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="28" t="s">
         <v>691</v>
       </c>
@@ -12185,6 +12188,20 @@
         <v>557</v>
       </c>
       <c r="D665" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A666" s="28" t="s">
+        <v>692</v>
+      </c>
+      <c r="B666" s="40">
+        <v>0.08</v>
+      </c>
+      <c r="C666" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="D666" s="51" t="s">
         <v>556</v>
       </c>
     </row>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8F1230-7FC5-4E0C-A60E-1E929CB57F29}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4BFE4C-9EB1-4B59-B8D4-30FB61D32FDF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="695">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2109,6 +2109,12 @@
   </si>
   <si>
     <t>Sugar Syrup - Production</t>
+  </si>
+  <si>
+    <t>Cold Foam - Production</t>
+  </si>
+  <si>
+    <t>Roast Beef - Production</t>
   </si>
 </sst>
 </file>
@@ -2883,7 +2889,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D666"/>
+  <dimension ref="A1:D916"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.54296875" customWidth="1"/>
@@ -12205,6 +12211,1522 @@
         <v>556</v>
       </c>
     </row>
+    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A667" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="B667" s="40">
+        <v>0.19</v>
+      </c>
+      <c r="C667" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D667" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A668" s="28" t="s">
+        <v>694</v>
+      </c>
+      <c r="B668" s="40">
+        <v>332.18</v>
+      </c>
+      <c r="C668" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="D668" s="51" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A669" s="28"/>
+      <c r="B669" s="40"/>
+      <c r="C669" s="49"/>
+      <c r="D669" s="51"/>
+    </row>
+    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A670" s="28"/>
+      <c r="B670" s="40"/>
+      <c r="C670" s="49"/>
+      <c r="D670" s="51"/>
+    </row>
+    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A671" s="28"/>
+      <c r="B671" s="40"/>
+      <c r="C671" s="49"/>
+      <c r="D671" s="51"/>
+    </row>
+    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A672" s="28"/>
+      <c r="B672" s="40"/>
+      <c r="C672" s="49"/>
+      <c r="D672" s="51"/>
+    </row>
+    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A673" s="28"/>
+      <c r="B673" s="40"/>
+      <c r="C673" s="49"/>
+      <c r="D673" s="51"/>
+    </row>
+    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A674" s="28"/>
+      <c r="B674" s="40"/>
+      <c r="C674" s="49"/>
+      <c r="D674" s="51"/>
+    </row>
+    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A675" s="28"/>
+      <c r="B675" s="40"/>
+      <c r="C675" s="49"/>
+      <c r="D675" s="51"/>
+    </row>
+    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A676" s="28"/>
+      <c r="B676" s="40"/>
+      <c r="C676" s="49"/>
+      <c r="D676" s="51"/>
+    </row>
+    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A677" s="28"/>
+      <c r="B677" s="40"/>
+      <c r="C677" s="49"/>
+      <c r="D677" s="51"/>
+    </row>
+    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A678" s="28"/>
+      <c r="B678" s="40"/>
+      <c r="C678" s="49"/>
+      <c r="D678" s="51"/>
+    </row>
+    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A679" s="28"/>
+      <c r="B679" s="40"/>
+      <c r="C679" s="49"/>
+      <c r="D679" s="51"/>
+    </row>
+    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A680" s="28"/>
+      <c r="B680" s="40"/>
+      <c r="C680" s="49"/>
+      <c r="D680" s="51"/>
+    </row>
+    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A681" s="28"/>
+      <c r="B681" s="40"/>
+      <c r="C681" s="49"/>
+      <c r="D681" s="51"/>
+    </row>
+    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A682" s="28"/>
+      <c r="B682" s="40"/>
+      <c r="C682" s="49"/>
+      <c r="D682" s="51"/>
+    </row>
+    <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A683" s="28"/>
+      <c r="B683" s="40"/>
+      <c r="C683" s="49"/>
+      <c r="D683" s="51"/>
+    </row>
+    <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A684" s="28"/>
+      <c r="B684" s="40"/>
+      <c r="C684" s="49"/>
+      <c r="D684" s="51"/>
+    </row>
+    <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A685" s="28"/>
+      <c r="B685" s="40"/>
+      <c r="C685" s="49"/>
+      <c r="D685" s="51"/>
+    </row>
+    <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A686" s="28"/>
+      <c r="B686" s="40"/>
+      <c r="C686" s="49"/>
+      <c r="D686" s="51"/>
+    </row>
+    <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A687" s="28"/>
+      <c r="B687" s="40"/>
+      <c r="C687" s="49"/>
+      <c r="D687" s="51"/>
+    </row>
+    <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A688" s="28"/>
+      <c r="B688" s="40"/>
+      <c r="C688" s="49"/>
+      <c r="D688" s="51"/>
+    </row>
+    <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A689" s="28"/>
+      <c r="B689" s="40"/>
+      <c r="C689" s="49"/>
+      <c r="D689" s="51"/>
+    </row>
+    <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A690" s="28"/>
+      <c r="B690" s="40"/>
+      <c r="C690" s="49"/>
+      <c r="D690" s="51"/>
+    </row>
+    <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A691" s="28"/>
+      <c r="B691" s="40"/>
+      <c r="C691" s="49"/>
+      <c r="D691" s="51"/>
+    </row>
+    <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A692" s="28"/>
+      <c r="B692" s="40"/>
+      <c r="C692" s="49"/>
+      <c r="D692" s="51"/>
+    </row>
+    <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A693" s="28"/>
+      <c r="B693" s="40"/>
+      <c r="C693" s="49"/>
+      <c r="D693" s="51"/>
+    </row>
+    <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A694" s="28"/>
+      <c r="B694" s="40"/>
+      <c r="C694" s="49"/>
+      <c r="D694" s="51"/>
+    </row>
+    <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A695" s="28"/>
+      <c r="B695" s="40"/>
+      <c r="C695" s="49"/>
+      <c r="D695" s="51"/>
+    </row>
+    <row r="696" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A696" s="28"/>
+      <c r="B696" s="40"/>
+      <c r="C696" s="49"/>
+      <c r="D696" s="51"/>
+    </row>
+    <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A697" s="28"/>
+      <c r="B697" s="40"/>
+      <c r="C697" s="49"/>
+      <c r="D697" s="51"/>
+    </row>
+    <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A698" s="28"/>
+      <c r="B698" s="40"/>
+      <c r="C698" s="49"/>
+      <c r="D698" s="51"/>
+    </row>
+    <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A699" s="28"/>
+      <c r="B699" s="40"/>
+      <c r="C699" s="49"/>
+      <c r="D699" s="51"/>
+    </row>
+    <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A700" s="28"/>
+      <c r="B700" s="40"/>
+      <c r="C700" s="49"/>
+      <c r="D700" s="51"/>
+    </row>
+    <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A701" s="28"/>
+      <c r="B701" s="40"/>
+      <c r="C701" s="49"/>
+      <c r="D701" s="51"/>
+    </row>
+    <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A702" s="28"/>
+      <c r="B702" s="40"/>
+      <c r="C702" s="49"/>
+      <c r="D702" s="51"/>
+    </row>
+    <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A703" s="28"/>
+      <c r="B703" s="40"/>
+      <c r="C703" s="49"/>
+      <c r="D703" s="51"/>
+    </row>
+    <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A704" s="28"/>
+      <c r="B704" s="40"/>
+      <c r="C704" s="49"/>
+      <c r="D704" s="51"/>
+    </row>
+    <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A705" s="28"/>
+      <c r="B705" s="40"/>
+      <c r="C705" s="49"/>
+      <c r="D705" s="51"/>
+    </row>
+    <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A706" s="28"/>
+      <c r="B706" s="40"/>
+      <c r="C706" s="49"/>
+      <c r="D706" s="51"/>
+    </row>
+    <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A707" s="28"/>
+      <c r="B707" s="40"/>
+      <c r="C707" s="49"/>
+      <c r="D707" s="51"/>
+    </row>
+    <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A708" s="28"/>
+      <c r="B708" s="40"/>
+      <c r="C708" s="49"/>
+      <c r="D708" s="51"/>
+    </row>
+    <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A709" s="28"/>
+      <c r="B709" s="40"/>
+      <c r="C709" s="49"/>
+      <c r="D709" s="51"/>
+    </row>
+    <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A710" s="28"/>
+      <c r="B710" s="40"/>
+      <c r="C710" s="49"/>
+      <c r="D710" s="51"/>
+    </row>
+    <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A711" s="28"/>
+      <c r="B711" s="40"/>
+      <c r="C711" s="49"/>
+      <c r="D711" s="51"/>
+    </row>
+    <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A712" s="28"/>
+      <c r="B712" s="40"/>
+      <c r="C712" s="49"/>
+      <c r="D712" s="51"/>
+    </row>
+    <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A713" s="28"/>
+      <c r="B713" s="40"/>
+      <c r="C713" s="49"/>
+      <c r="D713" s="51"/>
+    </row>
+    <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A714" s="28"/>
+      <c r="B714" s="40"/>
+      <c r="C714" s="49"/>
+      <c r="D714" s="51"/>
+    </row>
+    <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A715" s="28"/>
+      <c r="B715" s="40"/>
+      <c r="C715" s="49"/>
+      <c r="D715" s="51"/>
+    </row>
+    <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A716" s="28"/>
+      <c r="B716" s="40"/>
+      <c r="C716" s="49"/>
+      <c r="D716" s="51"/>
+    </row>
+    <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A717" s="28"/>
+      <c r="B717" s="40"/>
+      <c r="C717" s="49"/>
+      <c r="D717" s="51"/>
+    </row>
+    <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A718" s="28"/>
+      <c r="B718" s="40"/>
+      <c r="C718" s="49"/>
+      <c r="D718" s="51"/>
+    </row>
+    <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A719" s="28"/>
+      <c r="B719" s="40"/>
+      <c r="C719" s="49"/>
+      <c r="D719" s="51"/>
+    </row>
+    <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A720" s="28"/>
+      <c r="B720" s="40"/>
+      <c r="C720" s="49"/>
+      <c r="D720" s="51"/>
+    </row>
+    <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A721" s="28"/>
+      <c r="B721" s="40"/>
+      <c r="C721" s="49"/>
+      <c r="D721" s="51"/>
+    </row>
+    <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A722" s="28"/>
+      <c r="B722" s="40"/>
+      <c r="C722" s="49"/>
+      <c r="D722" s="51"/>
+    </row>
+    <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A723" s="28"/>
+      <c r="B723" s="40"/>
+      <c r="C723" s="49"/>
+      <c r="D723" s="51"/>
+    </row>
+    <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A724" s="28"/>
+      <c r="B724" s="40"/>
+      <c r="C724" s="49"/>
+      <c r="D724" s="51"/>
+    </row>
+    <row r="725" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A725" s="28"/>
+      <c r="B725" s="40"/>
+      <c r="C725" s="49"/>
+      <c r="D725" s="51"/>
+    </row>
+    <row r="726" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A726" s="28"/>
+      <c r="B726" s="40"/>
+      <c r="C726" s="49"/>
+      <c r="D726" s="51"/>
+    </row>
+    <row r="727" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A727" s="28"/>
+      <c r="B727" s="40"/>
+      <c r="C727" s="49"/>
+      <c r="D727" s="51"/>
+    </row>
+    <row r="728" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A728" s="28"/>
+      <c r="B728" s="40"/>
+      <c r="C728" s="49"/>
+      <c r="D728" s="51"/>
+    </row>
+    <row r="729" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A729" s="28"/>
+      <c r="B729" s="40"/>
+      <c r="C729" s="49"/>
+      <c r="D729" s="51"/>
+    </row>
+    <row r="730" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A730" s="28"/>
+      <c r="B730" s="40"/>
+      <c r="C730" s="49"/>
+      <c r="D730" s="51"/>
+    </row>
+    <row r="731" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A731" s="28"/>
+      <c r="B731" s="40"/>
+      <c r="C731" s="49"/>
+      <c r="D731" s="51"/>
+    </row>
+    <row r="732" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A732" s="28"/>
+      <c r="B732" s="40"/>
+      <c r="C732" s="49"/>
+      <c r="D732" s="51"/>
+    </row>
+    <row r="733" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A733" s="28"/>
+      <c r="B733" s="40"/>
+      <c r="C733" s="49"/>
+      <c r="D733" s="51"/>
+    </row>
+    <row r="734" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A734" s="28"/>
+      <c r="B734" s="40"/>
+      <c r="C734" s="49"/>
+      <c r="D734" s="51"/>
+    </row>
+    <row r="735" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A735" s="28"/>
+      <c r="B735" s="40"/>
+      <c r="C735" s="49"/>
+      <c r="D735" s="51"/>
+    </row>
+    <row r="736" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A736" s="28"/>
+      <c r="B736" s="40"/>
+      <c r="C736" s="49"/>
+      <c r="D736" s="51"/>
+    </row>
+    <row r="737" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A737" s="28"/>
+      <c r="B737" s="40"/>
+      <c r="C737" s="49"/>
+      <c r="D737" s="51"/>
+    </row>
+    <row r="738" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A738" s="28"/>
+      <c r="B738" s="40"/>
+      <c r="C738" s="49"/>
+      <c r="D738" s="51"/>
+    </row>
+    <row r="739" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A739" s="28"/>
+      <c r="B739" s="40"/>
+      <c r="C739" s="49"/>
+      <c r="D739" s="51"/>
+    </row>
+    <row r="740" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A740" s="28"/>
+      <c r="B740" s="40"/>
+      <c r="C740" s="49"/>
+      <c r="D740" s="51"/>
+    </row>
+    <row r="741" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A741" s="28"/>
+      <c r="B741" s="40"/>
+      <c r="C741" s="49"/>
+      <c r="D741" s="51"/>
+    </row>
+    <row r="742" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A742" s="28"/>
+      <c r="B742" s="40"/>
+      <c r="C742" s="49"/>
+      <c r="D742" s="51"/>
+    </row>
+    <row r="743" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A743" s="28"/>
+      <c r="B743" s="40"/>
+      <c r="C743" s="49"/>
+      <c r="D743" s="51"/>
+    </row>
+    <row r="744" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A744" s="28"/>
+      <c r="B744" s="40"/>
+      <c r="C744" s="49"/>
+      <c r="D744" s="51"/>
+    </row>
+    <row r="745" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A745" s="28"/>
+      <c r="B745" s="40"/>
+      <c r="C745" s="49"/>
+      <c r="D745" s="51"/>
+    </row>
+    <row r="746" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A746" s="28"/>
+      <c r="B746" s="40"/>
+      <c r="C746" s="49"/>
+      <c r="D746" s="51"/>
+    </row>
+    <row r="747" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A747" s="28"/>
+      <c r="B747" s="40"/>
+      <c r="C747" s="49"/>
+      <c r="D747" s="51"/>
+    </row>
+    <row r="748" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A748" s="28"/>
+      <c r="B748" s="40"/>
+      <c r="C748" s="49"/>
+      <c r="D748" s="51"/>
+    </row>
+    <row r="749" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A749" s="28"/>
+      <c r="B749" s="40"/>
+      <c r="C749" s="49"/>
+      <c r="D749" s="51"/>
+    </row>
+    <row r="750" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A750" s="28"/>
+      <c r="B750" s="40"/>
+      <c r="C750" s="49"/>
+      <c r="D750" s="51"/>
+    </row>
+    <row r="751" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A751" s="28"/>
+      <c r="B751" s="40"/>
+      <c r="C751" s="49"/>
+      <c r="D751" s="51"/>
+    </row>
+    <row r="752" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A752" s="28"/>
+      <c r="B752" s="40"/>
+      <c r="C752" s="49"/>
+      <c r="D752" s="51"/>
+    </row>
+    <row r="753" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A753" s="28"/>
+      <c r="B753" s="40"/>
+      <c r="C753" s="49"/>
+      <c r="D753" s="51"/>
+    </row>
+    <row r="754" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A754" s="28"/>
+      <c r="B754" s="40"/>
+      <c r="C754" s="49"/>
+      <c r="D754" s="51"/>
+    </row>
+    <row r="755" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A755" s="28"/>
+      <c r="B755" s="40"/>
+      <c r="C755" s="49"/>
+      <c r="D755" s="51"/>
+    </row>
+    <row r="756" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A756" s="28"/>
+      <c r="B756" s="40"/>
+      <c r="C756" s="49"/>
+      <c r="D756" s="51"/>
+    </row>
+    <row r="757" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A757" s="28"/>
+      <c r="B757" s="40"/>
+      <c r="C757" s="49"/>
+      <c r="D757" s="51"/>
+    </row>
+    <row r="758" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A758" s="28"/>
+      <c r="B758" s="40"/>
+      <c r="C758" s="49"/>
+      <c r="D758" s="51"/>
+    </row>
+    <row r="759" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A759" s="28"/>
+      <c r="B759" s="40"/>
+      <c r="C759" s="49"/>
+      <c r="D759" s="51"/>
+    </row>
+    <row r="760" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A760" s="28"/>
+      <c r="B760" s="40"/>
+      <c r="C760" s="49"/>
+      <c r="D760" s="51"/>
+    </row>
+    <row r="761" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A761" s="28"/>
+      <c r="B761" s="40"/>
+      <c r="C761" s="49"/>
+      <c r="D761" s="51"/>
+    </row>
+    <row r="762" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A762" s="28"/>
+      <c r="B762" s="40"/>
+      <c r="C762" s="49"/>
+      <c r="D762" s="51"/>
+    </row>
+    <row r="763" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A763" s="28"/>
+      <c r="B763" s="40"/>
+      <c r="C763" s="49"/>
+      <c r="D763" s="51"/>
+    </row>
+    <row r="764" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A764" s="28"/>
+      <c r="B764" s="40"/>
+      <c r="C764" s="49"/>
+      <c r="D764" s="51"/>
+    </row>
+    <row r="765" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A765" s="28"/>
+      <c r="B765" s="40"/>
+      <c r="C765" s="49"/>
+      <c r="D765" s="51"/>
+    </row>
+    <row r="766" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A766" s="28"/>
+      <c r="B766" s="40"/>
+      <c r="C766" s="49"/>
+      <c r="D766" s="51"/>
+    </row>
+    <row r="767" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A767" s="28"/>
+      <c r="B767" s="40"/>
+      <c r="C767" s="49"/>
+      <c r="D767" s="51"/>
+    </row>
+    <row r="768" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A768" s="28"/>
+      <c r="B768" s="40"/>
+      <c r="C768" s="49"/>
+      <c r="D768" s="51"/>
+    </row>
+    <row r="769" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A769" s="28"/>
+      <c r="B769" s="40"/>
+      <c r="C769" s="49"/>
+      <c r="D769" s="51"/>
+    </row>
+    <row r="770" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A770" s="28"/>
+      <c r="B770" s="40"/>
+      <c r="C770" s="49"/>
+      <c r="D770" s="51"/>
+    </row>
+    <row r="771" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A771" s="28"/>
+      <c r="B771" s="40"/>
+      <c r="C771" s="49"/>
+      <c r="D771" s="51"/>
+    </row>
+    <row r="772" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A772" s="28"/>
+      <c r="B772" s="40"/>
+      <c r="C772" s="49"/>
+      <c r="D772" s="51"/>
+    </row>
+    <row r="773" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A773" s="28"/>
+      <c r="B773" s="40"/>
+      <c r="C773" s="49"/>
+      <c r="D773" s="51"/>
+    </row>
+    <row r="774" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A774" s="28"/>
+      <c r="B774" s="40"/>
+      <c r="C774" s="49"/>
+      <c r="D774" s="51"/>
+    </row>
+    <row r="775" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A775" s="28"/>
+      <c r="B775" s="40"/>
+      <c r="C775" s="49"/>
+      <c r="D775" s="51"/>
+    </row>
+    <row r="776" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A776" s="28"/>
+      <c r="B776" s="40"/>
+      <c r="C776" s="49"/>
+      <c r="D776" s="51"/>
+    </row>
+    <row r="777" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A777" s="28"/>
+      <c r="B777" s="40"/>
+      <c r="C777" s="49"/>
+      <c r="D777" s="51"/>
+    </row>
+    <row r="778" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A778" s="28"/>
+      <c r="B778" s="40"/>
+      <c r="C778" s="49"/>
+      <c r="D778" s="51"/>
+    </row>
+    <row r="779" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A779" s="28"/>
+      <c r="B779" s="40"/>
+      <c r="C779" s="49"/>
+      <c r="D779" s="51"/>
+    </row>
+    <row r="780" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A780" s="28"/>
+      <c r="B780" s="40"/>
+      <c r="C780" s="49"/>
+      <c r="D780" s="51"/>
+    </row>
+    <row r="781" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A781" s="28"/>
+      <c r="B781" s="40"/>
+      <c r="C781" s="49"/>
+      <c r="D781" s="51"/>
+    </row>
+    <row r="782" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A782" s="28"/>
+      <c r="B782" s="40"/>
+      <c r="C782" s="49"/>
+      <c r="D782" s="51"/>
+    </row>
+    <row r="783" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A783" s="28"/>
+      <c r="B783" s="40"/>
+      <c r="C783" s="49"/>
+      <c r="D783" s="51"/>
+    </row>
+    <row r="784" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A784" s="28"/>
+      <c r="B784" s="40"/>
+      <c r="C784" s="49"/>
+      <c r="D784" s="51"/>
+    </row>
+    <row r="785" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A785" s="28"/>
+      <c r="B785" s="40"/>
+      <c r="C785" s="49"/>
+      <c r="D785" s="51"/>
+    </row>
+    <row r="786" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A786" s="28"/>
+      <c r="B786" s="40"/>
+      <c r="C786" s="49"/>
+      <c r="D786" s="51"/>
+    </row>
+    <row r="787" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A787" s="28"/>
+      <c r="B787" s="40"/>
+      <c r="C787" s="49"/>
+      <c r="D787" s="51"/>
+    </row>
+    <row r="788" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A788" s="28"/>
+      <c r="B788" s="40"/>
+      <c r="C788" s="49"/>
+      <c r="D788" s="51"/>
+    </row>
+    <row r="789" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A789" s="28"/>
+      <c r="B789" s="40"/>
+      <c r="C789" s="49"/>
+      <c r="D789" s="51"/>
+    </row>
+    <row r="790" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A790" s="28"/>
+      <c r="B790" s="40"/>
+      <c r="C790" s="49"/>
+      <c r="D790" s="51"/>
+    </row>
+    <row r="791" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A791" s="28"/>
+      <c r="B791" s="40"/>
+      <c r="C791" s="49"/>
+      <c r="D791" s="51"/>
+    </row>
+    <row r="792" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A792" s="28"/>
+      <c r="B792" s="40"/>
+      <c r="C792" s="49"/>
+      <c r="D792" s="51"/>
+    </row>
+    <row r="793" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A793" s="28"/>
+      <c r="B793" s="40"/>
+      <c r="C793" s="49"/>
+      <c r="D793" s="51"/>
+    </row>
+    <row r="794" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A794" s="28"/>
+      <c r="B794" s="40"/>
+      <c r="C794" s="49"/>
+      <c r="D794" s="51"/>
+    </row>
+    <row r="795" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A795" s="28"/>
+      <c r="B795" s="40"/>
+      <c r="C795" s="49"/>
+      <c r="D795" s="51"/>
+    </row>
+    <row r="796" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A796" s="28"/>
+      <c r="B796" s="40"/>
+      <c r="C796" s="49"/>
+      <c r="D796" s="51"/>
+    </row>
+    <row r="797" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A797" s="28"/>
+      <c r="B797" s="40"/>
+      <c r="C797" s="49"/>
+      <c r="D797" s="51"/>
+    </row>
+    <row r="798" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A798" s="28"/>
+      <c r="B798" s="40"/>
+      <c r="C798" s="49"/>
+      <c r="D798" s="51"/>
+    </row>
+    <row r="799" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A799" s="28"/>
+      <c r="B799" s="40"/>
+      <c r="C799" s="49"/>
+      <c r="D799" s="51"/>
+    </row>
+    <row r="800" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A800" s="28"/>
+      <c r="B800" s="40"/>
+      <c r="C800" s="49"/>
+      <c r="D800" s="51"/>
+    </row>
+    <row r="801" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A801" s="28"/>
+      <c r="B801" s="40"/>
+      <c r="C801" s="49"/>
+      <c r="D801" s="51"/>
+    </row>
+    <row r="802" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A802" s="28"/>
+      <c r="B802" s="40"/>
+      <c r="C802" s="49"/>
+      <c r="D802" s="51"/>
+    </row>
+    <row r="803" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A803" s="28"/>
+      <c r="B803" s="40"/>
+      <c r="C803" s="49"/>
+      <c r="D803" s="51"/>
+    </row>
+    <row r="804" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A804" s="28"/>
+      <c r="B804" s="40"/>
+      <c r="C804" s="49"/>
+      <c r="D804" s="51"/>
+    </row>
+    <row r="805" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A805" s="28"/>
+      <c r="B805" s="40"/>
+      <c r="C805" s="49"/>
+      <c r="D805" s="51"/>
+    </row>
+    <row r="806" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A806" s="28"/>
+      <c r="B806" s="40"/>
+      <c r="C806" s="49"/>
+      <c r="D806" s="51"/>
+    </row>
+    <row r="807" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A807" s="28"/>
+      <c r="B807" s="40"/>
+      <c r="C807" s="49"/>
+      <c r="D807" s="51"/>
+    </row>
+    <row r="808" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A808" s="28"/>
+      <c r="B808" s="40"/>
+      <c r="C808" s="49"/>
+      <c r="D808" s="51"/>
+    </row>
+    <row r="809" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A809" s="28"/>
+      <c r="B809" s="40"/>
+      <c r="C809" s="49"/>
+      <c r="D809" s="51"/>
+    </row>
+    <row r="810" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A810" s="28"/>
+      <c r="B810" s="40"/>
+      <c r="C810" s="49"/>
+      <c r="D810" s="51"/>
+    </row>
+    <row r="811" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A811" s="28"/>
+      <c r="B811" s="40"/>
+      <c r="C811" s="49"/>
+      <c r="D811" s="51"/>
+    </row>
+    <row r="812" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A812" s="28"/>
+      <c r="B812" s="40"/>
+      <c r="C812" s="49"/>
+      <c r="D812" s="51"/>
+    </row>
+    <row r="813" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A813" s="28"/>
+      <c r="B813" s="40"/>
+      <c r="C813" s="49"/>
+      <c r="D813" s="51"/>
+    </row>
+    <row r="814" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A814" s="28"/>
+      <c r="B814" s="40"/>
+      <c r="C814" s="49"/>
+      <c r="D814" s="51"/>
+    </row>
+    <row r="815" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A815" s="28"/>
+      <c r="B815" s="40"/>
+      <c r="C815" s="49"/>
+      <c r="D815" s="51"/>
+    </row>
+    <row r="816" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A816" s="28"/>
+      <c r="B816" s="40"/>
+      <c r="C816" s="49"/>
+      <c r="D816" s="51"/>
+    </row>
+    <row r="817" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A817" s="28"/>
+      <c r="B817" s="40"/>
+      <c r="C817" s="49"/>
+      <c r="D817" s="51"/>
+    </row>
+    <row r="818" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A818" s="28"/>
+      <c r="B818" s="40"/>
+      <c r="C818" s="49"/>
+      <c r="D818" s="51"/>
+    </row>
+    <row r="819" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A819" s="28"/>
+      <c r="B819" s="40"/>
+      <c r="C819" s="49"/>
+      <c r="D819" s="51"/>
+    </row>
+    <row r="820" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A820" s="28"/>
+      <c r="B820" s="40"/>
+      <c r="C820" s="49"/>
+      <c r="D820" s="51"/>
+    </row>
+    <row r="821" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A821" s="28"/>
+      <c r="B821" s="40"/>
+      <c r="C821" s="49"/>
+      <c r="D821" s="51"/>
+    </row>
+    <row r="822" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A822" s="28"/>
+      <c r="B822" s="40"/>
+      <c r="C822" s="49"/>
+      <c r="D822" s="51"/>
+    </row>
+    <row r="823" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A823" s="28"/>
+      <c r="B823" s="40"/>
+      <c r="C823" s="49"/>
+      <c r="D823" s="51"/>
+    </row>
+    <row r="824" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A824" s="28"/>
+      <c r="B824" s="40"/>
+      <c r="C824" s="49"/>
+      <c r="D824" s="51"/>
+    </row>
+    <row r="825" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A825" s="28"/>
+      <c r="B825" s="40"/>
+      <c r="C825" s="49"/>
+      <c r="D825" s="51"/>
+    </row>
+    <row r="826" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A826" s="28"/>
+      <c r="B826" s="40"/>
+      <c r="C826" s="49"/>
+      <c r="D826" s="51"/>
+    </row>
+    <row r="827" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A827" s="28"/>
+      <c r="B827" s="40"/>
+      <c r="C827" s="49"/>
+      <c r="D827" s="51"/>
+    </row>
+    <row r="828" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A828" s="28"/>
+      <c r="B828" s="40"/>
+      <c r="C828" s="49"/>
+      <c r="D828" s="51"/>
+    </row>
+    <row r="829" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A829" s="28"/>
+      <c r="B829" s="40"/>
+      <c r="C829" s="49"/>
+      <c r="D829" s="51"/>
+    </row>
+    <row r="830" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A830" s="28"/>
+      <c r="B830" s="40"/>
+      <c r="C830" s="49"/>
+      <c r="D830" s="51"/>
+    </row>
+    <row r="831" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A831" s="28"/>
+      <c r="B831" s="40"/>
+      <c r="C831" s="49"/>
+      <c r="D831" s="51"/>
+    </row>
+    <row r="832" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A832" s="28"/>
+      <c r="B832" s="40"/>
+      <c r="C832" s="49"/>
+      <c r="D832" s="51"/>
+    </row>
+    <row r="833" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A833" s="28"/>
+      <c r="B833" s="40"/>
+      <c r="C833" s="49"/>
+      <c r="D833" s="51"/>
+    </row>
+    <row r="834" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A834" s="28"/>
+      <c r="B834" s="40"/>
+      <c r="C834" s="49"/>
+      <c r="D834" s="51"/>
+    </row>
+    <row r="835" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A835" s="28"/>
+      <c r="B835" s="40"/>
+      <c r="C835" s="49"/>
+      <c r="D835" s="51"/>
+    </row>
+    <row r="836" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A836" s="28"/>
+      <c r="B836" s="40"/>
+      <c r="C836" s="49"/>
+      <c r="D836" s="51"/>
+    </row>
+    <row r="837" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A837" s="28"/>
+      <c r="B837" s="40"/>
+      <c r="C837" s="49"/>
+      <c r="D837" s="51"/>
+    </row>
+    <row r="838" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A838" s="28"/>
+      <c r="B838" s="40"/>
+      <c r="C838" s="49"/>
+      <c r="D838" s="51"/>
+    </row>
+    <row r="839" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A839" s="28"/>
+      <c r="B839" s="40"/>
+      <c r="C839" s="49"/>
+      <c r="D839" s="51"/>
+    </row>
+    <row r="840" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A840" s="28"/>
+      <c r="B840" s="40"/>
+      <c r="C840" s="49"/>
+      <c r="D840" s="51"/>
+    </row>
+    <row r="841" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A841" s="28"/>
+      <c r="B841" s="40"/>
+      <c r="C841" s="49"/>
+      <c r="D841" s="51"/>
+    </row>
+    <row r="842" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A842" s="28"/>
+      <c r="B842" s="40"/>
+      <c r="C842" s="49"/>
+      <c r="D842" s="51"/>
+    </row>
+    <row r="843" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A843" s="28"/>
+      <c r="B843" s="40"/>
+      <c r="C843" s="49"/>
+      <c r="D843" s="51"/>
+    </row>
+    <row r="844" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A844" s="28"/>
+      <c r="B844" s="40"/>
+      <c r="C844" s="49"/>
+      <c r="D844" s="51"/>
+    </row>
+    <row r="845" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A845" s="28"/>
+      <c r="B845" s="40"/>
+      <c r="C845" s="49"/>
+      <c r="D845" s="51"/>
+    </row>
+    <row r="846" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A846" s="28"/>
+      <c r="B846" s="40"/>
+      <c r="C846" s="49"/>
+      <c r="D846" s="51"/>
+    </row>
+    <row r="847" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A847" s="28"/>
+      <c r="B847" s="40"/>
+      <c r="C847" s="49"/>
+      <c r="D847" s="51"/>
+    </row>
+    <row r="848" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A848" s="28"/>
+      <c r="B848" s="40"/>
+      <c r="C848" s="49"/>
+      <c r="D848" s="51"/>
+    </row>
+    <row r="849" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A849" s="28"/>
+      <c r="B849" s="40"/>
+      <c r="C849" s="49"/>
+      <c r="D849" s="51"/>
+    </row>
+    <row r="850" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A850" s="28"/>
+      <c r="B850" s="40"/>
+      <c r="C850" s="49"/>
+      <c r="D850" s="51"/>
+    </row>
+    <row r="851" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A851" s="28"/>
+      <c r="B851" s="40"/>
+      <c r="C851" s="49"/>
+      <c r="D851" s="51"/>
+    </row>
+    <row r="852" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A852" s="28"/>
+      <c r="B852" s="40"/>
+      <c r="C852" s="49"/>
+      <c r="D852" s="51"/>
+    </row>
+    <row r="853" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A853" s="28"/>
+      <c r="B853" s="40"/>
+      <c r="C853" s="49"/>
+      <c r="D853" s="51"/>
+    </row>
+    <row r="854" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A854" s="28"/>
+      <c r="B854" s="40"/>
+      <c r="C854" s="49"/>
+      <c r="D854" s="51"/>
+    </row>
+    <row r="855" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A855" s="28"/>
+      <c r="B855" s="40"/>
+      <c r="C855" s="49"/>
+      <c r="D855" s="51"/>
+    </row>
+    <row r="856" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A856" s="28"/>
+      <c r="B856" s="40"/>
+      <c r="C856" s="49"/>
+      <c r="D856" s="51"/>
+    </row>
+    <row r="857" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A857" s="28"/>
+      <c r="B857" s="40"/>
+      <c r="C857" s="49"/>
+      <c r="D857" s="51"/>
+    </row>
+    <row r="858" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A858" s="28"/>
+      <c r="B858" s="40"/>
+      <c r="C858" s="49"/>
+      <c r="D858" s="51"/>
+    </row>
+    <row r="859" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A859" s="28"/>
+      <c r="B859" s="40"/>
+      <c r="C859" s="49"/>
+      <c r="D859" s="51"/>
+    </row>
+    <row r="860" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A860" s="28"/>
+      <c r="B860" s="40"/>
+      <c r="C860" s="49"/>
+      <c r="D860" s="51"/>
+    </row>
+    <row r="861" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A861" s="28"/>
+      <c r="B861" s="40"/>
+      <c r="C861" s="49"/>
+      <c r="D861" s="51"/>
+    </row>
+    <row r="862" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A862" s="28"/>
+      <c r="B862" s="40"/>
+      <c r="C862" s="49"/>
+      <c r="D862" s="51"/>
+    </row>
+    <row r="863" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A863" s="28"/>
+      <c r="B863" s="40"/>
+      <c r="C863" s="49"/>
+      <c r="D863" s="51"/>
+    </row>
+    <row r="864" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A864" s="28"/>
+      <c r="B864" s="40"/>
+      <c r="C864" s="49"/>
+      <c r="D864" s="51"/>
+    </row>
+    <row r="865" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A865" s="28"/>
+      <c r="B865" s="40"/>
+      <c r="C865" s="49"/>
+      <c r="D865" s="51"/>
+    </row>
+    <row r="866" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A866" s="28"/>
+      <c r="B866" s="40"/>
+      <c r="C866" s="49"/>
+      <c r="D866" s="51"/>
+    </row>
+    <row r="867" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A867" s="28"/>
+      <c r="B867" s="40"/>
+      <c r="C867" s="49"/>
+      <c r="D867" s="51"/>
+    </row>
+    <row r="868" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A868" s="28"/>
+      <c r="B868" s="40"/>
+      <c r="C868" s="49"/>
+      <c r="D868" s="51"/>
+    </row>
+    <row r="869" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A869" s="28"/>
+      <c r="B869" s="40"/>
+      <c r="C869" s="49"/>
+      <c r="D869" s="51"/>
+    </row>
+    <row r="870" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A870" s="28"/>
+      <c r="B870" s="40"/>
+      <c r="C870" s="49"/>
+      <c r="D870" s="51"/>
+    </row>
+    <row r="871" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A871" s="28"/>
+      <c r="B871" s="40"/>
+      <c r="C871" s="49"/>
+      <c r="D871" s="51"/>
+    </row>
+    <row r="872" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A872" s="28"/>
+      <c r="B872" s="40"/>
+      <c r="C872" s="49"/>
+      <c r="D872" s="51"/>
+    </row>
+    <row r="873" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A873" s="28"/>
+      <c r="B873" s="40"/>
+      <c r="C873" s="49"/>
+      <c r="D873" s="51"/>
+    </row>
+    <row r="874" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A874" s="28"/>
+      <c r="B874" s="40"/>
+      <c r="C874" s="49"/>
+      <c r="D874" s="51"/>
+    </row>
+    <row r="875" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A875" s="28"/>
+      <c r="B875" s="40"/>
+      <c r="C875" s="49"/>
+      <c r="D875" s="51"/>
+    </row>
+    <row r="876" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A876" s="28"/>
+      <c r="B876" s="40"/>
+      <c r="C876" s="49"/>
+      <c r="D876" s="51"/>
+    </row>
+    <row r="877" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A877" s="28"/>
+      <c r="B877" s="40"/>
+      <c r="C877" s="49"/>
+      <c r="D877" s="51"/>
+    </row>
+    <row r="878" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A878" s="28"/>
+      <c r="B878" s="40"/>
+      <c r="C878" s="49"/>
+      <c r="D878" s="51"/>
+    </row>
+    <row r="879" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A879" s="28"/>
+      <c r="B879" s="40"/>
+      <c r="C879" s="49"/>
+      <c r="D879" s="51"/>
+    </row>
+    <row r="880" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A880" s="28"/>
+      <c r="B880" s="40"/>
+      <c r="C880" s="49"/>
+      <c r="D880" s="51"/>
+    </row>
+    <row r="881" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A881" s="28"/>
+      <c r="B881" s="40"/>
+      <c r="C881" s="49"/>
+      <c r="D881" s="51"/>
+    </row>
+    <row r="882" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A882" s="28"/>
+      <c r="B882" s="40"/>
+      <c r="C882" s="49"/>
+      <c r="D882" s="51"/>
+    </row>
+    <row r="883" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A883" s="28"/>
+      <c r="B883" s="40"/>
+      <c r="C883" s="49"/>
+      <c r="D883" s="51"/>
+    </row>
+    <row r="884" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A884" s="28"/>
+      <c r="B884" s="40"/>
+      <c r="C884" s="49"/>
+      <c r="D884" s="51"/>
+    </row>
+    <row r="885" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A885" s="28"/>
+      <c r="B885" s="40"/>
+      <c r="C885" s="49"/>
+      <c r="D885" s="51"/>
+    </row>
+    <row r="886" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A886" s="28"/>
+      <c r="B886" s="40"/>
+      <c r="C886" s="49"/>
+      <c r="D886" s="51"/>
+    </row>
+    <row r="887" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A887" s="28"/>
+      <c r="B887" s="40"/>
+      <c r="C887" s="49"/>
+      <c r="D887" s="51"/>
+    </row>
+    <row r="888" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A888" s="28"/>
+      <c r="B888" s="40"/>
+      <c r="C888" s="49"/>
+      <c r="D888" s="51"/>
+    </row>
+    <row r="889" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A889" s="28"/>
+      <c r="B889" s="40"/>
+      <c r="C889" s="49"/>
+      <c r="D889" s="51"/>
+    </row>
+    <row r="890" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A890" s="28"/>
+      <c r="B890" s="40"/>
+      <c r="C890" s="49"/>
+      <c r="D890" s="51"/>
+    </row>
+    <row r="891" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A891" s="28"/>
+      <c r="B891" s="40"/>
+      <c r="C891" s="49"/>
+      <c r="D891" s="51"/>
+    </row>
+    <row r="892" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A892" s="28"/>
+      <c r="B892" s="40"/>
+      <c r="C892" s="49"/>
+      <c r="D892" s="51"/>
+    </row>
+    <row r="893" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A893" s="28"/>
+      <c r="B893" s="40"/>
+      <c r="C893" s="49"/>
+      <c r="D893" s="51"/>
+    </row>
+    <row r="894" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A894" s="28"/>
+      <c r="B894" s="40"/>
+      <c r="C894" s="49"/>
+      <c r="D894" s="51"/>
+    </row>
+    <row r="895" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A895" s="28"/>
+      <c r="B895" s="40"/>
+      <c r="C895" s="49"/>
+      <c r="D895" s="51"/>
+    </row>
+    <row r="896" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A896" s="28"/>
+      <c r="B896" s="40"/>
+      <c r="C896" s="49"/>
+      <c r="D896" s="51"/>
+    </row>
+    <row r="897" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A897" s="28"/>
+      <c r="B897" s="40"/>
+      <c r="C897" s="49"/>
+      <c r="D897" s="51"/>
+    </row>
+    <row r="898" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A898" s="28"/>
+      <c r="B898" s="40"/>
+      <c r="C898" s="49"/>
+      <c r="D898" s="51"/>
+    </row>
+    <row r="899" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A899" s="28"/>
+      <c r="B899" s="40"/>
+      <c r="C899" s="49"/>
+      <c r="D899" s="51"/>
+    </row>
+    <row r="900" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A900" s="28"/>
+      <c r="B900" s="40"/>
+      <c r="C900" s="49"/>
+      <c r="D900" s="51"/>
+    </row>
+    <row r="901" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A901" s="28"/>
+      <c r="B901" s="40"/>
+      <c r="C901" s="49"/>
+      <c r="D901" s="51"/>
+    </row>
+    <row r="902" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A902" s="28"/>
+      <c r="B902" s="40"/>
+      <c r="C902" s="49"/>
+      <c r="D902" s="51"/>
+    </row>
+    <row r="903" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A903" s="28"/>
+      <c r="B903" s="40"/>
+      <c r="C903" s="49"/>
+      <c r="D903" s="51"/>
+    </row>
+    <row r="904" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A904" s="28"/>
+      <c r="B904" s="40"/>
+      <c r="C904" s="49"/>
+      <c r="D904" s="51"/>
+    </row>
+    <row r="905" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A905" s="28"/>
+      <c r="B905" s="40"/>
+      <c r="C905" s="49"/>
+      <c r="D905" s="51"/>
+    </row>
+    <row r="906" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A906" s="28"/>
+      <c r="B906" s="40"/>
+      <c r="C906" s="49"/>
+      <c r="D906" s="51"/>
+    </row>
+    <row r="907" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A907" s="28"/>
+      <c r="B907" s="40"/>
+      <c r="C907" s="49"/>
+      <c r="D907" s="51"/>
+    </row>
+    <row r="908" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A908" s="28"/>
+      <c r="B908" s="40"/>
+      <c r="C908" s="49"/>
+      <c r="D908" s="51"/>
+    </row>
+    <row r="909" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A909" s="28"/>
+      <c r="B909" s="40"/>
+      <c r="C909" s="49"/>
+      <c r="D909" s="51"/>
+    </row>
+    <row r="910" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A910" s="28"/>
+      <c r="B910" s="40"/>
+      <c r="C910" s="49"/>
+      <c r="D910" s="51"/>
+    </row>
+    <row r="911" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A911" s="28"/>
+      <c r="B911" s="40"/>
+      <c r="C911" s="49"/>
+      <c r="D911" s="51"/>
+    </row>
+    <row r="912" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A912" s="28"/>
+      <c r="B912" s="40"/>
+      <c r="C912" s="49"/>
+      <c r="D912" s="51"/>
+    </row>
+    <row r="913" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A913" s="28"/>
+      <c r="B913" s="40"/>
+      <c r="C913" s="49"/>
+      <c r="D913" s="51"/>
+    </row>
+    <row r="914" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A914" s="28"/>
+      <c r="B914" s="40"/>
+      <c r="C914" s="49"/>
+      <c r="D914" s="51"/>
+    </row>
+    <row r="915" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A915" s="28"/>
+      <c r="B915" s="40"/>
+      <c r="C915" s="49"/>
+      <c r="D915" s="51"/>
+    </row>
+    <row r="916" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A916" s="28"/>
+      <c r="B916" s="40"/>
+      <c r="C916" s="49"/>
+      <c r="D916" s="51"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6739F979-B2A5-4539-9D33-4334DC00DA9D}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC3F0A6-22DF-4DC2-BA71-BE3CE02A9F29}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="16200" windowHeight="9970" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="712">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2160,6 +2160,12 @@
   </si>
   <si>
     <t>pcs</t>
+  </si>
+  <si>
+    <t>Chocolate Sauce - Production (per ml)</t>
+  </si>
+  <si>
+    <t>Cookie Production (per gram)</t>
   </si>
 </sst>
 </file>
@@ -2331,7 +2337,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2548,11 +2554,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2685,6 +2702,28 @@
     </xf>
     <xf numFmtId="165" fontId="7" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3000,19 +3039,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:G682"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D685"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>460</v>
       </c>
@@ -3026,7 +3065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>468</v>
       </c>
@@ -3040,7 +3079,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>480</v>
       </c>
@@ -3054,7 +3093,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>469</v>
       </c>
@@ -3068,7 +3107,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>461</v>
       </c>
@@ -3082,7 +3121,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>481</v>
       </c>
@@ -3096,7 +3135,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>482</v>
       </c>
@@ -3110,7 +3149,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>483</v>
       </c>
@@ -3124,7 +3163,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>473</v>
       </c>
@@ -3138,7 +3177,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>474</v>
       </c>
@@ -3152,7 +3191,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>484</v>
       </c>
@@ -3166,7 +3205,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>485</v>
       </c>
@@ -3180,7 +3219,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
         <v>475</v>
       </c>
@@ -3194,7 +3233,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>476</v>
       </c>
@@ -3208,7 +3247,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>477</v>
       </c>
@@ -3222,7 +3261,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>478</v>
       </c>
@@ -3236,7 +3275,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>479</v>
       </c>
@@ -3250,7 +3289,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>486</v>
       </c>
@@ -3264,7 +3303,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>487</v>
       </c>
@@ -3278,7 +3317,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>488</v>
       </c>
@@ -3292,7 +3331,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>489</v>
       </c>
@@ -3306,7 +3345,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>490</v>
       </c>
@@ -3320,7 +3359,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>491</v>
       </c>
@@ -3334,7 +3373,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
         <v>492</v>
       </c>
@@ -3348,7 +3387,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>493</v>
       </c>
@@ -3362,7 +3401,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>494</v>
       </c>
@@ -3376,7 +3415,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>495</v>
       </c>
@@ -3390,7 +3429,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
         <v>496</v>
       </c>
@@ -3404,7 +3443,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>497</v>
       </c>
@@ -3418,7 +3457,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>498</v>
       </c>
@@ -3432,7 +3471,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>499</v>
       </c>
@@ -3446,7 +3485,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
         <v>500</v>
       </c>
@@ -3460,7 +3499,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>501</v>
       </c>
@@ -3474,7 +3513,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
         <v>502</v>
       </c>
@@ -3488,7 +3527,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
         <v>503</v>
       </c>
@@ -3502,7 +3541,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
         <v>504</v>
       </c>
@@ -3516,7 +3555,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>505</v>
       </c>
@@ -3530,7 +3569,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
         <v>506</v>
       </c>
@@ -3544,7 +3583,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
         <v>507</v>
       </c>
@@ -3558,7 +3597,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
         <v>508</v>
       </c>
@@ -3572,7 +3611,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>509</v>
       </c>
@@ -3586,7 +3625,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
         <v>510</v>
       </c>
@@ -3600,7 +3639,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="s">
         <v>511</v>
       </c>
@@ -3614,7 +3653,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
         <v>512</v>
       </c>
@@ -3628,7 +3667,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
         <v>462</v>
       </c>
@@ -3642,7 +3681,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="28" t="s">
         <v>513</v>
       </c>
@@ -3656,7 +3695,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
         <v>514</v>
       </c>
@@ -3670,7 +3709,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
         <v>515</v>
       </c>
@@ -3684,7 +3723,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
         <v>516</v>
       </c>
@@ -3698,7 +3737,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
         <v>517</v>
       </c>
@@ -3712,7 +3751,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
         <v>518</v>
       </c>
@@ -3726,7 +3765,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="28" t="s">
         <v>519</v>
       </c>
@@ -3740,7 +3779,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
         <v>520</v>
       </c>
@@ -3754,7 +3793,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
         <v>521</v>
       </c>
@@ -3768,7 +3807,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="28" t="s">
         <v>522</v>
       </c>
@@ -3782,7 +3821,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
         <v>523</v>
       </c>
@@ -3796,7 +3835,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
         <v>524</v>
       </c>
@@ -3810,7 +3849,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
         <v>525</v>
       </c>
@@ -3824,7 +3863,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
         <v>526</v>
       </c>
@@ -3838,7 +3877,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
         <v>527</v>
       </c>
@@ -3852,7 +3891,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
         <v>528</v>
       </c>
@@ -3866,7 +3905,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>463</v>
       </c>
@@ -3880,7 +3919,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
         <v>529</v>
       </c>
@@ -3894,7 +3933,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>530</v>
       </c>
@@ -3908,7 +3947,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
         <v>531</v>
       </c>
@@ -3922,7 +3961,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
         <v>532</v>
       </c>
@@ -3936,7 +3975,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
         <v>533</v>
       </c>
@@ -3950,7 +3989,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="28" t="s">
         <v>534</v>
       </c>
@@ -3964,7 +4003,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="s">
         <v>535</v>
       </c>
@@ -3978,7 +4017,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>536</v>
       </c>
@@ -3992,7 +4031,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
         <v>537</v>
       </c>
@@ -4006,7 +4045,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
         <v>538</v>
       </c>
@@ -4020,7 +4059,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
         <v>539</v>
       </c>
@@ -4034,7 +4073,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="30" t="s">
         <v>541</v>
       </c>
@@ -4048,7 +4087,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
         <v>540</v>
       </c>
@@ -4062,7 +4101,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
         <v>542</v>
       </c>
@@ -4076,7 +4115,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="28" t="s">
         <v>543</v>
       </c>
@@ -4090,7 +4129,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="31" t="s">
         <v>544</v>
       </c>
@@ -4104,7 +4143,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="23" t="s">
         <v>545</v>
       </c>
@@ -4118,7 +4157,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="31" t="s">
         <v>546</v>
       </c>
@@ -4132,7 +4171,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="s">
         <v>547</v>
       </c>
@@ -4146,7 +4185,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="23" t="s">
         <v>548</v>
       </c>
@@ -4160,7 +4199,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="s">
         <v>549</v>
       </c>
@@ -4174,7 +4213,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="32" t="s">
         <v>550</v>
       </c>
@@ -4188,7 +4227,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="s">
         <v>551</v>
       </c>
@@ -4202,7 +4241,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
         <v>552</v>
       </c>
@@ -4216,7 +4255,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="23" t="s">
         <v>553</v>
       </c>
@@ -4230,7 +4269,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
         <v>554</v>
       </c>
@@ -4244,7 +4283,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="16" t="s">
         <v>555</v>
       </c>
@@ -4258,7 +4297,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="16" t="s">
         <v>556</v>
       </c>
@@ -4272,7 +4311,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="s">
         <v>557</v>
       </c>
@@ -4286,7 +4325,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="28" t="s">
         <v>558</v>
       </c>
@@ -4300,7 +4339,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
         <v>559</v>
       </c>
@@ -4314,7 +4353,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="23" t="s">
         <v>560</v>
       </c>
@@ -4328,7 +4367,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="s">
         <v>561</v>
       </c>
@@ -4342,7 +4381,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="23" t="s">
         <v>562</v>
       </c>
@@ -4356,7 +4395,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="s">
         <v>563</v>
       </c>
@@ -4370,7 +4409,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="23" t="s">
         <v>564</v>
       </c>
@@ -4384,7 +4423,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="28" t="s">
         <v>565</v>
       </c>
@@ -4398,7 +4437,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>566</v>
       </c>
@@ -4412,7 +4451,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="28" t="s">
         <v>567</v>
       </c>
@@ -4426,7 +4465,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="s">
         <v>568</v>
       </c>
@@ -4440,7 +4479,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="24" t="s">
         <v>569</v>
       </c>
@@ -4454,7 +4493,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>570</v>
       </c>
@@ -4468,7 +4507,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
         <v>571</v>
       </c>
@@ -4482,7 +4521,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="24" t="s">
         <v>572</v>
       </c>
@@ -4496,7 +4535,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>472</v>
       </c>
@@ -4510,7 +4549,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>573</v>
       </c>
@@ -4524,7 +4563,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="24" t="s">
         <v>574</v>
       </c>
@@ -4538,7 +4577,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>575</v>
       </c>
@@ -4552,7 +4591,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>576</v>
       </c>
@@ -4566,7 +4605,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="28" t="s">
         <v>577</v>
       </c>
@@ -4580,7 +4619,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>471</v>
       </c>
@@ -4594,7 +4633,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>578</v>
       </c>
@@ -4608,7 +4647,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>579</v>
       </c>
@@ -4622,7 +4661,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>580</v>
       </c>
@@ -4636,7 +4675,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
         <v>581</v>
       </c>
@@ -4650,7 +4689,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>582</v>
       </c>
@@ -4664,7 +4703,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
         <v>583</v>
       </c>
@@ -4678,7 +4717,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>584</v>
       </c>
@@ -4692,7 +4731,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>585</v>
       </c>
@@ -4706,7 +4745,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="23" t="s">
         <v>586</v>
       </c>
@@ -4720,7 +4759,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="25" t="s">
         <v>587</v>
       </c>
@@ -4734,7 +4773,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="s">
         <v>588</v>
       </c>
@@ -4748,7 +4787,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="23" t="s">
         <v>589</v>
       </c>
@@ -4762,7 +4801,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="23" t="s">
         <v>590</v>
       </c>
@@ -4776,7 +4815,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="26" t="s">
         <v>591</v>
       </c>
@@ -4790,7 +4829,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="33" t="s">
         <v>592</v>
       </c>
@@ -4804,7 +4843,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="33" t="s">
         <v>593</v>
       </c>
@@ -4818,7 +4857,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="33" t="s">
         <v>594</v>
       </c>
@@ -4832,7 +4871,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="26" t="s">
         <v>595</v>
       </c>
@@ -4846,7 +4885,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="26" t="s">
         <v>596</v>
       </c>
@@ -4860,7 +4899,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="26" t="s">
         <v>597</v>
       </c>
@@ -4874,7 +4913,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="26" t="s">
         <v>598</v>
       </c>
@@ -4888,7 +4927,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="26" t="s">
         <v>599</v>
       </c>
@@ -4902,7 +4941,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="26" t="s">
         <v>600</v>
       </c>
@@ -4915,12 +4954,8 @@
       <c r="D137" s="49" t="s">
         <v>465</v>
       </c>
-      <c r="G137">
-        <f>27.7/60</f>
-        <v>0.46166666666666667</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="26" t="s">
         <v>601</v>
       </c>
@@ -4934,7 +4969,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="26" t="s">
         <v>602</v>
       </c>
@@ -4948,7 +4983,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="26" t="s">
         <v>603</v>
       </c>
@@ -4962,7 +4997,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="26" t="s">
         <v>604</v>
       </c>
@@ -4976,7 +5011,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="26" t="s">
         <v>605</v>
       </c>
@@ -4990,7 +5025,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="26" t="s">
         <v>606</v>
       </c>
@@ -5004,12 +5039,12 @@
         <v>465</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="26" t="s">
         <v>607</v>
       </c>
       <c r="B144" s="38">
-        <v>0.46200000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="C144" s="47" t="s">
         <v>466</v>
@@ -5018,7 +5053,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="26" t="s">
         <v>608</v>
       </c>
@@ -5032,8 +5067,8 @@
         <v>465</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="26" t="s">
+    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="58" t="s">
         <v>609</v>
       </c>
       <c r="B146" s="38">
@@ -5046,7 +5081,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>0</v>
       </c>
@@ -5060,7 +5095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>3</v>
       </c>
@@ -5074,7 +5109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>6</v>
       </c>
@@ -5088,7 +5123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>8</v>
       </c>
@@ -5102,7 +5137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>9</v>
       </c>
@@ -5116,7 +5151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>610</v>
       </c>
@@ -5130,7 +5165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>11</v>
       </c>
@@ -5144,7 +5179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>12</v>
       </c>
@@ -5158,7 +5193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>611</v>
       </c>
@@ -5172,7 +5207,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>13</v>
       </c>
@@ -5186,7 +5221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>14</v>
       </c>
@@ -5200,7 +5235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>15</v>
       </c>
@@ -5214,7 +5249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>16</v>
       </c>
@@ -5228,7 +5263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>17</v>
       </c>
@@ -5242,7 +5277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>18</v>
       </c>
@@ -5256,7 +5291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>19</v>
       </c>
@@ -5270,7 +5305,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>20</v>
       </c>
@@ -5284,7 +5319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>21</v>
       </c>
@@ -5298,7 +5333,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>22</v>
       </c>
@@ -5312,7 +5347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>24</v>
       </c>
@@ -5326,7 +5361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>25</v>
       </c>
@@ -5340,7 +5375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>26</v>
       </c>
@@ -5354,7 +5389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>27</v>
       </c>
@@ -5368,7 +5403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>29</v>
       </c>
@@ -5382,7 +5417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>30</v>
       </c>
@@ -5396,7 +5431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>31</v>
       </c>
@@ -5410,7 +5445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>33</v>
       </c>
@@ -5424,7 +5459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>34</v>
       </c>
@@ -5438,7 +5473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>35</v>
       </c>
@@ -5452,7 +5487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>612</v>
       </c>
@@ -5466,7 +5501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>37</v>
       </c>
@@ -5480,7 +5515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>38</v>
       </c>
@@ -5494,7 +5529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>39</v>
       </c>
@@ -5508,7 +5543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>613</v>
       </c>
@@ -5522,7 +5557,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
         <v>41</v>
       </c>
@@ -5536,7 +5571,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>42</v>
       </c>
@@ -5550,7 +5585,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>614</v>
       </c>
@@ -5564,7 +5599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
         <v>43</v>
       </c>
@@ -5578,7 +5613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>44</v>
       </c>
@@ -5592,7 +5627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
         <v>45</v>
       </c>
@@ -5606,7 +5641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>615</v>
       </c>
@@ -5620,7 +5655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
         <v>46</v>
       </c>
@@ -5634,7 +5669,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
         <v>48</v>
       </c>
@@ -5648,7 +5683,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
         <v>49</v>
       </c>
@@ -5662,7 +5697,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
         <v>50</v>
       </c>
@@ -5676,7 +5711,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>51</v>
       </c>
@@ -5690,7 +5725,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>52</v>
       </c>
@@ -5704,7 +5739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>53</v>
       </c>
@@ -5718,7 +5753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>54</v>
       </c>
@@ -5732,7 +5767,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
         <v>55</v>
       </c>
@@ -5746,7 +5781,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
         <v>56</v>
       </c>
@@ -5760,7 +5795,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
         <v>57</v>
       </c>
@@ -5774,7 +5809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>58</v>
       </c>
@@ -5788,7 +5823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>59</v>
       </c>
@@ -5802,7 +5837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
         <v>60</v>
       </c>
@@ -5816,7 +5851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>61</v>
       </c>
@@ -5830,7 +5865,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>62</v>
       </c>
@@ -5844,7 +5879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>63</v>
       </c>
@@ -5858,7 +5893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>64</v>
       </c>
@@ -5872,7 +5907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>65</v>
       </c>
@@ -5886,7 +5921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>66</v>
       </c>
@@ -5900,7 +5935,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>67</v>
       </c>
@@ -5914,7 +5949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>68</v>
       </c>
@@ -5928,7 +5963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>69</v>
       </c>
@@ -5942,7 +5977,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>70</v>
       </c>
@@ -5956,7 +5991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>71</v>
       </c>
@@ -5970,7 +6005,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>72</v>
       </c>
@@ -5984,7 +6019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>73</v>
       </c>
@@ -5998,7 +6033,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>74</v>
       </c>
@@ -6012,7 +6047,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>75</v>
       </c>
@@ -6026,7 +6061,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>76</v>
       </c>
@@ -6040,7 +6075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>77</v>
       </c>
@@ -6054,7 +6089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>79</v>
       </c>
@@ -6068,7 +6103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>80</v>
       </c>
@@ -6082,7 +6117,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>81</v>
       </c>
@@ -6096,7 +6131,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>82</v>
       </c>
@@ -6110,7 +6145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>83</v>
       </c>
@@ -6124,7 +6159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>616</v>
       </c>
@@ -6138,7 +6173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>84</v>
       </c>
@@ -6152,7 +6187,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>85</v>
       </c>
@@ -6166,7 +6201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>86</v>
       </c>
@@ -6180,7 +6215,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>87</v>
       </c>
@@ -6194,7 +6229,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>88</v>
       </c>
@@ -6208,7 +6243,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>89</v>
       </c>
@@ -6222,7 +6257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>90</v>
       </c>
@@ -6236,7 +6271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>91</v>
       </c>
@@ -6250,7 +6285,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>92</v>
       </c>
@@ -6264,7 +6299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>93</v>
       </c>
@@ -6278,7 +6313,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>94</v>
       </c>
@@ -6292,7 +6327,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>96</v>
       </c>
@@ -6306,7 +6341,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>97</v>
       </c>
@@ -6320,7 +6355,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>98</v>
       </c>
@@ -6334,7 +6369,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>99</v>
       </c>
@@ -6348,7 +6383,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>100</v>
       </c>
@@ -6362,7 +6397,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>101</v>
       </c>
@@ -6376,7 +6411,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>102</v>
       </c>
@@ -6390,7 +6425,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>103</v>
       </c>
@@ -6404,7 +6439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>104</v>
       </c>
@@ -6418,7 +6453,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>105</v>
       </c>
@@ -6432,7 +6467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>106</v>
       </c>
@@ -6446,7 +6481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>107</v>
       </c>
@@ -6460,7 +6495,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>108</v>
       </c>
@@ -6474,7 +6509,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>110</v>
       </c>
@@ -6488,7 +6523,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>111</v>
       </c>
@@ -6502,7 +6537,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>112</v>
       </c>
@@ -6516,7 +6551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>113</v>
       </c>
@@ -6530,7 +6565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>114</v>
       </c>
@@ -6544,7 +6579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>115</v>
       </c>
@@ -6558,7 +6593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>116</v>
       </c>
@@ -6572,7 +6607,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>617</v>
       </c>
@@ -6586,7 +6621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>117</v>
       </c>
@@ -6600,7 +6635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>118</v>
       </c>
@@ -6614,7 +6649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>119</v>
       </c>
@@ -6628,7 +6663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>618</v>
       </c>
@@ -6642,7 +6677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>120</v>
       </c>
@@ -6656,7 +6691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>121</v>
       </c>
@@ -6670,7 +6705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>619</v>
       </c>
@@ -6684,7 +6719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>122</v>
       </c>
@@ -6698,7 +6733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>620</v>
       </c>
@@ -6712,7 +6747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>621</v>
       </c>
@@ -6726,7 +6761,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>123</v>
       </c>
@@ -6740,7 +6775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>124</v>
       </c>
@@ -6754,7 +6789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>125</v>
       </c>
@@ -6768,7 +6803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>126</v>
       </c>
@@ -6782,7 +6817,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>127</v>
       </c>
@@ -6796,7 +6831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>128</v>
       </c>
@@ -6810,7 +6845,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>622</v>
       </c>
@@ -6824,7 +6859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>623</v>
       </c>
@@ -6838,7 +6873,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>129</v>
       </c>
@@ -6852,7 +6887,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>130</v>
       </c>
@@ -6866,7 +6901,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>132</v>
       </c>
@@ -6880,7 +6915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>133</v>
       </c>
@@ -6894,7 +6929,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>134</v>
       </c>
@@ -6908,7 +6943,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>135</v>
       </c>
@@ -6922,7 +6957,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>624</v>
       </c>
@@ -6936,7 +6971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>136</v>
       </c>
@@ -6950,7 +6985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>625</v>
       </c>
@@ -6964,7 +6999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>137</v>
       </c>
@@ -6978,7 +7013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>138</v>
       </c>
@@ -6992,7 +7027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>139</v>
       </c>
@@ -7006,7 +7041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>140</v>
       </c>
@@ -7020,7 +7055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>626</v>
       </c>
@@ -7034,7 +7069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>141</v>
       </c>
@@ -7048,7 +7083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>142</v>
       </c>
@@ -7062,7 +7097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>143</v>
       </c>
@@ -7076,7 +7111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>144</v>
       </c>
@@ -7090,7 +7125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>145</v>
       </c>
@@ -7104,7 +7139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>146</v>
       </c>
@@ -7118,7 +7153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>147</v>
       </c>
@@ -7132,7 +7167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>148</v>
       </c>
@@ -7146,7 +7181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>627</v>
       </c>
@@ -7160,7 +7195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>628</v>
       </c>
@@ -7174,7 +7209,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>629</v>
       </c>
@@ -7188,7 +7223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>630</v>
       </c>
@@ -7202,7 +7237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>631</v>
       </c>
@@ -7216,7 +7251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>632</v>
       </c>
@@ -7230,7 +7265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>149</v>
       </c>
@@ -7244,7 +7279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>150</v>
       </c>
@@ -7258,7 +7293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>151</v>
       </c>
@@ -7272,7 +7307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>152</v>
       </c>
@@ -7286,7 +7321,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>153</v>
       </c>
@@ -7300,7 +7335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>154</v>
       </c>
@@ -7314,7 +7349,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>155</v>
       </c>
@@ -7328,7 +7363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>156</v>
       </c>
@@ -7342,7 +7377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>157</v>
       </c>
@@ -7356,7 +7391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>158</v>
       </c>
@@ -7370,7 +7405,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>159</v>
       </c>
@@ -7384,7 +7419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>160</v>
       </c>
@@ -7398,7 +7433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>161</v>
       </c>
@@ -7412,7 +7447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>162</v>
       </c>
@@ -7426,7 +7461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>163</v>
       </c>
@@ -7440,7 +7475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>164</v>
       </c>
@@ -7454,7 +7489,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>165</v>
       </c>
@@ -7468,7 +7503,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>166</v>
       </c>
@@ -7482,7 +7517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>167</v>
       </c>
@@ -7496,7 +7531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4" t="s">
         <v>168</v>
       </c>
@@ -7510,7 +7545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4" t="s">
         <v>169</v>
       </c>
@@ -7524,7 +7559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4" t="s">
         <v>170</v>
       </c>
@@ -7538,7 +7573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4" t="s">
         <v>171</v>
       </c>
@@ -7552,7 +7587,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
         <v>633</v>
       </c>
@@ -7566,7 +7601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
         <v>172</v>
       </c>
@@ -7580,7 +7615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
         <v>634</v>
       </c>
@@ -7594,7 +7629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
         <v>173</v>
       </c>
@@ -7608,7 +7643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
         <v>174</v>
       </c>
@@ -7622,7 +7657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
         <v>175</v>
       </c>
@@ -7636,7 +7671,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
         <v>177</v>
       </c>
@@ -7650,7 +7685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
         <v>178</v>
       </c>
@@ -7664,7 +7699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
         <v>179</v>
       </c>
@@ -7678,7 +7713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
         <v>180</v>
       </c>
@@ -7692,7 +7727,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>181</v>
       </c>
@@ -7706,7 +7741,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
         <v>182</v>
       </c>
@@ -7720,7 +7755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
         <v>183</v>
       </c>
@@ -7734,7 +7769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
         <v>184</v>
       </c>
@@ -7748,7 +7783,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
         <v>185</v>
       </c>
@@ -7762,7 +7797,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
         <v>186</v>
       </c>
@@ -7776,7 +7811,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
         <v>187</v>
       </c>
@@ -7790,7 +7825,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
         <v>188</v>
       </c>
@@ -7804,7 +7839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
         <v>189</v>
       </c>
@@ -7818,7 +7853,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
         <v>190</v>
       </c>
@@ -7832,7 +7867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
         <v>191</v>
       </c>
@@ -7846,7 +7881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
         <v>192</v>
       </c>
@@ -7860,7 +7895,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
         <v>193</v>
       </c>
@@ -7874,7 +7909,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
         <v>194</v>
       </c>
@@ -7888,7 +7923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
         <v>195</v>
       </c>
@@ -7902,7 +7937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
         <v>196</v>
       </c>
@@ -7916,7 +7951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
         <v>197</v>
       </c>
@@ -7930,7 +7965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
         <v>198</v>
       </c>
@@ -7944,7 +7979,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
         <v>200</v>
       </c>
@@ -7958,7 +7993,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
         <v>202</v>
       </c>
@@ -7972,7 +8007,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
         <v>203</v>
       </c>
@@ -7986,7 +8021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
         <v>204</v>
       </c>
@@ -8000,7 +8035,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>205</v>
       </c>
@@ -8014,7 +8049,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>206</v>
       </c>
@@ -8028,7 +8063,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>207</v>
       </c>
@@ -8042,7 +8077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>208</v>
       </c>
@@ -8056,7 +8091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>209</v>
       </c>
@@ -8070,7 +8105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>210</v>
       </c>
@@ -8084,7 +8119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>211</v>
       </c>
@@ -8098,7 +8133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>212</v>
       </c>
@@ -8112,7 +8147,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>213</v>
       </c>
@@ -8126,7 +8161,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>214</v>
       </c>
@@ -8140,7 +8175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>215</v>
       </c>
@@ -8154,7 +8189,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>216</v>
       </c>
@@ -8168,7 +8203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>217</v>
       </c>
@@ -8182,7 +8217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>218</v>
       </c>
@@ -8196,7 +8231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>219</v>
       </c>
@@ -8210,7 +8245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>220</v>
       </c>
@@ -8224,7 +8259,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>635</v>
       </c>
@@ -8238,7 +8273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>636</v>
       </c>
@@ -8252,7 +8287,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>637</v>
       </c>
@@ -8266,7 +8301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>221</v>
       </c>
@@ -8280,7 +8315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>638</v>
       </c>
@@ -8294,7 +8329,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>222</v>
       </c>
@@ -8308,7 +8343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>223</v>
       </c>
@@ -8322,7 +8357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>224</v>
       </c>
@@ -8336,7 +8371,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>225</v>
       </c>
@@ -8350,7 +8385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>226</v>
       </c>
@@ -8364,7 +8399,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>227</v>
       </c>
@@ -8378,7 +8413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>228</v>
       </c>
@@ -8392,7 +8427,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>229</v>
       </c>
@@ -8406,7 +8441,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>230</v>
       </c>
@@ -8420,7 +8455,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>231</v>
       </c>
@@ -8434,7 +8469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>232</v>
       </c>
@@ -8448,7 +8483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>233</v>
       </c>
@@ -8462,7 +8497,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>234</v>
       </c>
@@ -8476,7 +8511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>235</v>
       </c>
@@ -8490,7 +8525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>236</v>
       </c>
@@ -8504,7 +8539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>237</v>
       </c>
@@ -8518,7 +8553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>639</v>
       </c>
@@ -8532,7 +8567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>640</v>
       </c>
@@ -8546,7 +8581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>641</v>
       </c>
@@ -8560,7 +8595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>642</v>
       </c>
@@ -8574,7 +8609,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>238</v>
       </c>
@@ -8588,7 +8623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>239</v>
       </c>
@@ -8602,7 +8637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>240</v>
       </c>
@@ -8616,7 +8651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>241</v>
       </c>
@@ -8630,7 +8665,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>643</v>
       </c>
@@ -8644,7 +8679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>242</v>
       </c>
@@ -8658,7 +8693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>243</v>
       </c>
@@ -8672,7 +8707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>644</v>
       </c>
@@ -8686,7 +8721,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>244</v>
       </c>
@@ -8700,7 +8735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>245</v>
       </c>
@@ -8714,7 +8749,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>246</v>
       </c>
@@ -8728,7 +8763,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>247</v>
       </c>
@@ -8742,7 +8777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>248</v>
       </c>
@@ -8756,7 +8791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>249</v>
       </c>
@@ -8770,7 +8805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>250</v>
       </c>
@@ -8784,7 +8819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>645</v>
       </c>
@@ -8798,7 +8833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>251</v>
       </c>
@@ -8812,7 +8847,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>646</v>
       </c>
@@ -8826,7 +8861,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>252</v>
       </c>
@@ -8840,7 +8875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>253</v>
       </c>
@@ -8854,7 +8889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>254</v>
       </c>
@@ -8868,7 +8903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>255</v>
       </c>
@@ -8882,7 +8917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>256</v>
       </c>
@@ -8896,7 +8931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>257</v>
       </c>
@@ -8910,7 +8945,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>647</v>
       </c>
@@ -8924,7 +8959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>648</v>
       </c>
@@ -8938,7 +8973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>259</v>
       </c>
@@ -8952,7 +8987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>260</v>
       </c>
@@ -8966,7 +9001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>261</v>
       </c>
@@ -8980,7 +9015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>262</v>
       </c>
@@ -8994,7 +9029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>649</v>
       </c>
@@ -9008,7 +9043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>263</v>
       </c>
@@ -9022,7 +9057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>264</v>
       </c>
@@ -9036,7 +9071,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>265</v>
       </c>
@@ -9050,7 +9085,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>266</v>
       </c>
@@ -9064,7 +9099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>267</v>
       </c>
@@ -9078,7 +9113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>268</v>
       </c>
@@ -9092,7 +9127,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>269</v>
       </c>
@@ -9106,7 +9141,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>270</v>
       </c>
@@ -9120,7 +9155,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>271</v>
       </c>
@@ -9134,7 +9169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>272</v>
       </c>
@@ -9148,7 +9183,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>273</v>
       </c>
@@ -9162,7 +9197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>274</v>
       </c>
@@ -9176,7 +9211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>275</v>
       </c>
@@ -9190,7 +9225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>276</v>
       </c>
@@ -9204,7 +9239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>277</v>
       </c>
@@ -9218,7 +9253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>278</v>
       </c>
@@ -9232,7 +9267,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>279</v>
       </c>
@@ -9246,7 +9281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>280</v>
       </c>
@@ -9260,7 +9295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>281</v>
       </c>
@@ -9274,7 +9309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>282</v>
       </c>
@@ -9288,7 +9323,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>283</v>
       </c>
@@ -9302,7 +9337,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>284</v>
       </c>
@@ -9316,7 +9351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>650</v>
       </c>
@@ -9330,7 +9365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>285</v>
       </c>
@@ -9344,7 +9379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>286</v>
       </c>
@@ -9358,7 +9393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>287</v>
       </c>
@@ -9372,7 +9407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>288</v>
       </c>
@@ -9386,7 +9421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>289</v>
       </c>
@@ -9400,7 +9435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>290</v>
       </c>
@@ -9414,7 +9449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>291</v>
       </c>
@@ -9428,7 +9463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>292</v>
       </c>
@@ -9442,7 +9477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>293</v>
       </c>
@@ -9456,7 +9491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>294</v>
       </c>
@@ -9470,7 +9505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>295</v>
       </c>
@@ -9484,7 +9519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>296</v>
       </c>
@@ -9498,7 +9533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>297</v>
       </c>
@@ -9512,7 +9547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>298</v>
       </c>
@@ -9526,7 +9561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>299</v>
       </c>
@@ -9540,7 +9575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>651</v>
       </c>
@@ -9554,7 +9589,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>301</v>
       </c>
@@ -9568,7 +9603,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>302</v>
       </c>
@@ -9582,7 +9617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>303</v>
       </c>
@@ -9596,7 +9631,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>304</v>
       </c>
@@ -9610,7 +9645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>305</v>
       </c>
@@ -9624,7 +9659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>306</v>
       </c>
@@ -9638,7 +9673,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>652</v>
       </c>
@@ -9652,7 +9687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>653</v>
       </c>
@@ -9666,7 +9701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>307</v>
       </c>
@@ -9680,7 +9715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>308</v>
       </c>
@@ -9694,7 +9729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>654</v>
       </c>
@@ -9708,7 +9743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>309</v>
       </c>
@@ -9722,7 +9757,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>310</v>
       </c>
@@ -9736,7 +9771,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>311</v>
       </c>
@@ -9750,7 +9785,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>312</v>
       </c>
@@ -9764,7 +9799,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>313</v>
       </c>
@@ -9778,7 +9813,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>314</v>
       </c>
@@ -9792,7 +9827,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>315</v>
       </c>
@@ -9806,7 +9841,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
         <v>316</v>
       </c>
@@ -9820,7 +9855,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
         <v>317</v>
       </c>
@@ -9834,7 +9869,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
         <v>318</v>
       </c>
@@ -9848,7 +9883,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
         <v>319</v>
       </c>
@@ -9862,7 +9897,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>320</v>
       </c>
@@ -9876,7 +9911,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>321</v>
       </c>
@@ -9890,7 +9925,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>322</v>
       </c>
@@ -9904,7 +9939,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
         <v>323</v>
       </c>
@@ -9918,7 +9953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
         <v>324</v>
       </c>
@@ -9932,7 +9967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
         <v>325</v>
       </c>
@@ -9946,7 +9981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
         <v>326</v>
       </c>
@@ -9960,7 +9995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
         <v>655</v>
       </c>
@@ -9974,7 +10009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
         <v>656</v>
       </c>
@@ -9988,7 +10023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
         <v>657</v>
       </c>
@@ -10002,7 +10037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
         <v>658</v>
       </c>
@@ -10016,7 +10051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
         <v>659</v>
       </c>
@@ -10030,7 +10065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
         <v>327</v>
       </c>
@@ -10044,7 +10079,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
         <v>328</v>
       </c>
@@ -10058,7 +10093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
         <v>329</v>
       </c>
@@ -10072,7 +10107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
         <v>330</v>
       </c>
@@ -10086,7 +10121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
         <v>331</v>
       </c>
@@ -10100,7 +10135,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
         <v>332</v>
       </c>
@@ -10114,7 +10149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
         <v>333</v>
       </c>
@@ -10128,7 +10163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
         <v>334</v>
       </c>
@@ -10142,7 +10177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
         <v>660</v>
       </c>
@@ -10156,7 +10191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
         <v>661</v>
       </c>
@@ -10170,7 +10205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
         <v>335</v>
       </c>
@@ -10184,7 +10219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
         <v>662</v>
       </c>
@@ -10198,7 +10233,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
         <v>663</v>
       </c>
@@ -10212,7 +10247,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
         <v>336</v>
       </c>
@@ -10226,7 +10261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
         <v>337</v>
       </c>
@@ -10240,7 +10275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
         <v>338</v>
       </c>
@@ -10254,7 +10289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
         <v>339</v>
       </c>
@@ -10268,7 +10303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
         <v>340</v>
       </c>
@@ -10282,7 +10317,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
         <v>341</v>
       </c>
@@ -10296,7 +10331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
         <v>342</v>
       </c>
@@ -10310,7 +10345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
         <v>343</v>
       </c>
@@ -10324,7 +10359,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
         <v>664</v>
       </c>
@@ -10338,7 +10373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
         <v>665</v>
       </c>
@@ -10352,7 +10387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
         <v>666</v>
       </c>
@@ -10366,7 +10401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
         <v>667</v>
       </c>
@@ -10380,7 +10415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
         <v>668</v>
       </c>
@@ -10394,7 +10429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
         <v>669</v>
       </c>
@@ -10408,7 +10443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
         <v>670</v>
       </c>
@@ -10422,7 +10457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
         <v>671</v>
       </c>
@@ -10436,7 +10471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
         <v>672</v>
       </c>
@@ -10450,7 +10485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
         <v>673</v>
       </c>
@@ -10464,7 +10499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
         <v>674</v>
       </c>
@@ -10478,7 +10513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
         <v>675</v>
       </c>
@@ -10492,7 +10527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
         <v>676</v>
       </c>
@@ -10506,7 +10541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
         <v>677</v>
       </c>
@@ -10520,7 +10555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
         <v>678</v>
       </c>
@@ -10534,7 +10569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
         <v>679</v>
       </c>
@@ -10548,7 +10583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
         <v>680</v>
       </c>
@@ -10562,7 +10597,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
         <v>681</v>
       </c>
@@ -10576,7 +10611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
         <v>682</v>
       </c>
@@ -10590,7 +10625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
         <v>683</v>
       </c>
@@ -10604,7 +10639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
         <v>344</v>
       </c>
@@ -10618,7 +10653,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
         <v>345</v>
       </c>
@@ -10632,7 +10667,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
         <v>346</v>
       </c>
@@ -10646,7 +10681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
         <v>347</v>
       </c>
@@ -10660,7 +10695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
         <v>348</v>
       </c>
@@ -10674,7 +10709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
         <v>349</v>
       </c>
@@ -10688,7 +10723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
         <v>350</v>
       </c>
@@ -10702,7 +10737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
         <v>351</v>
       </c>
@@ -10716,7 +10751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
         <v>352</v>
       </c>
@@ -10730,7 +10765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
         <v>353</v>
       </c>
@@ -10744,7 +10779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
         <v>684</v>
       </c>
@@ -10758,7 +10793,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
         <v>354</v>
       </c>
@@ -10772,7 +10807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
         <v>355</v>
       </c>
@@ -10786,7 +10821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
         <v>685</v>
       </c>
@@ -10800,7 +10835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
         <v>356</v>
       </c>
@@ -10814,7 +10849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
         <v>357</v>
       </c>
@@ -10828,7 +10863,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
         <v>358</v>
       </c>
@@ -10842,7 +10877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
         <v>359</v>
       </c>
@@ -10856,7 +10891,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
         <v>686</v>
       </c>
@@ -10870,7 +10905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
         <v>360</v>
       </c>
@@ -10884,7 +10919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
         <v>361</v>
       </c>
@@ -10898,7 +10933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
         <v>362</v>
       </c>
@@ -10912,7 +10947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
         <v>363</v>
       </c>
@@ -10926,7 +10961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
         <v>364</v>
       </c>
@@ -10940,7 +10975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
         <v>365</v>
       </c>
@@ -10954,7 +10989,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
         <v>366</v>
       </c>
@@ -10968,7 +11003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
         <v>367</v>
       </c>
@@ -10982,7 +11017,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
         <v>368</v>
       </c>
@@ -10996,7 +11031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
         <v>369</v>
       </c>
@@ -11010,7 +11045,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
         <v>370</v>
       </c>
@@ -11024,7 +11059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
         <v>371</v>
       </c>
@@ -11038,7 +11073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
         <v>372</v>
       </c>
@@ -11052,7 +11087,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
         <v>373</v>
       </c>
@@ -11066,7 +11101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
         <v>374</v>
       </c>
@@ -11080,7 +11115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
         <v>375</v>
       </c>
@@ -11094,7 +11129,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
         <v>376</v>
       </c>
@@ -11108,7 +11143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
         <v>687</v>
       </c>
@@ -11122,7 +11157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
         <v>688</v>
       </c>
@@ -11136,7 +11171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
         <v>689</v>
       </c>
@@ -11150,7 +11185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
         <v>690</v>
       </c>
@@ -11164,7 +11199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
         <v>691</v>
       </c>
@@ -11178,7 +11213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
         <v>377</v>
       </c>
@@ -11192,7 +11227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
         <v>378</v>
       </c>
@@ -11206,7 +11241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
         <v>379</v>
       </c>
@@ -11220,7 +11255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
         <v>380</v>
       </c>
@@ -11234,7 +11269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
         <v>381</v>
       </c>
@@ -11248,7 +11283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
         <v>382</v>
       </c>
@@ -11262,7 +11297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
         <v>692</v>
       </c>
@@ -11276,7 +11311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
         <v>383</v>
       </c>
@@ -11290,7 +11325,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
         <v>384</v>
       </c>
@@ -11304,7 +11339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
         <v>385</v>
       </c>
@@ -11318,7 +11353,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
         <v>386</v>
       </c>
@@ -11332,7 +11367,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
         <v>387</v>
       </c>
@@ -11346,7 +11381,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
         <v>388</v>
       </c>
@@ -11360,7 +11395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
         <v>389</v>
       </c>
@@ -11374,7 +11409,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
         <v>390</v>
       </c>
@@ -11388,7 +11423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
         <v>693</v>
       </c>
@@ -11402,7 +11437,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
         <v>391</v>
       </c>
@@ -11416,7 +11451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
         <v>392</v>
       </c>
@@ -11430,7 +11465,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
         <v>393</v>
       </c>
@@ -11444,7 +11479,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
         <v>694</v>
       </c>
@@ -11458,7 +11493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
         <v>394</v>
       </c>
@@ -11472,7 +11507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
         <v>695</v>
       </c>
@@ -11486,7 +11521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
         <v>395</v>
       </c>
@@ -11500,7 +11535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
         <v>396</v>
       </c>
@@ -11514,7 +11549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
         <v>397</v>
       </c>
@@ -11528,7 +11563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
         <v>398</v>
       </c>
@@ -11542,7 +11577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
         <v>399</v>
       </c>
@@ -11556,7 +11591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
         <v>400</v>
       </c>
@@ -11570,7 +11605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
         <v>401</v>
       </c>
@@ -11584,7 +11619,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
         <v>402</v>
       </c>
@@ -11598,7 +11633,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
         <v>403</v>
       </c>
@@ -11612,7 +11647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
         <v>404</v>
       </c>
@@ -11626,7 +11661,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
         <v>405</v>
       </c>
@@ -11640,7 +11675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
         <v>696</v>
       </c>
@@ -11654,7 +11689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
         <v>406</v>
       </c>
@@ -11668,7 +11703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
         <v>697</v>
       </c>
@@ -11682,7 +11717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
         <v>407</v>
       </c>
@@ -11696,7 +11731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
         <v>408</v>
       </c>
@@ -11710,7 +11745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
         <v>409</v>
       </c>
@@ -11724,7 +11759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
         <v>410</v>
       </c>
@@ -11738,7 +11773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
         <v>411</v>
       </c>
@@ -11752,7 +11787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
         <v>412</v>
       </c>
@@ -11766,7 +11801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
         <v>413</v>
       </c>
@@ -11780,7 +11815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
         <v>414</v>
       </c>
@@ -11794,7 +11829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
         <v>415</v>
       </c>
@@ -11808,7 +11843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
         <v>416</v>
       </c>
@@ -11822,7 +11857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
         <v>417</v>
       </c>
@@ -11836,7 +11871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
         <v>698</v>
       </c>
@@ -11850,7 +11885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
         <v>418</v>
       </c>
@@ -11864,7 +11899,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
         <v>419</v>
       </c>
@@ -11878,7 +11913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
         <v>420</v>
       </c>
@@ -11892,7 +11927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
         <v>421</v>
       </c>
@@ -11906,7 +11941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
         <v>422</v>
       </c>
@@ -11920,7 +11955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
         <v>423</v>
       </c>
@@ -11934,7 +11969,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
         <v>425</v>
       </c>
@@ -11948,7 +11983,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
         <v>427</v>
       </c>
@@ -11962,7 +11997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
         <v>699</v>
       </c>
@@ -11976,7 +12011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
         <v>428</v>
       </c>
@@ -11990,7 +12025,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
         <v>429</v>
       </c>
@@ -12004,7 +12039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
         <v>430</v>
       </c>
@@ -12018,7 +12053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
         <v>700</v>
       </c>
@@ -12032,7 +12067,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
         <v>431</v>
       </c>
@@ -12046,7 +12081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
         <v>432</v>
       </c>
@@ -12060,7 +12095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
         <v>433</v>
       </c>
@@ -12074,7 +12109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
         <v>434</v>
       </c>
@@ -12088,7 +12123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
         <v>435</v>
       </c>
@@ -12102,7 +12137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
         <v>436</v>
       </c>
@@ -12116,7 +12151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
         <v>437</v>
       </c>
@@ -12130,7 +12165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
         <v>438</v>
       </c>
@@ -12144,7 +12179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
         <v>439</v>
       </c>
@@ -12158,7 +12193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
         <v>440</v>
       </c>
@@ -12172,7 +12207,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
         <v>441</v>
       </c>
@@ -12186,7 +12221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
         <v>442</v>
       </c>
@@ -12200,7 +12235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
         <v>443</v>
       </c>
@@ -12214,7 +12249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
         <v>444</v>
       </c>
@@ -12228,7 +12263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="7" t="s">
         <v>445</v>
       </c>
@@ -12242,7 +12277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="7" t="s">
         <v>446</v>
       </c>
@@ -12256,7 +12291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="8" t="s">
         <v>447</v>
       </c>
@@ -12270,7 +12305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="10" t="s">
         <v>448</v>
       </c>
@@ -12284,7 +12319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="10" t="s">
         <v>449</v>
       </c>
@@ -12298,7 +12333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="10" t="s">
         <v>450</v>
       </c>
@@ -12312,7 +12347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="4" t="s">
         <v>451</v>
       </c>
@@ -12326,7 +12361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="10" t="s">
         <v>452</v>
       </c>
@@ -12340,7 +12375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="10" t="s">
         <v>453</v>
       </c>
@@ -12354,7 +12389,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="4" t="s">
         <v>454</v>
       </c>
@@ -12368,7 +12403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="4" t="s">
         <v>455</v>
       </c>
@@ -12382,7 +12417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="4" t="s">
         <v>456</v>
       </c>
@@ -12396,7 +12431,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="10" t="s">
         <v>457</v>
       </c>
@@ -12410,7 +12445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="10" t="s">
         <v>458</v>
       </c>
@@ -12424,7 +12459,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A674" s="4" t="s">
         <v>459</v>
       </c>
@@ -12438,7 +12473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="50" t="s">
         <v>701</v>
       </c>
@@ -12452,7 +12487,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="50" t="s">
         <v>702</v>
       </c>
@@ -12466,7 +12501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="50" t="s">
         <v>703</v>
       </c>
@@ -12480,7 +12515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="50" t="s">
         <v>704</v>
       </c>
@@ -12494,7 +12529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="4" t="s">
         <v>705</v>
       </c>
@@ -12508,7 +12543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A680" s="51" t="s">
         <v>706</v>
       </c>
@@ -12522,7 +12557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="51" t="s">
         <v>707</v>
       </c>
@@ -12536,19 +12571,50 @@
         <v>7</v>
       </c>
     </row>
-    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A682" s="4" t="s">
+    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A682" s="60" t="s">
         <v>708</v>
       </c>
-      <c r="B682" s="54">
+      <c r="B682" s="59">
         <v>0.91</v>
       </c>
-      <c r="C682" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D682" s="6" t="s">
+      <c r="C682" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="D682" s="61" t="s">
         <v>2</v>
       </c>
+    </row>
+    <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A683" s="62" t="s">
+        <v>710</v>
+      </c>
+      <c r="B683" s="63">
+        <v>0.26</v>
+      </c>
+      <c r="C683" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="D683" s="64" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A684" s="62" t="s">
+        <v>711</v>
+      </c>
+      <c r="B684" s="63">
+        <v>0.22</v>
+      </c>
+      <c r="C684" s="64" t="s">
+        <v>466</v>
+      </c>
+      <c r="D684" s="64" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A685" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC3F0A6-22DF-4DC2-BA71-BE3CE02A9F29}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30F3ED4-8B3F-45ED-8115-E34D16CA2DFF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="0" yWindow="2820" windowWidth="21600" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="717">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2166,6 +2166,21 @@
   </si>
   <si>
     <t>Cookie Production (per gram)</t>
+  </si>
+  <si>
+    <t>Coffee Stirrer (per piece)</t>
+  </si>
+  <si>
+    <t>operating</t>
+  </si>
+  <si>
+    <t>Spork (per piece)</t>
+  </si>
+  <si>
+    <t>Alumimun Pan (small, per piece)</t>
+  </si>
+  <si>
+    <t>Plastic Cup 12oz for bar (per piece)</t>
   </si>
 </sst>
 </file>
@@ -2569,7 +2584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2702,9 +2717,6 @@
     </xf>
     <xf numFmtId="165" fontId="7" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3039,7 +3051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D685"/>
+  <dimension ref="A1:D688"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -5068,7 +5080,7 @@
       </c>
     </row>
     <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="58" t="s">
+      <c r="A146" s="57" t="s">
         <v>609</v>
       </c>
       <c r="B146" s="38">
@@ -12572,51 +12584,105 @@
       </c>
     </row>
     <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A682" s="60" t="s">
+      <c r="A682" s="59" t="s">
         <v>708</v>
       </c>
-      <c r="B682" s="59">
+      <c r="B682" s="58">
         <v>0.91</v>
       </c>
-      <c r="C682" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="D682" s="61" t="s">
+      <c r="C682" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="D682" s="60" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A683" s="62" t="s">
+      <c r="A683" s="61" t="s">
         <v>710</v>
       </c>
-      <c r="B683" s="63">
+      <c r="B683" s="62">
         <v>0.26</v>
       </c>
-      <c r="C683" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="D683" s="64" t="s">
+      <c r="C683" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D683" s="63" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A684" s="62" t="s">
+      <c r="A684" s="61" t="s">
         <v>711</v>
       </c>
-      <c r="B684" s="63">
+      <c r="B684" s="62">
         <v>0.22</v>
       </c>
-      <c r="C684" s="64" t="s">
+      <c r="C684" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="D684" s="64" t="s">
+      <c r="D684" s="63" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A685" s="57"/>
+      <c r="A685" s="61" t="s">
+        <v>712</v>
+      </c>
+      <c r="B685" s="62">
+        <v>0.59</v>
+      </c>
+      <c r="C685" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D685" s="63" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A686" s="61" t="s">
+        <v>714</v>
+      </c>
+      <c r="B686" s="62">
+        <v>3.1</v>
+      </c>
+      <c r="C686" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D686" s="63" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A687" s="61" t="s">
+        <v>715</v>
+      </c>
+      <c r="B687" s="62">
+        <v>6.9</v>
+      </c>
+      <c r="C687" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D687" s="63" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A688" s="61" t="s">
+        <v>716</v>
+      </c>
+      <c r="B688" s="62">
+        <v>6.3</v>
+      </c>
+      <c r="C688" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D688" s="63" t="s">
+        <v>713</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30F3ED4-8B3F-45ED-8115-E34D16CA2DFF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52B3A78-2AB8-4D2B-BA80-29CB4764E642}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2820" windowWidth="21600" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="725">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2181,6 +2181,30 @@
   </si>
   <si>
     <t>Plastic Cup 12oz for bar (per piece)</t>
+  </si>
+  <si>
+    <t>Dragon Fruit</t>
+  </si>
+  <si>
+    <t>Cashew Nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nata bits- 1000g </t>
+  </si>
+  <si>
+    <t>Togue</t>
+  </si>
+  <si>
+    <t>Pancake Mix- Maya</t>
+  </si>
+  <si>
+    <t>Gulaman - Mango</t>
+  </si>
+  <si>
+    <t>Langka</t>
+  </si>
+  <si>
+    <t>Sampaloc</t>
   </si>
 </sst>
 </file>
@@ -2242,7 +2266,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2349,6 +2373,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E0B3"/>
+        <bgColor rgb="FFC5E0B3"/>
       </patternFill>
     </fill>
   </fills>
@@ -2584,7 +2614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2735,6 +2765,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3051,7 +3084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D688"/>
+  <dimension ref="A1:D696"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -12681,6 +12714,118 @@
         <v>713</v>
       </c>
     </row>
+    <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A689" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="B689" s="64">
+        <v>0.499</v>
+      </c>
+      <c r="C689" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D689" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A690" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="B690" s="64">
+        <v>0.4</v>
+      </c>
+      <c r="C690" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D690" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A691" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="B691" s="64">
+        <v>0.36</v>
+      </c>
+      <c r="C691" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D691" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A692" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="B692" s="64">
+        <v>0.2</v>
+      </c>
+      <c r="C692" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D692" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A693" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="B693" s="64">
+        <v>0.25</v>
+      </c>
+      <c r="C693" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D693" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A694" s="50" t="s">
+        <v>722</v>
+      </c>
+      <c r="B694" s="64">
+        <v>0.64</v>
+      </c>
+      <c r="C694" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D694" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A695" s="50" t="s">
+        <v>723</v>
+      </c>
+      <c r="B695" s="64">
+        <v>0.85</v>
+      </c>
+      <c r="C695" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D695" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A696" s="50" t="s">
+        <v>724</v>
+      </c>
+      <c r="B696" s="64">
+        <v>0.15</v>
+      </c>
+      <c r="C696" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D696" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52B3A78-2AB8-4D2B-BA80-29CB4764E642}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2479C865-BCF8-457E-9389-D966945D1ADC}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2820" windowWidth="21600" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12635,7 +12635,7 @@
         <v>710</v>
       </c>
       <c r="B683" s="62">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="C683" s="63" t="s">
         <v>1</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2479C865-BCF8-457E-9389-D966945D1ADC}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0247101-7484-4333-AD39-D404FB02CDB8}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="690" yWindow="3510" windowWidth="21600" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="726">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2205,6 +2205,9 @@
   </si>
   <si>
     <t>Sampaloc</t>
+  </si>
+  <si>
+    <t>Sauce Cup- big</t>
   </si>
 </sst>
 </file>
@@ -2266,7 +2269,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2381,8 +2384,14 @@
         <bgColor rgb="FFC5E0B3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E0B3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -2610,11 +2619,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2769,6 +2808,15 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3084,7 +3132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D696"/>
+  <dimension ref="A1:D697"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -12812,7 +12860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="696" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A696" s="50" t="s">
         <v>724</v>
       </c>
@@ -12824,6 +12872,20 @@
       </c>
       <c r="D696" s="6" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A697" s="65" t="s">
+        <v>725</v>
+      </c>
+      <c r="B697" s="67">
+        <v>1.3</v>
+      </c>
+      <c r="C697" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D697" s="66" t="s">
+        <v>713</v>
       </c>
     </row>
   </sheetData>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0247101-7484-4333-AD39-D404FB02CDB8}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4401D82-0511-4790-947B-4533EAA30FDE}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="3510" windowWidth="21600" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -389,9 +389,6 @@
     <t>Coconut Water - Vita Coco</t>
   </si>
   <si>
-    <t>Coffee Beans - Silcafe</t>
-  </si>
-  <si>
     <t>Coke Original 320 ml</t>
   </si>
   <si>
@@ -2208,6 +2205,9 @@
   </si>
   <si>
     <t>Sauce Cup- big</t>
+  </si>
+  <si>
+    <t>Coffee Beans (per gram)</t>
   </si>
 </sst>
 </file>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B3" s="36">
         <v>0.19</v>
@@ -3169,96 +3169,96 @@
         <v>1</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B4" s="37">
         <v>12.63</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B5" s="36">
         <v>0.13</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B6" s="36">
         <v>0.36</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B7" s="37">
         <v>270</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B8" s="37">
         <v>350</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B9" s="37">
         <v>36.5</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B10" s="38">
         <v>0.24299999999999999</v>
@@ -3267,12 +3267,12 @@
         <v>1</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B11" s="38">
         <v>0.111</v>
@@ -3281,194 +3281,194 @@
         <v>1</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B12" s="37">
         <v>261.39999999999998</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B13" s="37">
         <v>153.33000000000001</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B14" s="38">
         <v>219.96</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B15" s="38">
         <v>24.75</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B16" s="37">
         <v>85</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B17" s="37">
         <v>73.12</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B18" s="40">
         <v>72.010000000000005</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B19" s="41">
         <v>8</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B20" s="41">
         <v>72.91</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B21" s="41">
         <v>10</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B22" s="42">
         <v>18.5</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B23" s="38">
         <v>23.66</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B24" s="38">
         <v>196.62</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B25" s="38">
         <v>11.02</v>
@@ -3477,12 +3477,12 @@
         <v>32</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B26" s="38">
         <v>8.65</v>
@@ -3491,12 +3491,12 @@
         <v>32</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B27" s="38">
         <v>0.85199999999999998</v>
@@ -3505,40 +3505,40 @@
         <v>1</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B28" s="34">
         <v>0.53</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B29" s="38">
         <v>36.03</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B30" s="36">
         <v>0.31</v>
@@ -3547,68 +3547,68 @@
         <v>1</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B31" s="37">
         <v>25.39</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B32" s="37">
         <v>80.88</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B33" s="41">
         <v>179.51</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B34" s="37">
         <v>77.59</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B35" s="38">
         <v>0.312</v>
@@ -3617,68 +3617,68 @@
         <v>1</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B36" s="38">
         <v>124.44</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B37" s="37">
         <v>18</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B38" s="37">
         <v>193.88</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B39" s="38">
         <v>86.83</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B40" s="43">
         <v>0.6</v>
@@ -3687,12 +3687,12 @@
         <v>1</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B41" s="44">
         <v>0.379</v>
@@ -3701,12 +3701,12 @@
         <v>1</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B42" s="44">
         <v>0.16500000000000001</v>
@@ -3715,250 +3715,250 @@
         <v>1</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B43" s="44">
         <v>0.46</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B44" s="45">
         <v>7</v>
       </c>
       <c r="C44" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B45" s="41">
         <v>39</v>
       </c>
       <c r="C45" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B46" s="37">
         <v>30</v>
       </c>
       <c r="C46" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="28" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B47" s="37">
         <v>72.87</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B48" s="37">
         <v>30</v>
       </c>
       <c r="C48" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B49" s="37">
         <v>317.8</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B50" s="37">
         <v>70</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B51" s="38">
         <v>0.86199999999999999</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B52" s="38">
         <v>0.128</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="28" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B53" s="37">
         <v>14.92</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B54" s="37">
         <v>17.3</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B55" s="38">
         <v>1</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="28" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B56" s="37">
         <v>112.14</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B57" s="38">
         <v>0.71</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B58" s="38">
         <v>0.18</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B59" s="38">
         <v>0.3</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B60" s="36">
         <v>0.46</v>
@@ -3967,68 +3967,68 @@
         <v>1</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B61" s="38">
         <v>0.39100000000000001</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B62" s="38">
         <v>0.28999999999999998</v>
       </c>
       <c r="C62" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B63" s="38">
         <v>0.17599999999999999</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B64" s="37">
         <v>63.92</v>
       </c>
       <c r="C64" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B65" s="46">
         <v>0.54</v>
@@ -4037,12 +4037,12 @@
         <v>1</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B66" s="34">
         <v>0.71</v>
@@ -4051,82 +4051,82 @@
         <v>1</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B67" s="37">
         <v>43.56</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B68" s="34">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="C68" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="28" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B69" s="34">
         <v>118.91</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B70" s="37">
         <v>34.799999999999997</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B71" s="38">
         <v>17.5</v>
       </c>
       <c r="C71" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D71" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B72" s="36">
         <v>0.153</v>
@@ -4135,236 +4135,236 @@
         <v>1</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B73" s="38">
         <v>37.444000000000003</v>
       </c>
       <c r="C73" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D73" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B74" s="38">
         <v>15.24</v>
       </c>
       <c r="C74" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D74" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="30" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B75" s="37">
         <v>208.78</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D75" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B76" s="37">
         <v>203.77</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B77" s="37">
         <v>102</v>
       </c>
       <c r="C77" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="28" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B78" s="37">
         <v>20.399999999999999</v>
       </c>
       <c r="C78" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D78" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="31" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B79" s="37">
         <v>11.73</v>
       </c>
       <c r="C79" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D79" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="23" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B80" s="38">
         <v>3.1E-2</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="31" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B81" s="38">
         <v>23.2</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D81" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B82" s="37">
         <v>75</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="23" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B83" s="37">
         <v>75</v>
       </c>
       <c r="C83" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D83" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B84" s="38">
         <v>46.36</v>
       </c>
       <c r="C84" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D84" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="32" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B85" s="37">
         <v>20</v>
       </c>
       <c r="C85" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B86" s="34">
         <v>0.18</v>
       </c>
       <c r="C86" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D86" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B87" s="38">
         <v>47.7</v>
       </c>
       <c r="C87" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D87" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="23" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B88" s="37">
         <v>43.28</v>
       </c>
       <c r="C88" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B89" s="38">
         <v>0.223</v>
@@ -4373,40 +4373,40 @@
         <v>1</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="16" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B90" s="37">
         <v>255.59</v>
       </c>
       <c r="C90" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D90" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="16" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B91" s="37">
         <v>38.03</v>
       </c>
       <c r="C91" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D91" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B92" s="38">
         <v>0.26</v>
@@ -4415,26 +4415,26 @@
         <v>1</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="28" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B93" s="37">
         <v>20.399999999999999</v>
       </c>
       <c r="C93" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D93" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B94" s="36">
         <v>0.11</v>
@@ -4443,152 +4443,152 @@
         <v>1</v>
       </c>
       <c r="D94" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="23" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B95" s="38">
         <v>34.24</v>
       </c>
       <c r="C95" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D95" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B96" s="37">
         <v>77</v>
       </c>
       <c r="C96" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="23" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B97" s="37">
         <v>130.91</v>
       </c>
       <c r="C97" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B98" s="34">
         <v>118.01</v>
       </c>
       <c r="C98" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D98" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="23" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B99" s="38">
         <v>43.75</v>
       </c>
       <c r="C99" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="28" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B100" s="37">
         <v>25.55</v>
       </c>
       <c r="C100" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D100" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B101" s="37">
         <v>200</v>
       </c>
       <c r="C101" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D101" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="28" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B102" s="37">
         <v>30</v>
       </c>
       <c r="C102" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B103" s="37">
         <v>22.25</v>
       </c>
       <c r="C103" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D103" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="24" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B104" s="37">
         <v>155.62</v>
       </c>
       <c r="C104" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B105" s="38">
         <v>0.22800000000000001</v>
@@ -4597,40 +4597,40 @@
         <v>1</v>
       </c>
       <c r="D105" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B106" s="38">
         <v>66</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D106" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="24" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B107" s="37">
         <v>36</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D107" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B108" s="34">
         <v>0.42</v>
@@ -4639,54 +4639,54 @@
         <v>1</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B109" s="37">
         <v>74.78</v>
       </c>
       <c r="C109" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D109" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="24" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B110" s="37">
         <v>8</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D110" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B111" s="37">
         <v>125</v>
       </c>
       <c r="C111" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B112" s="38">
         <v>0.16500000000000001</v>
@@ -4695,82 +4695,82 @@
         <v>1</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="28" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B113" s="37">
         <v>49.5</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D113" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B114" s="38">
         <v>0.56000000000000005</v>
       </c>
       <c r="C114" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B115" s="37">
         <v>86.22</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B116" s="38">
         <v>175</v>
       </c>
       <c r="C116" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B117" s="37">
         <v>57.15</v>
       </c>
       <c r="C117" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B118" s="38">
         <v>0.13400000000000001</v>
@@ -4779,26 +4779,26 @@
         <v>1</v>
       </c>
       <c r="D118" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B119" s="36">
         <v>0.12</v>
       </c>
       <c r="C119" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B120" s="38">
         <v>14.35</v>
@@ -4807,54 +4807,54 @@
         <v>32</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B121" s="37">
         <v>117.25</v>
       </c>
       <c r="C121" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D121" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B122" s="37">
         <v>38</v>
       </c>
       <c r="C122" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B123" s="38">
         <v>37.33</v>
       </c>
       <c r="C123" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="25" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B124" s="38">
         <v>0.222</v>
@@ -4863,12 +4863,12 @@
         <v>1</v>
       </c>
       <c r="D124" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B125" s="38">
         <v>0.22900000000000001</v>
@@ -4877,12 +4877,12 @@
         <v>1</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="23" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B126" s="38">
         <v>33</v>
@@ -4891,40 +4891,40 @@
         <v>32</v>
       </c>
       <c r="D126" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="23" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B127" s="38">
         <v>29.5</v>
       </c>
       <c r="C127" s="47" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D127" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="26" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B128" s="43">
         <v>0.24</v>
       </c>
       <c r="C128" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D128" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="33" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B129" s="44">
         <v>0.40799999999999997</v>
@@ -4933,138 +4933,138 @@
         <v>1</v>
       </c>
       <c r="D129" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="33" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B130" s="43">
         <v>34</v>
       </c>
       <c r="C130" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D130" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="33" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B131" s="43">
         <v>209.55</v>
       </c>
       <c r="C131" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D131" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="26" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B132" s="43">
         <v>0.05</v>
       </c>
       <c r="C132" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="26" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B133" s="43">
         <v>0.81</v>
       </c>
       <c r="C133" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D133" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="26" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B134" s="43">
         <v>10</v>
       </c>
       <c r="C134" s="47" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="26" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B135" s="38">
         <v>8.5</v>
       </c>
       <c r="C135" s="47" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D135" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B136" s="38">
         <v>0.28000000000000003</v>
       </c>
       <c r="C136" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="26" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B137" s="38">
         <v>0.35</v>
       </c>
       <c r="C137" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="26" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B138" s="38">
         <v>0.08</v>
       </c>
       <c r="C138" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="26" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B139" s="38">
         <v>0.19</v>
@@ -5073,26 +5073,26 @@
         <v>1</v>
       </c>
       <c r="D139" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="26" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B140" s="38">
         <v>332.18</v>
       </c>
       <c r="C140" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D140" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="26" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B141" s="38">
         <v>0.27200000000000002</v>
@@ -5101,77 +5101,77 @@
         <v>4</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="26" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B142" s="38">
         <v>166.79</v>
       </c>
       <c r="C142" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D142" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="26" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B143" s="38">
         <v>119.93</v>
       </c>
       <c r="C143" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D143" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="26" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B144" s="38">
         <v>0.52</v>
       </c>
       <c r="C144" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D144" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="26" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B145" s="38">
-        <v>34.29</v>
+        <v>27.72</v>
       </c>
       <c r="C145" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D145" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="57" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B146" s="38">
-        <v>34.29</v>
+        <v>32.22</v>
       </c>
       <c r="C146" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D146" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5246,7 +5246,7 @@
     </row>
     <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B152" s="53">
         <v>0.18</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B155" s="53">
         <v>0.21428571428571427</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B176" s="54">
         <v>0.19</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B180" s="54">
         <v>75</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B183" s="54">
         <v>2.2000000000000002</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B187" s="54">
         <v>0.24</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B224" s="54">
         <v>394</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B256" s="54">
         <v>55</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
-        <v>119</v>
+        <v>725</v>
       </c>
       <c r="B259" s="54">
         <v>0.73</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B260" s="54">
         <v>9.5000000000000001E-2</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B261" s="54">
         <v>37</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B262" s="54">
         <v>37</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B263" s="54">
         <v>0.23</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B264" s="54">
         <v>0.49</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B265" s="54">
         <v>0.14285714285714285</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B266" s="54">
         <v>0.18823529411764706</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B267" s="54">
         <v>0.30737704918032788</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B268" s="54">
         <v>7.0000000000000007E-2</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B269" s="54">
         <v>70</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B270" s="54">
         <v>1.327</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B271" s="54">
         <v>0.88105726872246692</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B272" s="54">
         <v>0.32900000000000001</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B273" s="54">
         <v>0.32</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B274" s="54">
         <v>0.21249999999999999</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B275" s="54">
         <v>0.35</v>
@@ -6982,13 +6982,13 @@
     </row>
     <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B276" s="54">
         <v>0.12</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D276" s="6" t="s">
         <v>7</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B277" s="54">
         <v>0.89</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B278" s="54">
         <v>0.496</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B279" s="54">
         <v>0.8666666666666667</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B280" s="54">
         <v>0.13500000000000001</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B281" s="54">
         <v>0.80645161290322576</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B282" s="54">
         <v>0.96199999999999997</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B283" s="54">
         <v>2</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B284" s="54">
         <v>0.22500000000000001</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B285" s="54">
         <v>0.13</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B286" s="54">
         <v>0.84199999999999997</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B287" s="54">
         <v>0.6</v>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B288" s="54">
         <v>0.51</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B289" s="54">
         <v>0.47</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B290" s="54">
         <v>0.38900000000000001</v>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B291" s="54">
         <v>0.55800000000000005</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B292" s="54">
         <v>0.7</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B293" s="54">
         <v>0.32500000000000001</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B294" s="54">
         <v>0.91400000000000003</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B295" s="54">
         <v>0.81</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B296" s="54">
         <v>1.01</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B297" s="54">
         <v>0.40500000000000003</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B298" s="54">
         <v>0.372</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B299" s="54">
         <v>16</v>
@@ -7318,7 +7318,7 @@
     </row>
     <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B300" s="54">
         <v>12</v>
@@ -7332,7 +7332,7 @@
     </row>
     <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B301" s="54">
         <v>20</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B302" s="54">
         <v>0.13</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B303" s="54">
         <v>2.7857142857142856</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B304" s="54">
         <v>95</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B305" s="54">
         <v>2.67</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B306" s="54">
         <v>0.08</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B307" s="54">
         <v>0.42499999999999999</v>
@@ -7430,7 +7430,7 @@
     </row>
     <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B308" s="54">
         <v>5.8400000000000001E-2</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B309" s="54">
         <v>6.5000000000000002E-2</v>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B310" s="54">
         <v>7.0000000000000007E-2</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B311" s="54">
         <v>0.16</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B312" s="54">
         <v>0.11</v>
@@ -7500,7 +7500,7 @@
     </row>
     <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B313" s="54">
         <v>7.0000000000000007E-2</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B314" s="54">
         <v>0.4</v>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B315" s="54">
         <v>0.11899999999999999</v>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B316" s="54">
         <v>5.5E-2</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B317" s="54">
         <v>0.21</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B318" s="54">
         <v>5.5E-2</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B319" s="54">
         <v>5.5E-2</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B320" s="54">
         <v>50</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B321" s="54">
         <v>0.22500000000000001</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B322" s="54">
         <v>0.312</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B323" s="54">
         <v>7</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B324" s="54">
         <v>14</v>
@@ -7668,7 +7668,7 @@
     </row>
     <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B325" s="54">
         <v>0.17</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B326" s="54">
         <v>0.31</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B327" s="54">
         <v>0.81</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B328" s="54">
         <v>0.12222222222222222</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B329" s="54">
         <v>0.18</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B330" s="54">
         <v>0.88200000000000001</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B331" s="54">
         <v>0.37</v>
@@ -7761,12 +7761,12 @@
         <v>4</v>
       </c>
       <c r="D331" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B332" s="54">
         <v>5</v>
@@ -7780,7 +7780,7 @@
     </row>
     <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B333" s="54">
         <v>1.2386666666666666</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B334" s="54">
         <v>0.33900000000000002</v>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B335" s="54">
         <v>0.18</v>
@@ -7822,7 +7822,7 @@
     </row>
     <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B336" s="54">
         <v>0.47333333333333333</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B337" s="54">
         <v>7.4999999999999997E-2</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B338" s="54">
         <v>2.4700000000000002</v>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B339" s="54">
         <v>0.82</v>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B340" s="54">
         <v>0.106</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B341" s="54">
         <v>0.11700000000000001</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B342" s="54">
         <v>0.45900000000000002</v>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B343" s="54">
         <v>0.71899999999999997</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B344" s="54">
         <v>1.5</v>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B345" s="54">
         <v>0.25600000000000001</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B346" s="54">
         <v>0.19400000000000001</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B347" s="54">
         <v>0.48399999999999999</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B348" s="54">
         <v>0.52</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B349" s="54">
         <v>0.23499999999999999</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B350" s="54">
         <v>0.30499999999999999</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B351" s="54">
         <v>1.224</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B352" s="54">
         <v>0.46</v>
@@ -8060,13 +8060,13 @@
     </row>
     <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B353" s="54">
         <v>200</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>28</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B354" s="54">
         <v>2.46</v>
@@ -8083,12 +8083,12 @@
         <v>4</v>
       </c>
       <c r="D354" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B355" s="54">
         <v>1.079</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B356" s="54">
         <v>0.91500000000000004</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B357" s="54">
         <v>0.12</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B358" s="54">
         <v>0.23</v>
@@ -8144,13 +8144,13 @@
     </row>
     <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B359" s="54">
         <v>0.28000000000000003</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>28</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B360" s="54">
         <v>0.54700000000000004</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B361" s="54">
         <v>1.1272727272727272</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B362" s="54">
         <v>1.3779999999999999</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B363" s="54">
         <v>0.95</v>
@@ -8214,7 +8214,7 @@
     </row>
     <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B364" s="54">
         <v>0.4</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B365" s="54">
         <v>0.73299999999999998</v>
@@ -8242,13 +8242,13 @@
     </row>
     <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B366" s="54">
         <v>185</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>28</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B367" s="54">
         <v>1</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B368" s="54">
         <v>45</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B369" s="54">
         <v>0.38800000000000001</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B370" s="54">
         <v>0.125</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B371" s="54">
         <v>0.21</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B372" s="54">
         <v>0.09</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B373" s="54">
         <v>3.0880000000000001</v>
@@ -8354,13 +8354,13 @@
     </row>
     <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B374" s="54">
         <v>100</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>4</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B375" s="54">
         <v>14</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B376" s="54">
         <v>14</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B377" s="54">
         <v>0.26400000000000001</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B378" s="54">
         <v>0.23</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B379" s="54">
         <v>0.54700000000000004</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B380" s="54">
         <v>0.21</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B381" s="54">
         <v>0.185</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B382" s="54">
         <v>1.45</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B383" s="54">
         <v>0.11899999999999999</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B384" s="54">
         <v>0.16</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B385" s="54">
         <v>0.33</v>
@@ -8517,12 +8517,12 @@
         <v>4</v>
       </c>
       <c r="D385" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B386" s="54">
         <v>0.51900000000000002</v>
@@ -8536,7 +8536,7 @@
     </row>
     <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B387" s="54">
         <v>0.69</v>
@@ -8550,7 +8550,7 @@
     </row>
     <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B388" s="54">
         <v>0.3</v>
@@ -8564,7 +8564,7 @@
     </row>
     <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B389" s="54">
         <v>0.67800000000000005</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B390" s="54">
         <v>0.81799999999999995</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B391" s="54">
         <v>0.99</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B392" s="54">
         <v>0.36499999999999999</v>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B393" s="54">
         <v>0.64500000000000002</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B394" s="54">
         <v>0.315</v>
@@ -8648,7 +8648,7 @@
     </row>
     <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B395" s="54">
         <v>0.25</v>
@@ -8662,7 +8662,7 @@
     </row>
     <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B396" s="54">
         <v>0.17</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B397" s="54">
         <v>0.17599999999999999</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B398" s="54">
         <v>9.5000000000000001E-2</v>
@@ -8704,7 +8704,7 @@
     </row>
     <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B399" s="54">
         <v>0.308</v>
@@ -8718,7 +8718,7 @@
     </row>
     <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B400" s="54">
         <v>15</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B401" s="54">
         <v>0.55000000000000004</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B402" s="54">
         <v>0.24</v>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B403" s="54">
         <v>0.22500000000000001</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B404" s="54">
         <v>0.27500000000000002</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B405" s="54">
         <v>0.26</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B406" s="54">
         <v>0.23</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B407" s="54">
         <v>0.187</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B408" s="54">
         <v>0.26800000000000002</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B409" s="54">
         <v>0.186</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B410" s="54">
         <v>1.26</v>
@@ -8872,7 +8872,7 @@
     </row>
     <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B411" s="54">
         <v>1.01</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B412" s="54">
         <v>0.76500000000000001</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B413" s="54">
         <v>1.01</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B414" s="54">
         <v>0.23899999999999999</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B415" s="54">
         <v>0.30499999999999999</v>
@@ -8942,7 +8942,7 @@
     </row>
     <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B416" s="54">
         <v>0.185</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B417" s="54">
         <v>1.05</v>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B418" s="54">
         <v>1.1599999999999999</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B419" s="54">
         <v>1.1599999999999999</v>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B420" s="54">
         <v>1</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B421" s="54">
         <v>0.64500000000000002</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B422" s="54">
         <v>1350</v>
@@ -9035,18 +9035,18 @@
         <v>32</v>
       </c>
       <c r="D422" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B423" s="54">
         <v>175</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D423" s="6" t="s">
         <v>28</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B424" s="54">
         <v>55</v>
@@ -9068,7 +9068,7 @@
     </row>
     <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B425" s="54">
         <v>0.11</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B426" s="54">
         <v>0.17</v>
@@ -9096,7 +9096,7 @@
     </row>
     <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B427" s="54">
         <v>0.12</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B428" s="54">
         <v>0.189</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B429" s="54">
         <v>5.37</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B430" s="54">
         <v>4.351</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B431" s="54">
         <v>0.8</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B432" s="54">
         <v>0.74</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B433" s="54">
         <v>0.55000000000000004</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B434" s="54">
         <v>2.2000000000000002</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B435" s="54">
         <v>3.42</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B436" s="54">
         <v>0.106</v>
@@ -9236,7 +9236,7 @@
     </row>
     <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B437" s="54">
         <v>0.15</v>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B438" s="54">
         <v>0.77600000000000002</v>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B439" s="54">
         <v>1.05</v>
@@ -9278,7 +9278,7 @@
     </row>
     <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B440" s="54">
         <v>0.2</v>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B441" s="54">
         <v>0.18</v>
@@ -9306,7 +9306,7 @@
     </row>
     <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B442" s="54">
         <v>0.18</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B443" s="54">
         <v>0.86</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B444" s="54">
         <v>1.2</v>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B445" s="54">
         <v>55</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B446" s="54">
         <v>0.35</v>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B447" s="54">
         <v>1.4379999999999999</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B448" s="54">
         <v>2.5499999999999998</v>
@@ -9404,7 +9404,7 @@
     </row>
     <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B449" s="54">
         <v>0.2</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B450" s="54">
         <v>9.5000000000000001E-2</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B451" s="54">
         <v>0.28499999999999998</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B452" s="54">
         <v>0.2</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B453" s="54">
         <v>1</v>
@@ -9474,7 +9474,7 @@
     </row>
     <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B454" s="54">
         <v>2.5680000000000001</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B455" s="54">
         <v>4.1500000000000004</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B456" s="54">
         <v>0.6</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B457" s="54">
         <v>0.17799999999999999</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B458" s="54">
         <v>0.17799999999999999</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B459" s="54">
         <v>0.318</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B460" s="54">
         <v>0.3</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B461" s="54">
         <v>0.14099999999999999</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B462" s="54">
         <v>0.189</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B463" s="54">
         <v>8.5000000000000006E-2</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B464" s="54">
         <v>0.2</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B465" s="54">
         <v>0.34499999999999997</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B466" s="54">
         <v>0.08</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B467" s="54">
         <v>0.08</v>
@@ -9670,13 +9670,13 @@
     </row>
     <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B468" s="54">
         <v>385</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D468" s="6" t="s">
         <v>28</v>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B469" s="54">
         <v>0.46</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B470" s="54">
         <v>0.441</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B471" s="54">
         <v>0.20399999999999999</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B472" s="54">
         <v>0.18</v>
@@ -9740,7 +9740,7 @@
     </row>
     <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B473" s="54">
         <v>0.13200000000000001</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B474" s="54">
         <v>0.312</v>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B475" s="54">
         <v>40</v>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B476" s="54">
         <v>0.11</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B477" s="54">
         <v>1.55</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B478" s="54">
         <v>12.3</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B479" s="54">
         <v>7.4999999999999997E-2</v>
@@ -9838,7 +9838,7 @@
     </row>
     <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B480" s="54">
         <v>0.43</v>
@@ -9847,12 +9847,12 @@
         <v>4</v>
       </c>
       <c r="D480" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B481" s="54">
         <v>0.43</v>
@@ -9861,12 +9861,12 @@
         <v>4</v>
       </c>
       <c r="D481" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B482" s="54">
         <v>0.43</v>
@@ -9875,12 +9875,12 @@
         <v>4</v>
       </c>
       <c r="D482" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B483" s="54">
         <v>0.15</v>
@@ -9889,12 +9889,12 @@
         <v>4</v>
       </c>
       <c r="D483" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B484" s="54">
         <v>0.32</v>
@@ -9903,12 +9903,12 @@
         <v>4</v>
       </c>
       <c r="D484" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B485" s="54">
         <v>0.22</v>
@@ -9917,12 +9917,12 @@
         <v>4</v>
       </c>
       <c r="D485" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B486" s="54">
         <v>0.27500000000000002</v>
@@ -9931,12 +9931,12 @@
         <v>4</v>
       </c>
       <c r="D486" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B487" s="54">
         <v>0.28000000000000003</v>
@@ -9945,12 +9945,12 @@
         <v>4</v>
       </c>
       <c r="D487" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B488" s="54">
         <v>0.28000000000000003</v>
@@ -9959,12 +9959,12 @@
         <v>4</v>
       </c>
       <c r="D488" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B489" s="54">
         <v>0.3</v>
@@ -9973,12 +9973,12 @@
         <v>4</v>
       </c>
       <c r="D489" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B490" s="54">
         <v>0.22500000000000001</v>
@@ -9987,12 +9987,12 @@
         <v>4</v>
       </c>
       <c r="D490" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B491" s="54">
         <v>0.76700000000000002</v>
@@ -10001,12 +10001,12 @@
         <v>4</v>
       </c>
       <c r="D491" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B492" s="54">
         <v>1.014</v>
@@ -10015,12 +10015,12 @@
         <v>4</v>
       </c>
       <c r="D492" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B493" s="54">
         <v>0.14000000000000001</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B494" s="54">
         <v>0.443</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B495" s="54">
         <v>0.29599999999999999</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B496" s="54">
         <v>1.079</v>
@@ -10076,13 +10076,13 @@
     </row>
     <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B497" s="54">
         <v>1125</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D497" s="6" t="s">
         <v>5</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B498" s="54">
         <v>0.53</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B499" s="54">
         <v>0.53</v>
@@ -10118,7 +10118,7 @@
     </row>
     <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B500" s="54">
         <v>0.53</v>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B501" s="54">
         <v>0.53</v>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B502" s="54">
         <v>0.53</v>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B503" s="54">
         <v>4</v>
@@ -10174,7 +10174,7 @@
     </row>
     <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B504" s="54">
         <v>0.08</v>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B505" s="54">
         <v>0.56499999999999995</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B506" s="54">
         <v>0.84</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B507" s="54">
         <v>0.29599999999999999</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B508" s="54">
         <v>1.02</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B509" s="54">
         <v>6.8000000000000005E-2</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B510" s="54">
         <v>0.24</v>
@@ -10272,7 +10272,7 @@
     </row>
     <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B511" s="54">
         <v>35</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B512" s="54">
         <v>0.5</v>
@@ -10300,7 +10300,7 @@
     </row>
     <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B513" s="54">
         <v>1.7789999999999999</v>
@@ -10314,7 +10314,7 @@
     </row>
     <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B514" s="54">
         <v>0.13</v>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B515" s="54">
         <v>1</v>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B516" s="54">
         <v>0.04</v>
@@ -10356,7 +10356,7 @@
     </row>
     <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B517" s="54">
         <v>5.5E-2</v>
@@ -10370,7 +10370,7 @@
     </row>
     <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B518" s="54">
         <v>60</v>
@@ -10384,7 +10384,7 @@
     </row>
     <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B519" s="54">
         <v>60</v>
@@ -10398,7 +10398,7 @@
     </row>
     <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B520" s="54">
         <v>0.59</v>
@@ -10407,12 +10407,12 @@
         <v>4</v>
       </c>
       <c r="D520" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B521" s="54">
         <v>0.08</v>
@@ -10426,7 +10426,7 @@
     </row>
     <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B522" s="54">
         <v>2.5000000000000001E-2</v>
@@ -10440,7 +10440,7 @@
     </row>
     <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B523" s="54">
         <v>0.39</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B524" s="54">
         <v>0.91</v>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B525" s="54">
         <v>0.91</v>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B526" s="54">
         <v>0.91</v>
@@ -10496,7 +10496,7 @@
     </row>
     <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B527" s="54">
         <v>0.71</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B528" s="54">
         <v>0.71</v>
@@ -10524,7 +10524,7 @@
     </row>
     <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B529" s="54">
         <v>0.71</v>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B530" s="54">
         <v>0.71</v>
@@ -10552,7 +10552,7 @@
     </row>
     <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B531" s="54">
         <v>0.91</v>
@@ -10566,7 +10566,7 @@
     </row>
     <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B532" s="54">
         <v>0.71</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B533" s="54">
         <v>0.71</v>
@@ -10594,7 +10594,7 @@
     </row>
     <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B534" s="54">
         <v>0.91</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B535" s="54">
         <v>0.91</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B536" s="54">
         <v>0.71</v>
@@ -10636,7 +10636,7 @@
     </row>
     <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B537" s="54">
         <v>0.71</v>
@@ -10650,7 +10650,7 @@
     </row>
     <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B538" s="54">
         <v>0.91</v>
@@ -10664,7 +10664,7 @@
     </row>
     <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B539" s="54">
         <v>0.91</v>
@@ -10678,7 +10678,7 @@
     </row>
     <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B540" s="54">
         <v>0.91</v>
@@ -10692,7 +10692,7 @@
     </row>
     <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B541" s="54">
         <v>0.91</v>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B542" s="54">
         <v>0.91</v>
@@ -10720,7 +10720,7 @@
     </row>
     <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B543" s="54">
         <v>0.71</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B544" s="54">
         <v>0.55000000000000004</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B545" s="54">
         <v>0.48</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B546" s="54">
         <v>0.76700000000000002</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B547" s="54">
         <v>0.26700000000000002</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B548" s="54">
         <v>7.0000000000000007E-2</v>
@@ -10804,7 +10804,7 @@
     </row>
     <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B549" s="54">
         <v>0.79600000000000004</v>
@@ -10818,7 +10818,7 @@
     </row>
     <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B550" s="54">
         <v>1.087</v>
@@ -10832,7 +10832,7 @@
     </row>
     <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B551" s="54">
         <v>1.091</v>
@@ -10846,7 +10846,7 @@
     </row>
     <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B552" s="54">
         <v>0.13</v>
@@ -10860,7 +10860,7 @@
     </row>
     <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B553" s="54">
         <v>0.28000000000000003</v>
@@ -10874,7 +10874,7 @@
     </row>
     <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B554" s="54">
         <v>1</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B555" s="54">
         <v>0.46500000000000002</v>
@@ -10902,7 +10902,7 @@
     </row>
     <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B556" s="54">
         <v>1.212</v>
@@ -10916,7 +10916,7 @@
     </row>
     <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B557" s="54">
         <v>0.125</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B558" s="54">
         <v>0.186</v>
@@ -10944,7 +10944,7 @@
     </row>
     <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B559" s="54">
         <v>0.29199999999999998</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B560" s="54">
         <v>0.105</v>
@@ -10972,7 +10972,7 @@
     </row>
     <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B561" s="54">
         <v>0.13</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B562" s="54">
         <v>0.67100000000000004</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B563" s="54">
         <v>0.61</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B564" s="54">
         <v>37</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B565" s="54">
         <v>0.08</v>
@@ -11042,7 +11042,7 @@
     </row>
     <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B566" s="54">
         <v>0.65500000000000003</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B567" s="54">
         <v>1.79</v>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B568" s="54">
         <v>0.36</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B569" s="54">
         <v>0.5</v>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B570" s="54">
         <v>1.07</v>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B571" s="54">
         <v>0.11</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B572" s="54">
         <v>0.505</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B573" s="54">
         <v>0.13800000000000001</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B574" s="54">
         <v>0.26100000000000001</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B575" s="54">
         <v>0.38400000000000001</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B576" s="54">
         <v>0.65</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B577" s="54">
         <v>7.0000000000000007E-2</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B578" s="54">
         <v>0.09</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B579" s="54">
         <v>1.8859999999999999</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B580" s="54">
         <v>0.33</v>
@@ -11252,7 +11252,7 @@
     </row>
     <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B581" s="54">
         <v>0.24</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B582" s="54">
         <v>0.95</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B583" s="54">
         <v>0.25</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B584" s="54">
         <v>0.15</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B585" s="54">
         <v>0.31</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B586" s="54">
         <v>1.1499999999999999</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B587" s="54">
         <v>1.05</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B588" s="54">
         <v>2.0499999999999998</v>
@@ -11364,7 +11364,7 @@
     </row>
     <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B589" s="54">
         <v>0.27</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B590" s="54">
         <v>1.5720000000000001</v>
@@ -11392,7 +11392,7 @@
     </row>
     <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B591" s="54">
         <v>0.13500000000000001</v>
@@ -11406,7 +11406,7 @@
     </row>
     <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B592" s="54">
         <v>0.19900000000000001</v>
@@ -11420,7 +11420,7 @@
     </row>
     <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B593" s="54">
         <v>0.3</v>
@@ -11434,7 +11434,7 @@
     </row>
     <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B594" s="54">
         <v>0.13</v>
@@ -11448,7 +11448,7 @@
     </row>
     <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B595" s="54">
         <v>0.25</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B596" s="54">
         <v>0.17699999999999999</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B597" s="54">
         <v>0.12</v>
@@ -11490,7 +11490,7 @@
     </row>
     <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B598" s="54">
         <v>1.347</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B599" s="54">
         <v>45</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B600" s="54">
         <v>0.84699999999999998</v>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B601" s="54">
         <v>0.5</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B602" s="54">
         <v>0.5</v>
@@ -11560,7 +11560,7 @@
     </row>
     <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B603" s="54">
         <v>0.35</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B604" s="54">
         <v>0.23499999999999999</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B605" s="54">
         <v>0.65</v>
@@ -11602,13 +11602,13 @@
     </row>
     <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B606" s="54">
         <v>220</v>
       </c>
       <c r="C606" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D606" s="6" t="s">
         <v>28</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B607" s="54">
         <v>1.7230000000000001</v>
@@ -11630,7 +11630,7 @@
     </row>
     <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B608" s="54">
         <v>0.45</v>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B609" s="54">
         <v>2.3119999999999998</v>
@@ -11658,7 +11658,7 @@
     </row>
     <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B610" s="54">
         <v>1.0529999999999999</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B611" s="54">
         <v>0.35499999999999998</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B612" s="54">
         <v>0.25</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B613" s="54">
         <v>0.52900000000000003</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B614" s="54">
         <v>0.5</v>
@@ -11728,7 +11728,7 @@
     </row>
     <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B615" s="54">
         <v>5.2999999999999999E-2</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B616" s="54">
         <v>1.2</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B617" s="54">
         <v>0.05</v>
@@ -11770,7 +11770,7 @@
     </row>
     <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B618" s="54">
         <v>0.8</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B619" s="54">
         <v>0.46</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B620" s="54">
         <v>0.06</v>
@@ -11812,13 +11812,13 @@
     </row>
     <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B621" s="54">
         <v>0.32</v>
       </c>
       <c r="C621" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D621" s="6" t="s">
         <v>7</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B622" s="54">
         <v>0.25</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B623" s="54">
         <v>0.52</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B624" s="54">
         <v>3.3580000000000001</v>
@@ -11868,7 +11868,7 @@
     </row>
     <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B625" s="54">
         <v>2.1</v>
@@ -11882,7 +11882,7 @@
     </row>
     <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B626" s="54">
         <v>1.35</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B627" s="54">
         <v>1.65</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B628" s="54">
         <v>0.39</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B629" s="54">
         <v>0.37</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B630" s="54">
         <v>0.39</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B631" s="54">
         <v>1.4390000000000001</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B632" s="54">
         <v>2</v>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B633" s="54">
         <v>0.74</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B634" s="54">
         <v>0.74</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B635" s="54">
         <v>0.9</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B636" s="54">
         <v>450</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B637" s="54">
         <v>0.3</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B638" s="54">
         <v>0.25</v>
@@ -12059,32 +12059,32 @@
         <v>4</v>
       </c>
       <c r="D638" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B639" s="54">
         <v>0.38</v>
       </c>
       <c r="C639" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D639" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B640" s="54">
         <v>0.22</v>
       </c>
       <c r="C640" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D640" s="6" t="s">
         <v>10</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B641" s="54">
         <v>1200</v>
@@ -12106,13 +12106,13 @@
     </row>
     <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B642" s="54">
         <v>0.19</v>
       </c>
       <c r="C642" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D642" s="6" t="s">
         <v>10</v>
@@ -12120,13 +12120,13 @@
     </row>
     <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B643" s="54">
         <v>0.82399999999999995</v>
       </c>
       <c r="C643" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D643" s="6" t="s">
         <v>7</v>
@@ -12134,13 +12134,13 @@
     </row>
     <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B644" s="54">
         <v>170</v>
       </c>
       <c r="C644" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D644" s="6" t="s">
         <v>4</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B645" s="54">
         <v>0.15</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B646" s="54">
         <v>0.08</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B647" s="54">
         <v>65</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B648" s="54">
         <v>0.3</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B649" s="54">
         <v>0.16</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B650" s="54">
         <v>0.57199999999999995</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B651" s="54">
         <v>0.28599999999999998</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B652" s="54">
         <v>1.7</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B653" s="54">
         <v>0.32</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B654" s="54">
         <v>83</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B655" s="54">
         <v>0.6</v>
@@ -12297,12 +12297,12 @@
         <v>4</v>
       </c>
       <c r="D655" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B656" s="54">
         <v>0.27500000000000002</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B657" s="54">
         <v>0.27500000000000002</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B658" s="54">
         <v>0.9</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B659" s="55">
         <v>0.6</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B660" s="54">
         <v>0.75</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B661" s="54">
         <v>0.3</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B662" s="56">
         <v>0.185</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B663" s="56">
         <v>0.12</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B664" s="56">
         <v>1.2649999999999999</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B665" s="56">
         <v>1.84</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B666" s="54">
         <v>0.74814814814814812</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B667" s="56">
         <v>0.15</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B668" s="56">
         <v>0.47199999999999998</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B669" s="54">
         <v>1.6</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B670" s="54">
         <v>1.6</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B671" s="54">
         <v>1.6</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B672" s="56">
         <v>2.8639999999999999</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B673" s="56">
         <v>1.579</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A674" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B674" s="54">
         <v>1.94</v>
@@ -12568,13 +12568,13 @@
     </row>
     <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="50" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B675" s="55">
         <v>0.11700000000000001</v>
       </c>
       <c r="C675" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D675" s="13" t="s">
         <v>5</v>
@@ -12582,13 +12582,13 @@
     </row>
     <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="50" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B676" s="55">
         <v>1.2</v>
       </c>
       <c r="C676" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D676" s="13" t="s">
         <v>5</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="50" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B677" s="55">
         <v>0.27500000000000002</v>
@@ -12610,13 +12610,13 @@
     </row>
     <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="50" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B678" s="55">
         <v>45</v>
       </c>
       <c r="C678" s="13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D678" s="13" t="s">
         <v>10</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B679" s="54">
         <v>3</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A680" s="51" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B680" s="54">
         <v>0.22</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="51" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B681" s="54">
         <v>0.17</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A682" s="59" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B682" s="58">
         <v>0.91</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A683" s="61" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B683" s="62">
         <v>0.38</v>
@@ -12689,26 +12689,26 @@
         <v>1</v>
       </c>
       <c r="D683" s="63" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A684" s="61" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B684" s="62">
         <v>0.22</v>
       </c>
       <c r="C684" s="63" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D684" s="63" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A685" s="61" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B685" s="62">
         <v>0.59</v>
@@ -12717,12 +12717,12 @@
         <v>32</v>
       </c>
       <c r="D685" s="63" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A686" s="61" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B686" s="62">
         <v>3.1</v>
@@ -12731,12 +12731,12 @@
         <v>32</v>
       </c>
       <c r="D686" s="63" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A687" s="61" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B687" s="62">
         <v>6.9</v>
@@ -12745,12 +12745,12 @@
         <v>32</v>
       </c>
       <c r="D687" s="63" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A688" s="61" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B688" s="62">
         <v>6.3</v>
@@ -12759,18 +12759,18 @@
         <v>32</v>
       </c>
       <c r="D688" s="63" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A689" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B689" s="64">
         <v>0.499</v>
       </c>
       <c r="C689" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D689" s="6" t="s">
         <v>10</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A690" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B690" s="64">
         <v>0.4</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A691" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B691" s="64">
         <v>0.36</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B692" s="64">
         <v>0.2</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A693" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B693" s="64">
         <v>0.25</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="50" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B694" s="64">
         <v>0.64</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A695" s="50" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B695" s="64">
         <v>0.85</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A696" s="50" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B696" s="64">
         <v>0.15</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="697" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A697" s="65" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B697" s="67">
         <v>1.3</v>
@@ -12885,7 +12885,7 @@
         <v>32</v>
       </c>
       <c r="D697" s="66" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4401D82-0511-4790-947B-4533EAA30FDE}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1400198F-4E57-4BE8-BD64-6FFA95654FD7}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2088" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="727">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2208,6 +2208,9 @@
   </si>
   <si>
     <t>Coffee Beans (per gram)</t>
+  </si>
+  <si>
+    <t>Ice</t>
   </si>
 </sst>
 </file>
@@ -2391,7 +2394,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -2649,11 +2652,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2817,6 +2829,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3132,7 +3153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D697"/>
+  <dimension ref="A1:D698"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -12888,6 +12909,20 @@
         <v>712</v>
       </c>
     </row>
+    <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A698" s="68" t="s">
+        <v>726</v>
+      </c>
+      <c r="B698" s="69">
+        <v>0</v>
+      </c>
+      <c r="C698" s="70" t="s">
+        <v>465</v>
+      </c>
+      <c r="D698" s="70" t="s">
+        <v>423</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1400198F-4E57-4BE8-BD64-6FFA95654FD7}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2024EA-3DD5-447F-ABCD-80D4A0735D46}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2091" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="732">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2211,6 +2211,21 @@
   </si>
   <si>
     <t>Ice</t>
+  </si>
+  <si>
+    <t>Plastic Cup for Café</t>
+  </si>
+  <si>
+    <t>Plastic Lid Dome for Café</t>
+  </si>
+  <si>
+    <t>Plastic Lid Strawless for Café</t>
+  </si>
+  <si>
+    <t>Straw (thin) individual</t>
+  </si>
+  <si>
+    <t>Boba Straw</t>
   </si>
 </sst>
 </file>
@@ -2394,7 +2409,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -2632,9 +2647,7 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2647,17 +2660,6 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -2665,7 +2667,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2824,19 +2826,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3153,7 +3152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D698"/>
+  <dimension ref="A1:D703"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -12895,17 +12894,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="697" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A697" s="65" t="s">
         <v>724</v>
       </c>
-      <c r="B697" s="67">
+      <c r="B697" s="66">
         <v>1.3</v>
       </c>
-      <c r="C697" s="66" t="s">
+      <c r="C697" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="D697" s="66" t="s">
+      <c r="D697" s="67" t="s">
         <v>712</v>
       </c>
     </row>
@@ -12916,11 +12915,81 @@
       <c r="B698" s="69">
         <v>0</v>
       </c>
-      <c r="C698" s="70" t="s">
+      <c r="C698" s="63" t="s">
         <v>465</v>
       </c>
-      <c r="D698" s="70" t="s">
+      <c r="D698" s="63" t="s">
         <v>423</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A699" s="68" t="s">
+        <v>727</v>
+      </c>
+      <c r="B699" s="69">
+        <v>3</v>
+      </c>
+      <c r="C699" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D699" s="63" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A700" s="68" t="s">
+        <v>729</v>
+      </c>
+      <c r="B700" s="69">
+        <v>2</v>
+      </c>
+      <c r="C700" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D700" s="63" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A701" s="68" t="s">
+        <v>728</v>
+      </c>
+      <c r="B701" s="69">
+        <v>1.6</v>
+      </c>
+      <c r="C701" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D701" s="63" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A702" s="68" t="s">
+        <v>730</v>
+      </c>
+      <c r="B702" s="69">
+        <v>0.25</v>
+      </c>
+      <c r="C702" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D702" s="63" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A703" s="68" t="s">
+        <v>731</v>
+      </c>
+      <c r="B703" s="69">
+        <v>0.4</v>
+      </c>
+      <c r="C703" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D703" s="63" t="s">
+        <v>712</v>
       </c>
     </row>
   </sheetData>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2024EA-3DD5-447F-ABCD-80D4A0735D46}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D2F755-9CF5-431F-ADAB-09B033744291}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2106" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="733">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2226,6 +2226,9 @@
   </si>
   <si>
     <t>Boba Straw</t>
+  </si>
+  <si>
+    <t>Paper Cup 16 oz with Logo</t>
   </si>
 </sst>
 </file>
@@ -3152,7 +3155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D703"/>
+  <dimension ref="A1:D704"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -12992,6 +12995,20 @@
         <v>712</v>
       </c>
     </row>
+    <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A704" s="68" t="s">
+        <v>732</v>
+      </c>
+      <c r="B704" s="69">
+        <v>4</v>
+      </c>
+      <c r="C704" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D704" s="63" t="s">
+        <v>712</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D2F755-9CF5-431F-ADAB-09B033744291}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA72092-AA12-41C6-BEAA-3783F852ABB6}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="3675" yWindow="4305" windowWidth="21600" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2109" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="734">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2229,6 +2229,9 @@
   </si>
   <si>
     <t>Paper Cup 16 oz with Logo</t>
+  </si>
+  <si>
+    <t>Plastic Lid - Black</t>
   </si>
 </sst>
 </file>
@@ -2670,7 +2673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2839,6 +2842,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="19" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3155,7 +3167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D704"/>
+  <dimension ref="A1:D705"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -13009,6 +13021,20 @@
         <v>712</v>
       </c>
     </row>
+    <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A705" s="70" t="s">
+        <v>733</v>
+      </c>
+      <c r="B705" s="71">
+        <v>1</v>
+      </c>
+      <c r="C705" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D705" s="72" t="s">
+        <v>712</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA72092-AA12-41C6-BEAA-3783F852ABB6}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5932DFF-F019-4D6B-B100-3A79FE7C763F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="4305" windowWidth="21600" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21660" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="737">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2232,6 +2232,15 @@
   </si>
   <si>
     <t>Plastic Lid - Black</t>
+  </si>
+  <si>
+    <t>Hibiscus Tea (per teabag)</t>
+  </si>
+  <si>
+    <t>Green Tea (per teabag)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamomile (per teabag) </t>
   </si>
 </sst>
 </file>
@@ -3167,7 +3176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D705"/>
+  <dimension ref="A1:D708"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -13035,6 +13044,48 @@
         <v>712</v>
       </c>
     </row>
+    <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A706" s="68" t="s">
+        <v>734</v>
+      </c>
+      <c r="B706" s="69">
+        <v>26</v>
+      </c>
+      <c r="C706" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D706" s="63" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A707" s="68" t="s">
+        <v>735</v>
+      </c>
+      <c r="B707" s="69">
+        <v>26</v>
+      </c>
+      <c r="C707" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D707" s="63" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A708" s="68" t="s">
+        <v>736</v>
+      </c>
+      <c r="B708" s="69">
+        <v>26</v>
+      </c>
+      <c r="C708" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="D708" s="63" t="s">
+        <v>712</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5932DFF-F019-4D6B-B100-3A79FE7C763F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84BD58D-EBFB-4A00-BAA6-668CED937B55}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21660" windowHeight="11175" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="738">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -269,9 +269,6 @@
     <t>can</t>
   </si>
   <si>
-    <t>Canned Tuna</t>
-  </si>
-  <si>
     <t>Capers</t>
   </si>
   <si>
@@ -2241,6 +2238,12 @@
   </si>
   <si>
     <t xml:space="preserve">Chamomile (per teabag) </t>
+  </si>
+  <si>
+    <t>Pita Bread 90grms - production</t>
+  </si>
+  <si>
+    <t>Canned Tuna (per gram)</t>
   </si>
 </sst>
 </file>
@@ -2424,7 +2427,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -2678,11 +2681,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2860,6 +2874,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="19" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3176,7 +3199,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D708"/>
+  <dimension ref="A1:D709"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -3190,7 +3213,7 @@
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
@@ -3204,7 +3227,7 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B3" s="36">
         <v>0.19</v>
@@ -3213,96 +3236,96 @@
         <v>1</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B4" s="37">
         <v>12.63</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B5" s="36">
         <v>0.13</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B6" s="36">
         <v>0.36</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B7" s="37">
         <v>270</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B8" s="37">
         <v>350</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B9" s="37">
         <v>36.5</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B10" s="38">
         <v>0.24299999999999999</v>
@@ -3311,12 +3334,12 @@
         <v>1</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B11" s="38">
         <v>0.111</v>
@@ -3325,194 +3348,194 @@
         <v>1</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B12" s="37">
         <v>261.39999999999998</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B13" s="37">
         <v>153.33000000000001</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B14" s="38">
         <v>219.96</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B15" s="38">
         <v>24.75</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B16" s="37">
         <v>85</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B17" s="37">
         <v>73.12</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B18" s="40">
         <v>72.010000000000005</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B19" s="41">
         <v>8</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B20" s="41">
         <v>72.91</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B21" s="41">
         <v>10</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B22" s="42">
         <v>18.5</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B23" s="38">
         <v>23.66</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B24" s="38">
         <v>196.62</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B25" s="38">
         <v>11.02</v>
@@ -3521,12 +3544,12 @@
         <v>32</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B26" s="38">
         <v>8.65</v>
@@ -3535,12 +3558,12 @@
         <v>32</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B27" s="38">
         <v>0.85199999999999998</v>
@@ -3549,40 +3572,40 @@
         <v>1</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B28" s="34">
         <v>0.53</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B29" s="38">
         <v>36.03</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B30" s="36">
         <v>0.31</v>
@@ -3591,68 +3614,68 @@
         <v>1</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B31" s="37">
         <v>25.39</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B32" s="37">
         <v>80.88</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B33" s="41">
         <v>179.51</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B34" s="37">
         <v>77.59</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B35" s="38">
         <v>0.312</v>
@@ -3661,68 +3684,68 @@
         <v>1</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B36" s="38">
         <v>124.44</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B37" s="37">
         <v>18</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B38" s="37">
         <v>193.88</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B39" s="38">
         <v>86.83</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B40" s="43">
         <v>0.6</v>
@@ -3731,12 +3754,12 @@
         <v>1</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B41" s="44">
         <v>0.379</v>
@@ -3745,12 +3768,12 @@
         <v>1</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B42" s="44">
         <v>0.16500000000000001</v>
@@ -3759,250 +3782,250 @@
         <v>1</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B43" s="44">
         <v>0.46</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B44" s="45">
         <v>7</v>
       </c>
       <c r="C44" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B45" s="41">
         <v>39</v>
       </c>
       <c r="C45" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B46" s="37">
         <v>30</v>
       </c>
       <c r="C46" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="28" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B47" s="37">
         <v>72.87</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B48" s="37">
         <v>30</v>
       </c>
       <c r="C48" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B49" s="37">
         <v>317.8</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B50" s="37">
         <v>70</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B51" s="38">
         <v>0.86199999999999999</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B52" s="38">
         <v>0.128</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="28" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B53" s="37">
         <v>14.92</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B54" s="37">
         <v>17.3</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B55" s="38">
         <v>1</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="28" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B56" s="37">
         <v>112.14</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B57" s="38">
         <v>0.71</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B58" s="38">
         <v>0.18</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B59" s="38">
         <v>0.3</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B60" s="36">
         <v>0.46</v>
@@ -4011,68 +4034,68 @@
         <v>1</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B61" s="38">
         <v>0.39100000000000001</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B62" s="38">
         <v>0.28999999999999998</v>
       </c>
       <c r="C62" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B63" s="38">
         <v>0.17599999999999999</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B64" s="37">
         <v>63.92</v>
       </c>
       <c r="C64" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B65" s="46">
         <v>0.54</v>
@@ -4081,12 +4104,12 @@
         <v>1</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B66" s="34">
         <v>0.71</v>
@@ -4095,82 +4118,82 @@
         <v>1</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B67" s="37">
         <v>43.56</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B68" s="34">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="C68" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="28" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B69" s="34">
         <v>118.91</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B70" s="37">
         <v>34.799999999999997</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B71" s="38">
         <v>17.5</v>
       </c>
       <c r="C71" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D71" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B72" s="36">
         <v>0.153</v>
@@ -4179,236 +4202,236 @@
         <v>1</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B73" s="38">
         <v>37.444000000000003</v>
       </c>
       <c r="C73" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D73" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B74" s="38">
         <v>15.24</v>
       </c>
       <c r="C74" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D74" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="30" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B75" s="37">
         <v>208.78</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D75" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B76" s="37">
         <v>203.77</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B77" s="37">
         <v>102</v>
       </c>
       <c r="C77" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="28" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B78" s="37">
         <v>20.399999999999999</v>
       </c>
       <c r="C78" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D78" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="31" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B79" s="37">
         <v>11.73</v>
       </c>
       <c r="C79" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D79" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="23" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B80" s="38">
         <v>3.1E-2</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="31" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B81" s="38">
         <v>23.2</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D81" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B82" s="37">
         <v>75</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="23" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B83" s="37">
         <v>75</v>
       </c>
       <c r="C83" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D83" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B84" s="38">
         <v>46.36</v>
       </c>
       <c r="C84" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D84" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="32" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B85" s="37">
         <v>20</v>
       </c>
       <c r="C85" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B86" s="34">
         <v>0.18</v>
       </c>
       <c r="C86" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D86" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B87" s="38">
         <v>47.7</v>
       </c>
       <c r="C87" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D87" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="23" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B88" s="37">
         <v>43.28</v>
       </c>
       <c r="C88" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B89" s="38">
         <v>0.223</v>
@@ -4417,40 +4440,40 @@
         <v>1</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="16" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B90" s="37">
         <v>255.59</v>
       </c>
       <c r="C90" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D90" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="16" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B91" s="37">
         <v>38.03</v>
       </c>
       <c r="C91" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D91" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B92" s="38">
         <v>0.26</v>
@@ -4459,26 +4482,26 @@
         <v>1</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="28" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B93" s="37">
         <v>20.399999999999999</v>
       </c>
       <c r="C93" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D93" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B94" s="36">
         <v>0.11</v>
@@ -4487,152 +4510,152 @@
         <v>1</v>
       </c>
       <c r="D94" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B95" s="38">
         <v>34.24</v>
       </c>
       <c r="C95" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D95" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B96" s="37">
         <v>77</v>
       </c>
       <c r="C96" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B97" s="37">
         <v>130.91</v>
       </c>
       <c r="C97" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B98" s="34">
         <v>118.01</v>
       </c>
       <c r="C98" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D98" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="23" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B99" s="38">
         <v>43.75</v>
       </c>
       <c r="C99" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="28" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B100" s="37">
         <v>25.55</v>
       </c>
       <c r="C100" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D100" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B101" s="37">
         <v>200</v>
       </c>
       <c r="C101" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D101" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="28" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B102" s="37">
         <v>30</v>
       </c>
       <c r="C102" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B103" s="37">
         <v>22.25</v>
       </c>
       <c r="C103" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D103" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="24" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B104" s="37">
         <v>155.62</v>
       </c>
       <c r="C104" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B105" s="38">
         <v>0.22800000000000001</v>
@@ -4641,40 +4664,40 @@
         <v>1</v>
       </c>
       <c r="D105" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B106" s="38">
         <v>66</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D106" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="24" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B107" s="37">
         <v>36</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D107" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B108" s="34">
         <v>0.42</v>
@@ -4683,54 +4706,54 @@
         <v>1</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B109" s="37">
         <v>74.78</v>
       </c>
       <c r="C109" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D109" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="24" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B110" s="37">
         <v>8</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D110" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B111" s="37">
         <v>125</v>
       </c>
       <c r="C111" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B112" s="38">
         <v>0.16500000000000001</v>
@@ -4739,82 +4762,82 @@
         <v>1</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="28" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B113" s="37">
         <v>49.5</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D113" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B114" s="38">
         <v>0.56000000000000005</v>
       </c>
       <c r="C114" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B115" s="37">
         <v>86.22</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B116" s="38">
         <v>175</v>
       </c>
       <c r="C116" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B117" s="37">
         <v>57.15</v>
       </c>
       <c r="C117" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B118" s="38">
         <v>0.13400000000000001</v>
@@ -4823,26 +4846,26 @@
         <v>1</v>
       </c>
       <c r="D118" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B119" s="36">
         <v>0.12</v>
       </c>
       <c r="C119" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B120" s="38">
         <v>14.35</v>
@@ -4851,54 +4874,54 @@
         <v>32</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B121" s="37">
         <v>117.25</v>
       </c>
       <c r="C121" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D121" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B122" s="37">
         <v>38</v>
       </c>
       <c r="C122" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="23" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B123" s="38">
         <v>37.33</v>
       </c>
       <c r="C123" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="25" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B124" s="38">
         <v>0.222</v>
@@ -4907,12 +4930,12 @@
         <v>1</v>
       </c>
       <c r="D124" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B125" s="38">
         <v>0.22900000000000001</v>
@@ -4921,12 +4944,12 @@
         <v>1</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="23" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B126" s="38">
         <v>33</v>
@@ -4935,40 +4958,40 @@
         <v>32</v>
       </c>
       <c r="D126" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="23" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B127" s="38">
         <v>29.5</v>
       </c>
       <c r="C127" s="47" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D127" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="26" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B128" s="43">
         <v>0.24</v>
       </c>
       <c r="C128" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D128" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="33" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B129" s="44">
         <v>0.40799999999999997</v>
@@ -4977,138 +5000,138 @@
         <v>1</v>
       </c>
       <c r="D129" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="33" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B130" s="43">
         <v>34</v>
       </c>
       <c r="C130" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D130" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="33" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B131" s="43">
         <v>209.55</v>
       </c>
       <c r="C131" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D131" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="26" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B132" s="43">
         <v>0.05</v>
       </c>
       <c r="C132" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="26" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B133" s="43">
         <v>0.81</v>
       </c>
       <c r="C133" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D133" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="26" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B134" s="43">
         <v>10</v>
       </c>
       <c r="C134" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="26" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B135" s="38">
         <v>8.5</v>
       </c>
       <c r="C135" s="47" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D135" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="26" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B136" s="38">
         <v>0.28000000000000003</v>
       </c>
       <c r="C136" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B137" s="38">
         <v>0.35</v>
       </c>
       <c r="C137" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="26" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B138" s="38">
         <v>0.08</v>
       </c>
       <c r="C138" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="26" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B139" s="38">
         <v>0.19</v>
@@ -5117,26 +5140,26 @@
         <v>1</v>
       </c>
       <c r="D139" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="26" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B140" s="38">
         <v>332.18</v>
       </c>
       <c r="C140" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D140" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="26" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B141" s="38">
         <v>0.27200000000000002</v>
@@ -5145,77 +5168,77 @@
         <v>4</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="26" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B142" s="38">
         <v>166.79</v>
       </c>
       <c r="C142" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D142" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="26" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B143" s="38">
         <v>119.93</v>
       </c>
       <c r="C143" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D143" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="26" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B144" s="38">
         <v>0.52</v>
       </c>
       <c r="C144" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D144" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="26" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B145" s="38">
         <v>27.72</v>
       </c>
       <c r="C145" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D145" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="57" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B146" s="38">
         <v>32.22</v>
       </c>
       <c r="C146" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D146" s="49" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5290,7 +5313,7 @@
     </row>
     <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B152" s="53">
         <v>0.18</v>
@@ -5332,7 +5355,7 @@
     </row>
     <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B155" s="53">
         <v>0.21428571428571427</v>
@@ -5626,7 +5649,7 @@
     </row>
     <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B176" s="54">
         <v>0.19</v>
@@ -5682,7 +5705,7 @@
     </row>
     <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B180" s="54">
         <v>75</v>
@@ -5724,7 +5747,7 @@
     </row>
     <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B183" s="54">
         <v>2.2000000000000002</v>
@@ -5780,7 +5803,7 @@
     </row>
     <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B187" s="54">
         <v>0.24</v>
@@ -6228,13 +6251,13 @@
     </row>
     <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
-        <v>79</v>
+        <v>737</v>
       </c>
       <c r="B219" s="54">
         <v>0.36099999999999999</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="D219" s="6" t="s">
         <v>28</v>
@@ -6242,7 +6265,7 @@
     </row>
     <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B220" s="54">
         <v>0.96140350877192982</v>
@@ -6256,7 +6279,7 @@
     </row>
     <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B221" s="54">
         <v>0.65</v>
@@ -6270,7 +6293,7 @@
     </row>
     <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B222" s="54">
         <v>0.19</v>
@@ -6284,7 +6307,7 @@
     </row>
     <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B223" s="54">
         <v>0.43</v>
@@ -6298,7 +6321,7 @@
     </row>
     <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B224" s="54">
         <v>394</v>
@@ -6312,7 +6335,7 @@
     </row>
     <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B225" s="54">
         <v>0.32</v>
@@ -6326,7 +6349,7 @@
     </row>
     <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B226" s="54">
         <v>2.8846153846153846</v>
@@ -6340,7 +6363,7 @@
     </row>
     <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B227" s="54">
         <v>0.18</v>
@@ -6354,7 +6377,7 @@
     </row>
     <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B228" s="54">
         <v>0.65</v>
@@ -6368,7 +6391,7 @@
     </row>
     <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B229" s="54">
         <v>0.40250000000000002</v>
@@ -6382,7 +6405,7 @@
     </row>
     <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B230" s="54">
         <v>0.31</v>
@@ -6396,7 +6419,7 @@
     </row>
     <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B231" s="54">
         <v>0.5</v>
@@ -6410,7 +6433,7 @@
     </row>
     <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B232" s="54">
         <v>1.18</v>
@@ -6424,7 +6447,7 @@
     </row>
     <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B233" s="54">
         <v>1.66</v>
@@ -6438,7 +6461,7 @@
     </row>
     <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B234" s="54">
         <v>0.46333333333333332</v>
@@ -6452,7 +6475,7 @@
     </row>
     <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B235" s="54">
         <v>0.26</v>
@@ -6461,12 +6484,12 @@
         <v>4</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B236" s="54">
         <v>0.24</v>
@@ -6475,12 +6498,12 @@
         <v>4</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B237" s="54">
         <v>0.21</v>
@@ -6489,12 +6512,12 @@
         <v>4</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B238" s="54">
         <v>0.33500000000000002</v>
@@ -6503,12 +6526,12 @@
         <v>4</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B239" s="54">
         <v>0.26500000000000001</v>
@@ -6517,12 +6540,12 @@
         <v>4</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B240" s="54">
         <v>0.17499999999999999</v>
@@ -6531,12 +6554,12 @@
         <v>4</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B241" s="54">
         <v>0.23499999999999999</v>
@@ -6545,12 +6568,12 @@
         <v>4</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B242" s="54">
         <v>0.18</v>
@@ -6559,12 +6582,12 @@
         <v>4</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B243" s="54">
         <v>0.55000000000000004</v>
@@ -6578,7 +6601,7 @@
     </row>
     <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B244" s="54">
         <v>0.25</v>
@@ -6592,7 +6615,7 @@
     </row>
     <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B245" s="54">
         <v>0.2</v>
@@ -6606,7 +6629,7 @@
     </row>
     <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B246" s="54">
         <v>0.12</v>
@@ -6620,7 +6643,7 @@
     </row>
     <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B247" s="54">
         <v>0.27</v>
@@ -6634,7 +6657,7 @@
     </row>
     <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B248" s="54">
         <v>1.9857142857142858</v>
@@ -6643,12 +6666,12 @@
         <v>4</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B249" s="54">
         <v>0.63636363636363635</v>
@@ -6657,12 +6680,12 @@
         <v>4</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B250" s="54">
         <v>0.65</v>
@@ -6671,12 +6694,12 @@
         <v>4</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B251" s="54">
         <v>0.745</v>
@@ -6690,7 +6713,7 @@
     </row>
     <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B252" s="54">
         <v>1.39</v>
@@ -6704,7 +6727,7 @@
     </row>
     <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B253" s="54">
         <v>2.7441860465116279</v>
@@ -6718,7 +6741,7 @@
     </row>
     <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B254" s="54">
         <v>2.3312883435582821</v>
@@ -6732,7 +6755,7 @@
     </row>
     <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B255" s="54">
         <v>55</v>
@@ -6746,7 +6769,7 @@
     </row>
     <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B256" s="54">
         <v>55</v>
@@ -6760,7 +6783,7 @@
     </row>
     <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B257" s="54">
         <v>1.0271428571428571</v>
@@ -6774,7 +6797,7 @@
     </row>
     <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B258" s="54">
         <v>0.15151515151515152</v>
@@ -6788,7 +6811,7 @@
     </row>
     <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B259" s="54">
         <v>0.73</v>
@@ -6802,7 +6825,7 @@
     </row>
     <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B260" s="54">
         <v>9.5000000000000001E-2</v>
@@ -6816,7 +6839,7 @@
     </row>
     <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B261" s="54">
         <v>37</v>
@@ -6830,7 +6853,7 @@
     </row>
     <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B262" s="54">
         <v>37</v>
@@ -6844,7 +6867,7 @@
     </row>
     <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B263" s="54">
         <v>0.23</v>
@@ -6858,7 +6881,7 @@
     </row>
     <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B264" s="54">
         <v>0.49</v>
@@ -6872,7 +6895,7 @@
     </row>
     <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B265" s="54">
         <v>0.14285714285714285</v>
@@ -6886,7 +6909,7 @@
     </row>
     <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B266" s="54">
         <v>0.18823529411764706</v>
@@ -6900,7 +6923,7 @@
     </row>
     <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B267" s="54">
         <v>0.30737704918032788</v>
@@ -6914,7 +6937,7 @@
     </row>
     <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B268" s="54">
         <v>7.0000000000000007E-2</v>
@@ -6928,7 +6951,7 @@
     </row>
     <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B269" s="54">
         <v>70</v>
@@ -6942,7 +6965,7 @@
     </row>
     <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B270" s="54">
         <v>1.327</v>
@@ -6956,7 +6979,7 @@
     </row>
     <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B271" s="54">
         <v>0.88105726872246692</v>
@@ -6970,7 +6993,7 @@
     </row>
     <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B272" s="54">
         <v>0.32900000000000001</v>
@@ -6984,7 +7007,7 @@
     </row>
     <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B273" s="54">
         <v>0.32</v>
@@ -6998,7 +7021,7 @@
     </row>
     <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B274" s="54">
         <v>0.21249999999999999</v>
@@ -7012,7 +7035,7 @@
     </row>
     <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B275" s="54">
         <v>0.35</v>
@@ -7026,13 +7049,13 @@
     </row>
     <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B276" s="54">
         <v>0.12</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D276" s="6" t="s">
         <v>7</v>
@@ -7040,7 +7063,7 @@
     </row>
     <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B277" s="54">
         <v>0.89</v>
@@ -7054,7 +7077,7 @@
     </row>
     <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B278" s="54">
         <v>0.496</v>
@@ -7068,7 +7091,7 @@
     </row>
     <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B279" s="54">
         <v>0.8666666666666667</v>
@@ -7082,7 +7105,7 @@
     </row>
     <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B280" s="54">
         <v>0.13500000000000001</v>
@@ -7096,7 +7119,7 @@
     </row>
     <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B281" s="54">
         <v>0.80645161290322576</v>
@@ -7110,7 +7133,7 @@
     </row>
     <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B282" s="54">
         <v>0.96199999999999997</v>
@@ -7124,7 +7147,7 @@
     </row>
     <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B283" s="54">
         <v>2</v>
@@ -7138,7 +7161,7 @@
     </row>
     <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B284" s="54">
         <v>0.22500000000000001</v>
@@ -7152,7 +7175,7 @@
     </row>
     <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B285" s="54">
         <v>0.13</v>
@@ -7166,7 +7189,7 @@
     </row>
     <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B286" s="54">
         <v>0.84199999999999997</v>
@@ -7180,7 +7203,7 @@
     </row>
     <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B287" s="54">
         <v>0.6</v>
@@ -7194,7 +7217,7 @@
     </row>
     <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B288" s="54">
         <v>0.51</v>
@@ -7208,7 +7231,7 @@
     </row>
     <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B289" s="54">
         <v>0.47</v>
@@ -7222,7 +7245,7 @@
     </row>
     <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B290" s="54">
         <v>0.38900000000000001</v>
@@ -7236,7 +7259,7 @@
     </row>
     <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B291" s="54">
         <v>0.55800000000000005</v>
@@ -7250,7 +7273,7 @@
     </row>
     <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B292" s="54">
         <v>0.7</v>
@@ -7264,7 +7287,7 @@
     </row>
     <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B293" s="54">
         <v>0.32500000000000001</v>
@@ -7278,7 +7301,7 @@
     </row>
     <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B294" s="54">
         <v>0.91400000000000003</v>
@@ -7292,7 +7315,7 @@
     </row>
     <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B295" s="54">
         <v>0.81</v>
@@ -7306,7 +7329,7 @@
     </row>
     <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B296" s="54">
         <v>1.01</v>
@@ -7320,7 +7343,7 @@
     </row>
     <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B297" s="54">
         <v>0.40500000000000003</v>
@@ -7334,7 +7357,7 @@
     </row>
     <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B298" s="54">
         <v>0.372</v>
@@ -7348,7 +7371,7 @@
     </row>
     <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B299" s="54">
         <v>16</v>
@@ -7362,7 +7385,7 @@
     </row>
     <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B300" s="54">
         <v>12</v>
@@ -7376,7 +7399,7 @@
     </row>
     <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B301" s="54">
         <v>20</v>
@@ -7390,7 +7413,7 @@
     </row>
     <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B302" s="54">
         <v>0.13</v>
@@ -7404,7 +7427,7 @@
     </row>
     <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B303" s="54">
         <v>2.7857142857142856</v>
@@ -7418,7 +7441,7 @@
     </row>
     <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B304" s="54">
         <v>95</v>
@@ -7432,7 +7455,7 @@
     </row>
     <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B305" s="54">
         <v>2.67</v>
@@ -7446,7 +7469,7 @@
     </row>
     <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B306" s="54">
         <v>0.08</v>
@@ -7460,7 +7483,7 @@
     </row>
     <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B307" s="54">
         <v>0.42499999999999999</v>
@@ -7474,7 +7497,7 @@
     </row>
     <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B308" s="54">
         <v>5.8400000000000001E-2</v>
@@ -7488,7 +7511,7 @@
     </row>
     <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B309" s="54">
         <v>6.5000000000000002E-2</v>
@@ -7502,7 +7525,7 @@
     </row>
     <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B310" s="54">
         <v>7.0000000000000007E-2</v>
@@ -7516,7 +7539,7 @@
     </row>
     <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B311" s="54">
         <v>0.16</v>
@@ -7530,7 +7553,7 @@
     </row>
     <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B312" s="54">
         <v>0.11</v>
@@ -7544,7 +7567,7 @@
     </row>
     <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B313" s="54">
         <v>7.0000000000000007E-2</v>
@@ -7558,7 +7581,7 @@
     </row>
     <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B314" s="54">
         <v>0.4</v>
@@ -7572,7 +7595,7 @@
     </row>
     <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B315" s="54">
         <v>0.11899999999999999</v>
@@ -7586,7 +7609,7 @@
     </row>
     <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B316" s="54">
         <v>5.5E-2</v>
@@ -7600,7 +7623,7 @@
     </row>
     <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B317" s="54">
         <v>0.21</v>
@@ -7614,7 +7637,7 @@
     </row>
     <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B318" s="54">
         <v>5.5E-2</v>
@@ -7628,7 +7651,7 @@
     </row>
     <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B319" s="54">
         <v>5.5E-2</v>
@@ -7642,7 +7665,7 @@
     </row>
     <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B320" s="54">
         <v>50</v>
@@ -7656,7 +7679,7 @@
     </row>
     <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B321" s="54">
         <v>0.22500000000000001</v>
@@ -7670,7 +7693,7 @@
     </row>
     <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B322" s="54">
         <v>0.312</v>
@@ -7684,7 +7707,7 @@
     </row>
     <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B323" s="54">
         <v>7</v>
@@ -7698,7 +7721,7 @@
     </row>
     <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B324" s="54">
         <v>14</v>
@@ -7712,7 +7735,7 @@
     </row>
     <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B325" s="54">
         <v>0.17</v>
@@ -7726,7 +7749,7 @@
     </row>
     <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B326" s="54">
         <v>0.31</v>
@@ -7740,7 +7763,7 @@
     </row>
     <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B327" s="54">
         <v>0.81</v>
@@ -7754,7 +7777,7 @@
     </row>
     <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B328" s="54">
         <v>0.12222222222222222</v>
@@ -7768,7 +7791,7 @@
     </row>
     <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B329" s="54">
         <v>0.18</v>
@@ -7782,7 +7805,7 @@
     </row>
     <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B330" s="54">
         <v>0.88200000000000001</v>
@@ -7796,7 +7819,7 @@
     </row>
     <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B331" s="54">
         <v>0.37</v>
@@ -7805,12 +7828,12 @@
         <v>4</v>
       </c>
       <c r="D331" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B332" s="54">
         <v>5</v>
@@ -7824,7 +7847,7 @@
     </row>
     <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B333" s="54">
         <v>1.2386666666666666</v>
@@ -7838,7 +7861,7 @@
     </row>
     <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B334" s="54">
         <v>0.33900000000000002</v>
@@ -7852,7 +7875,7 @@
     </row>
     <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B335" s="54">
         <v>0.18</v>
@@ -7866,7 +7889,7 @@
     </row>
     <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B336" s="54">
         <v>0.47333333333333333</v>
@@ -7880,7 +7903,7 @@
     </row>
     <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B337" s="54">
         <v>7.4999999999999997E-2</v>
@@ -7894,7 +7917,7 @@
     </row>
     <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B338" s="54">
         <v>2.4700000000000002</v>
@@ -7908,7 +7931,7 @@
     </row>
     <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B339" s="54">
         <v>0.82</v>
@@ -7922,7 +7945,7 @@
     </row>
     <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B340" s="54">
         <v>0.106</v>
@@ -7936,7 +7959,7 @@
     </row>
     <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B341" s="54">
         <v>0.11700000000000001</v>
@@ -7950,7 +7973,7 @@
     </row>
     <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B342" s="54">
         <v>0.45900000000000002</v>
@@ -7964,7 +7987,7 @@
     </row>
     <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B343" s="54">
         <v>0.71899999999999997</v>
@@ -7978,7 +8001,7 @@
     </row>
     <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B344" s="54">
         <v>1.5</v>
@@ -7992,7 +8015,7 @@
     </row>
     <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B345" s="54">
         <v>0.25600000000000001</v>
@@ -8006,7 +8029,7 @@
     </row>
     <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B346" s="54">
         <v>0.19400000000000001</v>
@@ -8020,7 +8043,7 @@
     </row>
     <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B347" s="54">
         <v>0.48399999999999999</v>
@@ -8034,7 +8057,7 @@
     </row>
     <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B348" s="54">
         <v>0.52</v>
@@ -8048,7 +8071,7 @@
     </row>
     <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B349" s="54">
         <v>0.23499999999999999</v>
@@ -8062,7 +8085,7 @@
     </row>
     <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B350" s="54">
         <v>0.30499999999999999</v>
@@ -8076,7 +8099,7 @@
     </row>
     <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B351" s="54">
         <v>1.224</v>
@@ -8090,7 +8113,7 @@
     </row>
     <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B352" s="54">
         <v>0.46</v>
@@ -8104,13 +8127,13 @@
     </row>
     <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B353" s="54">
         <v>200</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>28</v>
@@ -8118,7 +8141,7 @@
     </row>
     <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B354" s="54">
         <v>2.46</v>
@@ -8127,12 +8150,12 @@
         <v>4</v>
       </c>
       <c r="D354" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B355" s="54">
         <v>1.079</v>
@@ -8146,7 +8169,7 @@
     </row>
     <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B356" s="54">
         <v>0.91500000000000004</v>
@@ -8160,7 +8183,7 @@
     </row>
     <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B357" s="54">
         <v>0.12</v>
@@ -8174,7 +8197,7 @@
     </row>
     <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B358" s="54">
         <v>0.23</v>
@@ -8188,13 +8211,13 @@
     </row>
     <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B359" s="54">
         <v>0.28000000000000003</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>28</v>
@@ -8202,7 +8225,7 @@
     </row>
     <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B360" s="54">
         <v>0.54700000000000004</v>
@@ -8216,7 +8239,7 @@
     </row>
     <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B361" s="54">
         <v>1.1272727272727272</v>
@@ -8230,7 +8253,7 @@
     </row>
     <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B362" s="54">
         <v>1.3779999999999999</v>
@@ -8244,7 +8267,7 @@
     </row>
     <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B363" s="54">
         <v>0.95</v>
@@ -8258,7 +8281,7 @@
     </row>
     <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B364" s="54">
         <v>0.4</v>
@@ -8272,7 +8295,7 @@
     </row>
     <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B365" s="54">
         <v>0.73299999999999998</v>
@@ -8286,13 +8309,13 @@
     </row>
     <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B366" s="54">
         <v>185</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>28</v>
@@ -8300,7 +8323,7 @@
     </row>
     <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B367" s="54">
         <v>1</v>
@@ -8314,7 +8337,7 @@
     </row>
     <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B368" s="54">
         <v>45</v>
@@ -8328,7 +8351,7 @@
     </row>
     <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B369" s="54">
         <v>0.38800000000000001</v>
@@ -8342,7 +8365,7 @@
     </row>
     <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B370" s="54">
         <v>0.125</v>
@@ -8356,7 +8379,7 @@
     </row>
     <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B371" s="54">
         <v>0.21</v>
@@ -8370,7 +8393,7 @@
     </row>
     <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B372" s="54">
         <v>0.09</v>
@@ -8384,7 +8407,7 @@
     </row>
     <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B373" s="54">
         <v>3.0880000000000001</v>
@@ -8398,13 +8421,13 @@
     </row>
     <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B374" s="54">
         <v>100</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>4</v>
@@ -8412,7 +8435,7 @@
     </row>
     <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B375" s="54">
         <v>14</v>
@@ -8426,7 +8449,7 @@
     </row>
     <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B376" s="54">
         <v>14</v>
@@ -8440,7 +8463,7 @@
     </row>
     <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B377" s="54">
         <v>0.26400000000000001</v>
@@ -8454,7 +8477,7 @@
     </row>
     <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B378" s="54">
         <v>0.23</v>
@@ -8468,7 +8491,7 @@
     </row>
     <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B379" s="54">
         <v>0.54700000000000004</v>
@@ -8482,7 +8505,7 @@
     </row>
     <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B380" s="54">
         <v>0.21</v>
@@ -8496,7 +8519,7 @@
     </row>
     <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B381" s="54">
         <v>0.185</v>
@@ -8510,7 +8533,7 @@
     </row>
     <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B382" s="54">
         <v>1.45</v>
@@ -8524,7 +8547,7 @@
     </row>
     <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B383" s="54">
         <v>0.11899999999999999</v>
@@ -8538,7 +8561,7 @@
     </row>
     <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B384" s="54">
         <v>0.16</v>
@@ -8552,7 +8575,7 @@
     </row>
     <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B385" s="54">
         <v>0.33</v>
@@ -8561,12 +8584,12 @@
         <v>4</v>
       </c>
       <c r="D385" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B386" s="54">
         <v>0.51900000000000002</v>
@@ -8580,7 +8603,7 @@
     </row>
     <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B387" s="54">
         <v>0.69</v>
@@ -8589,12 +8612,12 @@
         <v>4</v>
       </c>
       <c r="D387" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B388" s="54">
         <v>0.3</v>
@@ -8608,7 +8631,7 @@
     </row>
     <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B389" s="54">
         <v>0.67800000000000005</v>
@@ -8622,7 +8645,7 @@
     </row>
     <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B390" s="54">
         <v>0.81799999999999995</v>
@@ -8636,7 +8659,7 @@
     </row>
     <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B391" s="54">
         <v>0.99</v>
@@ -8650,7 +8673,7 @@
     </row>
     <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B392" s="54">
         <v>0.36499999999999999</v>
@@ -8664,7 +8687,7 @@
     </row>
     <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B393" s="54">
         <v>0.64500000000000002</v>
@@ -8678,7 +8701,7 @@
     </row>
     <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B394" s="54">
         <v>0.315</v>
@@ -8692,7 +8715,7 @@
     </row>
     <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B395" s="54">
         <v>0.25</v>
@@ -8706,7 +8729,7 @@
     </row>
     <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B396" s="54">
         <v>0.17</v>
@@ -8720,7 +8743,7 @@
     </row>
     <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B397" s="54">
         <v>0.17599999999999999</v>
@@ -8734,7 +8757,7 @@
     </row>
     <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B398" s="54">
         <v>9.5000000000000001E-2</v>
@@ -8748,7 +8771,7 @@
     </row>
     <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B399" s="54">
         <v>0.308</v>
@@ -8762,7 +8785,7 @@
     </row>
     <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B400" s="54">
         <v>15</v>
@@ -8776,7 +8799,7 @@
     </row>
     <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B401" s="54">
         <v>0.55000000000000004</v>
@@ -8790,7 +8813,7 @@
     </row>
     <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B402" s="54">
         <v>0.24</v>
@@ -8804,7 +8827,7 @@
     </row>
     <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B403" s="54">
         <v>0.22500000000000001</v>
@@ -8818,7 +8841,7 @@
     </row>
     <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B404" s="54">
         <v>0.27500000000000002</v>
@@ -8832,7 +8855,7 @@
     </row>
     <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B405" s="54">
         <v>0.26</v>
@@ -8846,7 +8869,7 @@
     </row>
     <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B406" s="54">
         <v>0.23</v>
@@ -8860,7 +8883,7 @@
     </row>
     <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B407" s="54">
         <v>0.187</v>
@@ -8874,7 +8897,7 @@
     </row>
     <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B408" s="54">
         <v>0.26800000000000002</v>
@@ -8888,7 +8911,7 @@
     </row>
     <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B409" s="54">
         <v>0.186</v>
@@ -8902,7 +8925,7 @@
     </row>
     <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B410" s="54">
         <v>1.26</v>
@@ -8916,7 +8939,7 @@
     </row>
     <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B411" s="54">
         <v>1.01</v>
@@ -8930,7 +8953,7 @@
     </row>
     <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B412" s="54">
         <v>0.76500000000000001</v>
@@ -8944,7 +8967,7 @@
     </row>
     <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B413" s="54">
         <v>1.01</v>
@@ -8958,7 +8981,7 @@
     </row>
     <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B414" s="54">
         <v>0.23899999999999999</v>
@@ -8972,7 +8995,7 @@
     </row>
     <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B415" s="54">
         <v>0.30499999999999999</v>
@@ -8986,7 +9009,7 @@
     </row>
     <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B416" s="54">
         <v>0.185</v>
@@ -9000,7 +9023,7 @@
     </row>
     <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B417" s="54">
         <v>1.05</v>
@@ -9014,7 +9037,7 @@
     </row>
     <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B418" s="54">
         <v>1.1599999999999999</v>
@@ -9028,7 +9051,7 @@
     </row>
     <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B419" s="54">
         <v>1.1599999999999999</v>
@@ -9042,7 +9065,7 @@
     </row>
     <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B420" s="54">
         <v>1</v>
@@ -9056,7 +9079,7 @@
     </row>
     <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B421" s="54">
         <v>0.64500000000000002</v>
@@ -9070,7 +9093,7 @@
     </row>
     <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B422" s="54">
         <v>1350</v>
@@ -9079,18 +9102,18 @@
         <v>32</v>
       </c>
       <c r="D422" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B423" s="54">
         <v>175</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D423" s="6" t="s">
         <v>28</v>
@@ -9098,7 +9121,7 @@
     </row>
     <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B424" s="54">
         <v>55</v>
@@ -9112,7 +9135,7 @@
     </row>
     <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B425" s="54">
         <v>0.11</v>
@@ -9126,7 +9149,7 @@
     </row>
     <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B426" s="54">
         <v>0.17</v>
@@ -9140,7 +9163,7 @@
     </row>
     <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B427" s="54">
         <v>0.12</v>
@@ -9154,7 +9177,7 @@
     </row>
     <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B428" s="54">
         <v>0.189</v>
@@ -9168,7 +9191,7 @@
     </row>
     <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B429" s="54">
         <v>5.37</v>
@@ -9182,7 +9205,7 @@
     </row>
     <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B430" s="54">
         <v>4.351</v>
@@ -9196,7 +9219,7 @@
     </row>
     <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B431" s="54">
         <v>0.8</v>
@@ -9210,7 +9233,7 @@
     </row>
     <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B432" s="54">
         <v>0.74</v>
@@ -9224,7 +9247,7 @@
     </row>
     <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B433" s="54">
         <v>0.55000000000000004</v>
@@ -9238,7 +9261,7 @@
     </row>
     <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B434" s="54">
         <v>2.2000000000000002</v>
@@ -9252,7 +9275,7 @@
     </row>
     <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B435" s="54">
         <v>3.42</v>
@@ -9266,7 +9289,7 @@
     </row>
     <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B436" s="54">
         <v>0.106</v>
@@ -9280,7 +9303,7 @@
     </row>
     <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B437" s="54">
         <v>0.15</v>
@@ -9294,7 +9317,7 @@
     </row>
     <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B438" s="54">
         <v>0.77600000000000002</v>
@@ -9308,7 +9331,7 @@
     </row>
     <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B439" s="54">
         <v>1.05</v>
@@ -9322,7 +9345,7 @@
     </row>
     <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B440" s="54">
         <v>0.2</v>
@@ -9336,7 +9359,7 @@
     </row>
     <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B441" s="54">
         <v>0.18</v>
@@ -9350,7 +9373,7 @@
     </row>
     <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B442" s="54">
         <v>0.18</v>
@@ -9364,7 +9387,7 @@
     </row>
     <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B443" s="54">
         <v>0.86</v>
@@ -9378,7 +9401,7 @@
     </row>
     <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B444" s="54">
         <v>1.2</v>
@@ -9392,7 +9415,7 @@
     </row>
     <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B445" s="54">
         <v>55</v>
@@ -9406,7 +9429,7 @@
     </row>
     <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B446" s="54">
         <v>0.35</v>
@@ -9420,7 +9443,7 @@
     </row>
     <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B447" s="54">
         <v>1.4379999999999999</v>
@@ -9434,7 +9457,7 @@
     </row>
     <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B448" s="54">
         <v>2.5499999999999998</v>
@@ -9448,7 +9471,7 @@
     </row>
     <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B449" s="54">
         <v>0.2</v>
@@ -9462,7 +9485,7 @@
     </row>
     <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B450" s="54">
         <v>9.5000000000000001E-2</v>
@@ -9476,7 +9499,7 @@
     </row>
     <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B451" s="54">
         <v>0.28499999999999998</v>
@@ -9490,7 +9513,7 @@
     </row>
     <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B452" s="54">
         <v>0.2</v>
@@ -9504,7 +9527,7 @@
     </row>
     <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B453" s="54">
         <v>1</v>
@@ -9518,7 +9541,7 @@
     </row>
     <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B454" s="54">
         <v>2.5680000000000001</v>
@@ -9532,7 +9555,7 @@
     </row>
     <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B455" s="54">
         <v>4.1500000000000004</v>
@@ -9546,7 +9569,7 @@
     </row>
     <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B456" s="54">
         <v>0.6</v>
@@ -9560,7 +9583,7 @@
     </row>
     <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B457" s="54">
         <v>0.17799999999999999</v>
@@ -9574,7 +9597,7 @@
     </row>
     <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B458" s="54">
         <v>0.17799999999999999</v>
@@ -9588,7 +9611,7 @@
     </row>
     <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B459" s="54">
         <v>0.318</v>
@@ -9602,7 +9625,7 @@
     </row>
     <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B460" s="54">
         <v>0.3</v>
@@ -9616,7 +9639,7 @@
     </row>
     <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B461" s="54">
         <v>0.14099999999999999</v>
@@ -9630,7 +9653,7 @@
     </row>
     <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B462" s="54">
         <v>0.189</v>
@@ -9644,7 +9667,7 @@
     </row>
     <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B463" s="54">
         <v>8.5000000000000006E-2</v>
@@ -9658,7 +9681,7 @@
     </row>
     <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B464" s="54">
         <v>0.2</v>
@@ -9672,7 +9695,7 @@
     </row>
     <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B465" s="54">
         <v>0.34499999999999997</v>
@@ -9686,7 +9709,7 @@
     </row>
     <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B466" s="54">
         <v>0.08</v>
@@ -9700,7 +9723,7 @@
     </row>
     <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B467" s="54">
         <v>0.08</v>
@@ -9714,13 +9737,13 @@
     </row>
     <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B468" s="54">
         <v>385</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D468" s="6" t="s">
         <v>28</v>
@@ -9728,7 +9751,7 @@
     </row>
     <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B469" s="54">
         <v>0.46</v>
@@ -9742,7 +9765,7 @@
     </row>
     <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B470" s="54">
         <v>0.441</v>
@@ -9756,7 +9779,7 @@
     </row>
     <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B471" s="54">
         <v>0.20399999999999999</v>
@@ -9770,7 +9793,7 @@
     </row>
     <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B472" s="54">
         <v>0.18</v>
@@ -9784,7 +9807,7 @@
     </row>
     <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B473" s="54">
         <v>0.13200000000000001</v>
@@ -9798,7 +9821,7 @@
     </row>
     <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B474" s="54">
         <v>0.312</v>
@@ -9812,7 +9835,7 @@
     </row>
     <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B475" s="54">
         <v>40</v>
@@ -9826,7 +9849,7 @@
     </row>
     <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B476" s="54">
         <v>0.11</v>
@@ -9840,7 +9863,7 @@
     </row>
     <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B477" s="54">
         <v>1.55</v>
@@ -9854,7 +9877,7 @@
     </row>
     <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B478" s="54">
         <v>12.3</v>
@@ -9868,7 +9891,7 @@
     </row>
     <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B479" s="54">
         <v>7.4999999999999997E-2</v>
@@ -9882,7 +9905,7 @@
     </row>
     <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B480" s="54">
         <v>0.43</v>
@@ -9891,12 +9914,12 @@
         <v>4</v>
       </c>
       <c r="D480" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B481" s="54">
         <v>0.43</v>
@@ -9905,12 +9928,12 @@
         <v>4</v>
       </c>
       <c r="D481" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B482" s="54">
         <v>0.43</v>
@@ -9919,12 +9942,12 @@
         <v>4</v>
       </c>
       <c r="D482" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B483" s="54">
         <v>0.15</v>
@@ -9933,12 +9956,12 @@
         <v>4</v>
       </c>
       <c r="D483" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B484" s="54">
         <v>0.32</v>
@@ -9947,12 +9970,12 @@
         <v>4</v>
       </c>
       <c r="D484" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B485" s="54">
         <v>0.22</v>
@@ -9961,12 +9984,12 @@
         <v>4</v>
       </c>
       <c r="D485" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B486" s="54">
         <v>0.27500000000000002</v>
@@ -9975,12 +9998,12 @@
         <v>4</v>
       </c>
       <c r="D486" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B487" s="54">
         <v>0.28000000000000003</v>
@@ -9989,12 +10012,12 @@
         <v>4</v>
       </c>
       <c r="D487" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B488" s="54">
         <v>0.28000000000000003</v>
@@ -10003,12 +10026,12 @@
         <v>4</v>
       </c>
       <c r="D488" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B489" s="54">
         <v>0.3</v>
@@ -10017,12 +10040,12 @@
         <v>4</v>
       </c>
       <c r="D489" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B490" s="54">
         <v>0.22500000000000001</v>
@@ -10031,12 +10054,12 @@
         <v>4</v>
       </c>
       <c r="D490" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B491" s="54">
         <v>0.76700000000000002</v>
@@ -10045,12 +10068,12 @@
         <v>4</v>
       </c>
       <c r="D491" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B492" s="54">
         <v>1.014</v>
@@ -10059,12 +10082,12 @@
         <v>4</v>
       </c>
       <c r="D492" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B493" s="54">
         <v>0.14000000000000001</v>
@@ -10078,7 +10101,7 @@
     </row>
     <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B494" s="54">
         <v>0.443</v>
@@ -10092,7 +10115,7 @@
     </row>
     <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B495" s="54">
         <v>0.29599999999999999</v>
@@ -10106,7 +10129,7 @@
     </row>
     <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B496" s="54">
         <v>1.079</v>
@@ -10120,13 +10143,13 @@
     </row>
     <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B497" s="54">
         <v>1125</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D497" s="6" t="s">
         <v>5</v>
@@ -10134,7 +10157,7 @@
     </row>
     <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B498" s="54">
         <v>0.53</v>
@@ -10148,7 +10171,7 @@
     </row>
     <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B499" s="54">
         <v>0.53</v>
@@ -10162,7 +10185,7 @@
     </row>
     <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B500" s="54">
         <v>0.53</v>
@@ -10176,7 +10199,7 @@
     </row>
     <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B501" s="54">
         <v>0.53</v>
@@ -10190,7 +10213,7 @@
     </row>
     <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B502" s="54">
         <v>0.53</v>
@@ -10204,7 +10227,7 @@
     </row>
     <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B503" s="54">
         <v>4</v>
@@ -10213,12 +10236,12 @@
         <v>32</v>
       </c>
       <c r="D503" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B504" s="54">
         <v>0.08</v>
@@ -10232,7 +10255,7 @@
     </row>
     <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B505" s="54">
         <v>0.56499999999999995</v>
@@ -10246,7 +10269,7 @@
     </row>
     <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B506" s="54">
         <v>0.84</v>
@@ -10260,7 +10283,7 @@
     </row>
     <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B507" s="54">
         <v>0.29599999999999999</v>
@@ -10274,7 +10297,7 @@
     </row>
     <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B508" s="54">
         <v>1.02</v>
@@ -10288,7 +10311,7 @@
     </row>
     <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B509" s="54">
         <v>6.8000000000000005E-2</v>
@@ -10302,7 +10325,7 @@
     </row>
     <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B510" s="54">
         <v>0.24</v>
@@ -10316,7 +10339,7 @@
     </row>
     <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B511" s="54">
         <v>35</v>
@@ -10330,7 +10353,7 @@
     </row>
     <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B512" s="54">
         <v>0.5</v>
@@ -10344,7 +10367,7 @@
     </row>
     <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B513" s="54">
         <v>1.7789999999999999</v>
@@ -10358,7 +10381,7 @@
     </row>
     <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B514" s="54">
         <v>0.13</v>
@@ -10372,7 +10395,7 @@
     </row>
     <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B515" s="54">
         <v>1</v>
@@ -10386,7 +10409,7 @@
     </row>
     <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B516" s="54">
         <v>0.04</v>
@@ -10400,7 +10423,7 @@
     </row>
     <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B517" s="54">
         <v>5.5E-2</v>
@@ -10414,7 +10437,7 @@
     </row>
     <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B518" s="54">
         <v>60</v>
@@ -10428,7 +10451,7 @@
     </row>
     <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B519" s="54">
         <v>60</v>
@@ -10442,7 +10465,7 @@
     </row>
     <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B520" s="54">
         <v>0.59</v>
@@ -10451,12 +10474,12 @@
         <v>4</v>
       </c>
       <c r="D520" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B521" s="54">
         <v>0.08</v>
@@ -10470,7 +10493,7 @@
     </row>
     <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B522" s="54">
         <v>2.5000000000000001E-2</v>
@@ -10484,7 +10507,7 @@
     </row>
     <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B523" s="54">
         <v>0.39</v>
@@ -10498,7 +10521,7 @@
     </row>
     <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B524" s="54">
         <v>0.91</v>
@@ -10512,7 +10535,7 @@
     </row>
     <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B525" s="54">
         <v>0.91</v>
@@ -10526,7 +10549,7 @@
     </row>
     <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B526" s="54">
         <v>0.91</v>
@@ -10540,7 +10563,7 @@
     </row>
     <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B527" s="54">
         <v>0.71</v>
@@ -10554,7 +10577,7 @@
     </row>
     <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B528" s="54">
         <v>0.71</v>
@@ -10568,7 +10591,7 @@
     </row>
     <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B529" s="54">
         <v>0.71</v>
@@ -10582,7 +10605,7 @@
     </row>
     <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B530" s="54">
         <v>0.71</v>
@@ -10596,7 +10619,7 @@
     </row>
     <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B531" s="54">
         <v>0.91</v>
@@ -10610,7 +10633,7 @@
     </row>
     <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B532" s="54">
         <v>0.71</v>
@@ -10624,7 +10647,7 @@
     </row>
     <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B533" s="54">
         <v>0.71</v>
@@ -10638,7 +10661,7 @@
     </row>
     <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B534" s="54">
         <v>0.91</v>
@@ -10652,7 +10675,7 @@
     </row>
     <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B535" s="54">
         <v>0.91</v>
@@ -10666,7 +10689,7 @@
     </row>
     <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B536" s="54">
         <v>0.71</v>
@@ -10680,7 +10703,7 @@
     </row>
     <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B537" s="54">
         <v>0.71</v>
@@ -10694,7 +10717,7 @@
     </row>
     <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B538" s="54">
         <v>0.91</v>
@@ -10708,7 +10731,7 @@
     </row>
     <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B539" s="54">
         <v>0.91</v>
@@ -10722,7 +10745,7 @@
     </row>
     <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B540" s="54">
         <v>0.91</v>
@@ -10736,7 +10759,7 @@
     </row>
     <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B541" s="54">
         <v>0.91</v>
@@ -10750,7 +10773,7 @@
     </row>
     <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B542" s="54">
         <v>0.91</v>
@@ -10764,7 +10787,7 @@
     </row>
     <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B543" s="54">
         <v>0.71</v>
@@ -10778,7 +10801,7 @@
     </row>
     <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B544" s="54">
         <v>0.55000000000000004</v>
@@ -10792,7 +10815,7 @@
     </row>
     <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B545" s="54">
         <v>0.48</v>
@@ -10806,7 +10829,7 @@
     </row>
     <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B546" s="54">
         <v>0.76700000000000002</v>
@@ -10820,7 +10843,7 @@
     </row>
     <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B547" s="54">
         <v>0.26700000000000002</v>
@@ -10834,7 +10857,7 @@
     </row>
     <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B548" s="54">
         <v>7.0000000000000007E-2</v>
@@ -10848,7 +10871,7 @@
     </row>
     <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B549" s="54">
         <v>0.79600000000000004</v>
@@ -10862,7 +10885,7 @@
     </row>
     <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B550" s="54">
         <v>1.087</v>
@@ -10876,7 +10899,7 @@
     </row>
     <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B551" s="54">
         <v>1.091</v>
@@ -10890,7 +10913,7 @@
     </row>
     <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B552" s="54">
         <v>0.13</v>
@@ -10904,7 +10927,7 @@
     </row>
     <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B553" s="54">
         <v>0.28000000000000003</v>
@@ -10918,7 +10941,7 @@
     </row>
     <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B554" s="54">
         <v>1</v>
@@ -10932,7 +10955,7 @@
     </row>
     <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B555" s="54">
         <v>0.46500000000000002</v>
@@ -10946,7 +10969,7 @@
     </row>
     <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B556" s="54">
         <v>1.212</v>
@@ -10960,7 +10983,7 @@
     </row>
     <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B557" s="54">
         <v>0.125</v>
@@ -10974,7 +10997,7 @@
     </row>
     <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B558" s="54">
         <v>0.186</v>
@@ -10988,7 +11011,7 @@
     </row>
     <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B559" s="54">
         <v>0.29199999999999998</v>
@@ -11002,7 +11025,7 @@
     </row>
     <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B560" s="54">
         <v>0.105</v>
@@ -11016,7 +11039,7 @@
     </row>
     <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B561" s="54">
         <v>0.13</v>
@@ -11030,7 +11053,7 @@
     </row>
     <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B562" s="54">
         <v>0.67100000000000004</v>
@@ -11044,7 +11067,7 @@
     </row>
     <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B563" s="54">
         <v>0.61</v>
@@ -11058,7 +11081,7 @@
     </row>
     <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B564" s="54">
         <v>37</v>
@@ -11072,7 +11095,7 @@
     </row>
     <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B565" s="54">
         <v>0.08</v>
@@ -11086,7 +11109,7 @@
     </row>
     <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B566" s="54">
         <v>0.65500000000000003</v>
@@ -11100,7 +11123,7 @@
     </row>
     <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B567" s="54">
         <v>1.79</v>
@@ -11114,7 +11137,7 @@
     </row>
     <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B568" s="54">
         <v>0.36</v>
@@ -11128,7 +11151,7 @@
     </row>
     <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B569" s="54">
         <v>0.5</v>
@@ -11142,7 +11165,7 @@
     </row>
     <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B570" s="54">
         <v>1.07</v>
@@ -11156,7 +11179,7 @@
     </row>
     <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B571" s="54">
         <v>0.11</v>
@@ -11170,7 +11193,7 @@
     </row>
     <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B572" s="54">
         <v>0.505</v>
@@ -11184,7 +11207,7 @@
     </row>
     <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B573" s="54">
         <v>0.13800000000000001</v>
@@ -11198,7 +11221,7 @@
     </row>
     <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B574" s="54">
         <v>0.26100000000000001</v>
@@ -11212,7 +11235,7 @@
     </row>
     <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B575" s="54">
         <v>0.38400000000000001</v>
@@ -11226,7 +11249,7 @@
     </row>
     <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B576" s="54">
         <v>0.65</v>
@@ -11240,7 +11263,7 @@
     </row>
     <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B577" s="54">
         <v>7.0000000000000007E-2</v>
@@ -11254,7 +11277,7 @@
     </row>
     <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B578" s="54">
         <v>0.09</v>
@@ -11268,7 +11291,7 @@
     </row>
     <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B579" s="54">
         <v>1.8859999999999999</v>
@@ -11282,7 +11305,7 @@
     </row>
     <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B580" s="54">
         <v>0.33</v>
@@ -11296,7 +11319,7 @@
     </row>
     <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B581" s="54">
         <v>0.24</v>
@@ -11310,7 +11333,7 @@
     </row>
     <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B582" s="54">
         <v>0.95</v>
@@ -11324,7 +11347,7 @@
     </row>
     <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B583" s="54">
         <v>0.25</v>
@@ -11338,7 +11361,7 @@
     </row>
     <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B584" s="54">
         <v>0.15</v>
@@ -11352,7 +11375,7 @@
     </row>
     <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B585" s="54">
         <v>0.31</v>
@@ -11366,7 +11389,7 @@
     </row>
     <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B586" s="54">
         <v>1.1499999999999999</v>
@@ -11380,7 +11403,7 @@
     </row>
     <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B587" s="54">
         <v>1.05</v>
@@ -11394,7 +11417,7 @@
     </row>
     <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B588" s="54">
         <v>2.0499999999999998</v>
@@ -11408,7 +11431,7 @@
     </row>
     <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B589" s="54">
         <v>0.27</v>
@@ -11422,7 +11445,7 @@
     </row>
     <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B590" s="54">
         <v>1.5720000000000001</v>
@@ -11436,7 +11459,7 @@
     </row>
     <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B591" s="54">
         <v>0.13500000000000001</v>
@@ -11450,7 +11473,7 @@
     </row>
     <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B592" s="54">
         <v>0.19900000000000001</v>
@@ -11464,7 +11487,7 @@
     </row>
     <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B593" s="54">
         <v>0.3</v>
@@ -11478,7 +11501,7 @@
     </row>
     <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B594" s="54">
         <v>0.13</v>
@@ -11492,7 +11515,7 @@
     </row>
     <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B595" s="54">
         <v>0.25</v>
@@ -11506,7 +11529,7 @@
     </row>
     <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B596" s="54">
         <v>0.17699999999999999</v>
@@ -11520,7 +11543,7 @@
     </row>
     <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B597" s="54">
         <v>0.12</v>
@@ -11534,7 +11557,7 @@
     </row>
     <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B598" s="54">
         <v>1.347</v>
@@ -11548,7 +11571,7 @@
     </row>
     <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B599" s="54">
         <v>45</v>
@@ -11562,7 +11585,7 @@
     </row>
     <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B600" s="54">
         <v>0.84699999999999998</v>
@@ -11576,7 +11599,7 @@
     </row>
     <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B601" s="54">
         <v>0.5</v>
@@ -11590,7 +11613,7 @@
     </row>
     <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B602" s="54">
         <v>0.5</v>
@@ -11604,7 +11627,7 @@
     </row>
     <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B603" s="54">
         <v>0.35</v>
@@ -11618,7 +11641,7 @@
     </row>
     <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B604" s="54">
         <v>0.23499999999999999</v>
@@ -11632,7 +11655,7 @@
     </row>
     <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B605" s="54">
         <v>0.65</v>
@@ -11646,13 +11669,13 @@
     </row>
     <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B606" s="54">
         <v>220</v>
       </c>
       <c r="C606" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D606" s="6" t="s">
         <v>28</v>
@@ -11660,7 +11683,7 @@
     </row>
     <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B607" s="54">
         <v>1.7230000000000001</v>
@@ -11674,7 +11697,7 @@
     </row>
     <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B608" s="54">
         <v>0.45</v>
@@ -11688,7 +11711,7 @@
     </row>
     <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B609" s="54">
         <v>2.3119999999999998</v>
@@ -11702,7 +11725,7 @@
     </row>
     <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B610" s="54">
         <v>1.0529999999999999</v>
@@ -11716,7 +11739,7 @@
     </row>
     <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B611" s="54">
         <v>0.35499999999999998</v>
@@ -11730,7 +11753,7 @@
     </row>
     <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B612" s="54">
         <v>0.25</v>
@@ -11744,7 +11767,7 @@
     </row>
     <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B613" s="54">
         <v>0.52900000000000003</v>
@@ -11758,7 +11781,7 @@
     </row>
     <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B614" s="54">
         <v>0.5</v>
@@ -11772,7 +11795,7 @@
     </row>
     <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B615" s="54">
         <v>5.2999999999999999E-2</v>
@@ -11786,7 +11809,7 @@
     </row>
     <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B616" s="54">
         <v>1.2</v>
@@ -11800,7 +11823,7 @@
     </row>
     <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B617" s="54">
         <v>0.05</v>
@@ -11814,7 +11837,7 @@
     </row>
     <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B618" s="54">
         <v>0.8</v>
@@ -11828,7 +11851,7 @@
     </row>
     <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B619" s="54">
         <v>0.46</v>
@@ -11842,7 +11865,7 @@
     </row>
     <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B620" s="54">
         <v>0.06</v>
@@ -11856,13 +11879,13 @@
     </row>
     <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B621" s="54">
         <v>0.32</v>
       </c>
       <c r="C621" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D621" s="6" t="s">
         <v>7</v>
@@ -11870,7 +11893,7 @@
     </row>
     <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B622" s="54">
         <v>0.25</v>
@@ -11884,7 +11907,7 @@
     </row>
     <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B623" s="54">
         <v>0.52</v>
@@ -11898,7 +11921,7 @@
     </row>
     <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B624" s="54">
         <v>3.3580000000000001</v>
@@ -11912,7 +11935,7 @@
     </row>
     <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B625" s="54">
         <v>2.1</v>
@@ -11926,7 +11949,7 @@
     </row>
     <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B626" s="54">
         <v>1.35</v>
@@ -11940,7 +11963,7 @@
     </row>
     <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B627" s="54">
         <v>1.65</v>
@@ -11954,7 +11977,7 @@
     </row>
     <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B628" s="54">
         <v>0.39</v>
@@ -11968,7 +11991,7 @@
     </row>
     <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B629" s="54">
         <v>0.37</v>
@@ -11982,7 +12005,7 @@
     </row>
     <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B630" s="54">
         <v>0.39</v>
@@ -11996,7 +12019,7 @@
     </row>
     <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B631" s="54">
         <v>1.4390000000000001</v>
@@ -12010,7 +12033,7 @@
     </row>
     <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B632" s="54">
         <v>2</v>
@@ -12024,7 +12047,7 @@
     </row>
     <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B633" s="54">
         <v>0.74</v>
@@ -12038,7 +12061,7 @@
     </row>
     <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B634" s="54">
         <v>0.74</v>
@@ -12052,7 +12075,7 @@
     </row>
     <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B635" s="54">
         <v>0.9</v>
@@ -12066,7 +12089,7 @@
     </row>
     <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B636" s="54">
         <v>450</v>
@@ -12080,7 +12103,7 @@
     </row>
     <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B637" s="54">
         <v>0.3</v>
@@ -12094,7 +12117,7 @@
     </row>
     <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B638" s="54">
         <v>0.25</v>
@@ -12103,32 +12126,32 @@
         <v>4</v>
       </c>
       <c r="D638" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B639" s="54">
         <v>0.38</v>
       </c>
       <c r="C639" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D639" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B640" s="54">
         <v>0.22</v>
       </c>
       <c r="C640" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D640" s="6" t="s">
         <v>10</v>
@@ -12136,7 +12159,7 @@
     </row>
     <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B641" s="54">
         <v>1200</v>
@@ -12150,13 +12173,13 @@
     </row>
     <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B642" s="54">
         <v>0.19</v>
       </c>
       <c r="C642" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D642" s="6" t="s">
         <v>10</v>
@@ -12164,13 +12187,13 @@
     </row>
     <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B643" s="54">
         <v>0.82399999999999995</v>
       </c>
       <c r="C643" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D643" s="6" t="s">
         <v>7</v>
@@ -12178,13 +12201,13 @@
     </row>
     <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B644" s="54">
         <v>170</v>
       </c>
       <c r="C644" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D644" s="6" t="s">
         <v>4</v>
@@ -12192,7 +12215,7 @@
     </row>
     <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B645" s="54">
         <v>0.15</v>
@@ -12206,7 +12229,7 @@
     </row>
     <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B646" s="54">
         <v>0.08</v>
@@ -12220,7 +12243,7 @@
     </row>
     <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B647" s="54">
         <v>65</v>
@@ -12234,7 +12257,7 @@
     </row>
     <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B648" s="54">
         <v>0.3</v>
@@ -12248,7 +12271,7 @@
     </row>
     <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B649" s="54">
         <v>0.16</v>
@@ -12262,7 +12285,7 @@
     </row>
     <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B650" s="54">
         <v>0.57199999999999995</v>
@@ -12276,7 +12299,7 @@
     </row>
     <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B651" s="54">
         <v>0.28599999999999998</v>
@@ -12290,7 +12313,7 @@
     </row>
     <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B652" s="54">
         <v>1.7</v>
@@ -12304,7 +12327,7 @@
     </row>
     <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B653" s="54">
         <v>0.32</v>
@@ -12318,7 +12341,7 @@
     </row>
     <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B654" s="54">
         <v>83</v>
@@ -12332,7 +12355,7 @@
     </row>
     <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B655" s="54">
         <v>0.6</v>
@@ -12341,12 +12364,12 @@
         <v>4</v>
       </c>
       <c r="D655" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B656" s="54">
         <v>0.27500000000000002</v>
@@ -12360,7 +12383,7 @@
     </row>
     <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B657" s="54">
         <v>0.27500000000000002</v>
@@ -12374,7 +12397,7 @@
     </row>
     <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B658" s="54">
         <v>0.9</v>
@@ -12388,7 +12411,7 @@
     </row>
     <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B659" s="55">
         <v>0.6</v>
@@ -12402,7 +12425,7 @@
     </row>
     <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B660" s="54">
         <v>0.75</v>
@@ -12416,7 +12439,7 @@
     </row>
     <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B661" s="54">
         <v>0.3</v>
@@ -12430,7 +12453,7 @@
     </row>
     <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B662" s="56">
         <v>0.185</v>
@@ -12444,7 +12467,7 @@
     </row>
     <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B663" s="56">
         <v>0.12</v>
@@ -12458,7 +12481,7 @@
     </row>
     <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B664" s="56">
         <v>1.2649999999999999</v>
@@ -12472,7 +12495,7 @@
     </row>
     <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B665" s="56">
         <v>1.84</v>
@@ -12486,7 +12509,7 @@
     </row>
     <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B666" s="54">
         <v>0.74814814814814812</v>
@@ -12500,7 +12523,7 @@
     </row>
     <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B667" s="56">
         <v>0.15</v>
@@ -12514,7 +12537,7 @@
     </row>
     <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B668" s="56">
         <v>0.47199999999999998</v>
@@ -12528,7 +12551,7 @@
     </row>
     <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B669" s="54">
         <v>1.6</v>
@@ -12542,7 +12565,7 @@
     </row>
     <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B670" s="54">
         <v>1.6</v>
@@ -12556,7 +12579,7 @@
     </row>
     <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B671" s="54">
         <v>1.6</v>
@@ -12570,7 +12593,7 @@
     </row>
     <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B672" s="56">
         <v>2.8639999999999999</v>
@@ -12584,7 +12607,7 @@
     </row>
     <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B673" s="56">
         <v>1.579</v>
@@ -12598,7 +12621,7 @@
     </row>
     <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A674" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B674" s="54">
         <v>1.94</v>
@@ -12612,13 +12635,13 @@
     </row>
     <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="50" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B675" s="55">
         <v>0.11700000000000001</v>
       </c>
       <c r="C675" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D675" s="13" t="s">
         <v>5</v>
@@ -12626,13 +12649,13 @@
     </row>
     <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="50" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B676" s="55">
         <v>1.2</v>
       </c>
       <c r="C676" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D676" s="13" t="s">
         <v>5</v>
@@ -12640,7 +12663,7 @@
     </row>
     <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="50" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B677" s="55">
         <v>0.27500000000000002</v>
@@ -12654,13 +12677,13 @@
     </row>
     <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="50" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B678" s="55">
         <v>45</v>
       </c>
       <c r="C678" s="13" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D678" s="13" t="s">
         <v>10</v>
@@ -12668,7 +12691,7 @@
     </row>
     <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B679" s="54">
         <v>3</v>
@@ -12682,7 +12705,7 @@
     </row>
     <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A680" s="51" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B680" s="54">
         <v>0.22</v>
@@ -12696,7 +12719,7 @@
     </row>
     <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="51" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B681" s="54">
         <v>0.17</v>
@@ -12710,7 +12733,7 @@
     </row>
     <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A682" s="59" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B682" s="58">
         <v>0.91</v>
@@ -12724,7 +12747,7 @@
     </row>
     <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A683" s="61" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B683" s="62">
         <v>0.38</v>
@@ -12733,26 +12756,26 @@
         <v>1</v>
       </c>
       <c r="D683" s="63" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A684" s="61" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B684" s="62">
         <v>0.22</v>
       </c>
       <c r="C684" s="63" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D684" s="63" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A685" s="61" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B685" s="62">
         <v>0.59</v>
@@ -12761,12 +12784,12 @@
         <v>32</v>
       </c>
       <c r="D685" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A686" s="61" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B686" s="62">
         <v>3.1</v>
@@ -12775,12 +12798,12 @@
         <v>32</v>
       </c>
       <c r="D686" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A687" s="61" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B687" s="62">
         <v>6.9</v>
@@ -12789,12 +12812,12 @@
         <v>32</v>
       </c>
       <c r="D687" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A688" s="61" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B688" s="62">
         <v>6.3</v>
@@ -12803,18 +12826,18 @@
         <v>32</v>
       </c>
       <c r="D688" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A689" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B689" s="64">
         <v>0.499</v>
       </c>
       <c r="C689" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D689" s="6" t="s">
         <v>10</v>
@@ -12822,7 +12845,7 @@
     </row>
     <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A690" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B690" s="64">
         <v>0.4</v>
@@ -12836,7 +12859,7 @@
     </row>
     <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A691" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B691" s="64">
         <v>0.36</v>
@@ -12850,7 +12873,7 @@
     </row>
     <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B692" s="64">
         <v>0.2</v>
@@ -12864,7 +12887,7 @@
     </row>
     <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A693" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B693" s="64">
         <v>0.25</v>
@@ -12878,7 +12901,7 @@
     </row>
     <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="50" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B694" s="64">
         <v>0.64</v>
@@ -12892,7 +12915,7 @@
     </row>
     <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A695" s="50" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B695" s="64">
         <v>0.85</v>
@@ -12906,7 +12929,7 @@
     </row>
     <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A696" s="50" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B696" s="64">
         <v>0.15</v>
@@ -12920,7 +12943,7 @@
     </row>
     <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A697" s="65" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B697" s="66">
         <v>1.3</v>
@@ -12929,26 +12952,26 @@
         <v>32</v>
       </c>
       <c r="D697" s="67" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A698" s="68" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B698" s="69">
         <v>0</v>
       </c>
       <c r="C698" s="63" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D698" s="63" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A699" s="68" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B699" s="69">
         <v>3</v>
@@ -12957,12 +12980,12 @@
         <v>32</v>
       </c>
       <c r="D699" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A700" s="68" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B700" s="69">
         <v>2</v>
@@ -12971,12 +12994,12 @@
         <v>32</v>
       </c>
       <c r="D700" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A701" s="68" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B701" s="69">
         <v>1.6</v>
@@ -12985,12 +13008,12 @@
         <v>32</v>
       </c>
       <c r="D701" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A702" s="68" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B702" s="69">
         <v>0.25</v>
@@ -12999,12 +13022,12 @@
         <v>32</v>
       </c>
       <c r="D702" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A703" s="68" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B703" s="69">
         <v>0.4</v>
@@ -13013,12 +13036,12 @@
         <v>32</v>
       </c>
       <c r="D703" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A704" s="68" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B704" s="69">
         <v>4</v>
@@ -13027,12 +13050,12 @@
         <v>32</v>
       </c>
       <c r="D704" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A705" s="70" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B705" s="71">
         <v>1</v>
@@ -13041,12 +13064,12 @@
         <v>32</v>
       </c>
       <c r="D705" s="72" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A706" s="68" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B706" s="69">
         <v>26</v>
@@ -13055,12 +13078,12 @@
         <v>32</v>
       </c>
       <c r="D706" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A707" s="68" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B707" s="69">
         <v>26</v>
@@ -13069,12 +13092,12 @@
         <v>32</v>
       </c>
       <c r="D707" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A708" s="68" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B708" s="69">
         <v>26</v>
@@ -13083,7 +13106,21 @@
         <v>32</v>
       </c>
       <c r="D708" s="63" t="s">
-        <v>712</v>
+        <v>711</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A709" s="73" t="s">
+        <v>736</v>
+      </c>
+      <c r="B709" s="74">
+        <v>6.06</v>
+      </c>
+      <c r="C709" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D709" s="75" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84BD58D-EBFB-4A00-BAA6-668CED937B55}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474E7A57-9C60-4BD7-83C6-3512B807B814}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="742">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2244,6 +2244,18 @@
   </si>
   <si>
     <t>Canned Tuna (per gram)</t>
+  </si>
+  <si>
+    <t>Cooked Chicken Breast - production</t>
+  </si>
+  <si>
+    <t>Beef Filling - production</t>
+  </si>
+  <si>
+    <t>Tuna Filling - production</t>
+  </si>
+  <si>
+    <t>Chicken Filling - production</t>
   </si>
 </sst>
 </file>
@@ -3199,7 +3211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D709"/>
+  <dimension ref="A1:D713"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -13123,6 +13135,59 @@
         <v>463</v>
       </c>
     </row>
+    <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A710" s="73" t="s">
+        <v>738</v>
+      </c>
+      <c r="B710" s="74">
+        <v>0.48</v>
+      </c>
+      <c r="C710" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D710" s="75" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A711" s="73" t="s">
+        <v>739</v>
+      </c>
+      <c r="B711" s="74">
+        <v>0.37</v>
+      </c>
+      <c r="C711" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D711" s="75" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A712" s="73" t="s">
+        <v>740</v>
+      </c>
+      <c r="B712" s="74">
+        <v>0.26</v>
+      </c>
+      <c r="C712" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D712" s="75" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A713" s="73" t="s">
+        <v>741</v>
+      </c>
+      <c r="C713" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D713" s="75" t="s">
+        <v>463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474E7A57-9C60-4BD7-83C6-3512B807B814}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F8EA07-EEE6-43C0-A287-C16C6B20E34E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -2439,7 +2439,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -2693,22 +2693,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2886,15 +2875,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="19" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -13122,69 +13102,72 @@
       </c>
     </row>
     <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A709" s="73" t="s">
+      <c r="A709" s="68" t="s">
         <v>736</v>
       </c>
-      <c r="B709" s="74">
+      <c r="B709" s="69">
         <v>6.06</v>
       </c>
-      <c r="C709" s="75" t="s">
+      <c r="C709" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D709" s="75" t="s">
+      <c r="D709" s="63" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A710" s="73" t="s">
+      <c r="A710" s="68" t="s">
         <v>738</v>
       </c>
-      <c r="B710" s="74">
+      <c r="B710" s="69">
         <v>0.48</v>
       </c>
-      <c r="C710" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="D710" s="75" t="s">
+      <c r="C710" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D710" s="63" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A711" s="73" t="s">
+      <c r="A711" s="68" t="s">
         <v>739</v>
       </c>
-      <c r="B711" s="74">
-        <v>0.37</v>
-      </c>
-      <c r="C711" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="D711" s="75" t="s">
+      <c r="B711" s="69">
+        <v>0.54</v>
+      </c>
+      <c r="C711" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D711" s="63" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A712" s="73" t="s">
+      <c r="A712" s="68" t="s">
         <v>740</v>
       </c>
-      <c r="B712" s="74">
-        <v>0.26</v>
-      </c>
-      <c r="C712" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="D712" s="75" t="s">
+      <c r="B712" s="69">
+        <v>0.38</v>
+      </c>
+      <c r="C712" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D712" s="63" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A713" s="73" t="s">
+      <c r="A713" s="68" t="s">
         <v>741</v>
       </c>
-      <c r="C713" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="D713" s="75" t="s">
+      <c r="B713" s="69">
+        <v>0.39</v>
+      </c>
+      <c r="C713" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D713" s="63" t="s">
         <v>463</v>
       </c>
     </row>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F8EA07-EEE6-43C0-A287-C16C6B20E34E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF834B0-B6C1-4007-ACBD-AB095B513C1C}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="28800" windowHeight="11235" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="753">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2256,6 +2256,39 @@
   </si>
   <si>
     <t>Chicken Filling - production</t>
+  </si>
+  <si>
+    <t>Masa Picha -Ham &amp; Cheese</t>
+  </si>
+  <si>
+    <t>Masa Picha -All Meat</t>
+  </si>
+  <si>
+    <t>Biscoff - Sauce</t>
+  </si>
+  <si>
+    <t>Cassava Cups - Cheese</t>
+  </si>
+  <si>
+    <t>Cassava Cups - Corn</t>
+  </si>
+  <si>
+    <t>Cassava Cups - Macapuno</t>
+  </si>
+  <si>
+    <t>Masa Picha - Hawaiian</t>
+  </si>
+  <si>
+    <t>Ice Candy - Mango</t>
+  </si>
+  <si>
+    <t>Shotts - Pink Grape Fruit</t>
+  </si>
+  <si>
+    <t>Milk -Oat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caramel Sauce </t>
   </si>
 </sst>
 </file>
@@ -3191,7 +3224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D713"/>
+  <dimension ref="A1:D724"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -13171,6 +13204,160 @@
         <v>463</v>
       </c>
     </row>
+    <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A714" s="50" t="s">
+        <v>742</v>
+      </c>
+      <c r="B714" s="64">
+        <v>95</v>
+      </c>
+      <c r="C714" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D714" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A715" s="50" t="s">
+        <v>748</v>
+      </c>
+      <c r="B715" s="64">
+        <v>100</v>
+      </c>
+      <c r="C715" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D715" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A716" s="50" t="s">
+        <v>743</v>
+      </c>
+      <c r="B716" s="64">
+        <v>135</v>
+      </c>
+      <c r="C716" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D716" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A717" s="50" t="s">
+        <v>749</v>
+      </c>
+      <c r="B717" s="64">
+        <v>20</v>
+      </c>
+      <c r="C717" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D717" s="6" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A718" s="50" t="s">
+        <v>750</v>
+      </c>
+      <c r="B718" s="64">
+        <v>0.9</v>
+      </c>
+      <c r="C718" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D718" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A719" s="50" t="s">
+        <v>751</v>
+      </c>
+      <c r="B719" s="64">
+        <v>0.19</v>
+      </c>
+      <c r="C719" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D719" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A720" s="50" t="s">
+        <v>744</v>
+      </c>
+      <c r="B720" s="64">
+        <v>1.05</v>
+      </c>
+      <c r="C720" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D720" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A721" s="50" t="s">
+        <v>752</v>
+      </c>
+      <c r="B721" s="64">
+        <v>0.33</v>
+      </c>
+      <c r="C721" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D721" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A722" s="50" t="s">
+        <v>745</v>
+      </c>
+      <c r="B722" s="64">
+        <v>40</v>
+      </c>
+      <c r="C722" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="D722" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A723" s="50" t="s">
+        <v>746</v>
+      </c>
+      <c r="B723" s="64">
+        <v>40</v>
+      </c>
+      <c r="C723" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="D723" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A724" s="50" t="s">
+        <v>747</v>
+      </c>
+      <c r="B724" s="64">
+        <v>40</v>
+      </c>
+      <c r="C724" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="D724" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF834B0-B6C1-4007-ACBD-AB095B513C1C}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD19107-5CEC-4678-84E4-F443DF3F0CAF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="28800" windowHeight="11235" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6839,7 +6839,7 @@
         <v>724</v>
       </c>
       <c r="B259" s="54">
-        <v>0.73</v>
+        <v>0.9</v>
       </c>
       <c r="C259" s="6" t="s">
         <v>4</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD19107-5CEC-4678-84E4-F443DF3F0CAF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDF4414-9C76-433B-8D37-E35995C8A5C5}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="754">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -1409,9 +1409,6 @@
     <t xml:space="preserve">Water </t>
   </si>
   <si>
-    <t>Baggoong Alamang - Production</t>
-  </si>
-  <si>
     <t>Cream Dory 200grams Sweet and Sour</t>
   </si>
   <si>
@@ -2289,6 +2286,12 @@
   </si>
   <si>
     <t xml:space="preserve">Caramel Sauce </t>
+  </si>
+  <si>
+    <t>Bagoong Alamang - Production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Mousse - Production </t>
   </si>
 </sst>
 </file>
@@ -2730,7 +2733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2908,6 +2911,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3224,19 +3236,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D724"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D725"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>458</v>
       </c>
@@ -3250,9 +3262,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B3" s="36">
         <v>0.19</v>
@@ -3261,96 +3273,96 @@
         <v>1</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B4" s="37">
         <v>12.63</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B5" s="36">
         <v>0.13</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>459</v>
+        <v>752</v>
       </c>
       <c r="B6" s="36">
         <v>0.36</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B7" s="37">
         <v>270</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B8" s="37">
         <v>350</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B9" s="37">
         <v>36.5</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B10" s="38">
         <v>0.24299999999999999</v>
@@ -3359,12 +3371,12 @@
         <v>1</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B11" s="38">
         <v>0.111</v>
@@ -3373,194 +3385,194 @@
         <v>1</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B12" s="37">
         <v>261.39999999999998</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B13" s="37">
         <v>153.33000000000001</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B14" s="38">
         <v>219.96</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B15" s="38">
         <v>24.75</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B16" s="37">
         <v>85</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B17" s="37">
         <v>73.12</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B18" s="40">
         <v>72.010000000000005</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B19" s="41">
         <v>8</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B20" s="41">
         <v>72.91</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B21" s="41">
         <v>10</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B22" s="42">
         <v>18.5</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B23" s="38">
         <v>23.66</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B24" s="38">
         <v>196.62</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B25" s="38">
         <v>11.02</v>
@@ -3569,12 +3581,12 @@
         <v>32</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B26" s="38">
         <v>8.65</v>
@@ -3583,12 +3595,12 @@
         <v>32</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B27" s="38">
         <v>0.85199999999999998</v>
@@ -3597,40 +3609,40 @@
         <v>1</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B28" s="34">
         <v>0.53</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="17" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B29" s="38">
         <v>36.03</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="17" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B30" s="36">
         <v>0.31</v>
@@ -3639,68 +3651,68 @@
         <v>1</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B31" s="37">
         <v>25.39</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B32" s="37">
         <v>80.88</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B33" s="41">
         <v>179.51</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="23" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B34" s="37">
         <v>77.59</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B35" s="38">
         <v>0.312</v>
@@ -3709,68 +3721,68 @@
         <v>1</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B36" s="38">
         <v>124.44</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B37" s="37">
         <v>18</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="17" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B38" s="37">
         <v>193.88</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="23" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B39" s="38">
         <v>86.83</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B40" s="43">
         <v>0.6</v>
@@ -3779,12 +3791,12 @@
         <v>1</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="25" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B41" s="44">
         <v>0.379</v>
@@ -3793,12 +3805,12 @@
         <v>1</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B42" s="44">
         <v>0.16500000000000001</v>
@@ -3807,250 +3819,250 @@
         <v>1</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="23" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B43" s="44">
         <v>0.46</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="24" t="s">
+        <v>508</v>
+      </c>
+      <c r="B44" s="45">
+        <v>7</v>
+      </c>
+      <c r="C44" s="47" t="s">
+        <v>461</v>
+      </c>
+      <c r="D44" s="49" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="27" t="s">
         <v>509</v>
-      </c>
-      <c r="B44" s="45">
-        <v>7</v>
-      </c>
-      <c r="C44" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="D44" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="27" t="s">
-        <v>510</v>
       </c>
       <c r="B45" s="41">
         <v>39</v>
       </c>
       <c r="C45" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="23" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B46" s="37">
         <v>30</v>
       </c>
       <c r="C46" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B47" s="37">
         <v>72.87</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="23" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B48" s="37">
         <v>30</v>
       </c>
       <c r="C48" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B49" s="37">
         <v>317.8</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="23" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B50" s="37">
         <v>70</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B51" s="38">
         <v>0.86199999999999999</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B52" s="38">
         <v>0.128</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="28" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B53" s="37">
         <v>14.92</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B54" s="37">
         <v>17.3</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D54" s="49" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="B55" s="38">
+        <v>1</v>
+      </c>
+      <c r="C55" s="47" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="23" t="s">
+      <c r="D55" s="49" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="28" t="s">
         <v>519</v>
-      </c>
-      <c r="B55" s="38">
-        <v>1</v>
-      </c>
-      <c r="C55" s="47" t="s">
-        <v>464</v>
-      </c>
-      <c r="D55" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="28" t="s">
-        <v>520</v>
       </c>
       <c r="B56" s="37">
         <v>112.14</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B57" s="38">
         <v>0.71</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B58" s="38">
         <v>0.18</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B59" s="38">
         <v>0.3</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="23" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B60" s="36">
         <v>0.46</v>
@@ -4059,68 +4071,68 @@
         <v>1</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B61" s="38">
         <v>0.39100000000000001</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B62" s="38">
         <v>0.28999999999999998</v>
       </c>
       <c r="C62" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B63" s="38">
         <v>0.17599999999999999</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="23" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B64" s="37">
         <v>63.92</v>
       </c>
       <c r="C64" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="23" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B65" s="46">
         <v>0.54</v>
@@ -4129,12 +4141,12 @@
         <v>1</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="23" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B66" s="34">
         <v>0.71</v>
@@ -4143,82 +4155,82 @@
         <v>1</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B67" s="37">
         <v>43.56</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="23" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B68" s="34">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="C68" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="28" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B69" s="34">
         <v>118.91</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="24" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B70" s="37">
         <v>34.799999999999997</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="23" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B71" s="38">
         <v>17.5</v>
       </c>
       <c r="C71" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D71" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="23" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B72" s="36">
         <v>0.153</v>
@@ -4227,236 +4239,236 @@
         <v>1</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="23" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B73" s="38">
         <v>37.444000000000003</v>
       </c>
       <c r="C73" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D73" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B74" s="38">
         <v>15.24</v>
       </c>
       <c r="C74" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D74" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="30" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B75" s="37">
         <v>208.78</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D75" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="23" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B76" s="37">
         <v>203.77</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="23" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B77" s="37">
         <v>102</v>
       </c>
       <c r="C77" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="28" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B78" s="37">
         <v>20.399999999999999</v>
       </c>
       <c r="C78" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D78" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="31" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B79" s="37">
         <v>11.73</v>
       </c>
       <c r="C79" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D79" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="23" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B80" s="38">
         <v>3.1E-2</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="31" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B81" s="38">
         <v>23.2</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D81" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="23" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B82" s="37">
         <v>75</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="23" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B83" s="37">
         <v>75</v>
       </c>
       <c r="C83" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D83" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="23" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B84" s="38">
         <v>46.36</v>
       </c>
       <c r="C84" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D84" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="32" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B85" s="37">
         <v>20</v>
       </c>
       <c r="C85" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="23" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B86" s="34">
         <v>0.18</v>
       </c>
       <c r="C86" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D86" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B87" s="38">
         <v>47.7</v>
       </c>
       <c r="C87" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D87" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="23" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B88" s="37">
         <v>43.28</v>
       </c>
       <c r="C88" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="25" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B89" s="38">
         <v>0.223</v>
@@ -4465,40 +4477,40 @@
         <v>1</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="16" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B90" s="37">
         <v>255.59</v>
       </c>
       <c r="C90" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D90" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="16" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B91" s="37">
         <v>38.03</v>
       </c>
       <c r="C91" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D91" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="23" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B92" s="38">
         <v>0.26</v>
@@ -4507,26 +4519,26 @@
         <v>1</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="28" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B93" s="37">
         <v>20.399999999999999</v>
       </c>
       <c r="C93" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D93" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="23" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B94" s="36">
         <v>0.11</v>
@@ -4535,152 +4547,152 @@
         <v>1</v>
       </c>
       <c r="D94" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B95" s="38">
         <v>34.24</v>
       </c>
       <c r="C95" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D95" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B96" s="37">
         <v>77</v>
       </c>
       <c r="C96" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="23" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B97" s="37">
         <v>130.91</v>
       </c>
       <c r="C97" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B98" s="34">
         <v>118.01</v>
       </c>
       <c r="C98" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D98" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="23" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B99" s="38">
         <v>43.75</v>
       </c>
       <c r="C99" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="28" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B100" s="37">
         <v>25.55</v>
       </c>
       <c r="C100" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D100" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="23" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B101" s="37">
         <v>200</v>
       </c>
       <c r="C101" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D101" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="28" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B102" s="37">
         <v>30</v>
       </c>
       <c r="C102" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="24" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B103" s="37">
         <v>22.25</v>
       </c>
       <c r="C103" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D103" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="24" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B104" s="37">
         <v>155.62</v>
       </c>
       <c r="C104" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="23" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B105" s="38">
         <v>0.22800000000000001</v>
@@ -4689,40 +4701,40 @@
         <v>1</v>
       </c>
       <c r="D105" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="23" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B106" s="38">
         <v>66</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D106" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="24" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B107" s="37">
         <v>36</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D107" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B108" s="34">
         <v>0.42</v>
@@ -4731,54 +4743,54 @@
         <v>1</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B109" s="37">
         <v>74.78</v>
       </c>
       <c r="C109" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D109" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="24" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B110" s="37">
         <v>8</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D110" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B111" s="37">
         <v>125</v>
       </c>
       <c r="C111" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="23" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B112" s="38">
         <v>0.16500000000000001</v>
@@ -4787,82 +4799,82 @@
         <v>1</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="28" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B113" s="37">
         <v>49.5</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D113" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="23" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B114" s="38">
         <v>0.56000000000000005</v>
       </c>
       <c r="C114" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="23" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B115" s="37">
         <v>86.22</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="23" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B116" s="38">
         <v>175</v>
       </c>
       <c r="C116" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="23" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B117" s="37">
         <v>57.15</v>
       </c>
       <c r="C117" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="23" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B118" s="38">
         <v>0.13400000000000001</v>
@@ -4871,26 +4883,26 @@
         <v>1</v>
       </c>
       <c r="D118" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="23" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B119" s="36">
         <v>0.12</v>
       </c>
       <c r="C119" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="23" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B120" s="38">
         <v>14.35</v>
@@ -4899,54 +4911,54 @@
         <v>32</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="23" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B121" s="37">
         <v>117.25</v>
       </c>
       <c r="C121" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D121" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="23" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B122" s="37">
         <v>38</v>
       </c>
       <c r="C122" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="23" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B123" s="38">
         <v>37.33</v>
       </c>
       <c r="C123" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="25" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B124" s="38">
         <v>0.222</v>
@@ -4955,12 +4967,12 @@
         <v>1</v>
       </c>
       <c r="D124" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B125" s="38">
         <v>0.22900000000000001</v>
@@ -4969,12 +4981,12 @@
         <v>1</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="23" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B126" s="38">
         <v>33</v>
@@ -4983,40 +4995,40 @@
         <v>32</v>
       </c>
       <c r="D126" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="23" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B127" s="38">
         <v>29.5</v>
       </c>
       <c r="C127" s="47" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D127" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="26" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B128" s="43">
         <v>0.24</v>
       </c>
       <c r="C128" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D128" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="33" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B129" s="44">
         <v>0.40799999999999997</v>
@@ -5025,138 +5037,138 @@
         <v>1</v>
       </c>
       <c r="D129" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="33" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B130" s="43">
         <v>34</v>
       </c>
       <c r="C130" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D130" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B131" s="43">
         <v>209.55</v>
       </c>
       <c r="C131" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D131" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="26" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B132" s="43">
         <v>0.05</v>
       </c>
       <c r="C132" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="26" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B133" s="43">
         <v>0.81</v>
       </c>
       <c r="C133" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D133" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="26" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B134" s="43">
         <v>10</v>
       </c>
       <c r="C134" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B135" s="38">
         <v>8.5</v>
       </c>
       <c r="C135" s="47" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D135" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="26" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B136" s="38">
         <v>0.28000000000000003</v>
       </c>
       <c r="C136" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="26" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B137" s="38">
         <v>0.35</v>
       </c>
       <c r="C137" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B138" s="38">
         <v>0.08</v>
       </c>
       <c r="C138" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="26" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B139" s="38">
         <v>0.19</v>
@@ -5165,26 +5177,26 @@
         <v>1</v>
       </c>
       <c r="D139" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="26" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B140" s="38">
         <v>332.18</v>
       </c>
       <c r="C140" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D140" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="26" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B141" s="38">
         <v>0.27200000000000002</v>
@@ -5193,80 +5205,80 @@
         <v>4</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="26" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B142" s="38">
         <v>166.79</v>
       </c>
       <c r="C142" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D142" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="26" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B143" s="38">
         <v>119.93</v>
       </c>
       <c r="C143" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D143" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="26" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B144" s="38">
         <v>0.52</v>
       </c>
       <c r="C144" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D144" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="26" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B145" s="38">
         <v>27.72</v>
       </c>
       <c r="C145" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D145" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="57" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B146" s="38">
         <v>32.22</v>
       </c>
       <c r="C146" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D146" s="49" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>0</v>
       </c>
@@ -5280,7 +5292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>3</v>
       </c>
@@ -5294,7 +5306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>6</v>
       </c>
@@ -5308,7 +5320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>8</v>
       </c>
@@ -5322,7 +5334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>9</v>
       </c>
@@ -5336,9 +5348,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B152" s="53">
         <v>0.18</v>
@@ -5350,7 +5362,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>11</v>
       </c>
@@ -5364,7 +5376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>12</v>
       </c>
@@ -5378,9 +5390,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B155" s="53">
         <v>0.21428571428571427</v>
@@ -5392,7 +5404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>13</v>
       </c>
@@ -5406,7 +5418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>14</v>
       </c>
@@ -5420,7 +5432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>15</v>
       </c>
@@ -5434,7 +5446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>16</v>
       </c>
@@ -5448,7 +5460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>17</v>
       </c>
@@ -5462,7 +5474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>18</v>
       </c>
@@ -5476,7 +5488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>19</v>
       </c>
@@ -5490,7 +5502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>20</v>
       </c>
@@ -5504,7 +5516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>21</v>
       </c>
@@ -5518,7 +5530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>22</v>
       </c>
@@ -5532,7 +5544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>24</v>
       </c>
@@ -5546,7 +5558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>25</v>
       </c>
@@ -5560,7 +5572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>26</v>
       </c>
@@ -5574,7 +5586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>27</v>
       </c>
@@ -5588,7 +5600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>29</v>
       </c>
@@ -5602,7 +5614,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>30</v>
       </c>
@@ -5616,7 +5628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>31</v>
       </c>
@@ -5630,7 +5642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>33</v>
       </c>
@@ -5644,7 +5656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>34</v>
       </c>
@@ -5658,7 +5670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>35</v>
       </c>
@@ -5672,9 +5684,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B176" s="54">
         <v>0.19</v>
@@ -5686,7 +5698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>37</v>
       </c>
@@ -5700,7 +5712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>38</v>
       </c>
@@ -5714,7 +5726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>39</v>
       </c>
@@ -5728,9 +5740,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B180" s="54">
         <v>75</v>
@@ -5742,7 +5754,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>41</v>
       </c>
@@ -5756,7 +5768,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>42</v>
       </c>
@@ -5770,9 +5782,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B183" s="54">
         <v>2.2000000000000002</v>
@@ -5784,7 +5796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>43</v>
       </c>
@@ -5798,7 +5810,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>44</v>
       </c>
@@ -5812,7 +5824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>45</v>
       </c>
@@ -5826,9 +5838,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B187" s="54">
         <v>0.24</v>
@@ -5840,7 +5852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>46</v>
       </c>
@@ -5854,7 +5866,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>48</v>
       </c>
@@ -5868,7 +5880,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>49</v>
       </c>
@@ -5882,7 +5894,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>50</v>
       </c>
@@ -5896,7 +5908,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>51</v>
       </c>
@@ -5910,7 +5922,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>52</v>
       </c>
@@ -5924,7 +5936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>53</v>
       </c>
@@ -5938,7 +5950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>54</v>
       </c>
@@ -5952,7 +5964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>55</v>
       </c>
@@ -5966,7 +5978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>56</v>
       </c>
@@ -5980,7 +5992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>57</v>
       </c>
@@ -5994,7 +6006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>58</v>
       </c>
@@ -6008,7 +6020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>59</v>
       </c>
@@ -6022,7 +6034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>60</v>
       </c>
@@ -6036,7 +6048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>61</v>
       </c>
@@ -6050,7 +6062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>62</v>
       </c>
@@ -6064,7 +6076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>63</v>
       </c>
@@ -6078,7 +6090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>64</v>
       </c>
@@ -6092,7 +6104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>65</v>
       </c>
@@ -6106,7 +6118,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>66</v>
       </c>
@@ -6120,7 +6132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>67</v>
       </c>
@@ -6134,7 +6146,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>68</v>
       </c>
@@ -6148,7 +6160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>69</v>
       </c>
@@ -6162,7 +6174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>70</v>
       </c>
@@ -6176,7 +6188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>71</v>
       </c>
@@ -6190,7 +6202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>72</v>
       </c>
@@ -6204,7 +6216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>73</v>
       </c>
@@ -6218,7 +6230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>74</v>
       </c>
@@ -6232,7 +6244,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>75</v>
       </c>
@@ -6246,7 +6258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>76</v>
       </c>
@@ -6260,7 +6272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>77</v>
       </c>
@@ -6274,9 +6286,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B219" s="54">
         <v>0.36099999999999999</v>
@@ -6288,7 +6300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>79</v>
       </c>
@@ -6302,7 +6314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>80</v>
       </c>
@@ -6316,7 +6328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>81</v>
       </c>
@@ -6330,7 +6342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>82</v>
       </c>
@@ -6344,9 +6356,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B224" s="54">
         <v>394</v>
@@ -6358,7 +6370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>83</v>
       </c>
@@ -6372,7 +6384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>84</v>
       </c>
@@ -6386,7 +6398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>85</v>
       </c>
@@ -6400,7 +6412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>86</v>
       </c>
@@ -6414,7 +6426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>87</v>
       </c>
@@ -6428,7 +6440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>88</v>
       </c>
@@ -6442,7 +6454,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>89</v>
       </c>
@@ -6456,7 +6468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>90</v>
       </c>
@@ -6470,7 +6482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>91</v>
       </c>
@@ -6484,7 +6496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>92</v>
       </c>
@@ -6498,7 +6510,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>93</v>
       </c>
@@ -6512,7 +6524,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>95</v>
       </c>
@@ -6526,7 +6538,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>96</v>
       </c>
@@ -6540,7 +6552,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>97</v>
       </c>
@@ -6554,7 +6566,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>98</v>
       </c>
@@ -6568,7 +6580,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>99</v>
       </c>
@@ -6582,7 +6594,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>100</v>
       </c>
@@ -6596,7 +6608,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>101</v>
       </c>
@@ -6610,7 +6622,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>102</v>
       </c>
@@ -6624,7 +6636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>103</v>
       </c>
@@ -6638,7 +6650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>104</v>
       </c>
@@ -6652,7 +6664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>105</v>
       </c>
@@ -6666,7 +6678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>106</v>
       </c>
@@ -6680,7 +6692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>107</v>
       </c>
@@ -6694,7 +6706,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>109</v>
       </c>
@@ -6708,7 +6720,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>110</v>
       </c>
@@ -6722,7 +6734,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>111</v>
       </c>
@@ -6736,7 +6748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>112</v>
       </c>
@@ -6750,7 +6762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>113</v>
       </c>
@@ -6764,7 +6776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>114</v>
       </c>
@@ -6778,7 +6790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>115</v>
       </c>
@@ -6792,9 +6804,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B256" s="54">
         <v>55</v>
@@ -6806,7 +6818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>116</v>
       </c>
@@ -6820,7 +6832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>117</v>
       </c>
@@ -6834,9 +6846,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B259" s="54">
         <v>0.9</v>
@@ -6848,9 +6860,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B260" s="54">
         <v>9.5000000000000001E-2</v>
@@ -6862,7 +6874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>118</v>
       </c>
@@ -6876,7 +6888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>119</v>
       </c>
@@ -6890,9 +6902,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B263" s="54">
         <v>0.23</v>
@@ -6904,7 +6916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>120</v>
       </c>
@@ -6918,9 +6930,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B265" s="54">
         <v>0.14285714285714285</v>
@@ -6932,9 +6944,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B266" s="54">
         <v>0.18823529411764706</v>
@@ -6946,7 +6958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>121</v>
       </c>
@@ -6960,7 +6972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>122</v>
       </c>
@@ -6974,7 +6986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>123</v>
       </c>
@@ -6988,7 +7000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>124</v>
       </c>
@@ -7002,7 +7014,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>125</v>
       </c>
@@ -7016,7 +7028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>126</v>
       </c>
@@ -7030,9 +7042,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B273" s="54">
         <v>0.32</v>
@@ -7044,9 +7056,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B274" s="54">
         <v>0.21249999999999999</v>
@@ -7058,7 +7070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>127</v>
       </c>
@@ -7072,7 +7084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>128</v>
       </c>
@@ -7086,7 +7098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>130</v>
       </c>
@@ -7100,7 +7112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>131</v>
       </c>
@@ -7114,7 +7126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>132</v>
       </c>
@@ -7128,7 +7140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>133</v>
       </c>
@@ -7142,9 +7154,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B281" s="54">
         <v>0.80645161290322576</v>
@@ -7156,7 +7168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>134</v>
       </c>
@@ -7170,9 +7182,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B283" s="54">
         <v>2</v>
@@ -7184,7 +7196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>135</v>
       </c>
@@ -7198,7 +7210,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>136</v>
       </c>
@@ -7212,7 +7224,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>137</v>
       </c>
@@ -7226,7 +7238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>138</v>
       </c>
@@ -7240,9 +7252,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B288" s="54">
         <v>0.51</v>
@@ -7254,7 +7266,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>139</v>
       </c>
@@ -7268,7 +7280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>140</v>
       </c>
@@ -7282,7 +7294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>141</v>
       </c>
@@ -7296,7 +7308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>142</v>
       </c>
@@ -7310,7 +7322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>143</v>
       </c>
@@ -7324,7 +7336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>144</v>
       </c>
@@ -7338,7 +7350,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>145</v>
       </c>
@@ -7352,7 +7364,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>146</v>
       </c>
@@ -7366,9 +7378,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B297" s="54">
         <v>0.40500000000000003</v>
@@ -7380,9 +7392,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B298" s="54">
         <v>0.372</v>
@@ -7394,9 +7406,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B299" s="54">
         <v>16</v>
@@ -7408,9 +7420,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B300" s="54">
         <v>12</v>
@@ -7422,9 +7434,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B301" s="54">
         <v>20</v>
@@ -7436,9 +7448,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B302" s="54">
         <v>0.13</v>
@@ -7450,7 +7462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>147</v>
       </c>
@@ -7464,7 +7476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>148</v>
       </c>
@@ -7478,7 +7490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>149</v>
       </c>
@@ -7492,7 +7504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>150</v>
       </c>
@@ -7506,7 +7518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>151</v>
       </c>
@@ -7520,7 +7532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>152</v>
       </c>
@@ -7534,7 +7546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>153</v>
       </c>
@@ -7548,7 +7560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>154</v>
       </c>
@@ -7562,7 +7574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>155</v>
       </c>
@@ -7576,7 +7588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>156</v>
       </c>
@@ -7590,7 +7602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>157</v>
       </c>
@@ -7604,7 +7616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>158</v>
       </c>
@@ -7618,7 +7630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>159</v>
       </c>
@@ -7632,7 +7644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>160</v>
       </c>
@@ -7646,7 +7658,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>161</v>
       </c>
@@ -7660,7 +7672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>162</v>
       </c>
@@ -7674,7 +7686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>163</v>
       </c>
@@ -7688,7 +7700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>164</v>
       </c>
@@ -7702,7 +7714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>165</v>
       </c>
@@ -7716,7 +7728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>166</v>
       </c>
@@ -7730,7 +7742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>167</v>
       </c>
@@ -7744,7 +7756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>168</v>
       </c>
@@ -7758,7 +7770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>169</v>
       </c>
@@ -7772,9 +7784,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B326" s="54">
         <v>0.31</v>
@@ -7786,7 +7798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>170</v>
       </c>
@@ -7800,9 +7812,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B328" s="54">
         <v>0.12222222222222222</v>
@@ -7814,7 +7826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>171</v>
       </c>
@@ -7828,7 +7840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>172</v>
       </c>
@@ -7842,7 +7854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>173</v>
       </c>
@@ -7856,7 +7868,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>175</v>
       </c>
@@ -7870,7 +7882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>176</v>
       </c>
@@ -7884,7 +7896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>177</v>
       </c>
@@ -7898,7 +7910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>178</v>
       </c>
@@ -7912,7 +7924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>179</v>
       </c>
@@ -7926,7 +7938,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>180</v>
       </c>
@@ -7940,7 +7952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>181</v>
       </c>
@@ -7954,7 +7966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>182</v>
       </c>
@@ -7968,7 +7980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>183</v>
       </c>
@@ -7982,7 +7994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>184</v>
       </c>
@@ -7996,7 +8008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>185</v>
       </c>
@@ -8010,7 +8022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>186</v>
       </c>
@@ -8024,7 +8036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>187</v>
       </c>
@@ -8038,7 +8050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>188</v>
       </c>
@@ -8052,7 +8064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>189</v>
       </c>
@@ -8066,7 +8078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>190</v>
       </c>
@@ -8080,7 +8092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>191</v>
       </c>
@@ -8094,7 +8106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>192</v>
       </c>
@@ -8108,7 +8120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>193</v>
       </c>
@@ -8122,7 +8134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>194</v>
       </c>
@@ -8136,7 +8148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>195</v>
       </c>
@@ -8150,7 +8162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>196</v>
       </c>
@@ -8164,7 +8176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>198</v>
       </c>
@@ -8178,7 +8190,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>200</v>
       </c>
@@ -8192,7 +8204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>201</v>
       </c>
@@ -8206,7 +8218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>202</v>
       </c>
@@ -8220,7 +8232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>203</v>
       </c>
@@ -8234,7 +8246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>204</v>
       </c>
@@ -8248,7 +8260,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>205</v>
       </c>
@@ -8262,7 +8274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>206</v>
       </c>
@@ -8276,7 +8288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>207</v>
       </c>
@@ -8290,7 +8302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>208</v>
       </c>
@@ -8304,7 +8316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>209</v>
       </c>
@@ -8318,7 +8330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>210</v>
       </c>
@@ -8332,7 +8344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>211</v>
       </c>
@@ -8346,7 +8358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>212</v>
       </c>
@@ -8360,7 +8372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>213</v>
       </c>
@@ -8374,7 +8386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>214</v>
       </c>
@@ -8388,7 +8400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>215</v>
       </c>
@@ -8402,7 +8414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>216</v>
       </c>
@@ -8416,7 +8428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>217</v>
       </c>
@@ -8430,7 +8442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>218</v>
       </c>
@@ -8444,9 +8456,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B374" s="54">
         <v>100</v>
@@ -8458,9 +8470,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B375" s="54">
         <v>14</v>
@@ -8472,9 +8484,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B376" s="54">
         <v>14</v>
@@ -8486,7 +8498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>219</v>
       </c>
@@ -8500,9 +8512,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B378" s="54">
         <v>0.23</v>
@@ -8514,7 +8526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>220</v>
       </c>
@@ -8528,7 +8540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>221</v>
       </c>
@@ -8542,7 +8554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>222</v>
       </c>
@@ -8556,7 +8568,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>223</v>
       </c>
@@ -8570,7 +8582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>224</v>
       </c>
@@ -8584,7 +8596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>225</v>
       </c>
@@ -8598,7 +8610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>226</v>
       </c>
@@ -8612,7 +8624,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>227</v>
       </c>
@@ -8626,7 +8638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>228</v>
       </c>
@@ -8640,7 +8652,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>229</v>
       </c>
@@ -8654,7 +8666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>230</v>
       </c>
@@ -8668,7 +8680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>231</v>
       </c>
@@ -8682,7 +8694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>232</v>
       </c>
@@ -8696,7 +8708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>233</v>
       </c>
@@ -8710,7 +8722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>234</v>
       </c>
@@ -8724,7 +8736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>235</v>
       </c>
@@ -8738,9 +8750,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B395" s="54">
         <v>0.25</v>
@@ -8752,9 +8764,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B396" s="54">
         <v>0.17</v>
@@ -8766,9 +8778,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B397" s="54">
         <v>0.17599999999999999</v>
@@ -8780,9 +8792,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B398" s="54">
         <v>9.5000000000000001E-2</v>
@@ -8794,7 +8806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>236</v>
       </c>
@@ -8808,7 +8820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>237</v>
       </c>
@@ -8822,7 +8834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>238</v>
       </c>
@@ -8836,7 +8848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>239</v>
       </c>
@@ -8850,9 +8862,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B403" s="54">
         <v>0.22500000000000001</v>
@@ -8864,7 +8876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>240</v>
       </c>
@@ -8878,7 +8890,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>241</v>
       </c>
@@ -8892,9 +8904,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B406" s="54">
         <v>0.23</v>
@@ -8906,7 +8918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>242</v>
       </c>
@@ -8920,7 +8932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>243</v>
       </c>
@@ -8934,7 +8946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>244</v>
       </c>
@@ -8948,7 +8960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>245</v>
       </c>
@@ -8962,7 +8974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>246</v>
       </c>
@@ -8976,7 +8988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>247</v>
       </c>
@@ -8990,7 +9002,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>248</v>
       </c>
@@ -9004,9 +9016,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B414" s="54">
         <v>0.23899999999999999</v>
@@ -9018,7 +9030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>249</v>
       </c>
@@ -9032,9 +9044,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B416" s="54">
         <v>0.185</v>
@@ -9046,7 +9058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>250</v>
       </c>
@@ -9060,7 +9072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>251</v>
       </c>
@@ -9074,7 +9086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>252</v>
       </c>
@@ -9088,7 +9100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>253</v>
       </c>
@@ -9102,7 +9114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>254</v>
       </c>
@@ -9116,7 +9128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>255</v>
       </c>
@@ -9130,9 +9142,9 @@
         <v>256</v>
       </c>
     </row>
-    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B423" s="54">
         <v>175</v>
@@ -9144,9 +9156,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B424" s="54">
         <v>55</v>
@@ -9158,7 +9170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>257</v>
       </c>
@@ -9172,7 +9184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>258</v>
       </c>
@@ -9186,7 +9198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>259</v>
       </c>
@@ -9200,7 +9212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>260</v>
       </c>
@@ -9214,9 +9226,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B429" s="54">
         <v>5.37</v>
@@ -9228,7 +9240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>261</v>
       </c>
@@ -9242,7 +9254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>262</v>
       </c>
@@ -9256,7 +9268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>263</v>
       </c>
@@ -9270,7 +9282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>264</v>
       </c>
@@ -9284,7 +9296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>265</v>
       </c>
@@ -9298,7 +9310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>266</v>
       </c>
@@ -9312,7 +9324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>267</v>
       </c>
@@ -9326,7 +9338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>268</v>
       </c>
@@ -9340,7 +9352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>269</v>
       </c>
@@ -9354,7 +9366,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>270</v>
       </c>
@@ -9368,7 +9380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>271</v>
       </c>
@@ -9382,7 +9394,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>272</v>
       </c>
@@ -9396,7 +9408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>273</v>
       </c>
@@ -9410,7 +9422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>274</v>
       </c>
@@ -9424,7 +9436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>275</v>
       </c>
@@ -9438,7 +9450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>276</v>
       </c>
@@ -9452,7 +9464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>277</v>
       </c>
@@ -9466,7 +9478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>278</v>
       </c>
@@ -9480,7 +9492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>279</v>
       </c>
@@ -9494,7 +9506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>280</v>
       </c>
@@ -9508,7 +9520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>281</v>
       </c>
@@ -9522,7 +9534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>282</v>
       </c>
@@ -9536,9 +9548,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B452" s="54">
         <v>0.2</v>
@@ -9550,7 +9562,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>283</v>
       </c>
@@ -9564,7 +9576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>284</v>
       </c>
@@ -9578,7 +9590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>285</v>
       </c>
@@ -9592,7 +9604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>286</v>
       </c>
@@ -9606,7 +9618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>287</v>
       </c>
@@ -9620,7 +9632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>288</v>
       </c>
@@ -9634,7 +9646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>289</v>
       </c>
@@ -9648,7 +9660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>290</v>
       </c>
@@ -9662,7 +9674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>291</v>
       </c>
@@ -9676,7 +9688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>292</v>
       </c>
@@ -9690,7 +9702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>293</v>
       </c>
@@ -9704,7 +9716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>294</v>
       </c>
@@ -9718,7 +9730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>295</v>
       </c>
@@ -9732,7 +9744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>296</v>
       </c>
@@ -9746,7 +9758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>297</v>
       </c>
@@ -9760,9 +9772,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B468" s="54">
         <v>385</v>
@@ -9774,7 +9786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>299</v>
       </c>
@@ -9788,7 +9800,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>300</v>
       </c>
@@ -9802,7 +9814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>301</v>
       </c>
@@ -9816,7 +9828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>302</v>
       </c>
@@ -9830,7 +9842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>303</v>
       </c>
@@ -9844,7 +9856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>304</v>
       </c>
@@ -9858,9 +9870,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B475" s="54">
         <v>40</v>
@@ -9872,9 +9884,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B476" s="54">
         <v>0.11</v>
@@ -9886,7 +9898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>305</v>
       </c>
@@ -9900,7 +9912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>306</v>
       </c>
@@ -9914,9 +9926,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B479" s="54">
         <v>7.4999999999999997E-2</v>
@@ -9928,7 +9940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>307</v>
       </c>
@@ -9942,7 +9954,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>308</v>
       </c>
@@ -9956,7 +9968,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>309</v>
       </c>
@@ -9970,7 +9982,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>310</v>
       </c>
@@ -9984,7 +9996,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>311</v>
       </c>
@@ -9998,7 +10010,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>312</v>
       </c>
@@ -10012,7 +10024,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>313</v>
       </c>
@@ -10026,7 +10038,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>314</v>
       </c>
@@ -10040,7 +10052,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>315</v>
       </c>
@@ -10054,7 +10066,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>316</v>
       </c>
@@ -10068,7 +10080,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>317</v>
       </c>
@@ -10082,7 +10094,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>318</v>
       </c>
@@ -10096,7 +10108,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>319</v>
       </c>
@@ -10110,7 +10122,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>320</v>
       </c>
@@ -10124,7 +10136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>321</v>
       </c>
@@ -10138,7 +10150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>322</v>
       </c>
@@ -10152,7 +10164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>323</v>
       </c>
@@ -10166,7 +10178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="4" t="s">
         <v>324</v>
       </c>
@@ -10180,9 +10192,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B498" s="54">
         <v>0.53</v>
@@ -10194,9 +10206,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B499" s="54">
         <v>0.53</v>
@@ -10208,9 +10220,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B500" s="54">
         <v>0.53</v>
@@ -10222,9 +10234,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B501" s="54">
         <v>0.53</v>
@@ -10236,9 +10248,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B502" s="54">
         <v>0.53</v>
@@ -10250,7 +10262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>325</v>
       </c>
@@ -10264,7 +10276,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>326</v>
       </c>
@@ -10278,7 +10290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>327</v>
       </c>
@@ -10292,7 +10304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>328</v>
       </c>
@@ -10306,7 +10318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>329</v>
       </c>
@@ -10320,7 +10332,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>330</v>
       </c>
@@ -10334,7 +10346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>331</v>
       </c>
@@ -10348,7 +10360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>332</v>
       </c>
@@ -10362,9 +10374,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B511" s="54">
         <v>35</v>
@@ -10376,9 +10388,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B512" s="54">
         <v>0.5</v>
@@ -10390,7 +10402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>333</v>
       </c>
@@ -10404,9 +10416,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B514" s="54">
         <v>0.13</v>
@@ -10418,9 +10430,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B515" s="54">
         <v>1</v>
@@ -10432,7 +10444,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
         <v>334</v>
       </c>
@@ -10446,7 +10458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="4" t="s">
         <v>335</v>
       </c>
@@ -10460,7 +10472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
         <v>336</v>
       </c>
@@ -10474,7 +10486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="4" t="s">
         <v>337</v>
       </c>
@@ -10488,7 +10500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
         <v>338</v>
       </c>
@@ -10502,7 +10514,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>339</v>
       </c>
@@ -10516,7 +10528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
         <v>340</v>
       </c>
@@ -10530,7 +10542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="4" t="s">
         <v>341</v>
       </c>
@@ -10544,9 +10556,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B524" s="54">
         <v>0.91</v>
@@ -10558,9 +10570,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B525" s="54">
         <v>0.91</v>
@@ -10572,9 +10584,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B526" s="54">
         <v>0.91</v>
@@ -10586,9 +10598,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B527" s="54">
         <v>0.71</v>
@@ -10600,9 +10612,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B528" s="54">
         <v>0.71</v>
@@ -10614,9 +10626,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B529" s="54">
         <v>0.71</v>
@@ -10628,9 +10640,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B530" s="54">
         <v>0.71</v>
@@ -10642,9 +10654,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B531" s="54">
         <v>0.91</v>
@@ -10656,9 +10668,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B532" s="54">
         <v>0.71</v>
@@ -10670,9 +10682,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B533" s="54">
         <v>0.71</v>
@@ -10684,9 +10696,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B534" s="54">
         <v>0.91</v>
@@ -10698,9 +10710,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B535" s="54">
         <v>0.91</v>
@@ -10712,9 +10724,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B536" s="54">
         <v>0.71</v>
@@ -10726,9 +10738,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B537" s="54">
         <v>0.71</v>
@@ -10740,9 +10752,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B538" s="54">
         <v>0.91</v>
@@ -10754,9 +10766,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B539" s="54">
         <v>0.91</v>
@@ -10768,9 +10780,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B540" s="54">
         <v>0.91</v>
@@ -10782,9 +10794,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B541" s="54">
         <v>0.91</v>
@@ -10796,9 +10808,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B542" s="54">
         <v>0.91</v>
@@ -10810,9 +10822,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B543" s="54">
         <v>0.71</v>
@@ -10824,7 +10836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="4" t="s">
         <v>342</v>
       </c>
@@ -10838,7 +10850,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="4" t="s">
         <v>343</v>
       </c>
@@ -10852,7 +10864,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="4" t="s">
         <v>344</v>
       </c>
@@ -10866,7 +10878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="4" t="s">
         <v>345</v>
       </c>
@@ -10880,7 +10892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="4" t="s">
         <v>346</v>
       </c>
@@ -10894,7 +10906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="4" t="s">
         <v>347</v>
       </c>
@@ -10908,7 +10920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="4" t="s">
         <v>348</v>
       </c>
@@ -10922,7 +10934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="4" t="s">
         <v>349</v>
       </c>
@@ -10936,7 +10948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="4" t="s">
         <v>350</v>
       </c>
@@ -10950,7 +10962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="4" t="s">
         <v>351</v>
       </c>
@@ -10964,9 +10976,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B554" s="54">
         <v>1</v>
@@ -10978,7 +10990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="4" t="s">
         <v>352</v>
       </c>
@@ -10992,7 +11004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="4" t="s">
         <v>353</v>
       </c>
@@ -11006,9 +11018,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B557" s="54">
         <v>0.125</v>
@@ -11020,7 +11032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="4" t="s">
         <v>354</v>
       </c>
@@ -11034,7 +11046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="4" t="s">
         <v>355</v>
       </c>
@@ -11048,7 +11060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="4" t="s">
         <v>356</v>
       </c>
@@ -11062,7 +11074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="4" t="s">
         <v>357</v>
       </c>
@@ -11076,9 +11088,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B562" s="54">
         <v>0.67100000000000004</v>
@@ -11090,7 +11102,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="4" t="s">
         <v>358</v>
       </c>
@@ -11104,7 +11116,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="4" t="s">
         <v>359</v>
       </c>
@@ -11118,7 +11130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="4" t="s">
         <v>360</v>
       </c>
@@ -11132,7 +11144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="4" t="s">
         <v>361</v>
       </c>
@@ -11146,7 +11158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="4" t="s">
         <v>362</v>
       </c>
@@ -11160,7 +11172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="4" t="s">
         <v>363</v>
       </c>
@@ -11174,7 +11186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="4" t="s">
         <v>364</v>
       </c>
@@ -11188,7 +11200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="4" t="s">
         <v>365</v>
       </c>
@@ -11202,7 +11214,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="4" t="s">
         <v>366</v>
       </c>
@@ -11216,7 +11228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="4" t="s">
         <v>367</v>
       </c>
@@ -11230,7 +11242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="4" t="s">
         <v>368</v>
       </c>
@@ -11244,7 +11256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="4" t="s">
         <v>369</v>
       </c>
@@ -11258,7 +11270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="4" t="s">
         <v>370</v>
       </c>
@@ -11272,7 +11284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="4" t="s">
         <v>371</v>
       </c>
@@ -11286,7 +11298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="4" t="s">
         <v>372</v>
       </c>
@@ -11300,7 +11312,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="4" t="s">
         <v>373</v>
       </c>
@@ -11314,7 +11326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="4" t="s">
         <v>374</v>
       </c>
@@ -11328,9 +11340,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B580" s="54">
         <v>0.33</v>
@@ -11342,9 +11354,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B581" s="54">
         <v>0.24</v>
@@ -11356,9 +11368,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B582" s="54">
         <v>0.95</v>
@@ -11370,9 +11382,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B583" s="54">
         <v>0.25</v>
@@ -11384,9 +11396,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B584" s="54">
         <v>0.15</v>
@@ -11398,7 +11410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="4" t="s">
         <v>375</v>
       </c>
@@ -11412,7 +11424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="4" t="s">
         <v>376</v>
       </c>
@@ -11426,7 +11438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="4" t="s">
         <v>377</v>
       </c>
@@ -11440,7 +11452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="4" t="s">
         <v>378</v>
       </c>
@@ -11454,7 +11466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="4" t="s">
         <v>379</v>
       </c>
@@ -11468,7 +11480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="4" t="s">
         <v>380</v>
       </c>
@@ -11482,9 +11494,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B591" s="54">
         <v>0.13500000000000001</v>
@@ -11496,7 +11508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="4" t="s">
         <v>381</v>
       </c>
@@ -11510,7 +11522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="4" t="s">
         <v>382</v>
       </c>
@@ -11524,7 +11536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="4" t="s">
         <v>383</v>
       </c>
@@ -11538,7 +11550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="4" t="s">
         <v>384</v>
       </c>
@@ -11552,7 +11564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="4" t="s">
         <v>385</v>
       </c>
@@ -11566,7 +11578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="4" t="s">
         <v>386</v>
       </c>
@@ -11580,7 +11592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="4" t="s">
         <v>387</v>
       </c>
@@ -11594,7 +11606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="4" t="s">
         <v>388</v>
       </c>
@@ -11608,9 +11620,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B600" s="54">
         <v>0.84699999999999998</v>
@@ -11622,7 +11634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="4" t="s">
         <v>389</v>
       </c>
@@ -11636,7 +11648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="4" t="s">
         <v>390</v>
       </c>
@@ -11650,7 +11662,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="4" t="s">
         <v>391</v>
       </c>
@@ -11664,9 +11676,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B604" s="54">
         <v>0.23499999999999999</v>
@@ -11678,7 +11690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="4" t="s">
         <v>392</v>
       </c>
@@ -11692,9 +11704,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B606" s="54">
         <v>220</v>
@@ -11706,7 +11718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="4" t="s">
         <v>393</v>
       </c>
@@ -11720,7 +11732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="4" t="s">
         <v>394</v>
       </c>
@@ -11734,7 +11746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="4" t="s">
         <v>395</v>
       </c>
@@ -11748,7 +11760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="4" t="s">
         <v>396</v>
       </c>
@@ -11762,7 +11774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="4" t="s">
         <v>397</v>
       </c>
@@ -11776,7 +11788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="4" t="s">
         <v>398</v>
       </c>
@@ -11790,7 +11802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="4" t="s">
         <v>399</v>
       </c>
@@ -11804,7 +11816,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="4" t="s">
         <v>400</v>
       </c>
@@ -11818,7 +11830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="4" t="s">
         <v>401</v>
       </c>
@@ -11832,7 +11844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="4" t="s">
         <v>402</v>
       </c>
@@ -11846,7 +11858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="4" t="s">
         <v>403</v>
       </c>
@@ -11860,9 +11872,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B618" s="54">
         <v>0.8</v>
@@ -11874,7 +11886,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="4" t="s">
         <v>404</v>
       </c>
@@ -11888,9 +11900,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B620" s="54">
         <v>0.06</v>
@@ -11902,7 +11914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="4" t="s">
         <v>405</v>
       </c>
@@ -11916,7 +11928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="4" t="s">
         <v>406</v>
       </c>
@@ -11930,7 +11942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="4" t="s">
         <v>407</v>
       </c>
@@ -11944,7 +11956,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="4" t="s">
         <v>408</v>
       </c>
@@ -11958,7 +11970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="4" t="s">
         <v>409</v>
       </c>
@@ -11972,7 +11984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="4" t="s">
         <v>410</v>
       </c>
@@ -11986,7 +11998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="4" t="s">
         <v>411</v>
       </c>
@@ -12000,7 +12012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="4" t="s">
         <v>412</v>
       </c>
@@ -12014,7 +12026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="4" t="s">
         <v>413</v>
       </c>
@@ -12028,7 +12040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="4" t="s">
         <v>414</v>
       </c>
@@ -12042,7 +12054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="4" t="s">
         <v>415</v>
       </c>
@@ -12056,9 +12068,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B632" s="54">
         <v>2</v>
@@ -12070,7 +12082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="4" t="s">
         <v>416</v>
       </c>
@@ -12084,7 +12096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="4" t="s">
         <v>417</v>
       </c>
@@ -12098,7 +12110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="4" t="s">
         <v>418</v>
       </c>
@@ -12112,7 +12124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="4" t="s">
         <v>419</v>
       </c>
@@ -12126,7 +12138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="4" t="s">
         <v>420</v>
       </c>
@@ -12140,7 +12152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="4" t="s">
         <v>421</v>
       </c>
@@ -12154,7 +12166,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="4" t="s">
         <v>423</v>
       </c>
@@ -12168,7 +12180,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="4" t="s">
         <v>425</v>
       </c>
@@ -12182,9 +12194,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B641" s="54">
         <v>1200</v>
@@ -12196,7 +12208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="4" t="s">
         <v>426</v>
       </c>
@@ -12210,7 +12222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="4" t="s">
         <v>427</v>
       </c>
@@ -12224,7 +12236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="4" t="s">
         <v>428</v>
       </c>
@@ -12238,9 +12250,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B645" s="54">
         <v>0.15</v>
@@ -12252,7 +12264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="4" t="s">
         <v>429</v>
       </c>
@@ -12266,7 +12278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="4" t="s">
         <v>430</v>
       </c>
@@ -12280,7 +12292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="4" t="s">
         <v>431</v>
       </c>
@@ -12294,7 +12306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="4" t="s">
         <v>432</v>
       </c>
@@ -12308,7 +12320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="4" t="s">
         <v>433</v>
       </c>
@@ -12322,7 +12334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="4" t="s">
         <v>434</v>
       </c>
@@ -12336,7 +12348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="4" t="s">
         <v>435</v>
       </c>
@@ -12350,7 +12362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="4" t="s">
         <v>436</v>
       </c>
@@ -12364,7 +12376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="4" t="s">
         <v>437</v>
       </c>
@@ -12378,7 +12390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="4" t="s">
         <v>438</v>
       </c>
@@ -12392,7 +12404,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="4" t="s">
         <v>439</v>
       </c>
@@ -12406,7 +12418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="4" t="s">
         <v>440</v>
       </c>
@@ -12420,7 +12432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="4" t="s">
         <v>441</v>
       </c>
@@ -12434,7 +12446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="4" t="s">
         <v>442</v>
       </c>
@@ -12448,7 +12460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="7" t="s">
         <v>443</v>
       </c>
@@ -12462,7 +12474,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="7" t="s">
         <v>444</v>
       </c>
@@ -12476,7 +12488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="8" t="s">
         <v>445</v>
       </c>
@@ -12490,7 +12502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="10" t="s">
         <v>446</v>
       </c>
@@ -12504,7 +12516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="10" t="s">
         <v>447</v>
       </c>
@@ -12518,7 +12530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="10" t="s">
         <v>448</v>
       </c>
@@ -12532,7 +12544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A666" s="4" t="s">
         <v>449</v>
       </c>
@@ -12546,7 +12558,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A667" s="10" t="s">
         <v>450</v>
       </c>
@@ -12560,7 +12572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A668" s="10" t="s">
         <v>451</v>
       </c>
@@ -12574,7 +12586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A669" s="4" t="s">
         <v>452</v>
       </c>
@@ -12588,7 +12600,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A670" s="4" t="s">
         <v>453</v>
       </c>
@@ -12602,7 +12614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A671" s="4" t="s">
         <v>454</v>
       </c>
@@ -12616,7 +12628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A672" s="10" t="s">
         <v>455</v>
       </c>
@@ -12630,7 +12642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A673" s="10" t="s">
         <v>456</v>
       </c>
@@ -12644,7 +12656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A674" s="4" t="s">
         <v>457</v>
       </c>
@@ -12658,37 +12670,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A675" s="50" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B675" s="55">
         <v>0.11700000000000001</v>
       </c>
       <c r="C675" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D675" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A676" s="50" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B676" s="55">
         <v>1.2</v>
       </c>
       <c r="C676" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D676" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A677" s="50" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B677" s="55">
         <v>0.27500000000000002</v>
@@ -12700,23 +12712,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A678" s="50" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B678" s="55">
         <v>45</v>
       </c>
       <c r="C678" s="13" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D678" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A679" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B679" s="54">
         <v>3</v>
@@ -12728,9 +12740,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A680" s="51" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B680" s="54">
         <v>0.22</v>
@@ -12742,9 +12754,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A681" s="51" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B681" s="54">
         <v>0.17</v>
@@ -12756,9 +12768,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A682" s="59" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B682" s="58">
         <v>0.91</v>
@@ -12770,9 +12782,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A683" s="61" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B683" s="62">
         <v>0.38</v>
@@ -12781,26 +12793,26 @@
         <v>1</v>
       </c>
       <c r="D683" s="63" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A684" s="61" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B684" s="62">
         <v>0.22</v>
       </c>
       <c r="C684" s="63" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D684" s="63" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A685" s="61" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B685" s="62">
         <v>0.59</v>
@@ -12809,12 +12821,12 @@
         <v>32</v>
       </c>
       <c r="D685" s="63" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A686" s="61" t="s">
         <v>711</v>
-      </c>
-    </row>
-    <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A686" s="61" t="s">
-        <v>712</v>
       </c>
       <c r="B686" s="62">
         <v>3.1</v>
@@ -12823,12 +12835,12 @@
         <v>32</v>
       </c>
       <c r="D686" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A687" s="61" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B687" s="62">
         <v>6.9</v>
@@ -12837,12 +12849,12 @@
         <v>32</v>
       </c>
       <c r="D687" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A688" s="61" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B688" s="62">
         <v>6.3</v>
@@ -12851,26 +12863,26 @@
         <v>32</v>
       </c>
       <c r="D688" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A689" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B689" s="64">
         <v>0.499</v>
       </c>
       <c r="C689" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D689" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A690" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B690" s="64">
         <v>0.4</v>
@@ -12882,9 +12894,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A691" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B691" s="64">
         <v>0.36</v>
@@ -12896,9 +12908,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A692" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B692" s="64">
         <v>0.2</v>
@@ -12910,9 +12922,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A693" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B693" s="64">
         <v>0.25</v>
@@ -12924,9 +12936,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A694" s="50" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B694" s="64">
         <v>0.64</v>
@@ -12938,9 +12950,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A695" s="50" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B695" s="64">
         <v>0.85</v>
@@ -12952,9 +12964,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="50" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B696" s="64">
         <v>0.15</v>
@@ -12966,9 +12978,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A697" s="65" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B697" s="66">
         <v>1.3</v>
@@ -12977,26 +12989,26 @@
         <v>32</v>
       </c>
       <c r="D697" s="67" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A698" s="68" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B698" s="69">
         <v>0</v>
       </c>
       <c r="C698" s="63" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D698" s="63" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A699" s="68" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B699" s="69">
         <v>3</v>
@@ -13005,12 +13017,12 @@
         <v>32</v>
       </c>
       <c r="D699" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A700" s="68" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B700" s="69">
         <v>2</v>
@@ -13019,12 +13031,12 @@
         <v>32</v>
       </c>
       <c r="D700" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A701" s="68" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B701" s="69">
         <v>1.6</v>
@@ -13033,12 +13045,12 @@
         <v>32</v>
       </c>
       <c r="D701" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A702" s="68" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B702" s="69">
         <v>0.25</v>
@@ -13047,12 +13059,12 @@
         <v>32</v>
       </c>
       <c r="D702" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A703" s="68" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B703" s="69">
         <v>0.4</v>
@@ -13061,12 +13073,12 @@
         <v>32</v>
       </c>
       <c r="D703" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A704" s="68" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B704" s="69">
         <v>4</v>
@@ -13075,12 +13087,12 @@
         <v>32</v>
       </c>
       <c r="D704" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A705" s="70" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B705" s="71">
         <v>1</v>
@@ -13089,12 +13101,12 @@
         <v>32</v>
       </c>
       <c r="D705" s="72" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A706" s="68" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B706" s="69">
         <v>26</v>
@@ -13103,12 +13115,12 @@
         <v>32</v>
       </c>
       <c r="D706" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A707" s="68" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B707" s="69">
         <v>26</v>
@@ -13117,12 +13129,12 @@
         <v>32</v>
       </c>
       <c r="D707" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A708" s="68" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B708" s="69">
         <v>26</v>
@@ -13131,12 +13143,12 @@
         <v>32</v>
       </c>
       <c r="D708" s="63" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A709" s="68" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B709" s="69">
         <v>6.06</v>
@@ -13145,12 +13157,12 @@
         <v>32</v>
       </c>
       <c r="D709" s="63" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A710" s="68" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B710" s="69">
         <v>0.48</v>
@@ -13159,12 +13171,12 @@
         <v>4</v>
       </c>
       <c r="D710" s="63" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A711" s="68" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B711" s="69">
         <v>0.54</v>
@@ -13173,12 +13185,12 @@
         <v>4</v>
       </c>
       <c r="D711" s="63" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A712" s="68" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B712" s="69">
         <v>0.38</v>
@@ -13187,12 +13199,12 @@
         <v>4</v>
       </c>
       <c r="D712" s="63" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A713" s="68" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B713" s="69">
         <v>0.39</v>
@@ -13201,12 +13213,12 @@
         <v>4</v>
       </c>
       <c r="D713" s="63" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A714" s="50" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B714" s="64">
         <v>95</v>
@@ -13218,9 +13230,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A715" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B715" s="64">
         <v>100</v>
@@ -13232,9 +13244,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A716" s="50" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B716" s="64">
         <v>135</v>
@@ -13246,9 +13258,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A717" s="50" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B717" s="64">
         <v>20</v>
@@ -13260,9 +13272,9 @@
         <v>422</v>
       </c>
     </row>
-    <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A718" s="50" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B718" s="64">
         <v>0.9</v>
@@ -13274,9 +13286,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A719" s="50" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B719" s="64">
         <v>0.19</v>
@@ -13288,9 +13300,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A720" s="50" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B720" s="64">
         <v>1.05</v>
@@ -13302,9 +13314,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A721" s="50" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B721" s="64">
         <v>0.33</v>
@@ -13316,46 +13328,60 @@
         <v>7</v>
       </c>
     </row>
-    <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A722" s="50" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B722" s="64">
         <v>40</v>
       </c>
       <c r="C722" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D722" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A723" s="50" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B723" s="64">
         <v>40</v>
       </c>
       <c r="C723" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D723" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A724" s="50" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B724" s="64">
         <v>40</v>
       </c>
       <c r="C724" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D724" s="6" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A725" s="73" t="s">
+        <v>753</v>
+      </c>
+      <c r="B725" s="74">
+        <v>0.35</v>
+      </c>
+      <c r="C725" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D725" s="75" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDF4414-9C76-433B-8D37-E35995C8A5C5}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AB4547-3CAC-47C8-8FA8-110B11FA172B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="2160" yWindow="2160" windowWidth="28800" windowHeight="11235" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="756">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2292,6 +2292,12 @@
   </si>
   <si>
     <t xml:space="preserve">Chocolate Mousse - Production </t>
+  </si>
+  <si>
+    <t>Pancake - Production (per piece)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salted Egg Powder </t>
   </si>
 </sst>
 </file>
@@ -3236,19 +3242,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D725"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D727"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>458</v>
       </c>
@@ -3262,7 +3268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>465</v>
       </c>
@@ -3276,7 +3282,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>477</v>
       </c>
@@ -3290,7 +3296,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>466</v>
       </c>
@@ -3304,7 +3310,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>752</v>
       </c>
@@ -3318,7 +3324,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>478</v>
       </c>
@@ -3332,7 +3338,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>479</v>
       </c>
@@ -3346,7 +3352,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>480</v>
       </c>
@@ -3360,7 +3366,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>470</v>
       </c>
@@ -3374,7 +3380,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>471</v>
       </c>
@@ -3388,7 +3394,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>481</v>
       </c>
@@ -3402,7 +3408,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>482</v>
       </c>
@@ -3416,7 +3422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
         <v>472</v>
       </c>
@@ -3430,7 +3436,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>473</v>
       </c>
@@ -3444,7 +3450,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>474</v>
       </c>
@@ -3458,7 +3464,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>475</v>
       </c>
@@ -3472,7 +3478,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>476</v>
       </c>
@@ -3486,7 +3492,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>483</v>
       </c>
@@ -3500,7 +3506,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>484</v>
       </c>
@@ -3514,7 +3520,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>485</v>
       </c>
@@ -3528,7 +3534,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>486</v>
       </c>
@@ -3542,7 +3548,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>487</v>
       </c>
@@ -3556,7 +3562,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>488</v>
       </c>
@@ -3570,7 +3576,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
         <v>489</v>
       </c>
@@ -3584,7 +3590,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>490</v>
       </c>
@@ -3598,7 +3604,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>491</v>
       </c>
@@ -3612,7 +3618,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>492</v>
       </c>
@@ -3626,7 +3632,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="17" t="s">
         <v>493</v>
       </c>
@@ -3640,7 +3646,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>494</v>
       </c>
@@ -3654,7 +3660,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>495</v>
       </c>
@@ -3668,7 +3674,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>496</v>
       </c>
@@ -3682,7 +3688,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
         <v>497</v>
       </c>
@@ -3696,7 +3702,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="23" t="s">
         <v>498</v>
       </c>
@@ -3710,7 +3716,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="17" t="s">
         <v>499</v>
       </c>
@@ -3724,7 +3730,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="23" t="s">
         <v>500</v>
       </c>
@@ -3738,7 +3744,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
         <v>501</v>
       </c>
@@ -3752,7 +3758,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="17" t="s">
         <v>502</v>
       </c>
@@ -3766,7 +3772,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="23" t="s">
         <v>503</v>
       </c>
@@ -3780,7 +3786,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
         <v>504</v>
       </c>
@@ -3794,7 +3800,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
         <v>505</v>
       </c>
@@ -3808,7 +3814,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>506</v>
       </c>
@@ -3822,7 +3828,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="23" t="s">
         <v>507</v>
       </c>
@@ -3836,7 +3842,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="s">
         <v>508</v>
       </c>
@@ -3850,7 +3856,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="27" t="s">
         <v>509</v>
       </c>
@@ -3864,7 +3870,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
         <v>459</v>
       </c>
@@ -3878,7 +3884,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="28" t="s">
         <v>510</v>
       </c>
@@ -3892,7 +3898,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="23" t="s">
         <v>511</v>
       </c>
@@ -3906,7 +3912,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
         <v>512</v>
       </c>
@@ -3920,7 +3926,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="23" t="s">
         <v>513</v>
       </c>
@@ -3934,7 +3940,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="25" t="s">
         <v>514</v>
       </c>
@@ -3948,7 +3954,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
         <v>515</v>
       </c>
@@ -3962,7 +3968,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="28" t="s">
         <v>516</v>
       </c>
@@ -3976,7 +3982,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
         <v>517</v>
       </c>
@@ -3990,7 +3996,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="23" t="s">
         <v>518</v>
       </c>
@@ -4004,7 +4010,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="28" t="s">
         <v>519</v>
       </c>
@@ -4018,7 +4024,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="23" t="s">
         <v>520</v>
       </c>
@@ -4032,7 +4038,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
         <v>521</v>
       </c>
@@ -4046,7 +4052,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
         <v>522</v>
       </c>
@@ -4060,7 +4066,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
         <v>523</v>
       </c>
@@ -4074,7 +4080,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="23" t="s">
         <v>524</v>
       </c>
@@ -4088,7 +4094,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
         <v>525</v>
       </c>
@@ -4102,7 +4108,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>460</v>
       </c>
@@ -4116,7 +4122,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
         <v>526</v>
       </c>
@@ -4130,7 +4136,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23" t="s">
         <v>527</v>
       </c>
@@ -4144,7 +4150,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
         <v>528</v>
       </c>
@@ -4158,7 +4164,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="23" t="s">
         <v>529</v>
       </c>
@@ -4172,7 +4178,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
         <v>530</v>
       </c>
@@ -4186,7 +4192,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="28" t="s">
         <v>531</v>
       </c>
@@ -4200,7 +4206,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="s">
         <v>532</v>
       </c>
@@ -4214,7 +4220,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="23" t="s">
         <v>533</v>
       </c>
@@ -4228,7 +4234,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23" t="s">
         <v>534</v>
       </c>
@@ -4242,7 +4248,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="23" t="s">
         <v>535</v>
       </c>
@@ -4256,7 +4262,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
         <v>536</v>
       </c>
@@ -4270,7 +4276,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="30" t="s">
         <v>538</v>
       </c>
@@ -4284,7 +4290,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
         <v>537</v>
       </c>
@@ -4298,7 +4304,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
         <v>539</v>
       </c>
@@ -4312,7 +4318,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="28" t="s">
         <v>540</v>
       </c>
@@ -4326,7 +4332,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="31" t="s">
         <v>541</v>
       </c>
@@ -4340,7 +4346,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="23" t="s">
         <v>542</v>
       </c>
@@ -4354,7 +4360,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="31" t="s">
         <v>543</v>
       </c>
@@ -4368,7 +4374,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="23" t="s">
         <v>544</v>
       </c>
@@ -4382,7 +4388,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="23" t="s">
         <v>545</v>
       </c>
@@ -4396,7 +4402,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="23" t="s">
         <v>546</v>
       </c>
@@ -4410,7 +4416,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="32" t="s">
         <v>547</v>
       </c>
@@ -4424,7 +4430,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23" t="s">
         <v>548</v>
       </c>
@@ -4438,7 +4444,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="23" t="s">
         <v>549</v>
       </c>
@@ -4452,7 +4458,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="23" t="s">
         <v>550</v>
       </c>
@@ -4466,7 +4472,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="25" t="s">
         <v>551</v>
       </c>
@@ -4480,7 +4486,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="16" t="s">
         <v>552</v>
       </c>
@@ -4494,7 +4500,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="16" t="s">
         <v>553</v>
       </c>
@@ -4508,7 +4514,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="23" t="s">
         <v>554</v>
       </c>
@@ -4522,7 +4528,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="28" t="s">
         <v>555</v>
       </c>
@@ -4536,7 +4542,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="23" t="s">
         <v>556</v>
       </c>
@@ -4550,7 +4556,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="23" t="s">
         <v>557</v>
       </c>
@@ -4564,7 +4570,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="23" t="s">
         <v>558</v>
       </c>
@@ -4578,7 +4584,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="23" t="s">
         <v>559</v>
       </c>
@@ -4592,7 +4598,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="23" t="s">
         <v>560</v>
       </c>
@@ -4606,7 +4612,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="23" t="s">
         <v>561</v>
       </c>
@@ -4620,7 +4626,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="28" t="s">
         <v>562</v>
       </c>
@@ -4634,7 +4640,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="23" t="s">
         <v>563</v>
       </c>
@@ -4648,7 +4654,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="28" t="s">
         <v>564</v>
       </c>
@@ -4662,7 +4668,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="s">
         <v>565</v>
       </c>
@@ -4676,7 +4682,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="24" t="s">
         <v>566</v>
       </c>
@@ -4690,7 +4696,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="23" t="s">
         <v>567</v>
       </c>
@@ -4704,7 +4710,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="23" t="s">
         <v>568</v>
       </c>
@@ -4718,7 +4724,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="24" t="s">
         <v>569</v>
       </c>
@@ -4732,7 +4738,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="23" t="s">
         <v>469</v>
       </c>
@@ -4746,7 +4752,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="23" t="s">
         <v>570</v>
       </c>
@@ -4760,7 +4766,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="24" t="s">
         <v>571</v>
       </c>
@@ -4774,7 +4780,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="23" t="s">
         <v>572</v>
       </c>
@@ -4788,7 +4794,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="23" t="s">
         <v>573</v>
       </c>
@@ -4802,7 +4808,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="28" t="s">
         <v>574</v>
       </c>
@@ -4816,7 +4822,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="23" t="s">
         <v>468</v>
       </c>
@@ -4830,7 +4836,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="23" t="s">
         <v>575</v>
       </c>
@@ -4844,7 +4850,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="23" t="s">
         <v>576</v>
       </c>
@@ -4858,7 +4864,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="23" t="s">
         <v>577</v>
       </c>
@@ -4872,7 +4878,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="23" t="s">
         <v>578</v>
       </c>
@@ -4886,7 +4892,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="23" t="s">
         <v>579</v>
       </c>
@@ -4900,7 +4906,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="23" t="s">
         <v>580</v>
       </c>
@@ -4914,7 +4920,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="23" t="s">
         <v>581</v>
       </c>
@@ -4928,7 +4934,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="23" t="s">
         <v>582</v>
       </c>
@@ -4942,7 +4948,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="23" t="s">
         <v>583</v>
       </c>
@@ -4956,7 +4962,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="25" t="s">
         <v>584</v>
       </c>
@@ -4970,7 +4976,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="23" t="s">
         <v>585</v>
       </c>
@@ -4984,7 +4990,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="23" t="s">
         <v>586</v>
       </c>
@@ -4998,7 +5004,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="23" t="s">
         <v>587</v>
       </c>
@@ -5012,7 +5018,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="26" t="s">
         <v>588</v>
       </c>
@@ -5026,7 +5032,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="33" t="s">
         <v>589</v>
       </c>
@@ -5040,7 +5046,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="33" t="s">
         <v>590</v>
       </c>
@@ -5054,7 +5060,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="33" t="s">
         <v>591</v>
       </c>
@@ -5068,7 +5074,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="26" t="s">
         <v>592</v>
       </c>
@@ -5082,7 +5088,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="26" t="s">
         <v>593</v>
       </c>
@@ -5096,7 +5102,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="26" t="s">
         <v>594</v>
       </c>
@@ -5110,7 +5116,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="26" t="s">
         <v>595</v>
       </c>
@@ -5124,7 +5130,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="26" t="s">
         <v>596</v>
       </c>
@@ -5138,7 +5144,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="26" t="s">
         <v>597</v>
       </c>
@@ -5152,7 +5158,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="26" t="s">
         <v>598</v>
       </c>
@@ -5166,7 +5172,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="26" t="s">
         <v>599</v>
       </c>
@@ -5180,7 +5186,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="26" t="s">
         <v>600</v>
       </c>
@@ -5194,7 +5200,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="26" t="s">
         <v>601</v>
       </c>
@@ -5208,7 +5214,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="26" t="s">
         <v>602</v>
       </c>
@@ -5222,7 +5228,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="26" t="s">
         <v>603</v>
       </c>
@@ -5236,7 +5242,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="26" t="s">
         <v>604</v>
       </c>
@@ -5250,7 +5256,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="26" t="s">
         <v>605</v>
       </c>
@@ -5264,7 +5270,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="57" t="s">
         <v>606</v>
       </c>
@@ -5278,7 +5284,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>0</v>
       </c>
@@ -5292,7 +5298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>3</v>
       </c>
@@ -5306,7 +5312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>6</v>
       </c>
@@ -5320,7 +5326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>8</v>
       </c>
@@ -5334,7 +5340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>9</v>
       </c>
@@ -5348,7 +5354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>607</v>
       </c>
@@ -5362,7 +5368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>11</v>
       </c>
@@ -5376,7 +5382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>12</v>
       </c>
@@ -5390,7 +5396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>608</v>
       </c>
@@ -5404,7 +5410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>13</v>
       </c>
@@ -5418,7 +5424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>14</v>
       </c>
@@ -5432,7 +5438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>15</v>
       </c>
@@ -5446,7 +5452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>16</v>
       </c>
@@ -5460,7 +5466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>17</v>
       </c>
@@ -5474,7 +5480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>18</v>
       </c>
@@ -5488,7 +5494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>19</v>
       </c>
@@ -5502,7 +5508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>20</v>
       </c>
@@ -5516,7 +5522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>21</v>
       </c>
@@ -5530,7 +5536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>22</v>
       </c>
@@ -5544,7 +5550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>24</v>
       </c>
@@ -5558,7 +5564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>25</v>
       </c>
@@ -5572,7 +5578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>26</v>
       </c>
@@ -5586,7 +5592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>27</v>
       </c>
@@ -5600,7 +5606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>29</v>
       </c>
@@ -5614,7 +5620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>30</v>
       </c>
@@ -5628,7 +5634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>31</v>
       </c>
@@ -5642,7 +5648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>33</v>
       </c>
@@ -5656,7 +5662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>34</v>
       </c>
@@ -5670,7 +5676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>35</v>
       </c>
@@ -5684,7 +5690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>609</v>
       </c>
@@ -5698,7 +5704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>37</v>
       </c>
@@ -5712,7 +5718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>38</v>
       </c>
@@ -5726,7 +5732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>39</v>
       </c>
@@ -5740,7 +5746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>610</v>
       </c>
@@ -5754,7 +5760,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
         <v>41</v>
       </c>
@@ -5768,7 +5774,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>42</v>
       </c>
@@ -5782,7 +5788,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>611</v>
       </c>
@@ -5796,7 +5802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
         <v>43</v>
       </c>
@@ -5810,7 +5816,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>44</v>
       </c>
@@ -5824,7 +5830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
         <v>45</v>
       </c>
@@ -5838,7 +5844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>612</v>
       </c>
@@ -5852,7 +5858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
         <v>46</v>
       </c>
@@ -5866,7 +5872,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
         <v>48</v>
       </c>
@@ -5880,7 +5886,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
         <v>49</v>
       </c>
@@ -5894,7 +5900,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
         <v>50</v>
       </c>
@@ -5908,7 +5914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>51</v>
       </c>
@@ -5922,7 +5928,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>52</v>
       </c>
@@ -5936,7 +5942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>53</v>
       </c>
@@ -5950,7 +5956,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>54</v>
       </c>
@@ -5964,7 +5970,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
         <v>55</v>
       </c>
@@ -5978,7 +5984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
         <v>56</v>
       </c>
@@ -5992,7 +5998,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
         <v>57</v>
       </c>
@@ -6006,7 +6012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>58</v>
       </c>
@@ -6020,7 +6026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>59</v>
       </c>
@@ -6034,7 +6040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
         <v>60</v>
       </c>
@@ -6048,7 +6054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>61</v>
       </c>
@@ -6062,7 +6068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>62</v>
       </c>
@@ -6076,7 +6082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>63</v>
       </c>
@@ -6090,7 +6096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>64</v>
       </c>
@@ -6104,7 +6110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>65</v>
       </c>
@@ -6118,7 +6124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>66</v>
       </c>
@@ -6132,7 +6138,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>67</v>
       </c>
@@ -6146,7 +6152,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>68</v>
       </c>
@@ -6160,7 +6166,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>69</v>
       </c>
@@ -6174,7 +6180,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>70</v>
       </c>
@@ -6188,7 +6194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>71</v>
       </c>
@@ -6202,7 +6208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>72</v>
       </c>
@@ -6216,7 +6222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>73</v>
       </c>
@@ -6230,7 +6236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>74</v>
       </c>
@@ -6244,7 +6250,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>75</v>
       </c>
@@ -6258,7 +6264,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>76</v>
       </c>
@@ -6272,7 +6278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>77</v>
       </c>
@@ -6286,7 +6292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>736</v>
       </c>
@@ -6300,7 +6306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>79</v>
       </c>
@@ -6314,7 +6320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>80</v>
       </c>
@@ -6328,7 +6334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>81</v>
       </c>
@@ -6342,7 +6348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>82</v>
       </c>
@@ -6356,7 +6362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>613</v>
       </c>
@@ -6370,7 +6376,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>83</v>
       </c>
@@ -6384,7 +6390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>84</v>
       </c>
@@ -6398,7 +6404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>85</v>
       </c>
@@ -6412,7 +6418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>86</v>
       </c>
@@ -6426,7 +6432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>87</v>
       </c>
@@ -6440,7 +6446,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>88</v>
       </c>
@@ -6454,7 +6460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>89</v>
       </c>
@@ -6468,7 +6474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>90</v>
       </c>
@@ -6482,7 +6488,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>91</v>
       </c>
@@ -6496,7 +6502,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>92</v>
       </c>
@@ -6510,7 +6516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>93</v>
       </c>
@@ -6524,7 +6530,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>95</v>
       </c>
@@ -6538,7 +6544,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>96</v>
       </c>
@@ -6552,7 +6558,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>97</v>
       </c>
@@ -6566,7 +6572,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>98</v>
       </c>
@@ -6580,7 +6586,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>99</v>
       </c>
@@ -6594,7 +6600,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>100</v>
       </c>
@@ -6608,7 +6614,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>101</v>
       </c>
@@ -6622,7 +6628,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>102</v>
       </c>
@@ -6636,7 +6642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>103</v>
       </c>
@@ -6650,7 +6656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>104</v>
       </c>
@@ -6664,7 +6670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>105</v>
       </c>
@@ -6678,7 +6684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>106</v>
       </c>
@@ -6692,7 +6698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>107</v>
       </c>
@@ -6706,7 +6712,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>109</v>
       </c>
@@ -6720,7 +6726,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>110</v>
       </c>
@@ -6734,7 +6740,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>111</v>
       </c>
@@ -6748,7 +6754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>112</v>
       </c>
@@ -6762,7 +6768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>113</v>
       </c>
@@ -6776,7 +6782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>114</v>
       </c>
@@ -6790,7 +6796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>115</v>
       </c>
@@ -6804,7 +6810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>614</v>
       </c>
@@ -6818,7 +6824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>116</v>
       </c>
@@ -6832,7 +6838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>117</v>
       </c>
@@ -6846,7 +6852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>723</v>
       </c>
@@ -6860,7 +6866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>615</v>
       </c>
@@ -6874,7 +6880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>118</v>
       </c>
@@ -6888,7 +6894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>119</v>
       </c>
@@ -6902,7 +6908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>616</v>
       </c>
@@ -6916,7 +6922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>120</v>
       </c>
@@ -6930,7 +6936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>617</v>
       </c>
@@ -6944,7 +6950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>618</v>
       </c>
@@ -6958,7 +6964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>121</v>
       </c>
@@ -6972,7 +6978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>122</v>
       </c>
@@ -6986,7 +6992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>123</v>
       </c>
@@ -7000,7 +7006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>124</v>
       </c>
@@ -7014,7 +7020,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>125</v>
       </c>
@@ -7028,7 +7034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>126</v>
       </c>
@@ -7042,7 +7048,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>619</v>
       </c>
@@ -7056,7 +7062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>620</v>
       </c>
@@ -7070,7 +7076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>127</v>
       </c>
@@ -7084,7 +7090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>128</v>
       </c>
@@ -7098,7 +7104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>130</v>
       </c>
@@ -7112,7 +7118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>131</v>
       </c>
@@ -7126,7 +7132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>132</v>
       </c>
@@ -7140,7 +7146,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>133</v>
       </c>
@@ -7154,7 +7160,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>621</v>
       </c>
@@ -7168,7 +7174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>134</v>
       </c>
@@ -7182,7 +7188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>622</v>
       </c>
@@ -7196,7 +7202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>135</v>
       </c>
@@ -7210,7 +7216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>136</v>
       </c>
@@ -7224,7 +7230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>137</v>
       </c>
@@ -7238,7 +7244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>138</v>
       </c>
@@ -7252,7 +7258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>623</v>
       </c>
@@ -7266,7 +7272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>139</v>
       </c>
@@ -7280,7 +7286,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>140</v>
       </c>
@@ -7294,7 +7300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>141</v>
       </c>
@@ -7308,7 +7314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>142</v>
       </c>
@@ -7322,7 +7328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>143</v>
       </c>
@@ -7336,7 +7342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>144</v>
       </c>
@@ -7350,7 +7356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>145</v>
       </c>
@@ -7364,7 +7370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>146</v>
       </c>
@@ -7378,7 +7384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>624</v>
       </c>
@@ -7392,7 +7398,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>625</v>
       </c>
@@ -7406,7 +7412,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>626</v>
       </c>
@@ -7420,7 +7426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>627</v>
       </c>
@@ -7434,7 +7440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>628</v>
       </c>
@@ -7448,7 +7454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>629</v>
       </c>
@@ -7462,7 +7468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>147</v>
       </c>
@@ -7476,7 +7482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>148</v>
       </c>
@@ -7490,7 +7496,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>149</v>
       </c>
@@ -7504,7 +7510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>150</v>
       </c>
@@ -7518,7 +7524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>151</v>
       </c>
@@ -7532,7 +7538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>152</v>
       </c>
@@ -7546,7 +7552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>153</v>
       </c>
@@ -7560,7 +7566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>154</v>
       </c>
@@ -7574,7 +7580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>155</v>
       </c>
@@ -7588,7 +7594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>156</v>
       </c>
@@ -7602,7 +7608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>157</v>
       </c>
@@ -7616,7 +7622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>158</v>
       </c>
@@ -7630,7 +7636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>159</v>
       </c>
@@ -7644,7 +7650,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>160</v>
       </c>
@@ -7658,7 +7664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>161</v>
       </c>
@@ -7672,7 +7678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>162</v>
       </c>
@@ -7686,7 +7692,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>163</v>
       </c>
@@ -7700,7 +7706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>164</v>
       </c>
@@ -7714,7 +7720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>165</v>
       </c>
@@ -7728,7 +7734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4" t="s">
         <v>166</v>
       </c>
@@ -7742,7 +7748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4" t="s">
         <v>167</v>
       </c>
@@ -7756,7 +7762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4" t="s">
         <v>168</v>
       </c>
@@ -7770,7 +7776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4" t="s">
         <v>169</v>
       </c>
@@ -7784,7 +7790,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
         <v>630</v>
       </c>
@@ -7798,7 +7804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
         <v>170</v>
       </c>
@@ -7812,7 +7818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
         <v>631</v>
       </c>
@@ -7826,7 +7832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
         <v>171</v>
       </c>
@@ -7840,7 +7846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
         <v>172</v>
       </c>
@@ -7854,7 +7860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
         <v>173</v>
       </c>
@@ -7868,7 +7874,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
         <v>175</v>
       </c>
@@ -7882,7 +7888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
         <v>176</v>
       </c>
@@ -7896,7 +7902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
         <v>177</v>
       </c>
@@ -7910,7 +7916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
         <v>178</v>
       </c>
@@ -7924,7 +7930,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>179</v>
       </c>
@@ -7938,7 +7944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
         <v>180</v>
       </c>
@@ -7952,7 +7958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
         <v>181</v>
       </c>
@@ -7966,7 +7972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
         <v>182</v>
       </c>
@@ -7980,7 +7986,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
         <v>183</v>
       </c>
@@ -7994,7 +8000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
         <v>184</v>
       </c>
@@ -8008,7 +8014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
         <v>185</v>
       </c>
@@ -8022,7 +8028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
         <v>186</v>
       </c>
@@ -8036,7 +8042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
         <v>187</v>
       </c>
@@ -8050,7 +8056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
         <v>188</v>
       </c>
@@ -8064,7 +8070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
         <v>189</v>
       </c>
@@ -8078,7 +8084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
         <v>190</v>
       </c>
@@ -8092,7 +8098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
         <v>191</v>
       </c>
@@ -8106,7 +8112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
         <v>192</v>
       </c>
@@ -8120,7 +8126,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
         <v>193</v>
       </c>
@@ -8134,7 +8140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
         <v>194</v>
       </c>
@@ -8148,7 +8154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
         <v>195</v>
       </c>
@@ -8162,7 +8168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
         <v>196</v>
       </c>
@@ -8176,7 +8182,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
         <v>198</v>
       </c>
@@ -8190,7 +8196,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
         <v>200</v>
       </c>
@@ -8204,7 +8210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
         <v>201</v>
       </c>
@@ -8218,7 +8224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
         <v>202</v>
       </c>
@@ -8232,7 +8238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>203</v>
       </c>
@@ -8246,7 +8252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>204</v>
       </c>
@@ -8260,7 +8266,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>205</v>
       </c>
@@ -8274,7 +8280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>206</v>
       </c>
@@ -8288,7 +8294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>207</v>
       </c>
@@ -8302,7 +8308,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>208</v>
       </c>
@@ -8316,7 +8322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>209</v>
       </c>
@@ -8330,7 +8336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>210</v>
       </c>
@@ -8344,7 +8350,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>211</v>
       </c>
@@ -8358,7 +8364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>212</v>
       </c>
@@ -8372,7 +8378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>213</v>
       </c>
@@ -8386,7 +8392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>214</v>
       </c>
@@ -8400,7 +8406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>215</v>
       </c>
@@ -8414,7 +8420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>216</v>
       </c>
@@ -8428,7 +8434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>217</v>
       </c>
@@ -8442,7 +8448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>218</v>
       </c>
@@ -8456,7 +8462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>632</v>
       </c>
@@ -8470,7 +8476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>633</v>
       </c>
@@ -8484,7 +8490,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>634</v>
       </c>
@@ -8498,7 +8504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>219</v>
       </c>
@@ -8512,7 +8518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>635</v>
       </c>
@@ -8526,7 +8532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>220</v>
       </c>
@@ -8540,7 +8546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>221</v>
       </c>
@@ -8554,7 +8560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>222</v>
       </c>
@@ -8568,7 +8574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>223</v>
       </c>
@@ -8582,7 +8588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>224</v>
       </c>
@@ -8596,7 +8602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>225</v>
       </c>
@@ -8610,7 +8616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>226</v>
       </c>
@@ -8624,7 +8630,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>227</v>
       </c>
@@ -8638,7 +8644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>228</v>
       </c>
@@ -8652,7 +8658,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>229</v>
       </c>
@@ -8666,7 +8672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
         <v>230</v>
       </c>
@@ -8680,7 +8686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
         <v>231</v>
       </c>
@@ -8694,7 +8700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
         <v>232</v>
       </c>
@@ -8708,7 +8714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
         <v>233</v>
       </c>
@@ -8722,7 +8728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
         <v>234</v>
       </c>
@@ -8736,7 +8742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
         <v>235</v>
       </c>
@@ -8750,7 +8756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
         <v>636</v>
       </c>
@@ -8764,7 +8770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
         <v>637</v>
       </c>
@@ -8778,7 +8784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
         <v>638</v>
       </c>
@@ -8792,7 +8798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
         <v>639</v>
       </c>
@@ -8806,7 +8812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
         <v>236</v>
       </c>
@@ -8820,7 +8826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
         <v>237</v>
       </c>
@@ -8834,7 +8840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
         <v>238</v>
       </c>
@@ -8848,7 +8854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
         <v>239</v>
       </c>
@@ -8862,7 +8868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
         <v>640</v>
       </c>
@@ -8876,7 +8882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
         <v>240</v>
       </c>
@@ -8890,7 +8896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
         <v>241</v>
       </c>
@@ -8904,7 +8910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
         <v>641</v>
       </c>
@@ -8918,7 +8924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
         <v>242</v>
       </c>
@@ -8932,7 +8938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
         <v>243</v>
       </c>
@@ -8946,7 +8952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
         <v>244</v>
       </c>
@@ -8960,7 +8966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
         <v>245</v>
       </c>
@@ -8974,7 +8980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
         <v>246</v>
       </c>
@@ -8988,7 +8994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
         <v>247</v>
       </c>
@@ -9002,7 +9008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
         <v>248</v>
       </c>
@@ -9016,7 +9022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
         <v>642</v>
       </c>
@@ -9030,7 +9036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
         <v>249</v>
       </c>
@@ -9044,7 +9050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
         <v>643</v>
       </c>
@@ -9058,7 +9064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
         <v>250</v>
       </c>
@@ -9072,7 +9078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
         <v>251</v>
       </c>
@@ -9086,7 +9092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
         <v>252</v>
       </c>
@@ -9100,7 +9106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
         <v>253</v>
       </c>
@@ -9114,7 +9120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
         <v>254</v>
       </c>
@@ -9128,7 +9134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
         <v>255</v>
       </c>
@@ -9142,7 +9148,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
         <v>644</v>
       </c>
@@ -9156,7 +9162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
         <v>645</v>
       </c>
@@ -9170,7 +9176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
         <v>257</v>
       </c>
@@ -9184,7 +9190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
         <v>258</v>
       </c>
@@ -9198,7 +9204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
         <v>259</v>
       </c>
@@ -9212,7 +9218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
         <v>260</v>
       </c>
@@ -9226,7 +9232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
         <v>646</v>
       </c>
@@ -9240,7 +9246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
         <v>261</v>
       </c>
@@ -9254,7 +9260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
         <v>262</v>
       </c>
@@ -9268,7 +9274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
         <v>263</v>
       </c>
@@ -9282,7 +9288,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
         <v>264</v>
       </c>
@@ -9296,7 +9302,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
         <v>265</v>
       </c>
@@ -9310,7 +9316,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
         <v>266</v>
       </c>
@@ -9324,7 +9330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
         <v>267</v>
       </c>
@@ -9338,7 +9344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
         <v>268</v>
       </c>
@@ -9352,7 +9358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
         <v>269</v>
       </c>
@@ -9366,7 +9372,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
         <v>270</v>
       </c>
@@ -9380,7 +9386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
         <v>271</v>
       </c>
@@ -9394,7 +9400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
         <v>272</v>
       </c>
@@ -9408,7 +9414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
         <v>273</v>
       </c>
@@ -9422,7 +9428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
         <v>274</v>
       </c>
@@ -9436,7 +9442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
         <v>275</v>
       </c>
@@ -9450,7 +9456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
         <v>276</v>
       </c>
@@ -9464,7 +9470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
         <v>277</v>
       </c>
@@ -9478,7 +9484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
         <v>278</v>
       </c>
@@ -9492,7 +9498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
         <v>279</v>
       </c>
@@ -9506,7 +9512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
         <v>280</v>
       </c>
@@ -9520,7 +9526,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
         <v>281</v>
       </c>
@@ -9534,7 +9540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
         <v>282</v>
       </c>
@@ -9548,7 +9554,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
         <v>647</v>
       </c>
@@ -9562,7 +9568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
         <v>283</v>
       </c>
@@ -9576,7 +9582,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
         <v>284</v>
       </c>
@@ -9590,7 +9596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
         <v>285</v>
       </c>
@@ -9604,7 +9610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
         <v>286</v>
       </c>
@@ -9618,7 +9624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
         <v>287</v>
       </c>
@@ -9632,7 +9638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
         <v>288</v>
       </c>
@@ -9646,7 +9652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
         <v>289</v>
       </c>
@@ -9660,7 +9666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
         <v>290</v>
       </c>
@@ -9674,7 +9680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
         <v>291</v>
       </c>
@@ -9688,7 +9694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
         <v>292</v>
       </c>
@@ -9702,7 +9708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
         <v>293</v>
       </c>
@@ -9716,7 +9722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
         <v>294</v>
       </c>
@@ -9730,7 +9736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
         <v>295</v>
       </c>
@@ -9744,7 +9750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
         <v>296</v>
       </c>
@@ -9758,7 +9764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
         <v>297</v>
       </c>
@@ -9772,7 +9778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
         <v>648</v>
       </c>
@@ -9786,7 +9792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
         <v>299</v>
       </c>
@@ -9800,7 +9806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
         <v>300</v>
       </c>
@@ -9814,7 +9820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
         <v>301</v>
       </c>
@@ -9828,7 +9834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
         <v>302</v>
       </c>
@@ -9842,7 +9848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
         <v>303</v>
       </c>
@@ -9856,7 +9862,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
         <v>304</v>
       </c>
@@ -9870,7 +9876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
         <v>649</v>
       </c>
@@ -9884,7 +9890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
         <v>650</v>
       </c>
@@ -9898,7 +9904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
         <v>305</v>
       </c>
@@ -9912,7 +9918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
         <v>306</v>
       </c>
@@ -9926,7 +9932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
         <v>651</v>
       </c>
@@ -9940,7 +9946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
         <v>307</v>
       </c>
@@ -9954,7 +9960,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
         <v>308</v>
       </c>
@@ -9968,7 +9974,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
         <v>309</v>
       </c>
@@ -9982,7 +9988,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
         <v>310</v>
       </c>
@@ -9996,7 +10002,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
         <v>311</v>
       </c>
@@ -10010,7 +10016,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
         <v>312</v>
       </c>
@@ -10024,7 +10030,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
         <v>313</v>
       </c>
@@ -10038,7 +10044,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
         <v>314</v>
       </c>
@@ -10052,7 +10058,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
         <v>315</v>
       </c>
@@ -10066,7 +10072,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
         <v>316</v>
       </c>
@@ -10080,7 +10086,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
         <v>317</v>
       </c>
@@ -10094,7 +10100,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
         <v>318</v>
       </c>
@@ -10108,7 +10114,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
         <v>319</v>
       </c>
@@ -10122,7 +10128,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
         <v>320</v>
       </c>
@@ -10136,7 +10142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
         <v>321</v>
       </c>
@@ -10150,7 +10156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
         <v>322</v>
       </c>
@@ -10164,7 +10170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
         <v>323</v>
       </c>
@@ -10178,7 +10184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
         <v>324</v>
       </c>
@@ -10192,7 +10198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
         <v>652</v>
       </c>
@@ -10206,7 +10212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
         <v>653</v>
       </c>
@@ -10220,7 +10226,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
         <v>654</v>
       </c>
@@ -10234,7 +10240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
         <v>655</v>
       </c>
@@ -10248,7 +10254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
         <v>656</v>
       </c>
@@ -10262,7 +10268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
         <v>325</v>
       </c>
@@ -10276,7 +10282,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
         <v>326</v>
       </c>
@@ -10290,7 +10296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
         <v>327</v>
       </c>
@@ -10304,7 +10310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
         <v>328</v>
       </c>
@@ -10318,7 +10324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
         <v>329</v>
       </c>
@@ -10332,7 +10338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
         <v>330</v>
       </c>
@@ -10346,7 +10352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
         <v>331</v>
       </c>
@@ -10360,7 +10366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
         <v>332</v>
       </c>
@@ -10374,7 +10380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
         <v>657</v>
       </c>
@@ -10388,7 +10394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
         <v>658</v>
       </c>
@@ -10402,7 +10408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
         <v>333</v>
       </c>
@@ -10416,7 +10422,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
         <v>659</v>
       </c>
@@ -10430,7 +10436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
         <v>660</v>
       </c>
@@ -10444,7 +10450,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
         <v>334</v>
       </c>
@@ -10458,7 +10464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
         <v>335</v>
       </c>
@@ -10472,7 +10478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
         <v>336</v>
       </c>
@@ -10486,7 +10492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
         <v>337</v>
       </c>
@@ -10500,7 +10506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
         <v>338</v>
       </c>
@@ -10514,7 +10520,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
         <v>339</v>
       </c>
@@ -10528,7 +10534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
         <v>340</v>
       </c>
@@ -10542,7 +10548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
         <v>341</v>
       </c>
@@ -10556,7 +10562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
         <v>661</v>
       </c>
@@ -10570,7 +10576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
         <v>662</v>
       </c>
@@ -10584,7 +10590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
         <v>663</v>
       </c>
@@ -10598,7 +10604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
         <v>664</v>
       </c>
@@ -10612,7 +10618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
         <v>665</v>
       </c>
@@ -10626,7 +10632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
         <v>666</v>
       </c>
@@ -10640,7 +10646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
         <v>667</v>
       </c>
@@ -10654,7 +10660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
         <v>668</v>
       </c>
@@ -10668,7 +10674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
         <v>669</v>
       </c>
@@ -10682,7 +10688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
         <v>670</v>
       </c>
@@ -10696,7 +10702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
         <v>671</v>
       </c>
@@ -10710,7 +10716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
         <v>672</v>
       </c>
@@ -10724,7 +10730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
         <v>673</v>
       </c>
@@ -10738,7 +10744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
         <v>674</v>
       </c>
@@ -10752,7 +10758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
         <v>675</v>
       </c>
@@ -10766,7 +10772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
         <v>676</v>
       </c>
@@ -10780,7 +10786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
         <v>677</v>
       </c>
@@ -10794,7 +10800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
         <v>678</v>
       </c>
@@ -10808,7 +10814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
         <v>679</v>
       </c>
@@ -10822,7 +10828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
         <v>680</v>
       </c>
@@ -10836,7 +10842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
         <v>342</v>
       </c>
@@ -10850,7 +10856,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
         <v>343</v>
       </c>
@@ -10864,7 +10870,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
         <v>344</v>
       </c>
@@ -10878,7 +10884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
         <v>345</v>
       </c>
@@ -10892,7 +10898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
         <v>346</v>
       </c>
@@ -10906,7 +10912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
         <v>347</v>
       </c>
@@ -10920,7 +10926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
         <v>348</v>
       </c>
@@ -10934,7 +10940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
         <v>349</v>
       </c>
@@ -10948,7 +10954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
         <v>350</v>
       </c>
@@ -10962,7 +10968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
         <v>351</v>
       </c>
@@ -10976,7 +10982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
         <v>681</v>
       </c>
@@ -10990,7 +10996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
         <v>352</v>
       </c>
@@ -11004,7 +11010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
         <v>353</v>
       </c>
@@ -11018,7 +11024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
         <v>682</v>
       </c>
@@ -11032,7 +11038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
         <v>354</v>
       </c>
@@ -11046,7 +11052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
         <v>355</v>
       </c>
@@ -11060,7 +11066,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
         <v>356</v>
       </c>
@@ -11074,7 +11080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
         <v>357</v>
       </c>
@@ -11088,7 +11094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
         <v>683</v>
       </c>
@@ -11102,7 +11108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
         <v>358</v>
       </c>
@@ -11116,7 +11122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
         <v>359</v>
       </c>
@@ -11130,7 +11136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
         <v>360</v>
       </c>
@@ -11144,7 +11150,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
         <v>361</v>
       </c>
@@ -11158,7 +11164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
         <v>362</v>
       </c>
@@ -11172,7 +11178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
         <v>363</v>
       </c>
@@ -11186,7 +11192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
         <v>364</v>
       </c>
@@ -11200,7 +11206,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
         <v>365</v>
       </c>
@@ -11214,7 +11220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
         <v>366</v>
       </c>
@@ -11228,7 +11234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
         <v>367</v>
       </c>
@@ -11242,7 +11248,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
         <v>368</v>
       </c>
@@ -11256,7 +11262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
         <v>369</v>
       </c>
@@ -11270,7 +11276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
         <v>370</v>
       </c>
@@ -11284,7 +11290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
         <v>371</v>
       </c>
@@ -11298,7 +11304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
         <v>372</v>
       </c>
@@ -11312,7 +11318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
         <v>373</v>
       </c>
@@ -11326,7 +11332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
         <v>374</v>
       </c>
@@ -11340,7 +11346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
         <v>684</v>
       </c>
@@ -11354,7 +11360,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
         <v>685</v>
       </c>
@@ -11368,7 +11374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
         <v>686</v>
       </c>
@@ -11382,7 +11388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
         <v>687</v>
       </c>
@@ -11396,7 +11402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
         <v>688</v>
       </c>
@@ -11410,7 +11416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
         <v>375</v>
       </c>
@@ -11424,7 +11430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
         <v>376</v>
       </c>
@@ -11438,7 +11444,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
         <v>377</v>
       </c>
@@ -11452,7 +11458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
         <v>378</v>
       </c>
@@ -11466,7 +11472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
         <v>379</v>
       </c>
@@ -11480,7 +11486,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
         <v>380</v>
       </c>
@@ -11494,7 +11500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
         <v>689</v>
       </c>
@@ -11508,7 +11514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
         <v>381</v>
       </c>
@@ -11522,7 +11528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
         <v>382</v>
       </c>
@@ -11536,7 +11542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
         <v>383</v>
       </c>
@@ -11550,7 +11556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
         <v>384</v>
       </c>
@@ -11564,7 +11570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
         <v>385</v>
       </c>
@@ -11578,7 +11584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
         <v>386</v>
       </c>
@@ -11592,7 +11598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
         <v>387</v>
       </c>
@@ -11606,7 +11612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
         <v>388</v>
       </c>
@@ -11620,7 +11626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
         <v>690</v>
       </c>
@@ -11634,7 +11640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
         <v>389</v>
       </c>
@@ -11648,7 +11654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
         <v>390</v>
       </c>
@@ -11662,7 +11668,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
         <v>391</v>
       </c>
@@ -11676,7 +11682,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
         <v>691</v>
       </c>
@@ -11690,7 +11696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
         <v>392</v>
       </c>
@@ -11704,7 +11710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
         <v>692</v>
       </c>
@@ -11718,7 +11724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
         <v>393</v>
       </c>
@@ -11732,7 +11738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
         <v>394</v>
       </c>
@@ -11746,7 +11752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
         <v>395</v>
       </c>
@@ -11760,7 +11766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
         <v>396</v>
       </c>
@@ -11774,7 +11780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
         <v>397</v>
       </c>
@@ -11788,7 +11794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
         <v>398</v>
       </c>
@@ -11802,7 +11808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
         <v>399</v>
       </c>
@@ -11816,7 +11822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
         <v>400</v>
       </c>
@@ -11830,7 +11836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
         <v>401</v>
       </c>
@@ -11844,7 +11850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
         <v>402</v>
       </c>
@@ -11858,7 +11864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
         <v>403</v>
       </c>
@@ -11872,7 +11878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
         <v>693</v>
       </c>
@@ -11886,7 +11892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
         <v>404</v>
       </c>
@@ -11900,7 +11906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
         <v>694</v>
       </c>
@@ -11914,7 +11920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
         <v>405</v>
       </c>
@@ -11928,7 +11934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
         <v>406</v>
       </c>
@@ -11942,7 +11948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
         <v>407</v>
       </c>
@@ -11956,7 +11962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
         <v>408</v>
       </c>
@@ -11970,7 +11976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
         <v>409</v>
       </c>
@@ -11984,7 +11990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
         <v>410</v>
       </c>
@@ -11998,7 +12004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
         <v>411</v>
       </c>
@@ -12012,7 +12018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
         <v>412</v>
       </c>
@@ -12026,7 +12032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
         <v>413</v>
       </c>
@@ -12040,7 +12046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
         <v>414</v>
       </c>
@@ -12054,7 +12060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
         <v>415</v>
       </c>
@@ -12068,7 +12074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
         <v>695</v>
       </c>
@@ -12082,7 +12088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
         <v>416</v>
       </c>
@@ -12096,7 +12102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
         <v>417</v>
       </c>
@@ -12110,7 +12116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
         <v>418</v>
       </c>
@@ -12124,7 +12130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
         <v>419</v>
       </c>
@@ -12138,7 +12144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
         <v>420</v>
       </c>
@@ -12152,7 +12158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
         <v>421</v>
       </c>
@@ -12166,7 +12172,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
         <v>423</v>
       </c>
@@ -12180,7 +12186,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
         <v>425</v>
       </c>
@@ -12194,7 +12200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
         <v>696</v>
       </c>
@@ -12208,7 +12214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
         <v>426</v>
       </c>
@@ -12222,7 +12228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
         <v>427</v>
       </c>
@@ -12236,7 +12242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
         <v>428</v>
       </c>
@@ -12250,7 +12256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
         <v>697</v>
       </c>
@@ -12264,7 +12270,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
         <v>429</v>
       </c>
@@ -12278,7 +12284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
         <v>430</v>
       </c>
@@ -12292,7 +12298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
         <v>431</v>
       </c>
@@ -12306,7 +12312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
         <v>432</v>
       </c>
@@ -12320,7 +12326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
         <v>433</v>
       </c>
@@ -12334,7 +12340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
         <v>434</v>
       </c>
@@ -12348,7 +12354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
         <v>435</v>
       </c>
@@ -12362,7 +12368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
         <v>436</v>
       </c>
@@ -12376,7 +12382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
         <v>437</v>
       </c>
@@ -12390,7 +12396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
         <v>438</v>
       </c>
@@ -12404,7 +12410,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
         <v>439</v>
       </c>
@@ -12418,7 +12424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
         <v>440</v>
       </c>
@@ -12432,7 +12438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
         <v>441</v>
       </c>
@@ -12446,7 +12452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
         <v>442</v>
       </c>
@@ -12460,7 +12466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="7" t="s">
         <v>443</v>
       </c>
@@ -12474,7 +12480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="7" t="s">
         <v>444</v>
       </c>
@@ -12488,7 +12494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="8" t="s">
         <v>445</v>
       </c>
@@ -12502,7 +12508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="10" t="s">
         <v>446</v>
       </c>
@@ -12516,7 +12522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="10" t="s">
         <v>447</v>
       </c>
@@ -12530,7 +12536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="10" t="s">
         <v>448</v>
       </c>
@@ -12544,7 +12550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="4" t="s">
         <v>449</v>
       </c>
@@ -12558,7 +12564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="10" t="s">
         <v>450</v>
       </c>
@@ -12572,7 +12578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="10" t="s">
         <v>451</v>
       </c>
@@ -12586,7 +12592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="4" t="s">
         <v>452</v>
       </c>
@@ -12600,7 +12606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="4" t="s">
         <v>453</v>
       </c>
@@ -12614,7 +12620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="4" t="s">
         <v>454</v>
       </c>
@@ -12628,7 +12634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="10" t="s">
         <v>455</v>
       </c>
@@ -12642,7 +12648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="10" t="s">
         <v>456</v>
       </c>
@@ -12656,7 +12662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A674" s="4" t="s">
         <v>457</v>
       </c>
@@ -12670,7 +12676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="50" t="s">
         <v>698</v>
       </c>
@@ -12684,7 +12690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="50" t="s">
         <v>699</v>
       </c>
@@ -12698,7 +12704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="50" t="s">
         <v>700</v>
       </c>
@@ -12712,7 +12718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="50" t="s">
         <v>701</v>
       </c>
@@ -12726,7 +12732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="4" t="s">
         <v>702</v>
       </c>
@@ -12740,7 +12746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A680" s="51" t="s">
         <v>703</v>
       </c>
@@ -12754,7 +12760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="51" t="s">
         <v>704</v>
       </c>
@@ -12768,7 +12774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A682" s="59" t="s">
         <v>705</v>
       </c>
@@ -12782,7 +12788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A683" s="61" t="s">
         <v>707</v>
       </c>
@@ -12796,7 +12802,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A684" s="61" t="s">
         <v>708</v>
       </c>
@@ -12810,7 +12816,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A685" s="61" t="s">
         <v>709</v>
       </c>
@@ -12824,7 +12830,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A686" s="61" t="s">
         <v>711</v>
       </c>
@@ -12838,7 +12844,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A687" s="61" t="s">
         <v>712</v>
       </c>
@@ -12852,7 +12858,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A688" s="61" t="s">
         <v>713</v>
       </c>
@@ -12866,7 +12872,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A689" s="4" t="s">
         <v>714</v>
       </c>
@@ -12880,7 +12886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A690" s="4" t="s">
         <v>715</v>
       </c>
@@ -12894,7 +12900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A691" s="4" t="s">
         <v>716</v>
       </c>
@@ -12908,7 +12914,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="4" t="s">
         <v>717</v>
       </c>
@@ -12922,7 +12928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A693" s="4" t="s">
         <v>718</v>
       </c>
@@ -12936,7 +12942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="50" t="s">
         <v>719</v>
       </c>
@@ -12950,7 +12956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A695" s="50" t="s">
         <v>720</v>
       </c>
@@ -12964,7 +12970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A696" s="50" t="s">
         <v>721</v>
       </c>
@@ -12978,7 +12984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A697" s="65" t="s">
         <v>722</v>
       </c>
@@ -12992,7 +12998,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A698" s="68" t="s">
         <v>724</v>
       </c>
@@ -13006,7 +13012,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A699" s="68" t="s">
         <v>725</v>
       </c>
@@ -13020,7 +13026,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A700" s="68" t="s">
         <v>727</v>
       </c>
@@ -13034,7 +13040,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A701" s="68" t="s">
         <v>726</v>
       </c>
@@ -13048,7 +13054,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A702" s="68" t="s">
         <v>728</v>
       </c>
@@ -13062,7 +13068,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A703" s="68" t="s">
         <v>729</v>
       </c>
@@ -13076,7 +13082,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A704" s="68" t="s">
         <v>730</v>
       </c>
@@ -13090,7 +13096,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A705" s="70" t="s">
         <v>731</v>
       </c>
@@ -13104,7 +13110,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A706" s="68" t="s">
         <v>732</v>
       </c>
@@ -13118,7 +13124,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A707" s="68" t="s">
         <v>733</v>
       </c>
@@ -13132,7 +13138,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A708" s="68" t="s">
         <v>734</v>
       </c>
@@ -13146,7 +13152,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A709" s="68" t="s">
         <v>735</v>
       </c>
@@ -13160,7 +13166,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A710" s="68" t="s">
         <v>737</v>
       </c>
@@ -13174,7 +13180,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A711" s="68" t="s">
         <v>738</v>
       </c>
@@ -13188,7 +13194,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A712" s="68" t="s">
         <v>739</v>
       </c>
@@ -13202,7 +13208,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A713" s="68" t="s">
         <v>740</v>
       </c>
@@ -13216,7 +13222,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A714" s="50" t="s">
         <v>741</v>
       </c>
@@ -13230,7 +13236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A715" s="50" t="s">
         <v>747</v>
       </c>
@@ -13244,7 +13250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A716" s="50" t="s">
         <v>742</v>
       </c>
@@ -13258,7 +13264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A717" s="50" t="s">
         <v>748</v>
       </c>
@@ -13272,7 +13278,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A718" s="50" t="s">
         <v>749</v>
       </c>
@@ -13286,7 +13292,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A719" s="50" t="s">
         <v>750</v>
       </c>
@@ -13300,7 +13306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A720" s="50" t="s">
         <v>743</v>
       </c>
@@ -13314,7 +13320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A721" s="50" t="s">
         <v>751</v>
       </c>
@@ -13328,7 +13334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A722" s="50" t="s">
         <v>744</v>
       </c>
@@ -13342,7 +13348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A723" s="50" t="s">
         <v>745</v>
       </c>
@@ -13356,7 +13362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A724" s="50" t="s">
         <v>746</v>
       </c>
@@ -13370,7 +13376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="725" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A725" s="73" t="s">
         <v>753</v>
       </c>
@@ -13382,6 +13388,34 @@
       </c>
       <c r="D725" s="75" t="s">
         <v>462</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A726" s="73" t="s">
+        <v>754</v>
+      </c>
+      <c r="B726" s="74">
+        <v>14.91</v>
+      </c>
+      <c r="C726" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D726" s="75" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A727" s="73" t="s">
+        <v>755</v>
+      </c>
+      <c r="B727" s="74">
+        <v>1.62</v>
+      </c>
+      <c r="C727" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D727" s="75" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AB4547-3CAC-47C8-8FA8-110B11FA172B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1396C1-5957-4A1D-9679-DBCB741B4074}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="28800" windowHeight="11235" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="11235" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="760">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2298,6 +2298,18 @@
   </si>
   <si>
     <t xml:space="preserve">Salted Egg Powder </t>
+  </si>
+  <si>
+    <t>Oil - from Pork Fats</t>
+  </si>
+  <si>
+    <t>Bayabas</t>
+  </si>
+  <si>
+    <t>Sinampalukang Manok - Production</t>
+  </si>
+  <si>
+    <t>Sampalok - Bunga - 200 grams</t>
   </si>
 </sst>
 </file>
@@ -2481,7 +2493,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -2735,11 +2747,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2919,14 +2944,11 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3242,7 +3264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D727"/>
+  <dimension ref="A1:D731"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -13363,59 +13385,115 @@
       </c>
     </row>
     <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A724" s="50" t="s">
+      <c r="A724" s="74" t="s">
         <v>746</v>
       </c>
-      <c r="B724" s="64">
+      <c r="B724" s="73">
         <v>40</v>
       </c>
-      <c r="C724" s="6" t="s">
+      <c r="C724" s="60" t="s">
         <v>706</v>
       </c>
-      <c r="D724" s="6" t="s">
+      <c r="D724" s="60" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="725" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A725" s="73" t="s">
+      <c r="A725" s="61" t="s">
         <v>753</v>
       </c>
-      <c r="B725" s="74">
+      <c r="B725" s="69">
         <v>0.35</v>
       </c>
-      <c r="C725" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="D725" s="75" t="s">
+      <c r="C725" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D725" s="63" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="726" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A726" s="73" t="s">
+      <c r="A726" s="61" t="s">
         <v>754</v>
       </c>
-      <c r="B726" s="74">
+      <c r="B726" s="69">
         <v>14.91</v>
       </c>
-      <c r="C726" s="75" t="s">
+      <c r="C726" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D726" s="75" t="s">
+      <c r="D726" s="63" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="727" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A727" s="73" t="s">
+      <c r="A727" s="61" t="s">
         <v>755</v>
       </c>
-      <c r="B727" s="74">
+      <c r="B727" s="69">
         <v>1.62</v>
       </c>
-      <c r="C727" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="D727" s="75" t="s">
+      <c r="C727" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D727" s="63" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A728" s="61" t="s">
+        <v>756</v>
+      </c>
+      <c r="B728" s="69">
+        <v>0</v>
+      </c>
+      <c r="C728" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D728" s="63" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A729" s="61" t="s">
+        <v>757</v>
+      </c>
+      <c r="B729" s="69">
+        <v>0.24</v>
+      </c>
+      <c r="C729" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D729" s="63" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A730" s="61" t="s">
+        <v>758</v>
+      </c>
+      <c r="B730" s="69">
+        <v>94.5</v>
+      </c>
+      <c r="C730" s="63" t="s">
+        <v>461</v>
+      </c>
+      <c r="D730" s="63" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A731" s="61" t="s">
+        <v>759</v>
+      </c>
+      <c r="B731" s="69">
+        <v>30</v>
+      </c>
+      <c r="C731" s="63" t="s">
+        <v>461</v>
+      </c>
+      <c r="D731" s="63" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1396C1-5957-4A1D-9679-DBCB741B4074}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6325522A-2364-41AC-8831-CFC54B9B1A69}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="11235" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="761">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2310,6 +2310,9 @@
   </si>
   <si>
     <t>Sampalok - Bunga - 200 grams</t>
+  </si>
+  <si>
+    <t>Barbeque Sauce - Production</t>
   </si>
 </sst>
 </file>
@@ -3264,7 +3267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
-  <dimension ref="A1:D731"/>
+  <dimension ref="A1:D806"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" customWidth="1"/>
@@ -13496,6 +13499,464 @@
         <v>462</v>
       </c>
     </row>
+    <row r="732" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A732" s="61" t="s">
+        <v>760</v>
+      </c>
+      <c r="B732" s="69">
+        <v>0.18</v>
+      </c>
+      <c r="C732" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D732" s="63" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A733" s="61"/>
+      <c r="B733" s="69"/>
+      <c r="C733" s="63"/>
+      <c r="D733" s="63"/>
+    </row>
+    <row r="734" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A734" s="61"/>
+      <c r="B734" s="69"/>
+      <c r="C734" s="63"/>
+      <c r="D734" s="63"/>
+    </row>
+    <row r="735" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A735" s="61"/>
+      <c r="B735" s="69"/>
+      <c r="C735" s="63"/>
+      <c r="D735" s="63"/>
+    </row>
+    <row r="736" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A736" s="61"/>
+      <c r="B736" s="69"/>
+      <c r="C736" s="63"/>
+      <c r="D736" s="63"/>
+    </row>
+    <row r="737" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A737" s="61"/>
+      <c r="B737" s="69"/>
+      <c r="C737" s="63"/>
+      <c r="D737" s="63"/>
+    </row>
+    <row r="738" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A738" s="61"/>
+      <c r="B738" s="69"/>
+      <c r="C738" s="63"/>
+      <c r="D738" s="63"/>
+    </row>
+    <row r="739" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A739" s="61"/>
+      <c r="B739" s="69"/>
+      <c r="C739" s="63"/>
+      <c r="D739" s="63"/>
+    </row>
+    <row r="740" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A740" s="61"/>
+      <c r="B740" s="69"/>
+      <c r="C740" s="63"/>
+      <c r="D740" s="63"/>
+    </row>
+    <row r="741" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A741" s="61"/>
+      <c r="B741" s="69"/>
+      <c r="C741" s="63"/>
+      <c r="D741" s="63"/>
+    </row>
+    <row r="742" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A742" s="61"/>
+      <c r="B742" s="69"/>
+      <c r="C742" s="63"/>
+      <c r="D742" s="63"/>
+    </row>
+    <row r="743" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A743" s="61"/>
+      <c r="B743" s="69"/>
+      <c r="C743" s="63"/>
+      <c r="D743" s="63"/>
+    </row>
+    <row r="744" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A744" s="61"/>
+      <c r="B744" s="69"/>
+      <c r="C744" s="63"/>
+      <c r="D744" s="63"/>
+    </row>
+    <row r="745" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A745" s="61"/>
+      <c r="B745" s="69"/>
+      <c r="C745" s="63"/>
+      <c r="D745" s="63"/>
+    </row>
+    <row r="746" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A746" s="61"/>
+      <c r="B746" s="69"/>
+      <c r="C746" s="63"/>
+      <c r="D746" s="63"/>
+    </row>
+    <row r="747" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A747" s="61"/>
+      <c r="B747" s="69"/>
+      <c r="C747" s="63"/>
+      <c r="D747" s="63"/>
+    </row>
+    <row r="748" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A748" s="61"/>
+      <c r="B748" s="69"/>
+      <c r="C748" s="63"/>
+      <c r="D748" s="63"/>
+    </row>
+    <row r="749" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A749" s="61"/>
+      <c r="B749" s="69"/>
+      <c r="C749" s="63"/>
+      <c r="D749" s="63"/>
+    </row>
+    <row r="750" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A750" s="61"/>
+      <c r="B750" s="69"/>
+      <c r="C750" s="63"/>
+      <c r="D750" s="63"/>
+    </row>
+    <row r="751" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A751" s="61"/>
+      <c r="B751" s="69"/>
+      <c r="C751" s="63"/>
+      <c r="D751" s="63"/>
+    </row>
+    <row r="752" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A752" s="61"/>
+      <c r="B752" s="69"/>
+      <c r="C752" s="63"/>
+      <c r="D752" s="63"/>
+    </row>
+    <row r="753" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A753" s="61"/>
+      <c r="B753" s="69"/>
+      <c r="C753" s="63"/>
+      <c r="D753" s="63"/>
+    </row>
+    <row r="754" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A754" s="61"/>
+      <c r="B754" s="69"/>
+      <c r="C754" s="63"/>
+      <c r="D754" s="63"/>
+    </row>
+    <row r="755" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A755" s="61"/>
+      <c r="B755" s="69"/>
+      <c r="C755" s="63"/>
+      <c r="D755" s="63"/>
+    </row>
+    <row r="756" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A756" s="61"/>
+      <c r="B756" s="69"/>
+      <c r="C756" s="63"/>
+      <c r="D756" s="63"/>
+    </row>
+    <row r="757" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A757" s="61"/>
+      <c r="B757" s="69"/>
+      <c r="C757" s="63"/>
+      <c r="D757" s="63"/>
+    </row>
+    <row r="758" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A758" s="61"/>
+      <c r="B758" s="69"/>
+      <c r="C758" s="63"/>
+      <c r="D758" s="63"/>
+    </row>
+    <row r="759" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A759" s="61"/>
+      <c r="B759" s="69"/>
+      <c r="C759" s="63"/>
+      <c r="D759" s="63"/>
+    </row>
+    <row r="760" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A760" s="61"/>
+      <c r="B760" s="69"/>
+      <c r="C760" s="63"/>
+      <c r="D760" s="63"/>
+    </row>
+    <row r="761" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A761" s="61"/>
+      <c r="B761" s="69"/>
+      <c r="C761" s="63"/>
+      <c r="D761" s="63"/>
+    </row>
+    <row r="762" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A762" s="61"/>
+      <c r="B762" s="69"/>
+      <c r="C762" s="63"/>
+      <c r="D762" s="63"/>
+    </row>
+    <row r="763" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A763" s="61"/>
+      <c r="B763" s="69"/>
+      <c r="C763" s="63"/>
+      <c r="D763" s="63"/>
+    </row>
+    <row r="764" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A764" s="61"/>
+      <c r="B764" s="69"/>
+      <c r="C764" s="63"/>
+      <c r="D764" s="63"/>
+    </row>
+    <row r="765" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A765" s="61"/>
+      <c r="B765" s="69"/>
+      <c r="C765" s="63"/>
+      <c r="D765" s="63"/>
+    </row>
+    <row r="766" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A766" s="61"/>
+      <c r="B766" s="69"/>
+      <c r="C766" s="63"/>
+      <c r="D766" s="63"/>
+    </row>
+    <row r="767" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A767" s="61"/>
+      <c r="B767" s="69"/>
+      <c r="C767" s="63"/>
+      <c r="D767" s="63"/>
+    </row>
+    <row r="768" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A768" s="61"/>
+      <c r="B768" s="69"/>
+      <c r="C768" s="63"/>
+      <c r="D768" s="63"/>
+    </row>
+    <row r="769" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A769" s="61"/>
+      <c r="B769" s="69"/>
+      <c r="C769" s="63"/>
+      <c r="D769" s="63"/>
+    </row>
+    <row r="770" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A770" s="61"/>
+      <c r="B770" s="69"/>
+      <c r="C770" s="63"/>
+      <c r="D770" s="63"/>
+    </row>
+    <row r="771" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A771" s="61"/>
+      <c r="B771" s="69"/>
+      <c r="C771" s="63"/>
+      <c r="D771" s="63"/>
+    </row>
+    <row r="772" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A772" s="61"/>
+      <c r="B772" s="69"/>
+      <c r="C772" s="63"/>
+      <c r="D772" s="63"/>
+    </row>
+    <row r="773" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A773" s="61"/>
+      <c r="B773" s="69"/>
+      <c r="C773" s="63"/>
+      <c r="D773" s="63"/>
+    </row>
+    <row r="774" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A774" s="61"/>
+      <c r="B774" s="69"/>
+      <c r="C774" s="63"/>
+      <c r="D774" s="63"/>
+    </row>
+    <row r="775" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A775" s="61"/>
+      <c r="B775" s="69"/>
+      <c r="C775" s="63"/>
+      <c r="D775" s="63"/>
+    </row>
+    <row r="776" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A776" s="61"/>
+      <c r="B776" s="69"/>
+      <c r="C776" s="63"/>
+      <c r="D776" s="63"/>
+    </row>
+    <row r="777" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A777" s="61"/>
+      <c r="B777" s="69"/>
+      <c r="C777" s="63"/>
+      <c r="D777" s="63"/>
+    </row>
+    <row r="778" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A778" s="61"/>
+      <c r="B778" s="69"/>
+      <c r="C778" s="63"/>
+      <c r="D778" s="63"/>
+    </row>
+    <row r="779" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A779" s="61"/>
+      <c r="B779" s="69"/>
+      <c r="C779" s="63"/>
+      <c r="D779" s="63"/>
+    </row>
+    <row r="780" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A780" s="61"/>
+      <c r="B780" s="69"/>
+      <c r="C780" s="63"/>
+      <c r="D780" s="63"/>
+    </row>
+    <row r="781" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A781" s="61"/>
+      <c r="B781" s="69"/>
+      <c r="C781" s="63"/>
+      <c r="D781" s="63"/>
+    </row>
+    <row r="782" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A782" s="61"/>
+      <c r="B782" s="69"/>
+      <c r="C782" s="63"/>
+      <c r="D782" s="63"/>
+    </row>
+    <row r="783" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A783" s="61"/>
+      <c r="B783" s="69"/>
+      <c r="C783" s="63"/>
+      <c r="D783" s="63"/>
+    </row>
+    <row r="784" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A784" s="61"/>
+      <c r="B784" s="69"/>
+      <c r="C784" s="63"/>
+      <c r="D784" s="63"/>
+    </row>
+    <row r="785" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A785" s="61"/>
+      <c r="B785" s="69"/>
+      <c r="C785" s="63"/>
+      <c r="D785" s="63"/>
+    </row>
+    <row r="786" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A786" s="61"/>
+      <c r="B786" s="69"/>
+      <c r="C786" s="63"/>
+      <c r="D786" s="63"/>
+    </row>
+    <row r="787" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A787" s="61"/>
+      <c r="B787" s="69"/>
+      <c r="C787" s="63"/>
+      <c r="D787" s="63"/>
+    </row>
+    <row r="788" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A788" s="61"/>
+      <c r="B788" s="69"/>
+      <c r="C788" s="63"/>
+      <c r="D788" s="63"/>
+    </row>
+    <row r="789" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A789" s="61"/>
+      <c r="B789" s="69"/>
+      <c r="C789" s="63"/>
+      <c r="D789" s="63"/>
+    </row>
+    <row r="790" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A790" s="61"/>
+      <c r="B790" s="69"/>
+      <c r="C790" s="63"/>
+      <c r="D790" s="63"/>
+    </row>
+    <row r="791" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A791" s="61"/>
+      <c r="B791" s="69"/>
+      <c r="C791" s="63"/>
+      <c r="D791" s="63"/>
+    </row>
+    <row r="792" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A792" s="61"/>
+      <c r="B792" s="69"/>
+      <c r="C792" s="63"/>
+      <c r="D792" s="63"/>
+    </row>
+    <row r="793" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A793" s="61"/>
+      <c r="B793" s="69"/>
+      <c r="C793" s="63"/>
+      <c r="D793" s="63"/>
+    </row>
+    <row r="794" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A794" s="61"/>
+      <c r="B794" s="69"/>
+      <c r="C794" s="63"/>
+      <c r="D794" s="63"/>
+    </row>
+    <row r="795" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A795" s="61"/>
+      <c r="B795" s="69"/>
+      <c r="C795" s="63"/>
+      <c r="D795" s="63"/>
+    </row>
+    <row r="796" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A796" s="61"/>
+      <c r="B796" s="69"/>
+      <c r="C796" s="63"/>
+      <c r="D796" s="63"/>
+    </row>
+    <row r="797" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A797" s="61"/>
+      <c r="B797" s="69"/>
+      <c r="C797" s="63"/>
+      <c r="D797" s="63"/>
+    </row>
+    <row r="798" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A798" s="61"/>
+      <c r="B798" s="69"/>
+      <c r="C798" s="63"/>
+      <c r="D798" s="63"/>
+    </row>
+    <row r="799" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A799" s="61"/>
+      <c r="B799" s="69"/>
+      <c r="C799" s="63"/>
+      <c r="D799" s="63"/>
+    </row>
+    <row r="800" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A800" s="61"/>
+      <c r="B800" s="69"/>
+      <c r="C800" s="63"/>
+      <c r="D800" s="63"/>
+    </row>
+    <row r="801" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A801" s="61"/>
+      <c r="B801" s="69"/>
+      <c r="C801" s="63"/>
+      <c r="D801" s="63"/>
+    </row>
+    <row r="802" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A802" s="61"/>
+      <c r="B802" s="69"/>
+      <c r="C802" s="63"/>
+      <c r="D802" s="63"/>
+    </row>
+    <row r="803" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A803" s="61"/>
+      <c r="B803" s="69"/>
+      <c r="C803" s="63"/>
+      <c r="D803" s="63"/>
+    </row>
+    <row r="804" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A804" s="61"/>
+      <c r="B804" s="69"/>
+      <c r="C804" s="63"/>
+      <c r="D804" s="63"/>
+    </row>
+    <row r="805" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A805" s="61"/>
+      <c r="B805" s="69"/>
+      <c r="C805" s="63"/>
+      <c r="D805" s="63"/>
+    </row>
+    <row r="806" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A806" s="61"/>
+      <c r="B806" s="69"/>
+      <c r="C806" s="63"/>
+      <c r="D806" s="63"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6325522A-2364-41AC-8831-CFC54B9B1A69}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6169B7-E9B8-4730-8343-E8589072467A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="770">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2313,6 +2313,33 @@
   </si>
   <si>
     <t>Barbeque Sauce - Production</t>
+  </si>
+  <si>
+    <t>Ube - Flavorade</t>
+  </si>
+  <si>
+    <t>Fibragel 100 - Gelato</t>
+  </si>
+  <si>
+    <t>Proteingel - Gelato</t>
+  </si>
+  <si>
+    <t>Sweetness Reducer - Gelato</t>
+  </si>
+  <si>
+    <t>Vanilla Tahiti (Yellow) - Gelato</t>
+  </si>
+  <si>
+    <t>Mocha - Flavorade</t>
+  </si>
+  <si>
+    <t>Coffee Costa De Oro</t>
+  </si>
+  <si>
+    <t>Mango Alfonso N</t>
+  </si>
+  <si>
+    <t>Crumbole Cacao</t>
   </si>
 </sst>
 </file>
@@ -3268,18 +3295,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
   <dimension ref="A1:D806"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>458</v>
       </c>
@@ -3293,7 +3320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>465</v>
       </c>
@@ -3307,7 +3334,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>477</v>
       </c>
@@ -3321,7 +3348,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>466</v>
       </c>
@@ -3335,7 +3362,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>752</v>
       </c>
@@ -3349,7 +3376,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>478</v>
       </c>
@@ -3363,7 +3390,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>479</v>
       </c>
@@ -3377,7 +3404,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>480</v>
       </c>
@@ -3391,7 +3418,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>470</v>
       </c>
@@ -3405,7 +3432,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
         <v>471</v>
       </c>
@@ -3419,7 +3446,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
         <v>481</v>
       </c>
@@ -3433,7 +3460,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>482</v>
       </c>
@@ -3447,7 +3474,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
         <v>472</v>
       </c>
@@ -3461,7 +3488,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
         <v>473</v>
       </c>
@@ -3475,7 +3502,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
         <v>474</v>
       </c>
@@ -3489,7 +3516,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
         <v>475</v>
       </c>
@@ -3503,7 +3530,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>476</v>
       </c>
@@ -3517,7 +3544,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>483</v>
       </c>
@@ -3531,7 +3558,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17" t="s">
         <v>484</v>
       </c>
@@ -3545,7 +3572,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
         <v>485</v>
       </c>
@@ -3559,7 +3586,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
         <v>486</v>
       </c>
@@ -3573,7 +3600,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17" t="s">
         <v>487</v>
       </c>
@@ -3587,7 +3614,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17" t="s">
         <v>488</v>
       </c>
@@ -3601,7 +3628,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
         <v>489</v>
       </c>
@@ -3615,7 +3642,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
         <v>490</v>
       </c>
@@ -3629,7 +3656,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="17" t="s">
         <v>491</v>
       </c>
@@ -3643,7 +3670,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="17" t="s">
         <v>492</v>
       </c>
@@ -3657,7 +3684,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="17" t="s">
         <v>493</v>
       </c>
@@ -3671,7 +3698,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="17" t="s">
         <v>494</v>
       </c>
@@ -3685,7 +3712,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="17" t="s">
         <v>495</v>
       </c>
@@ -3699,7 +3726,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="17" t="s">
         <v>496</v>
       </c>
@@ -3713,7 +3740,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="17" t="s">
         <v>497</v>
       </c>
@@ -3727,7 +3754,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="23" t="s">
         <v>498</v>
       </c>
@@ -3741,7 +3768,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="17" t="s">
         <v>499</v>
       </c>
@@ -3755,7 +3782,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="23" t="s">
         <v>500</v>
       </c>
@@ -3769,7 +3796,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="24" t="s">
         <v>501</v>
       </c>
@@ -3783,7 +3810,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="17" t="s">
         <v>502</v>
       </c>
@@ -3797,7 +3824,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="23" t="s">
         <v>503</v>
       </c>
@@ -3811,7 +3838,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26" t="s">
         <v>504</v>
       </c>
@@ -3825,7 +3852,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="25" t="s">
         <v>505</v>
       </c>
@@ -3839,7 +3866,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="25" t="s">
         <v>506</v>
       </c>
@@ -3853,7 +3880,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="23" t="s">
         <v>507</v>
       </c>
@@ -3867,7 +3894,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="24" t="s">
         <v>508</v>
       </c>
@@ -3881,7 +3908,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
         <v>509</v>
       </c>
@@ -3895,7 +3922,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="23" t="s">
         <v>459</v>
       </c>
@@ -3909,7 +3936,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
         <v>510</v>
       </c>
@@ -3923,7 +3950,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="23" t="s">
         <v>511</v>
       </c>
@@ -3937,7 +3964,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
         <v>512</v>
       </c>
@@ -3951,7 +3978,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="23" t="s">
         <v>513</v>
       </c>
@@ -3965,7 +3992,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="25" t="s">
         <v>514</v>
       </c>
@@ -3979,7 +4006,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="23" t="s">
         <v>515</v>
       </c>
@@ -3993,7 +4020,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="28" t="s">
         <v>516</v>
       </c>
@@ -4007,7 +4034,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="23" t="s">
         <v>517</v>
       </c>
@@ -4021,7 +4048,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="23" t="s">
         <v>518</v>
       </c>
@@ -4035,7 +4062,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="28" t="s">
         <v>519</v>
       </c>
@@ -4049,7 +4076,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="23" t="s">
         <v>520</v>
       </c>
@@ -4063,7 +4090,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="23" t="s">
         <v>521</v>
       </c>
@@ -4077,7 +4104,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="23" t="s">
         <v>522</v>
       </c>
@@ -4091,7 +4118,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="23" t="s">
         <v>523</v>
       </c>
@@ -4105,7 +4132,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="23" t="s">
         <v>524</v>
       </c>
@@ -4119,7 +4146,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="23" t="s">
         <v>525</v>
       </c>
@@ -4133,7 +4160,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17" t="s">
         <v>460</v>
       </c>
@@ -4147,7 +4174,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="23" t="s">
         <v>526</v>
       </c>
@@ -4161,7 +4188,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="23" t="s">
         <v>527</v>
       </c>
@@ -4175,7 +4202,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="23" t="s">
         <v>528</v>
       </c>
@@ -4189,7 +4216,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="23" t="s">
         <v>529</v>
       </c>
@@ -4203,7 +4230,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="23" t="s">
         <v>530</v>
       </c>
@@ -4217,7 +4244,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="28" t="s">
         <v>531</v>
       </c>
@@ -4231,7 +4258,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="24" t="s">
         <v>532</v>
       </c>
@@ -4245,7 +4272,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="23" t="s">
         <v>533</v>
       </c>
@@ -4259,7 +4286,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="23" t="s">
         <v>534</v>
       </c>
@@ -4273,7 +4300,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="23" t="s">
         <v>535</v>
       </c>
@@ -4287,7 +4314,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="23" t="s">
         <v>536</v>
       </c>
@@ -4301,7 +4328,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="30" t="s">
         <v>538</v>
       </c>
@@ -4315,7 +4342,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="23" t="s">
         <v>537</v>
       </c>
@@ -4329,7 +4356,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="23" t="s">
         <v>539</v>
       </c>
@@ -4343,7 +4370,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="28" t="s">
         <v>540</v>
       </c>
@@ -4357,7 +4384,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="31" t="s">
         <v>541</v>
       </c>
@@ -4371,7 +4398,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="23" t="s">
         <v>542</v>
       </c>
@@ -4385,7 +4412,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="31" t="s">
         <v>543</v>
       </c>
@@ -4399,7 +4426,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="23" t="s">
         <v>544</v>
       </c>
@@ -4413,7 +4440,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="23" t="s">
         <v>545</v>
       </c>
@@ -4427,7 +4454,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="23" t="s">
         <v>546</v>
       </c>
@@ -4441,7 +4468,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="32" t="s">
         <v>547</v>
       </c>
@@ -4455,7 +4482,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="23" t="s">
         <v>548</v>
       </c>
@@ -4469,7 +4496,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="23" t="s">
         <v>549</v>
       </c>
@@ -4483,7 +4510,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="23" t="s">
         <v>550</v>
       </c>
@@ -4497,7 +4524,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="25" t="s">
         <v>551</v>
       </c>
@@ -4511,7 +4538,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="16" t="s">
         <v>552</v>
       </c>
@@ -4525,7 +4552,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="16" t="s">
         <v>553</v>
       </c>
@@ -4539,7 +4566,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="23" t="s">
         <v>554</v>
       </c>
@@ -4553,7 +4580,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="28" t="s">
         <v>555</v>
       </c>
@@ -4567,7 +4594,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="23" t="s">
         <v>556</v>
       </c>
@@ -4581,7 +4608,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="23" t="s">
         <v>557</v>
       </c>
@@ -4595,7 +4622,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="23" t="s">
         <v>558</v>
       </c>
@@ -4609,7 +4636,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="23" t="s">
         <v>559</v>
       </c>
@@ -4623,7 +4650,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="23" t="s">
         <v>560</v>
       </c>
@@ -4637,7 +4664,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="23" t="s">
         <v>561</v>
       </c>
@@ -4651,7 +4678,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="28" t="s">
         <v>562</v>
       </c>
@@ -4665,7 +4692,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="23" t="s">
         <v>563</v>
       </c>
@@ -4679,7 +4706,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="28" t="s">
         <v>564</v>
       </c>
@@ -4693,7 +4720,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="24" t="s">
         <v>565</v>
       </c>
@@ -4707,7 +4734,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="24" t="s">
         <v>566</v>
       </c>
@@ -4721,7 +4748,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="23" t="s">
         <v>567</v>
       </c>
@@ -4735,7 +4762,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="23" t="s">
         <v>568</v>
       </c>
@@ -4749,7 +4776,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="24" t="s">
         <v>569</v>
       </c>
@@ -4763,7 +4790,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="23" t="s">
         <v>469</v>
       </c>
@@ -4777,7 +4804,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="23" t="s">
         <v>570</v>
       </c>
@@ -4791,7 +4818,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="24" t="s">
         <v>571</v>
       </c>
@@ -4805,7 +4832,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="23" t="s">
         <v>572</v>
       </c>
@@ -4819,7 +4846,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="23" t="s">
         <v>573</v>
       </c>
@@ -4833,7 +4860,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="28" t="s">
         <v>574</v>
       </c>
@@ -4847,7 +4874,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="23" t="s">
         <v>468</v>
       </c>
@@ -4861,7 +4888,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="23" t="s">
         <v>575</v>
       </c>
@@ -4875,7 +4902,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="23" t="s">
         <v>576</v>
       </c>
@@ -4889,7 +4916,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="23" t="s">
         <v>577</v>
       </c>
@@ -4903,7 +4930,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="23" t="s">
         <v>578</v>
       </c>
@@ -4917,7 +4944,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="23" t="s">
         <v>579</v>
       </c>
@@ -4931,7 +4958,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="23" t="s">
         <v>580</v>
       </c>
@@ -4945,7 +4972,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="23" t="s">
         <v>581</v>
       </c>
@@ -4959,7 +4986,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="23" t="s">
         <v>582</v>
       </c>
@@ -4973,7 +5000,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="23" t="s">
         <v>583</v>
       </c>
@@ -4987,7 +5014,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="25" t="s">
         <v>584</v>
       </c>
@@ -5001,7 +5028,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="23" t="s">
         <v>585</v>
       </c>
@@ -5015,7 +5042,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="23" t="s">
         <v>586</v>
       </c>
@@ -5029,7 +5056,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="23" t="s">
         <v>587</v>
       </c>
@@ -5043,7 +5070,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="26" t="s">
         <v>588</v>
       </c>
@@ -5057,7 +5084,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="33" t="s">
         <v>589</v>
       </c>
@@ -5071,7 +5098,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="33" t="s">
         <v>590</v>
       </c>
@@ -5085,7 +5112,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>591</v>
       </c>
@@ -5099,7 +5126,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="26" t="s">
         <v>592</v>
       </c>
@@ -5113,7 +5140,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="26" t="s">
         <v>593</v>
       </c>
@@ -5127,7 +5154,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="26" t="s">
         <v>594</v>
       </c>
@@ -5141,7 +5168,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26" t="s">
         <v>595</v>
       </c>
@@ -5155,7 +5182,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="26" t="s">
         <v>596</v>
       </c>
@@ -5169,7 +5196,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="26" t="s">
         <v>597</v>
       </c>
@@ -5183,7 +5210,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26" t="s">
         <v>598</v>
       </c>
@@ -5197,7 +5224,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="26" t="s">
         <v>599</v>
       </c>
@@ -5211,7 +5238,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="26" t="s">
         <v>600</v>
       </c>
@@ -5225,7 +5252,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="26" t="s">
         <v>601</v>
       </c>
@@ -5239,7 +5266,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="26" t="s">
         <v>602</v>
       </c>
@@ -5253,7 +5280,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="26" t="s">
         <v>603</v>
       </c>
@@ -5267,7 +5294,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="26" t="s">
         <v>604</v>
       </c>
@@ -5281,7 +5308,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="26" t="s">
         <v>605</v>
       </c>
@@ -5295,7 +5322,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="57" t="s">
         <v>606</v>
       </c>
@@ -5309,7 +5336,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>0</v>
       </c>
@@ -5323,7 +5350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>3</v>
       </c>
@@ -5337,7 +5364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>6</v>
       </c>
@@ -5351,7 +5378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>8</v>
       </c>
@@ -5365,7 +5392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>9</v>
       </c>
@@ -5379,7 +5406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>607</v>
       </c>
@@ -5393,7 +5420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>11</v>
       </c>
@@ -5407,7 +5434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>12</v>
       </c>
@@ -5421,7 +5448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>608</v>
       </c>
@@ -5435,7 +5462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>13</v>
       </c>
@@ -5449,7 +5476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>14</v>
       </c>
@@ -5463,7 +5490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>15</v>
       </c>
@@ -5477,7 +5504,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>16</v>
       </c>
@@ -5491,7 +5518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>17</v>
       </c>
@@ -5505,7 +5532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>18</v>
       </c>
@@ -5519,7 +5546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>19</v>
       </c>
@@ -5533,7 +5560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>20</v>
       </c>
@@ -5547,7 +5574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>21</v>
       </c>
@@ -5561,7 +5588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>22</v>
       </c>
@@ -5575,7 +5602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>24</v>
       </c>
@@ -5589,7 +5616,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>25</v>
       </c>
@@ -5603,7 +5630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>26</v>
       </c>
@@ -5617,7 +5644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>27</v>
       </c>
@@ -5631,7 +5658,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>29</v>
       </c>
@@ -5645,7 +5672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>30</v>
       </c>
@@ -5659,7 +5686,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>31</v>
       </c>
@@ -5673,7 +5700,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>33</v>
       </c>
@@ -5687,7 +5714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>34</v>
       </c>
@@ -5701,7 +5728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>35</v>
       </c>
@@ -5715,7 +5742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>609</v>
       </c>
@@ -5729,7 +5756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>37</v>
       </c>
@@ -5743,7 +5770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>38</v>
       </c>
@@ -5757,7 +5784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>39</v>
       </c>
@@ -5771,7 +5798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>610</v>
       </c>
@@ -5785,7 +5812,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>41</v>
       </c>
@@ -5799,7 +5826,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>42</v>
       </c>
@@ -5813,7 +5840,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>611</v>
       </c>
@@ -5827,7 +5854,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>43</v>
       </c>
@@ -5841,7 +5868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>44</v>
       </c>
@@ -5855,7 +5882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>45</v>
       </c>
@@ -5869,7 +5896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>612</v>
       </c>
@@ -5883,7 +5910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>46</v>
       </c>
@@ -5897,7 +5924,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>48</v>
       </c>
@@ -5911,7 +5938,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>49</v>
       </c>
@@ -5925,7 +5952,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>50</v>
       </c>
@@ -5939,7 +5966,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>51</v>
       </c>
@@ -5953,7 +5980,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>52</v>
       </c>
@@ -5967,7 +5994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>53</v>
       </c>
@@ -5981,7 +6008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>54</v>
       </c>
@@ -5995,7 +6022,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>55</v>
       </c>
@@ -6009,7 +6036,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>56</v>
       </c>
@@ -6023,7 +6050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>57</v>
       </c>
@@ -6037,7 +6064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>58</v>
       </c>
@@ -6051,7 +6078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>59</v>
       </c>
@@ -6065,7 +6092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>60</v>
       </c>
@@ -6079,7 +6106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>61</v>
       </c>
@@ -6093,7 +6120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>62</v>
       </c>
@@ -6107,7 +6134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>63</v>
       </c>
@@ -6121,7 +6148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>64</v>
       </c>
@@ -6135,7 +6162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>65</v>
       </c>
@@ -6149,7 +6176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>66</v>
       </c>
@@ -6163,7 +6190,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>67</v>
       </c>
@@ -6177,7 +6204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>68</v>
       </c>
@@ -6191,7 +6218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>69</v>
       </c>
@@ -6205,7 +6232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>70</v>
       </c>
@@ -6219,7 +6246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>71</v>
       </c>
@@ -6233,7 +6260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>72</v>
       </c>
@@ -6247,7 +6274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>73</v>
       </c>
@@ -6261,7 +6288,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>74</v>
       </c>
@@ -6275,7 +6302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>75</v>
       </c>
@@ -6289,7 +6316,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>76</v>
       </c>
@@ -6303,7 +6330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>77</v>
       </c>
@@ -6317,7 +6344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
         <v>736</v>
       </c>
@@ -6331,7 +6358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="4" t="s">
         <v>79</v>
       </c>
@@ -6345,7 +6372,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="4" t="s">
         <v>80</v>
       </c>
@@ -6359,7 +6386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="4" t="s">
         <v>81</v>
       </c>
@@ -6373,7 +6400,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="4" t="s">
         <v>82</v>
       </c>
@@ -6387,7 +6414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
         <v>613</v>
       </c>
@@ -6401,7 +6428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>83</v>
       </c>
@@ -6415,7 +6442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>84</v>
       </c>
@@ -6429,7 +6456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>85</v>
       </c>
@@ -6443,7 +6470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>86</v>
       </c>
@@ -6457,7 +6484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>87</v>
       </c>
@@ -6471,7 +6498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>88</v>
       </c>
@@ -6485,7 +6512,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>89</v>
       </c>
@@ -6499,7 +6526,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>90</v>
       </c>
@@ -6513,7 +6540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>91</v>
       </c>
@@ -6527,7 +6554,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>92</v>
       </c>
@@ -6541,7 +6568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>93</v>
       </c>
@@ -6555,7 +6582,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>95</v>
       </c>
@@ -6569,7 +6596,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>96</v>
       </c>
@@ -6583,7 +6610,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>97</v>
       </c>
@@ -6597,7 +6624,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>98</v>
       </c>
@@ -6611,7 +6638,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>99</v>
       </c>
@@ -6625,7 +6652,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>100</v>
       </c>
@@ -6639,7 +6666,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>101</v>
       </c>
@@ -6653,7 +6680,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>102</v>
       </c>
@@ -6667,7 +6694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>103</v>
       </c>
@@ -6681,7 +6708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>104</v>
       </c>
@@ -6695,7 +6722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>105</v>
       </c>
@@ -6709,7 +6736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>106</v>
       </c>
@@ -6723,7 +6750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>107</v>
       </c>
@@ -6737,7 +6764,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>109</v>
       </c>
@@ -6751,7 +6778,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>110</v>
       </c>
@@ -6765,7 +6792,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>111</v>
       </c>
@@ -6779,7 +6806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>112</v>
       </c>
@@ -6793,7 +6820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>113</v>
       </c>
@@ -6807,7 +6834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>114</v>
       </c>
@@ -6821,7 +6848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>115</v>
       </c>
@@ -6835,7 +6862,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>614</v>
       </c>
@@ -6849,7 +6876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>116</v>
       </c>
@@ -6863,7 +6890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>117</v>
       </c>
@@ -6877,7 +6904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>723</v>
       </c>
@@ -6891,7 +6918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>615</v>
       </c>
@@ -6905,7 +6932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>118</v>
       </c>
@@ -6919,7 +6946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>119</v>
       </c>
@@ -6933,7 +6960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>616</v>
       </c>
@@ -6947,7 +6974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>120</v>
       </c>
@@ -6961,7 +6988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>617</v>
       </c>
@@ -6975,7 +7002,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>618</v>
       </c>
@@ -6989,7 +7016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>121</v>
       </c>
@@ -7003,7 +7030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>122</v>
       </c>
@@ -7017,7 +7044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>123</v>
       </c>
@@ -7031,7 +7058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>124</v>
       </c>
@@ -7045,7 +7072,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>125</v>
       </c>
@@ -7059,7 +7086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>126</v>
       </c>
@@ -7073,7 +7100,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>619</v>
       </c>
@@ -7087,7 +7114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>620</v>
       </c>
@@ -7101,7 +7128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>127</v>
       </c>
@@ -7115,12 +7142,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>128</v>
       </c>
       <c r="B276" s="54">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="C276" s="6" t="s">
         <v>129</v>
@@ -7129,7 +7156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>130</v>
       </c>
@@ -7143,7 +7170,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>131</v>
       </c>
@@ -7157,7 +7184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>132</v>
       </c>
@@ -7171,7 +7198,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>133</v>
       </c>
@@ -7185,7 +7212,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>621</v>
       </c>
@@ -7199,7 +7226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>134</v>
       </c>
@@ -7213,7 +7240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>622</v>
       </c>
@@ -7227,7 +7254,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>135</v>
       </c>
@@ -7241,7 +7268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>136</v>
       </c>
@@ -7255,7 +7282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>137</v>
       </c>
@@ -7269,7 +7296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>138</v>
       </c>
@@ -7283,7 +7310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>623</v>
       </c>
@@ -7297,7 +7324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>139</v>
       </c>
@@ -7311,7 +7338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>140</v>
       </c>
@@ -7325,7 +7352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>141</v>
       </c>
@@ -7339,7 +7366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>142</v>
       </c>
@@ -7353,7 +7380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>143</v>
       </c>
@@ -7367,7 +7394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>144</v>
       </c>
@@ -7381,7 +7408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>145</v>
       </c>
@@ -7395,7 +7422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>146</v>
       </c>
@@ -7409,7 +7436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>624</v>
       </c>
@@ -7423,7 +7450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>625</v>
       </c>
@@ -7437,7 +7464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>626</v>
       </c>
@@ -7451,7 +7478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>627</v>
       </c>
@@ -7465,7 +7492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>628</v>
       </c>
@@ -7479,7 +7506,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>629</v>
       </c>
@@ -7493,7 +7520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>147</v>
       </c>
@@ -7507,7 +7534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>148</v>
       </c>
@@ -7521,7 +7548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>149</v>
       </c>
@@ -7535,7 +7562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>150</v>
       </c>
@@ -7549,7 +7576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>151</v>
       </c>
@@ -7563,7 +7590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>152</v>
       </c>
@@ -7577,7 +7604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>153</v>
       </c>
@@ -7591,7 +7618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>154</v>
       </c>
@@ -7605,7 +7632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>155</v>
       </c>
@@ -7619,7 +7646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
         <v>156</v>
       </c>
@@ -7633,7 +7660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
         <v>157</v>
       </c>
@@ -7647,7 +7674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
         <v>158</v>
       </c>
@@ -7661,7 +7688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
         <v>159</v>
       </c>
@@ -7675,7 +7702,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
         <v>160</v>
       </c>
@@ -7689,7 +7716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
         <v>161</v>
       </c>
@@ -7703,7 +7730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>162</v>
       </c>
@@ -7717,7 +7744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>163</v>
       </c>
@@ -7731,7 +7758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>164</v>
       </c>
@@ -7745,7 +7772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>165</v>
       </c>
@@ -7759,7 +7786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>166</v>
       </c>
@@ -7773,7 +7800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>167</v>
       </c>
@@ -7787,7 +7814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>168</v>
       </c>
@@ -7801,7 +7828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>169</v>
       </c>
@@ -7815,7 +7842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>630</v>
       </c>
@@ -7829,7 +7856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>170</v>
       </c>
@@ -7843,7 +7870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>631</v>
       </c>
@@ -7857,7 +7884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>171</v>
       </c>
@@ -7871,7 +7898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>172</v>
       </c>
@@ -7885,7 +7912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>173</v>
       </c>
@@ -7899,7 +7926,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>175</v>
       </c>
@@ -7913,7 +7940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>176</v>
       </c>
@@ -7927,7 +7954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>177</v>
       </c>
@@ -7941,7 +7968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>178</v>
       </c>
@@ -7955,7 +7982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>179</v>
       </c>
@@ -7969,7 +7996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>180</v>
       </c>
@@ -7983,7 +8010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>181</v>
       </c>
@@ -7997,7 +8024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>182</v>
       </c>
@@ -8011,7 +8038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>183</v>
       </c>
@@ -8025,7 +8052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>184</v>
       </c>
@@ -8039,7 +8066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>185</v>
       </c>
@@ -8053,7 +8080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>186</v>
       </c>
@@ -8067,7 +8094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>187</v>
       </c>
@@ -8081,7 +8108,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>188</v>
       </c>
@@ -8095,7 +8122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>189</v>
       </c>
@@ -8109,7 +8136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>190</v>
       </c>
@@ -8123,7 +8150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>191</v>
       </c>
@@ -8137,7 +8164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>192</v>
       </c>
@@ -8151,7 +8178,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>193</v>
       </c>
@@ -8165,7 +8192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>194</v>
       </c>
@@ -8179,7 +8206,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>195</v>
       </c>
@@ -8193,7 +8220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>196</v>
       </c>
@@ -8207,7 +8234,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>198</v>
       </c>
@@ -8221,7 +8248,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>200</v>
       </c>
@@ -8235,7 +8262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>201</v>
       </c>
@@ -8249,7 +8276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>202</v>
       </c>
@@ -8263,7 +8290,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>203</v>
       </c>
@@ -8277,7 +8304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>204</v>
       </c>
@@ -8291,7 +8318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>205</v>
       </c>
@@ -8305,7 +8332,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>206</v>
       </c>
@@ -8319,7 +8346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>207</v>
       </c>
@@ -8333,7 +8360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>208</v>
       </c>
@@ -8347,7 +8374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>209</v>
       </c>
@@ -8361,7 +8388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>210</v>
       </c>
@@ -8375,7 +8402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>211</v>
       </c>
@@ -8389,7 +8416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>212</v>
       </c>
@@ -8403,7 +8430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>213</v>
       </c>
@@ -8417,7 +8444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>214</v>
       </c>
@@ -8431,7 +8458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>215</v>
       </c>
@@ -8445,7 +8472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>216</v>
       </c>
@@ -8459,7 +8486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>217</v>
       </c>
@@ -8473,7 +8500,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>218</v>
       </c>
@@ -8487,7 +8514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>632</v>
       </c>
@@ -8501,7 +8528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>633</v>
       </c>
@@ -8515,7 +8542,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>634</v>
       </c>
@@ -8529,7 +8556,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>219</v>
       </c>
@@ -8543,7 +8570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>635</v>
       </c>
@@ -8557,7 +8584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>220</v>
       </c>
@@ -8571,7 +8598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>221</v>
       </c>
@@ -8585,7 +8612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>222</v>
       </c>
@@ -8599,7 +8626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>223</v>
       </c>
@@ -8613,7 +8640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>224</v>
       </c>
@@ -8627,7 +8654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>225</v>
       </c>
@@ -8641,7 +8668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>226</v>
       </c>
@@ -8655,7 +8682,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>227</v>
       </c>
@@ -8669,7 +8696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>228</v>
       </c>
@@ -8683,7 +8710,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>229</v>
       </c>
@@ -8697,7 +8724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>230</v>
       </c>
@@ -8711,7 +8738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>231</v>
       </c>
@@ -8725,7 +8752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>232</v>
       </c>
@@ -8739,7 +8766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>233</v>
       </c>
@@ -8753,7 +8780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>234</v>
       </c>
@@ -8767,7 +8794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>235</v>
       </c>
@@ -8781,7 +8808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>636</v>
       </c>
@@ -8795,7 +8822,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>637</v>
       </c>
@@ -8809,7 +8836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>638</v>
       </c>
@@ -8823,7 +8850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>639</v>
       </c>
@@ -8837,7 +8864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>236</v>
       </c>
@@ -8851,7 +8878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>237</v>
       </c>
@@ -8865,7 +8892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>238</v>
       </c>
@@ -8879,7 +8906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>239</v>
       </c>
@@ -8893,7 +8920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>640</v>
       </c>
@@ -8907,7 +8934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
         <v>240</v>
       </c>
@@ -8921,7 +8948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
         <v>241</v>
       </c>
@@ -8935,7 +8962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
         <v>641</v>
       </c>
@@ -8949,7 +8976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>242</v>
       </c>
@@ -8963,7 +8990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
         <v>243</v>
       </c>
@@ -8977,7 +9004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
         <v>244</v>
       </c>
@@ -8991,7 +9018,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>245</v>
       </c>
@@ -9005,7 +9032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>246</v>
       </c>
@@ -9019,7 +9046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>247</v>
       </c>
@@ -9033,7 +9060,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>248</v>
       </c>
@@ -9047,7 +9074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>642</v>
       </c>
@@ -9061,7 +9088,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>249</v>
       </c>
@@ -9075,7 +9102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>643</v>
       </c>
@@ -9089,7 +9116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>250</v>
       </c>
@@ -9103,7 +9130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>251</v>
       </c>
@@ -9117,7 +9144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>252</v>
       </c>
@@ -9131,7 +9158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>253</v>
       </c>
@@ -9145,7 +9172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>254</v>
       </c>
@@ -9159,7 +9186,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>255</v>
       </c>
@@ -9173,7 +9200,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>644</v>
       </c>
@@ -9187,7 +9214,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>645</v>
       </c>
@@ -9201,7 +9228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>257</v>
       </c>
@@ -9215,7 +9242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>258</v>
       </c>
@@ -9229,7 +9256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>259</v>
       </c>
@@ -9243,7 +9270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>260</v>
       </c>
@@ -9257,7 +9284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>646</v>
       </c>
@@ -9271,7 +9298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>261</v>
       </c>
@@ -9285,7 +9312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>262</v>
       </c>
@@ -9299,7 +9326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>263</v>
       </c>
@@ -9313,7 +9340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>264</v>
       </c>
@@ -9327,7 +9354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>265</v>
       </c>
@@ -9341,7 +9368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>266</v>
       </c>
@@ -9355,7 +9382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>267</v>
       </c>
@@ -9369,7 +9396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>268</v>
       </c>
@@ -9383,7 +9410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>269</v>
       </c>
@@ -9397,7 +9424,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>270</v>
       </c>
@@ -9411,7 +9438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>271</v>
       </c>
@@ -9425,7 +9452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>272</v>
       </c>
@@ -9439,7 +9466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>273</v>
       </c>
@@ -9453,7 +9480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>274</v>
       </c>
@@ -9467,7 +9494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>275</v>
       </c>
@@ -9481,7 +9508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>276</v>
       </c>
@@ -9495,7 +9522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>277</v>
       </c>
@@ -9509,7 +9536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>278</v>
       </c>
@@ -9523,7 +9550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>279</v>
       </c>
@@ -9537,7 +9564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>280</v>
       </c>
@@ -9551,7 +9578,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>281</v>
       </c>
@@ -9565,7 +9592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>282</v>
       </c>
@@ -9579,7 +9606,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
         <v>647</v>
       </c>
@@ -9593,7 +9620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>283</v>
       </c>
@@ -9607,7 +9634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>284</v>
       </c>
@@ -9621,7 +9648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>285</v>
       </c>
@@ -9635,7 +9662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>286</v>
       </c>
@@ -9649,7 +9676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>287</v>
       </c>
@@ -9663,7 +9690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>288</v>
       </c>
@@ -9677,7 +9704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>289</v>
       </c>
@@ -9691,7 +9718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>290</v>
       </c>
@@ -9705,7 +9732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>291</v>
       </c>
@@ -9719,7 +9746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>292</v>
       </c>
@@ -9733,7 +9760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>293</v>
       </c>
@@ -9747,7 +9774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>294</v>
       </c>
@@ -9761,7 +9788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>295</v>
       </c>
@@ -9775,7 +9802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>296</v>
       </c>
@@ -9789,7 +9816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>297</v>
       </c>
@@ -9803,7 +9830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
         <v>648</v>
       </c>
@@ -9817,7 +9844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>299</v>
       </c>
@@ -9831,7 +9858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>300</v>
       </c>
@@ -9845,7 +9872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>301</v>
       </c>
@@ -9859,7 +9886,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>302</v>
       </c>
@@ -9873,7 +9900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>303</v>
       </c>
@@ -9887,7 +9914,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>304</v>
       </c>
@@ -9901,7 +9928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
         <v>649</v>
       </c>
@@ -9915,7 +9942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
         <v>650</v>
       </c>
@@ -9929,7 +9956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>305</v>
       </c>
@@ -9943,7 +9970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>306</v>
       </c>
@@ -9957,7 +9984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
         <v>651</v>
       </c>
@@ -9971,7 +9998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>307</v>
       </c>
@@ -9985,7 +10012,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>308</v>
       </c>
@@ -9999,7 +10026,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>309</v>
       </c>
@@ -10013,7 +10040,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>310</v>
       </c>
@@ -10027,7 +10054,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>311</v>
       </c>
@@ -10041,7 +10068,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>312</v>
       </c>
@@ -10055,7 +10082,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>313</v>
       </c>
@@ -10069,7 +10096,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>314</v>
       </c>
@@ -10083,7 +10110,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>315</v>
       </c>
@@ -10097,7 +10124,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>316</v>
       </c>
@@ -10111,7 +10138,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>317</v>
       </c>
@@ -10125,7 +10152,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>318</v>
       </c>
@@ -10139,7 +10166,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>319</v>
       </c>
@@ -10153,7 +10180,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>320</v>
       </c>
@@ -10167,7 +10194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>321</v>
       </c>
@@ -10181,7 +10208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>322</v>
       </c>
@@ -10195,7 +10222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>323</v>
       </c>
@@ -10209,7 +10236,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="4" t="s">
         <v>324</v>
       </c>
@@ -10223,7 +10250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
         <v>652</v>
       </c>
@@ -10237,7 +10264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="4" t="s">
         <v>653</v>
       </c>
@@ -10251,7 +10278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
         <v>654</v>
       </c>
@@ -10265,7 +10292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="4" t="s">
         <v>655</v>
       </c>
@@ -10279,7 +10306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
         <v>656</v>
       </c>
@@ -10293,7 +10320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>325</v>
       </c>
@@ -10307,7 +10334,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>326</v>
       </c>
@@ -10321,7 +10348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>327</v>
       </c>
@@ -10335,7 +10362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>328</v>
       </c>
@@ -10349,7 +10376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>329</v>
       </c>
@@ -10363,7 +10390,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>330</v>
       </c>
@@ -10377,7 +10404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>331</v>
       </c>
@@ -10391,7 +10418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>332</v>
       </c>
@@ -10405,7 +10432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
         <v>657</v>
       </c>
@@ -10419,7 +10446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
         <v>658</v>
       </c>
@@ -10433,7 +10460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>333</v>
       </c>
@@ -10447,7 +10474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
         <v>659</v>
       </c>
@@ -10461,7 +10488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="4" t="s">
         <v>660</v>
       </c>
@@ -10475,7 +10502,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
         <v>334</v>
       </c>
@@ -10489,7 +10516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="4" t="s">
         <v>335</v>
       </c>
@@ -10503,7 +10530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
         <v>336</v>
       </c>
@@ -10517,7 +10544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="4" t="s">
         <v>337</v>
       </c>
@@ -10531,7 +10558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
         <v>338</v>
       </c>
@@ -10545,7 +10572,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>339</v>
       </c>
@@ -10559,7 +10586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
         <v>340</v>
       </c>
@@ -10573,7 +10600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="4" t="s">
         <v>341</v>
       </c>
@@ -10587,7 +10614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
         <v>661</v>
       </c>
@@ -10601,7 +10628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
         <v>662</v>
       </c>
@@ -10615,7 +10642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
         <v>663</v>
       </c>
@@ -10629,7 +10656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="4" t="s">
         <v>664</v>
       </c>
@@ -10643,7 +10670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
         <v>665</v>
       </c>
@@ -10657,7 +10684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
         <v>666</v>
       </c>
@@ -10671,7 +10698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
         <v>667</v>
       </c>
@@ -10685,7 +10712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="4" t="s">
         <v>668</v>
       </c>
@@ -10699,7 +10726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
         <v>669</v>
       </c>
@@ -10713,7 +10740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="4" t="s">
         <v>670</v>
       </c>
@@ -10727,7 +10754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
         <v>671</v>
       </c>
@@ -10741,7 +10768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="4" t="s">
         <v>672</v>
       </c>
@@ -10755,7 +10782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
         <v>673</v>
       </c>
@@ -10769,7 +10796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="4" t="s">
         <v>674</v>
       </c>
@@ -10783,7 +10810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="4" t="s">
         <v>675</v>
       </c>
@@ -10797,7 +10824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="4" t="s">
         <v>676</v>
       </c>
@@ -10811,7 +10838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="4" t="s">
         <v>677</v>
       </c>
@@ -10825,7 +10852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="4" t="s">
         <v>678</v>
       </c>
@@ -10839,7 +10866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="4" t="s">
         <v>679</v>
       </c>
@@ -10853,7 +10880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="4" t="s">
         <v>680</v>
       </c>
@@ -10867,7 +10894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="4" t="s">
         <v>342</v>
       </c>
@@ -10881,7 +10908,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="4" t="s">
         <v>343</v>
       </c>
@@ -10895,7 +10922,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="4" t="s">
         <v>344</v>
       </c>
@@ -10909,7 +10936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="4" t="s">
         <v>345</v>
       </c>
@@ -10923,7 +10950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="4" t="s">
         <v>346</v>
       </c>
@@ -10937,7 +10964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="4" t="s">
         <v>347</v>
       </c>
@@ -10951,7 +10978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="4" t="s">
         <v>348</v>
       </c>
@@ -10965,7 +10992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="4" t="s">
         <v>349</v>
       </c>
@@ -10979,7 +11006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="4" t="s">
         <v>350</v>
       </c>
@@ -10993,7 +11020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="4" t="s">
         <v>351</v>
       </c>
@@ -11007,7 +11034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="4" t="s">
         <v>681</v>
       </c>
@@ -11021,7 +11048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="4" t="s">
         <v>352</v>
       </c>
@@ -11035,7 +11062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="4" t="s">
         <v>353</v>
       </c>
@@ -11049,7 +11076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="4" t="s">
         <v>682</v>
       </c>
@@ -11063,7 +11090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="4" t="s">
         <v>354</v>
       </c>
@@ -11077,7 +11104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="4" t="s">
         <v>355</v>
       </c>
@@ -11091,7 +11118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="4" t="s">
         <v>356</v>
       </c>
@@ -11105,7 +11132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="4" t="s">
         <v>357</v>
       </c>
@@ -11119,7 +11146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="4" t="s">
         <v>683</v>
       </c>
@@ -11133,7 +11160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="4" t="s">
         <v>358</v>
       </c>
@@ -11147,7 +11174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="4" t="s">
         <v>359</v>
       </c>
@@ -11161,7 +11188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="4" t="s">
         <v>360</v>
       </c>
@@ -11175,7 +11202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="4" t="s">
         <v>361</v>
       </c>
@@ -11189,7 +11216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="4" t="s">
         <v>362</v>
       </c>
@@ -11203,7 +11230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="4" t="s">
         <v>363</v>
       </c>
@@ -11217,7 +11244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="4" t="s">
         <v>364</v>
       </c>
@@ -11231,7 +11258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="4" t="s">
         <v>365</v>
       </c>
@@ -11245,7 +11272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="4" t="s">
         <v>366</v>
       </c>
@@ -11259,7 +11286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="4" t="s">
         <v>367</v>
       </c>
@@ -11273,7 +11300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="4" t="s">
         <v>368</v>
       </c>
@@ -11287,7 +11314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="4" t="s">
         <v>369</v>
       </c>
@@ -11301,7 +11328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="4" t="s">
         <v>370</v>
       </c>
@@ -11315,7 +11342,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="4" t="s">
         <v>371</v>
       </c>
@@ -11329,7 +11356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="4" t="s">
         <v>372</v>
       </c>
@@ -11343,7 +11370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="4" t="s">
         <v>373</v>
       </c>
@@ -11357,7 +11384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="4" t="s">
         <v>374</v>
       </c>
@@ -11371,7 +11398,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="4" t="s">
         <v>684</v>
       </c>
@@ -11385,7 +11412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="4" t="s">
         <v>685</v>
       </c>
@@ -11399,7 +11426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="4" t="s">
         <v>686</v>
       </c>
@@ -11413,7 +11440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="4" t="s">
         <v>687</v>
       </c>
@@ -11427,7 +11454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="4" t="s">
         <v>688</v>
       </c>
@@ -11441,7 +11468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="4" t="s">
         <v>375</v>
       </c>
@@ -11455,7 +11482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="4" t="s">
         <v>376</v>
       </c>
@@ -11469,7 +11496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="4" t="s">
         <v>377</v>
       </c>
@@ -11483,7 +11510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="4" t="s">
         <v>378</v>
       </c>
@@ -11497,7 +11524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="4" t="s">
         <v>379</v>
       </c>
@@ -11511,7 +11538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="4" t="s">
         <v>380</v>
       </c>
@@ -11525,7 +11552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="4" t="s">
         <v>689</v>
       </c>
@@ -11539,7 +11566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="4" t="s">
         <v>381</v>
       </c>
@@ -11553,7 +11580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="4" t="s">
         <v>382</v>
       </c>
@@ -11567,7 +11594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="4" t="s">
         <v>383</v>
       </c>
@@ -11581,7 +11608,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="4" t="s">
         <v>384</v>
       </c>
@@ -11595,7 +11622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="4" t="s">
         <v>385</v>
       </c>
@@ -11609,7 +11636,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="4" t="s">
         <v>386</v>
       </c>
@@ -11623,7 +11650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="4" t="s">
         <v>387</v>
       </c>
@@ -11637,7 +11664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="4" t="s">
         <v>388</v>
       </c>
@@ -11651,7 +11678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="4" t="s">
         <v>690</v>
       </c>
@@ -11665,7 +11692,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="4" t="s">
         <v>389</v>
       </c>
@@ -11679,7 +11706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="4" t="s">
         <v>390</v>
       </c>
@@ -11693,7 +11720,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="4" t="s">
         <v>391</v>
       </c>
@@ -11707,7 +11734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="4" t="s">
         <v>691</v>
       </c>
@@ -11721,7 +11748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="4" t="s">
         <v>392</v>
       </c>
@@ -11735,7 +11762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="4" t="s">
         <v>692</v>
       </c>
@@ -11749,7 +11776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="4" t="s">
         <v>393</v>
       </c>
@@ -11763,7 +11790,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="4" t="s">
         <v>394</v>
       </c>
@@ -11777,7 +11804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="4" t="s">
         <v>395</v>
       </c>
@@ -11791,7 +11818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="4" t="s">
         <v>396</v>
       </c>
@@ -11805,7 +11832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="4" t="s">
         <v>397</v>
       </c>
@@ -11819,7 +11846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="4" t="s">
         <v>398</v>
       </c>
@@ -11833,7 +11860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="4" t="s">
         <v>399</v>
       </c>
@@ -11847,7 +11874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="4" t="s">
         <v>400</v>
       </c>
@@ -11861,7 +11888,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="4" t="s">
         <v>401</v>
       </c>
@@ -11875,7 +11902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="4" t="s">
         <v>402</v>
       </c>
@@ -11889,7 +11916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="4" t="s">
         <v>403</v>
       </c>
@@ -11903,7 +11930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="4" t="s">
         <v>693</v>
       </c>
@@ -11917,7 +11944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="4" t="s">
         <v>404</v>
       </c>
@@ -11931,7 +11958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="4" t="s">
         <v>694</v>
       </c>
@@ -11945,7 +11972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="4" t="s">
         <v>405</v>
       </c>
@@ -11959,7 +11986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="4" t="s">
         <v>406</v>
       </c>
@@ -11973,7 +12000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="4" t="s">
         <v>407</v>
       </c>
@@ -11987,7 +12014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="4" t="s">
         <v>408</v>
       </c>
@@ -12001,7 +12028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="4" t="s">
         <v>409</v>
       </c>
@@ -12015,7 +12042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="4" t="s">
         <v>410</v>
       </c>
@@ -12029,7 +12056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="4" t="s">
         <v>411</v>
       </c>
@@ -12043,7 +12070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="4" t="s">
         <v>412</v>
       </c>
@@ -12057,7 +12084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="4" t="s">
         <v>413</v>
       </c>
@@ -12071,7 +12098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="4" t="s">
         <v>414</v>
       </c>
@@ -12085,7 +12112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="4" t="s">
         <v>415</v>
       </c>
@@ -12099,7 +12126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="4" t="s">
         <v>695</v>
       </c>
@@ -12113,7 +12140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="4" t="s">
         <v>416</v>
       </c>
@@ -12127,7 +12154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="4" t="s">
         <v>417</v>
       </c>
@@ -12141,7 +12168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="4" t="s">
         <v>418</v>
       </c>
@@ -12155,7 +12182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="4" t="s">
         <v>419</v>
       </c>
@@ -12169,7 +12196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="4" t="s">
         <v>420</v>
       </c>
@@ -12183,7 +12210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="4" t="s">
         <v>421</v>
       </c>
@@ -12197,7 +12224,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="4" t="s">
         <v>423</v>
       </c>
@@ -12211,7 +12238,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="4" t="s">
         <v>425</v>
       </c>
@@ -12225,7 +12252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="4" t="s">
         <v>696</v>
       </c>
@@ -12239,7 +12266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="4" t="s">
         <v>426</v>
       </c>
@@ -12253,7 +12280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="4" t="s">
         <v>427</v>
       </c>
@@ -12267,7 +12294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="4" t="s">
         <v>428</v>
       </c>
@@ -12281,7 +12308,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="4" t="s">
         <v>697</v>
       </c>
@@ -12295,7 +12322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="4" t="s">
         <v>429</v>
       </c>
@@ -12309,7 +12336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="4" t="s">
         <v>430</v>
       </c>
@@ -12323,7 +12350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="4" t="s">
         <v>431</v>
       </c>
@@ -12337,7 +12364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="4" t="s">
         <v>432</v>
       </c>
@@ -12351,7 +12378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="4" t="s">
         <v>433</v>
       </c>
@@ -12365,7 +12392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="4" t="s">
         <v>434</v>
       </c>
@@ -12379,7 +12406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="4" t="s">
         <v>435</v>
       </c>
@@ -12393,7 +12420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="4" t="s">
         <v>436</v>
       </c>
@@ -12407,7 +12434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="4" t="s">
         <v>437</v>
       </c>
@@ -12421,7 +12448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="4" t="s">
         <v>438</v>
       </c>
@@ -12435,7 +12462,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="4" t="s">
         <v>439</v>
       </c>
@@ -12449,7 +12476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="4" t="s">
         <v>440</v>
       </c>
@@ -12463,7 +12490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="4" t="s">
         <v>441</v>
       </c>
@@ -12477,7 +12504,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="4" t="s">
         <v>442</v>
       </c>
@@ -12491,7 +12518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="7" t="s">
         <v>443</v>
       </c>
@@ -12505,7 +12532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="7" t="s">
         <v>444</v>
       </c>
@@ -12519,7 +12546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="8" t="s">
         <v>445</v>
       </c>
@@ -12533,7 +12560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="10" t="s">
         <v>446</v>
       </c>
@@ -12547,7 +12574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="10" t="s">
         <v>447</v>
       </c>
@@ -12561,7 +12588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="10" t="s">
         <v>448</v>
       </c>
@@ -12575,7 +12602,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A666" s="4" t="s">
         <v>449</v>
       </c>
@@ -12589,7 +12616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A667" s="10" t="s">
         <v>450</v>
       </c>
@@ -12603,7 +12630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A668" s="10" t="s">
         <v>451</v>
       </c>
@@ -12617,7 +12644,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A669" s="4" t="s">
         <v>452</v>
       </c>
@@ -12631,7 +12658,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A670" s="4" t="s">
         <v>453</v>
       </c>
@@ -12645,7 +12672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A671" s="4" t="s">
         <v>454</v>
       </c>
@@ -12659,7 +12686,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A672" s="10" t="s">
         <v>455</v>
       </c>
@@ -12673,7 +12700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A673" s="10" t="s">
         <v>456</v>
       </c>
@@ -12687,7 +12714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A674" s="4" t="s">
         <v>457</v>
       </c>
@@ -12701,7 +12728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A675" s="50" t="s">
         <v>698</v>
       </c>
@@ -12715,7 +12742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A676" s="50" t="s">
         <v>699</v>
       </c>
@@ -12729,7 +12756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A677" s="50" t="s">
         <v>700</v>
       </c>
@@ -12743,7 +12770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A678" s="50" t="s">
         <v>701</v>
       </c>
@@ -12757,7 +12784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A679" s="4" t="s">
         <v>702</v>
       </c>
@@ -12771,7 +12798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A680" s="51" t="s">
         <v>703</v>
       </c>
@@ -12785,7 +12812,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A681" s="51" t="s">
         <v>704</v>
       </c>
@@ -12799,7 +12826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A682" s="59" t="s">
         <v>705</v>
       </c>
@@ -12813,7 +12840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A683" s="61" t="s">
         <v>707</v>
       </c>
@@ -12827,7 +12854,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A684" s="61" t="s">
         <v>708</v>
       </c>
@@ -12841,7 +12868,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A685" s="61" t="s">
         <v>709</v>
       </c>
@@ -12855,7 +12882,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A686" s="61" t="s">
         <v>711</v>
       </c>
@@ -12869,7 +12896,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A687" s="61" t="s">
         <v>712</v>
       </c>
@@ -12883,7 +12910,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A688" s="61" t="s">
         <v>713</v>
       </c>
@@ -12897,7 +12924,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A689" s="4" t="s">
         <v>714</v>
       </c>
@@ -12911,7 +12938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A690" s="4" t="s">
         <v>715</v>
       </c>
@@ -12925,7 +12952,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A691" s="4" t="s">
         <v>716</v>
       </c>
@@ -12939,7 +12966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A692" s="4" t="s">
         <v>717</v>
       </c>
@@ -12953,7 +12980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A693" s="4" t="s">
         <v>718</v>
       </c>
@@ -12967,7 +12994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A694" s="50" t="s">
         <v>719</v>
       </c>
@@ -12981,7 +13008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A695" s="50" t="s">
         <v>720</v>
       </c>
@@ -12995,7 +13022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="50" t="s">
         <v>721</v>
       </c>
@@ -13009,7 +13036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A697" s="65" t="s">
         <v>722</v>
       </c>
@@ -13023,7 +13050,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A698" s="68" t="s">
         <v>724</v>
       </c>
@@ -13037,7 +13064,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A699" s="68" t="s">
         <v>725</v>
       </c>
@@ -13051,7 +13078,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A700" s="68" t="s">
         <v>727</v>
       </c>
@@ -13065,7 +13092,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A701" s="68" t="s">
         <v>726</v>
       </c>
@@ -13079,7 +13106,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A702" s="68" t="s">
         <v>728</v>
       </c>
@@ -13093,7 +13120,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A703" s="68" t="s">
         <v>729</v>
       </c>
@@ -13107,7 +13134,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A704" s="68" t="s">
         <v>730</v>
       </c>
@@ -13121,7 +13148,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A705" s="70" t="s">
         <v>731</v>
       </c>
@@ -13135,7 +13162,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A706" s="68" t="s">
         <v>732</v>
       </c>
@@ -13149,7 +13176,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A707" s="68" t="s">
         <v>733</v>
       </c>
@@ -13163,7 +13190,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A708" s="68" t="s">
         <v>734</v>
       </c>
@@ -13177,7 +13204,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A709" s="68" t="s">
         <v>735</v>
       </c>
@@ -13191,7 +13218,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A710" s="68" t="s">
         <v>737</v>
       </c>
@@ -13205,7 +13232,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A711" s="68" t="s">
         <v>738</v>
       </c>
@@ -13219,7 +13246,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A712" s="68" t="s">
         <v>739</v>
       </c>
@@ -13233,7 +13260,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A713" s="68" t="s">
         <v>740</v>
       </c>
@@ -13247,7 +13274,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A714" s="50" t="s">
         <v>741</v>
       </c>
@@ -13261,7 +13288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A715" s="50" t="s">
         <v>747</v>
       </c>
@@ -13275,7 +13302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A716" s="50" t="s">
         <v>742</v>
       </c>
@@ -13289,7 +13316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A717" s="50" t="s">
         <v>748</v>
       </c>
@@ -13303,7 +13330,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A718" s="50" t="s">
         <v>749</v>
       </c>
@@ -13317,7 +13344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A719" s="50" t="s">
         <v>750</v>
       </c>
@@ -13331,7 +13358,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A720" s="50" t="s">
         <v>743</v>
       </c>
@@ -13345,7 +13372,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A721" s="50" t="s">
         <v>751</v>
       </c>
@@ -13359,7 +13386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A722" s="50" t="s">
         <v>744</v>
       </c>
@@ -13373,7 +13400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A723" s="50" t="s">
         <v>745</v>
       </c>
@@ -13387,7 +13414,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A724" s="74" t="s">
         <v>746</v>
       </c>
@@ -13401,7 +13428,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="725" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A725" s="61" t="s">
         <v>753</v>
       </c>
@@ -13415,7 +13442,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="726" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A726" s="61" t="s">
         <v>754</v>
       </c>
@@ -13429,7 +13456,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="727" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A727" s="61" t="s">
         <v>755</v>
       </c>
@@ -13443,7 +13470,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="728" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A728" s="61" t="s">
         <v>756</v>
       </c>
@@ -13457,7 +13484,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="729" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A729" s="61" t="s">
         <v>757</v>
       </c>
@@ -13471,7 +13498,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="730" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A730" s="61" t="s">
         <v>758</v>
       </c>
@@ -13485,7 +13512,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="731" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A731" s="61" t="s">
         <v>759</v>
       </c>
@@ -13499,7 +13526,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="732" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A732" s="61" t="s">
         <v>760</v>
       </c>
@@ -13513,445 +13540,517 @@
         <v>462</v>
       </c>
     </row>
-    <row r="733" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A733" s="61"/>
-      <c r="B733" s="69"/>
-      <c r="C733" s="63"/>
-      <c r="D733" s="63"/>
-    </row>
-    <row r="734" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A734" s="61"/>
-      <c r="B734" s="69"/>
-      <c r="C734" s="63"/>
-      <c r="D734" s="63"/>
-    </row>
-    <row r="735" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A735" s="61"/>
-      <c r="B735" s="69"/>
-      <c r="C735" s="63"/>
-      <c r="D735" s="63"/>
-    </row>
-    <row r="736" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A736" s="61"/>
-      <c r="B736" s="69"/>
-      <c r="C736" s="63"/>
-      <c r="D736" s="63"/>
-    </row>
-    <row r="737" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A737" s="61"/>
-      <c r="B737" s="69"/>
-      <c r="C737" s="63"/>
-      <c r="D737" s="63"/>
-    </row>
-    <row r="738" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A738" s="61"/>
-      <c r="B738" s="69"/>
-      <c r="C738" s="63"/>
-      <c r="D738" s="63"/>
-    </row>
-    <row r="739" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A739" s="61"/>
-      <c r="B739" s="69"/>
-      <c r="C739" s="63"/>
-      <c r="D739" s="63"/>
-    </row>
-    <row r="740" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A740" s="61"/>
-      <c r="B740" s="69"/>
-      <c r="C740" s="63"/>
-      <c r="D740" s="63"/>
-    </row>
-    <row r="741" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A741" s="61"/>
-      <c r="B741" s="69"/>
-      <c r="C741" s="63"/>
-      <c r="D741" s="63"/>
-    </row>
-    <row r="742" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A733" s="61" t="s">
+        <v>761</v>
+      </c>
+      <c r="B733" s="69">
+        <v>0.74</v>
+      </c>
+      <c r="C733" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D733" s="63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A734" s="61" t="s">
+        <v>762</v>
+      </c>
+      <c r="B734" s="69">
+        <v>1.6</v>
+      </c>
+      <c r="C734" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D734" s="63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A735" s="61" t="s">
+        <v>763</v>
+      </c>
+      <c r="B735" s="69">
+        <v>1.55</v>
+      </c>
+      <c r="C735" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D735" s="63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A736" s="61" t="s">
+        <v>764</v>
+      </c>
+      <c r="B736" s="69">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C736" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D736" s="63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A737" s="61" t="s">
+        <v>765</v>
+      </c>
+      <c r="B737" s="69">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C737" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D737" s="63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A738" s="61" t="s">
+        <v>766</v>
+      </c>
+      <c r="B738" s="69">
+        <v>0.82</v>
+      </c>
+      <c r="C738" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D738" s="63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A739" s="61" t="s">
+        <v>767</v>
+      </c>
+      <c r="B739" s="69">
+        <v>1.5</v>
+      </c>
+      <c r="C739" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D739" s="63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A740" s="61" t="s">
+        <v>768</v>
+      </c>
+      <c r="B740" s="69">
+        <v>1.05</v>
+      </c>
+      <c r="C740" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D740" s="63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A741" s="61" t="s">
+        <v>769</v>
+      </c>
+      <c r="B741" s="69">
+        <v>1.3</v>
+      </c>
+      <c r="C741" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D741" s="63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A742" s="61"/>
       <c r="B742" s="69"/>
       <c r="C742" s="63"/>
       <c r="D742" s="63"/>
     </row>
-    <row r="743" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A743" s="61"/>
       <c r="B743" s="69"/>
       <c r="C743" s="63"/>
       <c r="D743" s="63"/>
     </row>
-    <row r="744" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A744" s="61"/>
       <c r="B744" s="69"/>
       <c r="C744" s="63"/>
       <c r="D744" s="63"/>
     </row>
-    <row r="745" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A745" s="61"/>
       <c r="B745" s="69"/>
       <c r="C745" s="63"/>
       <c r="D745" s="63"/>
     </row>
-    <row r="746" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A746" s="61"/>
       <c r="B746" s="69"/>
       <c r="C746" s="63"/>
       <c r="D746" s="63"/>
     </row>
-    <row r="747" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A747" s="61"/>
       <c r="B747" s="69"/>
       <c r="C747" s="63"/>
       <c r="D747" s="63"/>
     </row>
-    <row r="748" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A748" s="61"/>
       <c r="B748" s="69"/>
       <c r="C748" s="63"/>
       <c r="D748" s="63"/>
     </row>
-    <row r="749" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A749" s="61"/>
       <c r="B749" s="69"/>
       <c r="C749" s="63"/>
       <c r="D749" s="63"/>
     </row>
-    <row r="750" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A750" s="61"/>
       <c r="B750" s="69"/>
       <c r="C750" s="63"/>
       <c r="D750" s="63"/>
     </row>
-    <row r="751" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A751" s="61"/>
       <c r="B751" s="69"/>
       <c r="C751" s="63"/>
       <c r="D751" s="63"/>
     </row>
-    <row r="752" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A752" s="61"/>
       <c r="B752" s="69"/>
       <c r="C752" s="63"/>
       <c r="D752" s="63"/>
     </row>
-    <row r="753" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A753" s="61"/>
       <c r="B753" s="69"/>
       <c r="C753" s="63"/>
       <c r="D753" s="63"/>
     </row>
-    <row r="754" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A754" s="61"/>
       <c r="B754" s="69"/>
       <c r="C754" s="63"/>
       <c r="D754" s="63"/>
     </row>
-    <row r="755" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A755" s="61"/>
       <c r="B755" s="69"/>
       <c r="C755" s="63"/>
       <c r="D755" s="63"/>
     </row>
-    <row r="756" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A756" s="61"/>
       <c r="B756" s="69"/>
       <c r="C756" s="63"/>
       <c r="D756" s="63"/>
     </row>
-    <row r="757" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A757" s="61"/>
       <c r="B757" s="69"/>
       <c r="C757" s="63"/>
       <c r="D757" s="63"/>
     </row>
-    <row r="758" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A758" s="61"/>
       <c r="B758" s="69"/>
       <c r="C758" s="63"/>
       <c r="D758" s="63"/>
     </row>
-    <row r="759" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A759" s="61"/>
       <c r="B759" s="69"/>
       <c r="C759" s="63"/>
       <c r="D759" s="63"/>
     </row>
-    <row r="760" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A760" s="61"/>
       <c r="B760" s="69"/>
       <c r="C760" s="63"/>
       <c r="D760" s="63"/>
     </row>
-    <row r="761" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A761" s="61"/>
       <c r="B761" s="69"/>
       <c r="C761" s="63"/>
       <c r="D761" s="63"/>
     </row>
-    <row r="762" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A762" s="61"/>
       <c r="B762" s="69"/>
       <c r="C762" s="63"/>
       <c r="D762" s="63"/>
     </row>
-    <row r="763" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A763" s="61"/>
       <c r="B763" s="69"/>
       <c r="C763" s="63"/>
       <c r="D763" s="63"/>
     </row>
-    <row r="764" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A764" s="61"/>
       <c r="B764" s="69"/>
       <c r="C764" s="63"/>
       <c r="D764" s="63"/>
     </row>
-    <row r="765" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A765" s="61"/>
       <c r="B765" s="69"/>
       <c r="C765" s="63"/>
       <c r="D765" s="63"/>
     </row>
-    <row r="766" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A766" s="61"/>
       <c r="B766" s="69"/>
       <c r="C766" s="63"/>
       <c r="D766" s="63"/>
     </row>
-    <row r="767" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A767" s="61"/>
       <c r="B767" s="69"/>
       <c r="C767" s="63"/>
       <c r="D767" s="63"/>
     </row>
-    <row r="768" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A768" s="61"/>
       <c r="B768" s="69"/>
       <c r="C768" s="63"/>
       <c r="D768" s="63"/>
     </row>
-    <row r="769" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A769" s="61"/>
       <c r="B769" s="69"/>
       <c r="C769" s="63"/>
       <c r="D769" s="63"/>
     </row>
-    <row r="770" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A770" s="61"/>
       <c r="B770" s="69"/>
       <c r="C770" s="63"/>
       <c r="D770" s="63"/>
     </row>
-    <row r="771" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A771" s="61"/>
       <c r="B771" s="69"/>
       <c r="C771" s="63"/>
       <c r="D771" s="63"/>
     </row>
-    <row r="772" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A772" s="61"/>
       <c r="B772" s="69"/>
       <c r="C772" s="63"/>
       <c r="D772" s="63"/>
     </row>
-    <row r="773" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A773" s="61"/>
       <c r="B773" s="69"/>
       <c r="C773" s="63"/>
       <c r="D773" s="63"/>
     </row>
-    <row r="774" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A774" s="61"/>
       <c r="B774" s="69"/>
       <c r="C774" s="63"/>
       <c r="D774" s="63"/>
     </row>
-    <row r="775" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A775" s="61"/>
       <c r="B775" s="69"/>
       <c r="C775" s="63"/>
       <c r="D775" s="63"/>
     </row>
-    <row r="776" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A776" s="61"/>
       <c r="B776" s="69"/>
       <c r="C776" s="63"/>
       <c r="D776" s="63"/>
     </row>
-    <row r="777" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A777" s="61"/>
       <c r="B777" s="69"/>
       <c r="C777" s="63"/>
       <c r="D777" s="63"/>
     </row>
-    <row r="778" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A778" s="61"/>
       <c r="B778" s="69"/>
       <c r="C778" s="63"/>
       <c r="D778" s="63"/>
     </row>
-    <row r="779" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A779" s="61"/>
       <c r="B779" s="69"/>
       <c r="C779" s="63"/>
       <c r="D779" s="63"/>
     </row>
-    <row r="780" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A780" s="61"/>
       <c r="B780" s="69"/>
       <c r="C780" s="63"/>
       <c r="D780" s="63"/>
     </row>
-    <row r="781" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A781" s="61"/>
       <c r="B781" s="69"/>
       <c r="C781" s="63"/>
       <c r="D781" s="63"/>
     </row>
-    <row r="782" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A782" s="61"/>
       <c r="B782" s="69"/>
       <c r="C782" s="63"/>
       <c r="D782" s="63"/>
     </row>
-    <row r="783" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A783" s="61"/>
       <c r="B783" s="69"/>
       <c r="C783" s="63"/>
       <c r="D783" s="63"/>
     </row>
-    <row r="784" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A784" s="61"/>
       <c r="B784" s="69"/>
       <c r="C784" s="63"/>
       <c r="D784" s="63"/>
     </row>
-    <row r="785" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A785" s="61"/>
       <c r="B785" s="69"/>
       <c r="C785" s="63"/>
       <c r="D785" s="63"/>
     </row>
-    <row r="786" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A786" s="61"/>
       <c r="B786" s="69"/>
       <c r="C786" s="63"/>
       <c r="D786" s="63"/>
     </row>
-    <row r="787" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A787" s="61"/>
       <c r="B787" s="69"/>
       <c r="C787" s="63"/>
       <c r="D787" s="63"/>
     </row>
-    <row r="788" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A788" s="61"/>
       <c r="B788" s="69"/>
       <c r="C788" s="63"/>
       <c r="D788" s="63"/>
     </row>
-    <row r="789" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A789" s="61"/>
       <c r="B789" s="69"/>
       <c r="C789" s="63"/>
       <c r="D789" s="63"/>
     </row>
-    <row r="790" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A790" s="61"/>
       <c r="B790" s="69"/>
       <c r="C790" s="63"/>
       <c r="D790" s="63"/>
     </row>
-    <row r="791" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A791" s="61"/>
       <c r="B791" s="69"/>
       <c r="C791" s="63"/>
       <c r="D791" s="63"/>
     </row>
-    <row r="792" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A792" s="61"/>
       <c r="B792" s="69"/>
       <c r="C792" s="63"/>
       <c r="D792" s="63"/>
     </row>
-    <row r="793" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A793" s="61"/>
       <c r="B793" s="69"/>
       <c r="C793" s="63"/>
       <c r="D793" s="63"/>
     </row>
-    <row r="794" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A794" s="61"/>
       <c r="B794" s="69"/>
       <c r="C794" s="63"/>
       <c r="D794" s="63"/>
     </row>
-    <row r="795" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A795" s="61"/>
       <c r="B795" s="69"/>
       <c r="C795" s="63"/>
       <c r="D795" s="63"/>
     </row>
-    <row r="796" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A796" s="61"/>
       <c r="B796" s="69"/>
       <c r="C796" s="63"/>
       <c r="D796" s="63"/>
     </row>
-    <row r="797" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A797" s="61"/>
       <c r="B797" s="69"/>
       <c r="C797" s="63"/>
       <c r="D797" s="63"/>
     </row>
-    <row r="798" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A798" s="61"/>
       <c r="B798" s="69"/>
       <c r="C798" s="63"/>
       <c r="D798" s="63"/>
     </row>
-    <row r="799" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A799" s="61"/>
       <c r="B799" s="69"/>
       <c r="C799" s="63"/>
       <c r="D799" s="63"/>
     </row>
-    <row r="800" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A800" s="61"/>
       <c r="B800" s="69"/>
       <c r="C800" s="63"/>
       <c r="D800" s="63"/>
     </row>
-    <row r="801" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A801" s="61"/>
       <c r="B801" s="69"/>
       <c r="C801" s="63"/>
       <c r="D801" s="63"/>
     </row>
-    <row r="802" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A802" s="61"/>
       <c r="B802" s="69"/>
       <c r="C802" s="63"/>
       <c r="D802" s="63"/>
     </row>
-    <row r="803" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A803" s="61"/>
       <c r="B803" s="69"/>
       <c r="C803" s="63"/>
       <c r="D803" s="63"/>
     </row>
-    <row r="804" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A804" s="61"/>
       <c r="B804" s="69"/>
       <c r="C804" s="63"/>
       <c r="D804" s="63"/>
     </row>
-    <row r="805" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A805" s="61"/>
       <c r="B805" s="69"/>
       <c r="C805" s="63"/>
       <c r="D805" s="63"/>
     </row>
-    <row r="806" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A806" s="61"/>
       <c r="B806" s="69"/>
       <c r="C806" s="63"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6169B7-E9B8-4730-8343-E8589072467A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2053AF-9D43-4EC5-9D43-E849764F1A22}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="771">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2340,6 +2340,9 @@
   </si>
   <si>
     <t>Crumbole Cacao</t>
+  </si>
+  <si>
+    <t>Dextrose Powder</t>
   </si>
 </sst>
 </file>
@@ -13667,10 +13670,18 @@
       </c>
     </row>
     <row r="742" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A742" s="61"/>
-      <c r="B742" s="69"/>
-      <c r="C742" s="63"/>
-      <c r="D742" s="63"/>
+      <c r="A742" s="61" t="s">
+        <v>770</v>
+      </c>
+      <c r="B742" s="69">
+        <v>0.12</v>
+      </c>
+      <c r="C742" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D742" s="63" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="743" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A743" s="61"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2053AF-9D43-4EC5-9D43-E849764F1A22}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC841BC-E7A6-4237-917E-58853D97759A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="770">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -417,9 +417,6 @@
   </si>
   <si>
     <t>Cream - Full Whipping</t>
-  </si>
-  <si>
-    <t>liter</t>
   </si>
   <si>
     <t>Cream - Mascarpone</t>
@@ -3311,7 +3308,7 @@
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
@@ -3325,7 +3322,7 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B3" s="36">
         <v>0.19</v>
@@ -3334,96 +3331,96 @@
         <v>1</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B4" s="37">
         <v>12.63</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B5" s="36">
         <v>0.13</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B6" s="36">
         <v>0.36</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B7" s="37">
         <v>270</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B8" s="37">
         <v>350</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B9" s="37">
         <v>36.5</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B10" s="38">
         <v>0.24299999999999999</v>
@@ -3432,12 +3429,12 @@
         <v>1</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B11" s="38">
         <v>0.111</v>
@@ -3446,194 +3443,194 @@
         <v>1</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B12" s="37">
         <v>261.39999999999998</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B13" s="37">
         <v>153.33000000000001</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B14" s="38">
         <v>219.96</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B15" s="38">
         <v>24.75</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B16" s="37">
         <v>85</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B17" s="37">
         <v>73.12</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B18" s="40">
         <v>72.010000000000005</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B19" s="41">
         <v>8</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B20" s="41">
         <v>72.91</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B21" s="41">
         <v>10</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="22" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B22" s="42">
         <v>18.5</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B23" s="38">
         <v>23.66</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B24" s="38">
         <v>196.62</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B25" s="38">
         <v>11.02</v>
@@ -3642,12 +3639,12 @@
         <v>32</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="17" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B26" s="38">
         <v>8.65</v>
@@ -3656,12 +3653,12 @@
         <v>32</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B27" s="38">
         <v>0.85199999999999998</v>
@@ -3670,40 +3667,40 @@
         <v>1</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B28" s="34">
         <v>0.53</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B29" s="38">
         <v>36.03</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="17" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B30" s="36">
         <v>0.31</v>
@@ -3712,68 +3709,68 @@
         <v>1</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="17" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B31" s="37">
         <v>25.39</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B32" s="37">
         <v>80.88</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B33" s="41">
         <v>179.51</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="23" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B34" s="37">
         <v>77.59</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B35" s="38">
         <v>0.312</v>
@@ -3782,68 +3779,68 @@
         <v>1</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B36" s="38">
         <v>124.44</v>
       </c>
       <c r="C36" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="24" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B37" s="37">
         <v>18</v>
       </c>
       <c r="C37" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B38" s="37">
         <v>193.88</v>
       </c>
       <c r="C38" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="23" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B39" s="38">
         <v>86.83</v>
       </c>
       <c r="C39" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B40" s="43">
         <v>0.6</v>
@@ -3852,12 +3849,12 @@
         <v>1</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="25" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B41" s="44">
         <v>0.379</v>
@@ -3866,12 +3863,12 @@
         <v>1</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="25" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B42" s="44">
         <v>0.16500000000000001</v>
@@ -3880,250 +3877,250 @@
         <v>1</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="23" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B43" s="44">
         <v>0.46</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B44" s="45">
         <v>7</v>
       </c>
       <c r="C44" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B45" s="41">
         <v>39</v>
       </c>
       <c r="C45" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="23" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B46" s="37">
         <v>30</v>
       </c>
       <c r="C46" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B47" s="37">
         <v>72.87</v>
       </c>
       <c r="C47" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B48" s="37">
         <v>30</v>
       </c>
       <c r="C48" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B49" s="37">
         <v>317.8</v>
       </c>
       <c r="C49" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="23" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B50" s="37">
         <v>70</v>
       </c>
       <c r="C50" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="25" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B51" s="38">
         <v>0.86199999999999999</v>
       </c>
       <c r="C51" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="23" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B52" s="38">
         <v>0.128</v>
       </c>
       <c r="C52" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="28" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B53" s="37">
         <v>14.92</v>
       </c>
       <c r="C53" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B54" s="37">
         <v>17.3</v>
       </c>
       <c r="C54" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B55" s="38">
         <v>1</v>
       </c>
       <c r="C55" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="28" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B56" s="37">
         <v>112.14</v>
       </c>
       <c r="C56" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B57" s="38">
         <v>0.71</v>
       </c>
       <c r="C57" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B58" s="38">
         <v>0.18</v>
       </c>
       <c r="C58" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B59" s="38">
         <v>0.3</v>
       </c>
       <c r="C59" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B60" s="36">
         <v>0.46</v>
@@ -4132,68 +4129,68 @@
         <v>1</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="23" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B61" s="38">
         <v>0.39100000000000001</v>
       </c>
       <c r="C61" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B62" s="38">
         <v>0.28999999999999998</v>
       </c>
       <c r="C62" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B63" s="38">
         <v>0.17599999999999999</v>
       </c>
       <c r="C63" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B64" s="37">
         <v>63.92</v>
       </c>
       <c r="C64" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="23" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B65" s="46">
         <v>0.54</v>
@@ -4202,12 +4199,12 @@
         <v>1</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="23" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B66" s="34">
         <v>0.71</v>
@@ -4216,82 +4213,82 @@
         <v>1</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="23" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B67" s="37">
         <v>43.56</v>
       </c>
       <c r="C67" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B68" s="34">
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="C68" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D68" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B69" s="34">
         <v>118.91</v>
       </c>
       <c r="C69" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D69" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="24" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B70" s="37">
         <v>34.799999999999997</v>
       </c>
       <c r="C70" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B71" s="38">
         <v>17.5</v>
       </c>
       <c r="C71" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D71" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="23" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B72" s="36">
         <v>0.153</v>
@@ -4300,236 +4297,236 @@
         <v>1</v>
       </c>
       <c r="D72" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="23" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B73" s="38">
         <v>37.444000000000003</v>
       </c>
       <c r="C73" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D73" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="23" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B74" s="38">
         <v>15.24</v>
       </c>
       <c r="C74" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D74" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="30" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B75" s="37">
         <v>208.78</v>
       </c>
       <c r="C75" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D75" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B76" s="37">
         <v>203.77</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D76" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="23" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B77" s="37">
         <v>102</v>
       </c>
       <c r="C77" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D77" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="28" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B78" s="37">
         <v>20.399999999999999</v>
       </c>
       <c r="C78" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D78" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="31" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B79" s="37">
         <v>11.73</v>
       </c>
       <c r="C79" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D79" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="23" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B80" s="38">
         <v>3.1E-2</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D80" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="31" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B81" s="38">
         <v>23.2</v>
       </c>
       <c r="C81" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D81" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="23" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B82" s="37">
         <v>75</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D82" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="23" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B83" s="37">
         <v>75</v>
       </c>
       <c r="C83" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D83" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="23" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B84" s="38">
         <v>46.36</v>
       </c>
       <c r="C84" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D84" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="32" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B85" s="37">
         <v>20</v>
       </c>
       <c r="C85" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D85" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="23" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B86" s="34">
         <v>0.18</v>
       </c>
       <c r="C86" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D86" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="23" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B87" s="38">
         <v>47.7</v>
       </c>
       <c r="C87" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D87" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B88" s="37">
         <v>43.28</v>
       </c>
       <c r="C88" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D88" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="25" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B89" s="38">
         <v>0.223</v>
@@ -4538,40 +4535,40 @@
         <v>1</v>
       </c>
       <c r="D89" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="16" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B90" s="37">
         <v>255.59</v>
       </c>
       <c r="C90" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D90" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="16" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B91" s="37">
         <v>38.03</v>
       </c>
       <c r="C91" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D91" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="23" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B92" s="38">
         <v>0.26</v>
@@ -4580,26 +4577,26 @@
         <v>1</v>
       </c>
       <c r="D92" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="28" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B93" s="37">
         <v>20.399999999999999</v>
       </c>
       <c r="C93" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D93" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="23" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B94" s="36">
         <v>0.11</v>
@@ -4608,152 +4605,152 @@
         <v>1</v>
       </c>
       <c r="D94" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="23" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B95" s="38">
         <v>34.24</v>
       </c>
       <c r="C95" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D95" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B96" s="37">
         <v>77</v>
       </c>
       <c r="C96" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D96" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B97" s="37">
         <v>130.91</v>
       </c>
       <c r="C97" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D97" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="23" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B98" s="34">
         <v>118.01</v>
       </c>
       <c r="C98" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D98" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B99" s="38">
         <v>43.75</v>
       </c>
       <c r="C99" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D99" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="28" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B100" s="37">
         <v>25.55</v>
       </c>
       <c r="C100" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D100" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="23" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B101" s="37">
         <v>200</v>
       </c>
       <c r="C101" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D101" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="28" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B102" s="37">
         <v>30</v>
       </c>
       <c r="C102" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D102" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B103" s="37">
         <v>22.25</v>
       </c>
       <c r="C103" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D103" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="24" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B104" s="37">
         <v>155.62</v>
       </c>
       <c r="C104" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D104" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="23" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B105" s="38">
         <v>0.22800000000000001</v>
@@ -4762,40 +4759,40 @@
         <v>1</v>
       </c>
       <c r="D105" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="23" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B106" s="38">
         <v>66</v>
       </c>
       <c r="C106" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D106" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="24" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B107" s="37">
         <v>36</v>
       </c>
       <c r="C107" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D107" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="23" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B108" s="34">
         <v>0.42</v>
@@ -4804,54 +4801,54 @@
         <v>1</v>
       </c>
       <c r="D108" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="23" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B109" s="37">
         <v>74.78</v>
       </c>
       <c r="C109" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D109" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="24" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B110" s="37">
         <v>8</v>
       </c>
       <c r="C110" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D110" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="23" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B111" s="37">
         <v>125</v>
       </c>
       <c r="C111" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D111" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B112" s="38">
         <v>0.16500000000000001</v>
@@ -4860,82 +4857,82 @@
         <v>1</v>
       </c>
       <c r="D112" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="28" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B113" s="37">
         <v>49.5</v>
       </c>
       <c r="C113" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D113" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="23" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B114" s="38">
         <v>0.56000000000000005</v>
       </c>
       <c r="C114" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D114" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="23" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B115" s="37">
         <v>86.22</v>
       </c>
       <c r="C115" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D115" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="23" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B116" s="38">
         <v>175</v>
       </c>
       <c r="C116" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D116" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="23" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B117" s="37">
         <v>57.15</v>
       </c>
       <c r="C117" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D117" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="23" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B118" s="38">
         <v>0.13400000000000001</v>
@@ -4944,26 +4941,26 @@
         <v>1</v>
       </c>
       <c r="D118" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="23" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B119" s="36">
         <v>0.12</v>
       </c>
       <c r="C119" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D119" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="23" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B120" s="38">
         <v>14.35</v>
@@ -4972,54 +4969,54 @@
         <v>32</v>
       </c>
       <c r="D120" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="23" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B121" s="37">
         <v>117.25</v>
       </c>
       <c r="C121" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D121" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="23" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B122" s="37">
         <v>38</v>
       </c>
       <c r="C122" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D122" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="23" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B123" s="38">
         <v>37.33</v>
       </c>
       <c r="C123" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D123" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="25" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B124" s="38">
         <v>0.222</v>
@@ -5028,12 +5025,12 @@
         <v>1</v>
       </c>
       <c r="D124" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="23" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B125" s="38">
         <v>0.22900000000000001</v>
@@ -5042,12 +5039,12 @@
         <v>1</v>
       </c>
       <c r="D125" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B126" s="38">
         <v>33</v>
@@ -5056,40 +5053,40 @@
         <v>32</v>
       </c>
       <c r="D126" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="23" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B127" s="38">
         <v>29.5</v>
       </c>
       <c r="C127" s="47" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D127" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="26" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B128" s="43">
         <v>0.24</v>
       </c>
       <c r="C128" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D128" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="33" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B129" s="44">
         <v>0.40799999999999997</v>
@@ -5098,138 +5095,138 @@
         <v>1</v>
       </c>
       <c r="D129" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="33" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B130" s="43">
         <v>34</v>
       </c>
       <c r="C130" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D130" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B131" s="43">
         <v>209.55</v>
       </c>
       <c r="C131" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D131" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="26" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B132" s="43">
         <v>0.05</v>
       </c>
       <c r="C132" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D132" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="26" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B133" s="43">
         <v>0.81</v>
       </c>
       <c r="C133" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D133" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="26" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B134" s="43">
         <v>10</v>
       </c>
       <c r="C134" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D134" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="26" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B135" s="38">
         <v>8.5</v>
       </c>
       <c r="C135" s="47" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D135" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="26" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B136" s="38">
         <v>0.28000000000000003</v>
       </c>
       <c r="C136" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D136" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="26" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B137" s="38">
         <v>0.35</v>
       </c>
       <c r="C137" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="26" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B138" s="38">
         <v>0.08</v>
       </c>
       <c r="C138" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D138" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B139" s="38">
         <v>0.19</v>
@@ -5238,26 +5235,26 @@
         <v>1</v>
       </c>
       <c r="D139" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="26" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B140" s="38">
         <v>332.18</v>
       </c>
       <c r="C140" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D140" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="26" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B141" s="38">
         <v>0.27200000000000002</v>
@@ -5266,77 +5263,77 @@
         <v>4</v>
       </c>
       <c r="D141" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="26" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B142" s="38">
         <v>166.79</v>
       </c>
       <c r="C142" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D142" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="26" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B143" s="38">
         <v>119.93</v>
       </c>
       <c r="C143" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D143" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="26" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B144" s="38">
         <v>0.52</v>
       </c>
       <c r="C144" s="47" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D144" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="26" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B145" s="38">
         <v>27.72</v>
       </c>
       <c r="C145" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D145" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="57" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B146" s="38">
         <v>32.22</v>
       </c>
       <c r="C146" s="47" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D146" s="49" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -5411,7 +5408,7 @@
     </row>
     <row r="152" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B152" s="53">
         <v>0.18</v>
@@ -5453,7 +5450,7 @@
     </row>
     <row r="155" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B155" s="53">
         <v>0.21428571428571427</v>
@@ -5747,7 +5744,7 @@
     </row>
     <row r="176" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B176" s="54">
         <v>0.19</v>
@@ -5803,7 +5800,7 @@
     </row>
     <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B180" s="54">
         <v>75</v>
@@ -5845,7 +5842,7 @@
     </row>
     <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B183" s="54">
         <v>2.2000000000000002</v>
@@ -5901,7 +5898,7 @@
     </row>
     <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B187" s="54">
         <v>0.24</v>
@@ -6349,7 +6346,7 @@
     </row>
     <row r="219" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B219" s="54">
         <v>0.36099999999999999</v>
@@ -6419,7 +6416,7 @@
     </row>
     <row r="224" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B224" s="54">
         <v>394</v>
@@ -6867,7 +6864,7 @@
     </row>
     <row r="256" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B256" s="54">
         <v>55</v>
@@ -6909,7 +6906,7 @@
     </row>
     <row r="259" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B259" s="54">
         <v>0.9</v>
@@ -6923,7 +6920,7 @@
     </row>
     <row r="260" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B260" s="54">
         <v>9.5000000000000001E-2</v>
@@ -6965,7 +6962,7 @@
     </row>
     <row r="263" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B263" s="54">
         <v>0.23</v>
@@ -6993,7 +6990,7 @@
     </row>
     <row r="265" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B265" s="54">
         <v>0.14285714285714285</v>
@@ -7007,7 +7004,7 @@
     </row>
     <row r="266" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B266" s="54">
         <v>0.18823529411764706</v>
@@ -7105,7 +7102,7 @@
     </row>
     <row r="273" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B273" s="54">
         <v>0.32</v>
@@ -7119,7 +7116,7 @@
     </row>
     <row r="274" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B274" s="54">
         <v>0.21249999999999999</v>
@@ -7153,7 +7150,7 @@
         <v>0.47</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="D276" s="6" t="s">
         <v>7</v>
@@ -7161,7 +7158,7 @@
     </row>
     <row r="277" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B277" s="54">
         <v>0.89</v>
@@ -7175,7 +7172,7 @@
     </row>
     <row r="278" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B278" s="54">
         <v>0.496</v>
@@ -7189,7 +7186,7 @@
     </row>
     <row r="279" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B279" s="54">
         <v>0.8666666666666667</v>
@@ -7203,7 +7200,7 @@
     </row>
     <row r="280" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B280" s="54">
         <v>0.13500000000000001</v>
@@ -7217,7 +7214,7 @@
     </row>
     <row r="281" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B281" s="54">
         <v>0.80645161290322576</v>
@@ -7231,7 +7228,7 @@
     </row>
     <row r="282" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B282" s="54">
         <v>0.96199999999999997</v>
@@ -7245,7 +7242,7 @@
     </row>
     <row r="283" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B283" s="54">
         <v>2</v>
@@ -7259,7 +7256,7 @@
     </row>
     <row r="284" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B284" s="54">
         <v>0.22500000000000001</v>
@@ -7273,7 +7270,7 @@
     </row>
     <row r="285" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B285" s="54">
         <v>0.13</v>
@@ -7287,7 +7284,7 @@
     </row>
     <row r="286" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B286" s="54">
         <v>0.84199999999999997</v>
@@ -7301,7 +7298,7 @@
     </row>
     <row r="287" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B287" s="54">
         <v>0.6</v>
@@ -7315,7 +7312,7 @@
     </row>
     <row r="288" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B288" s="54">
         <v>0.51</v>
@@ -7329,7 +7326,7 @@
     </row>
     <row r="289" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B289" s="54">
         <v>0.47</v>
@@ -7343,7 +7340,7 @@
     </row>
     <row r="290" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B290" s="54">
         <v>0.38900000000000001</v>
@@ -7357,7 +7354,7 @@
     </row>
     <row r="291" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B291" s="54">
         <v>0.55800000000000005</v>
@@ -7371,7 +7368,7 @@
     </row>
     <row r="292" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B292" s="54">
         <v>0.7</v>
@@ -7385,7 +7382,7 @@
     </row>
     <row r="293" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B293" s="54">
         <v>0.32500000000000001</v>
@@ -7399,7 +7396,7 @@
     </row>
     <row r="294" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B294" s="54">
         <v>0.91400000000000003</v>
@@ -7413,7 +7410,7 @@
     </row>
     <row r="295" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B295" s="54">
         <v>0.81</v>
@@ -7427,7 +7424,7 @@
     </row>
     <row r="296" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B296" s="54">
         <v>1.01</v>
@@ -7441,7 +7438,7 @@
     </row>
     <row r="297" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B297" s="54">
         <v>0.40500000000000003</v>
@@ -7455,7 +7452,7 @@
     </row>
     <row r="298" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B298" s="54">
         <v>0.372</v>
@@ -7469,7 +7466,7 @@
     </row>
     <row r="299" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B299" s="54">
         <v>16</v>
@@ -7483,7 +7480,7 @@
     </row>
     <row r="300" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B300" s="54">
         <v>12</v>
@@ -7497,7 +7494,7 @@
     </row>
     <row r="301" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B301" s="54">
         <v>20</v>
@@ -7511,7 +7508,7 @@
     </row>
     <row r="302" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B302" s="54">
         <v>0.13</v>
@@ -7525,7 +7522,7 @@
     </row>
     <row r="303" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B303" s="54">
         <v>2.7857142857142856</v>
@@ -7539,7 +7536,7 @@
     </row>
     <row r="304" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B304" s="54">
         <v>95</v>
@@ -7553,7 +7550,7 @@
     </row>
     <row r="305" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B305" s="54">
         <v>2.67</v>
@@ -7567,7 +7564,7 @@
     </row>
     <row r="306" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B306" s="54">
         <v>0.08</v>
@@ -7581,7 +7578,7 @@
     </row>
     <row r="307" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B307" s="54">
         <v>0.42499999999999999</v>
@@ -7595,7 +7592,7 @@
     </row>
     <row r="308" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B308" s="54">
         <v>5.8400000000000001E-2</v>
@@ -7609,7 +7606,7 @@
     </row>
     <row r="309" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B309" s="54">
         <v>6.5000000000000002E-2</v>
@@ -7623,7 +7620,7 @@
     </row>
     <row r="310" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B310" s="54">
         <v>7.0000000000000007E-2</v>
@@ -7637,7 +7634,7 @@
     </row>
     <row r="311" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B311" s="54">
         <v>0.16</v>
@@ -7651,7 +7648,7 @@
     </row>
     <row r="312" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B312" s="54">
         <v>0.11</v>
@@ -7665,7 +7662,7 @@
     </row>
     <row r="313" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B313" s="54">
         <v>7.0000000000000007E-2</v>
@@ -7679,7 +7676,7 @@
     </row>
     <row r="314" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B314" s="54">
         <v>0.4</v>
@@ -7693,7 +7690,7 @@
     </row>
     <row r="315" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A315" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B315" s="54">
         <v>0.11899999999999999</v>
@@ -7707,7 +7704,7 @@
     </row>
     <row r="316" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B316" s="54">
         <v>5.5E-2</v>
@@ -7721,7 +7718,7 @@
     </row>
     <row r="317" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B317" s="54">
         <v>0.21</v>
@@ -7735,7 +7732,7 @@
     </row>
     <row r="318" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B318" s="54">
         <v>5.5E-2</v>
@@ -7749,7 +7746,7 @@
     </row>
     <row r="319" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B319" s="54">
         <v>5.5E-2</v>
@@ -7763,7 +7760,7 @@
     </row>
     <row r="320" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B320" s="54">
         <v>50</v>
@@ -7777,7 +7774,7 @@
     </row>
     <row r="321" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B321" s="54">
         <v>0.22500000000000001</v>
@@ -7791,7 +7788,7 @@
     </row>
     <row r="322" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B322" s="54">
         <v>0.312</v>
@@ -7805,7 +7802,7 @@
     </row>
     <row r="323" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B323" s="54">
         <v>7</v>
@@ -7819,7 +7816,7 @@
     </row>
     <row r="324" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B324" s="54">
         <v>14</v>
@@ -7833,7 +7830,7 @@
     </row>
     <row r="325" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B325" s="54">
         <v>0.17</v>
@@ -7847,7 +7844,7 @@
     </row>
     <row r="326" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B326" s="54">
         <v>0.31</v>
@@ -7861,7 +7858,7 @@
     </row>
     <row r="327" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B327" s="54">
         <v>0.81</v>
@@ -7875,7 +7872,7 @@
     </row>
     <row r="328" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B328" s="54">
         <v>0.12222222222222222</v>
@@ -7889,7 +7886,7 @@
     </row>
     <row r="329" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B329" s="54">
         <v>0.18</v>
@@ -7903,7 +7900,7 @@
     </row>
     <row r="330" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B330" s="54">
         <v>0.88200000000000001</v>
@@ -7917,7 +7914,7 @@
     </row>
     <row r="331" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B331" s="54">
         <v>0.37</v>
@@ -7926,12 +7923,12 @@
         <v>4</v>
       </c>
       <c r="D331" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B332" s="54">
         <v>5</v>
@@ -7945,7 +7942,7 @@
     </row>
     <row r="333" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B333" s="54">
         <v>1.2386666666666666</v>
@@ -7959,7 +7956,7 @@
     </row>
     <row r="334" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B334" s="54">
         <v>0.33900000000000002</v>
@@ -7973,7 +7970,7 @@
     </row>
     <row r="335" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B335" s="54">
         <v>0.18</v>
@@ -7987,7 +7984,7 @@
     </row>
     <row r="336" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B336" s="54">
         <v>0.47333333333333333</v>
@@ -8001,7 +7998,7 @@
     </row>
     <row r="337" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B337" s="54">
         <v>7.4999999999999997E-2</v>
@@ -8015,7 +8012,7 @@
     </row>
     <row r="338" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B338" s="54">
         <v>2.4700000000000002</v>
@@ -8029,7 +8026,7 @@
     </row>
     <row r="339" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B339" s="54">
         <v>0.82</v>
@@ -8043,7 +8040,7 @@
     </row>
     <row r="340" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B340" s="54">
         <v>0.106</v>
@@ -8057,7 +8054,7 @@
     </row>
     <row r="341" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B341" s="54">
         <v>0.11700000000000001</v>
@@ -8071,7 +8068,7 @@
     </row>
     <row r="342" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B342" s="54">
         <v>0.45900000000000002</v>
@@ -8085,7 +8082,7 @@
     </row>
     <row r="343" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B343" s="54">
         <v>0.71899999999999997</v>
@@ -8099,7 +8096,7 @@
     </row>
     <row r="344" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B344" s="54">
         <v>1.5</v>
@@ -8113,7 +8110,7 @@
     </row>
     <row r="345" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B345" s="54">
         <v>0.25600000000000001</v>
@@ -8127,7 +8124,7 @@
     </row>
     <row r="346" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B346" s="54">
         <v>0.19400000000000001</v>
@@ -8141,7 +8138,7 @@
     </row>
     <row r="347" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B347" s="54">
         <v>0.48399999999999999</v>
@@ -8155,7 +8152,7 @@
     </row>
     <row r="348" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B348" s="54">
         <v>0.52</v>
@@ -8169,7 +8166,7 @@
     </row>
     <row r="349" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B349" s="54">
         <v>0.23499999999999999</v>
@@ -8183,7 +8180,7 @@
     </row>
     <row r="350" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B350" s="54">
         <v>0.30499999999999999</v>
@@ -8197,7 +8194,7 @@
     </row>
     <row r="351" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B351" s="54">
         <v>1.224</v>
@@ -8211,7 +8208,7 @@
     </row>
     <row r="352" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B352" s="54">
         <v>0.46</v>
@@ -8225,13 +8222,13 @@
     </row>
     <row r="353" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B353" s="54">
         <v>200</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>28</v>
@@ -8239,7 +8236,7 @@
     </row>
     <row r="354" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B354" s="54">
         <v>2.46</v>
@@ -8248,12 +8245,12 @@
         <v>4</v>
       </c>
       <c r="D354" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B355" s="54">
         <v>1.079</v>
@@ -8267,7 +8264,7 @@
     </row>
     <row r="356" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B356" s="54">
         <v>0.91500000000000004</v>
@@ -8281,7 +8278,7 @@
     </row>
     <row r="357" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B357" s="54">
         <v>0.12</v>
@@ -8295,7 +8292,7 @@
     </row>
     <row r="358" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B358" s="54">
         <v>0.23</v>
@@ -8309,13 +8306,13 @@
     </row>
     <row r="359" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B359" s="54">
         <v>0.28000000000000003</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>28</v>
@@ -8323,7 +8320,7 @@
     </row>
     <row r="360" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B360" s="54">
         <v>0.54700000000000004</v>
@@ -8337,7 +8334,7 @@
     </row>
     <row r="361" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B361" s="54">
         <v>1.1272727272727272</v>
@@ -8351,7 +8348,7 @@
     </row>
     <row r="362" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B362" s="54">
         <v>1.3779999999999999</v>
@@ -8365,7 +8362,7 @@
     </row>
     <row r="363" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B363" s="54">
         <v>0.95</v>
@@ -8379,7 +8376,7 @@
     </row>
     <row r="364" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B364" s="54">
         <v>0.4</v>
@@ -8393,7 +8390,7 @@
     </row>
     <row r="365" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B365" s="54">
         <v>0.73299999999999998</v>
@@ -8407,13 +8404,13 @@
     </row>
     <row r="366" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B366" s="54">
         <v>185</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>28</v>
@@ -8421,7 +8418,7 @@
     </row>
     <row r="367" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B367" s="54">
         <v>1</v>
@@ -8435,7 +8432,7 @@
     </row>
     <row r="368" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B368" s="54">
         <v>45</v>
@@ -8449,7 +8446,7 @@
     </row>
     <row r="369" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B369" s="54">
         <v>0.38800000000000001</v>
@@ -8463,7 +8460,7 @@
     </row>
     <row r="370" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B370" s="54">
         <v>0.125</v>
@@ -8477,7 +8474,7 @@
     </row>
     <row r="371" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B371" s="54">
         <v>0.21</v>
@@ -8491,7 +8488,7 @@
     </row>
     <row r="372" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B372" s="54">
         <v>0.09</v>
@@ -8505,7 +8502,7 @@
     </row>
     <row r="373" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B373" s="54">
         <v>3.0880000000000001</v>
@@ -8519,13 +8516,13 @@
     </row>
     <row r="374" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B374" s="54">
         <v>100</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D374" s="6" t="s">
         <v>4</v>
@@ -8533,7 +8530,7 @@
     </row>
     <row r="375" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B375" s="54">
         <v>14</v>
@@ -8547,7 +8544,7 @@
     </row>
     <row r="376" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B376" s="54">
         <v>14</v>
@@ -8561,7 +8558,7 @@
     </row>
     <row r="377" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B377" s="54">
         <v>0.26400000000000001</v>
@@ -8575,7 +8572,7 @@
     </row>
     <row r="378" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B378" s="54">
         <v>0.23</v>
@@ -8589,7 +8586,7 @@
     </row>
     <row r="379" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B379" s="54">
         <v>0.54700000000000004</v>
@@ -8603,7 +8600,7 @@
     </row>
     <row r="380" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B380" s="54">
         <v>0.21</v>
@@ -8617,7 +8614,7 @@
     </row>
     <row r="381" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B381" s="54">
         <v>0.185</v>
@@ -8631,7 +8628,7 @@
     </row>
     <row r="382" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B382" s="54">
         <v>1.45</v>
@@ -8645,7 +8642,7 @@
     </row>
     <row r="383" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B383" s="54">
         <v>0.11899999999999999</v>
@@ -8659,7 +8656,7 @@
     </row>
     <row r="384" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B384" s="54">
         <v>0.16</v>
@@ -8673,7 +8670,7 @@
     </row>
     <row r="385" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B385" s="54">
         <v>0.33</v>
@@ -8682,12 +8679,12 @@
         <v>4</v>
       </c>
       <c r="D385" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B386" s="54">
         <v>0.51900000000000002</v>
@@ -8701,7 +8698,7 @@
     </row>
     <row r="387" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B387" s="54">
         <v>0.69</v>
@@ -8715,7 +8712,7 @@
     </row>
     <row r="388" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B388" s="54">
         <v>0.3</v>
@@ -8729,7 +8726,7 @@
     </row>
     <row r="389" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B389" s="54">
         <v>0.67800000000000005</v>
@@ -8743,7 +8740,7 @@
     </row>
     <row r="390" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B390" s="54">
         <v>0.81799999999999995</v>
@@ -8757,7 +8754,7 @@
     </row>
     <row r="391" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B391" s="54">
         <v>0.99</v>
@@ -8771,7 +8768,7 @@
     </row>
     <row r="392" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B392" s="54">
         <v>0.36499999999999999</v>
@@ -8785,7 +8782,7 @@
     </row>
     <row r="393" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B393" s="54">
         <v>0.64500000000000002</v>
@@ -8799,7 +8796,7 @@
     </row>
     <row r="394" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B394" s="54">
         <v>0.315</v>
@@ -8813,7 +8810,7 @@
     </row>
     <row r="395" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B395" s="54">
         <v>0.25</v>
@@ -8827,7 +8824,7 @@
     </row>
     <row r="396" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B396" s="54">
         <v>0.17</v>
@@ -8841,7 +8838,7 @@
     </row>
     <row r="397" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B397" s="54">
         <v>0.17599999999999999</v>
@@ -8855,7 +8852,7 @@
     </row>
     <row r="398" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B398" s="54">
         <v>9.5000000000000001E-2</v>
@@ -8869,7 +8866,7 @@
     </row>
     <row r="399" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B399" s="54">
         <v>0.308</v>
@@ -8883,7 +8880,7 @@
     </row>
     <row r="400" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B400" s="54">
         <v>15</v>
@@ -8897,7 +8894,7 @@
     </row>
     <row r="401" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B401" s="54">
         <v>0.55000000000000004</v>
@@ -8911,7 +8908,7 @@
     </row>
     <row r="402" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B402" s="54">
         <v>0.24</v>
@@ -8925,7 +8922,7 @@
     </row>
     <row r="403" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B403" s="54">
         <v>0.22500000000000001</v>
@@ -8939,7 +8936,7 @@
     </row>
     <row r="404" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B404" s="54">
         <v>0.27500000000000002</v>
@@ -8953,7 +8950,7 @@
     </row>
     <row r="405" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A405" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B405" s="54">
         <v>0.26</v>
@@ -8967,7 +8964,7 @@
     </row>
     <row r="406" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A406" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B406" s="54">
         <v>0.23</v>
@@ -8981,7 +8978,7 @@
     </row>
     <row r="407" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B407" s="54">
         <v>0.187</v>
@@ -8995,7 +8992,7 @@
     </row>
     <row r="408" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B408" s="54">
         <v>0.26800000000000002</v>
@@ -9009,7 +9006,7 @@
     </row>
     <row r="409" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A409" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B409" s="54">
         <v>0.186</v>
@@ -9023,7 +9020,7 @@
     </row>
     <row r="410" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B410" s="54">
         <v>1.26</v>
@@ -9037,7 +9034,7 @@
     </row>
     <row r="411" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B411" s="54">
         <v>1.01</v>
@@ -9051,7 +9048,7 @@
     </row>
     <row r="412" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B412" s="54">
         <v>0.76500000000000001</v>
@@ -9065,7 +9062,7 @@
     </row>
     <row r="413" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B413" s="54">
         <v>1.01</v>
@@ -9079,7 +9076,7 @@
     </row>
     <row r="414" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B414" s="54">
         <v>0.23899999999999999</v>
@@ -9093,7 +9090,7 @@
     </row>
     <row r="415" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B415" s="54">
         <v>0.30499999999999999</v>
@@ -9107,7 +9104,7 @@
     </row>
     <row r="416" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B416" s="54">
         <v>0.185</v>
@@ -9121,7 +9118,7 @@
     </row>
     <row r="417" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B417" s="54">
         <v>1.05</v>
@@ -9135,7 +9132,7 @@
     </row>
     <row r="418" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B418" s="54">
         <v>1.1599999999999999</v>
@@ -9149,7 +9146,7 @@
     </row>
     <row r="419" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B419" s="54">
         <v>1.1599999999999999</v>
@@ -9163,7 +9160,7 @@
     </row>
     <row r="420" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B420" s="54">
         <v>1</v>
@@ -9177,7 +9174,7 @@
     </row>
     <row r="421" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B421" s="54">
         <v>0.64500000000000002</v>
@@ -9191,7 +9188,7 @@
     </row>
     <row r="422" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B422" s="54">
         <v>1350</v>
@@ -9200,18 +9197,18 @@
         <v>32</v>
       </c>
       <c r="D422" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B423" s="54">
         <v>175</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D423" s="6" t="s">
         <v>28</v>
@@ -9219,7 +9216,7 @@
     </row>
     <row r="424" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B424" s="54">
         <v>55</v>
@@ -9233,7 +9230,7 @@
     </row>
     <row r="425" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B425" s="54">
         <v>0.11</v>
@@ -9247,7 +9244,7 @@
     </row>
     <row r="426" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B426" s="54">
         <v>0.17</v>
@@ -9261,7 +9258,7 @@
     </row>
     <row r="427" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B427" s="54">
         <v>0.12</v>
@@ -9275,7 +9272,7 @@
     </row>
     <row r="428" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B428" s="54">
         <v>0.189</v>
@@ -9289,7 +9286,7 @@
     </row>
     <row r="429" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B429" s="54">
         <v>5.37</v>
@@ -9303,7 +9300,7 @@
     </row>
     <row r="430" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B430" s="54">
         <v>4.351</v>
@@ -9317,7 +9314,7 @@
     </row>
     <row r="431" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B431" s="54">
         <v>0.8</v>
@@ -9331,7 +9328,7 @@
     </row>
     <row r="432" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B432" s="54">
         <v>0.74</v>
@@ -9345,7 +9342,7 @@
     </row>
     <row r="433" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B433" s="54">
         <v>0.55000000000000004</v>
@@ -9359,7 +9356,7 @@
     </row>
     <row r="434" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B434" s="54">
         <v>2.2000000000000002</v>
@@ -9373,7 +9370,7 @@
     </row>
     <row r="435" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B435" s="54">
         <v>3.42</v>
@@ -9387,7 +9384,7 @@
     </row>
     <row r="436" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B436" s="54">
         <v>0.106</v>
@@ -9401,7 +9398,7 @@
     </row>
     <row r="437" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B437" s="54">
         <v>0.15</v>
@@ -9415,7 +9412,7 @@
     </row>
     <row r="438" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B438" s="54">
         <v>0.77600000000000002</v>
@@ -9429,7 +9426,7 @@
     </row>
     <row r="439" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B439" s="54">
         <v>1.05</v>
@@ -9443,7 +9440,7 @@
     </row>
     <row r="440" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B440" s="54">
         <v>0.2</v>
@@ -9457,7 +9454,7 @@
     </row>
     <row r="441" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B441" s="54">
         <v>0.18</v>
@@ -9471,7 +9468,7 @@
     </row>
     <row r="442" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B442" s="54">
         <v>0.18</v>
@@ -9485,7 +9482,7 @@
     </row>
     <row r="443" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B443" s="54">
         <v>0.86</v>
@@ -9499,7 +9496,7 @@
     </row>
     <row r="444" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B444" s="54">
         <v>1.2</v>
@@ -9513,7 +9510,7 @@
     </row>
     <row r="445" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B445" s="54">
         <v>55</v>
@@ -9527,7 +9524,7 @@
     </row>
     <row r="446" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B446" s="54">
         <v>0.35</v>
@@ -9541,7 +9538,7 @@
     </row>
     <row r="447" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B447" s="54">
         <v>1.4379999999999999</v>
@@ -9555,7 +9552,7 @@
     </row>
     <row r="448" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B448" s="54">
         <v>2.5499999999999998</v>
@@ -9569,7 +9566,7 @@
     </row>
     <row r="449" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B449" s="54">
         <v>0.2</v>
@@ -9583,7 +9580,7 @@
     </row>
     <row r="450" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B450" s="54">
         <v>9.5000000000000001E-2</v>
@@ -9597,7 +9594,7 @@
     </row>
     <row r="451" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B451" s="54">
         <v>0.28499999999999998</v>
@@ -9611,7 +9608,7 @@
     </row>
     <row r="452" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B452" s="54">
         <v>0.2</v>
@@ -9625,7 +9622,7 @@
     </row>
     <row r="453" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B453" s="54">
         <v>1</v>
@@ -9639,7 +9636,7 @@
     </row>
     <row r="454" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B454" s="54">
         <v>2.5680000000000001</v>
@@ -9653,7 +9650,7 @@
     </row>
     <row r="455" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B455" s="54">
         <v>4.1500000000000004</v>
@@ -9667,7 +9664,7 @@
     </row>
     <row r="456" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B456" s="54">
         <v>0.6</v>
@@ -9681,7 +9678,7 @@
     </row>
     <row r="457" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B457" s="54">
         <v>0.17799999999999999</v>
@@ -9695,7 +9692,7 @@
     </row>
     <row r="458" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B458" s="54">
         <v>0.17799999999999999</v>
@@ -9709,7 +9706,7 @@
     </row>
     <row r="459" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B459" s="54">
         <v>0.318</v>
@@ -9723,7 +9720,7 @@
     </row>
     <row r="460" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B460" s="54">
         <v>0.3</v>
@@ -9737,7 +9734,7 @@
     </row>
     <row r="461" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B461" s="54">
         <v>0.14099999999999999</v>
@@ -9751,7 +9748,7 @@
     </row>
     <row r="462" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B462" s="54">
         <v>0.189</v>
@@ -9765,7 +9762,7 @@
     </row>
     <row r="463" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B463" s="54">
         <v>8.5000000000000006E-2</v>
@@ -9779,7 +9776,7 @@
     </row>
     <row r="464" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B464" s="54">
         <v>0.2</v>
@@ -9793,7 +9790,7 @@
     </row>
     <row r="465" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B465" s="54">
         <v>0.34499999999999997</v>
@@ -9807,7 +9804,7 @@
     </row>
     <row r="466" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B466" s="54">
         <v>0.08</v>
@@ -9821,7 +9818,7 @@
     </row>
     <row r="467" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B467" s="54">
         <v>0.08</v>
@@ -9835,13 +9832,13 @@
     </row>
     <row r="468" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B468" s="54">
         <v>385</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D468" s="6" t="s">
         <v>28</v>
@@ -9849,7 +9846,7 @@
     </row>
     <row r="469" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B469" s="54">
         <v>0.46</v>
@@ -9863,7 +9860,7 @@
     </row>
     <row r="470" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B470" s="54">
         <v>0.441</v>
@@ -9877,7 +9874,7 @@
     </row>
     <row r="471" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B471" s="54">
         <v>0.20399999999999999</v>
@@ -9891,7 +9888,7 @@
     </row>
     <row r="472" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B472" s="54">
         <v>0.18</v>
@@ -9905,7 +9902,7 @@
     </row>
     <row r="473" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B473" s="54">
         <v>0.13200000000000001</v>
@@ -9919,7 +9916,7 @@
     </row>
     <row r="474" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B474" s="54">
         <v>0.312</v>
@@ -9933,7 +9930,7 @@
     </row>
     <row r="475" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B475" s="54">
         <v>40</v>
@@ -9947,7 +9944,7 @@
     </row>
     <row r="476" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B476" s="54">
         <v>0.11</v>
@@ -9961,7 +9958,7 @@
     </row>
     <row r="477" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B477" s="54">
         <v>1.55</v>
@@ -9975,7 +9972,7 @@
     </row>
     <row r="478" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B478" s="54">
         <v>12.3</v>
@@ -9989,7 +9986,7 @@
     </row>
     <row r="479" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B479" s="54">
         <v>7.4999999999999997E-2</v>
@@ -10003,7 +10000,7 @@
     </row>
     <row r="480" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B480" s="54">
         <v>0.43</v>
@@ -10012,12 +10009,12 @@
         <v>4</v>
       </c>
       <c r="D480" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="481" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B481" s="54">
         <v>0.43</v>
@@ -10026,12 +10023,12 @@
         <v>4</v>
       </c>
       <c r="D481" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="482" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B482" s="54">
         <v>0.43</v>
@@ -10040,12 +10037,12 @@
         <v>4</v>
       </c>
       <c r="D482" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="483" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B483" s="54">
         <v>0.15</v>
@@ -10054,12 +10051,12 @@
         <v>4</v>
       </c>
       <c r="D483" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="484" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B484" s="54">
         <v>0.32</v>
@@ -10068,12 +10065,12 @@
         <v>4</v>
       </c>
       <c r="D484" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="485" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B485" s="54">
         <v>0.22</v>
@@ -10082,12 +10079,12 @@
         <v>4</v>
       </c>
       <c r="D485" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="486" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B486" s="54">
         <v>0.27500000000000002</v>
@@ -10096,12 +10093,12 @@
         <v>4</v>
       </c>
       <c r="D486" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="487" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B487" s="54">
         <v>0.28000000000000003</v>
@@ -10110,12 +10107,12 @@
         <v>4</v>
       </c>
       <c r="D487" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B488" s="54">
         <v>0.28000000000000003</v>
@@ -10124,12 +10121,12 @@
         <v>4</v>
       </c>
       <c r="D488" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="489" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B489" s="54">
         <v>0.3</v>
@@ -10138,12 +10135,12 @@
         <v>4</v>
       </c>
       <c r="D489" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="490" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B490" s="54">
         <v>0.22500000000000001</v>
@@ -10152,12 +10149,12 @@
         <v>4</v>
       </c>
       <c r="D490" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="491" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B491" s="54">
         <v>0.76700000000000002</v>
@@ -10166,12 +10163,12 @@
         <v>4</v>
       </c>
       <c r="D491" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="492" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B492" s="54">
         <v>1.014</v>
@@ -10180,12 +10177,12 @@
         <v>4</v>
       </c>
       <c r="D492" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="493" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B493" s="54">
         <v>0.14000000000000001</v>
@@ -10199,7 +10196,7 @@
     </row>
     <row r="494" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B494" s="54">
         <v>0.443</v>
@@ -10213,7 +10210,7 @@
     </row>
     <row r="495" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B495" s="54">
         <v>0.29599999999999999</v>
@@ -10227,7 +10224,7 @@
     </row>
     <row r="496" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B496" s="54">
         <v>1.079</v>
@@ -10241,13 +10238,13 @@
     </row>
     <row r="497" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A497" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B497" s="54">
         <v>1125</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D497" s="6" t="s">
         <v>5</v>
@@ -10255,7 +10252,7 @@
     </row>
     <row r="498" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A498" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B498" s="54">
         <v>0.53</v>
@@ -10269,7 +10266,7 @@
     </row>
     <row r="499" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A499" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B499" s="54">
         <v>0.53</v>
@@ -10283,7 +10280,7 @@
     </row>
     <row r="500" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A500" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B500" s="54">
         <v>0.53</v>
@@ -10297,7 +10294,7 @@
     </row>
     <row r="501" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A501" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B501" s="54">
         <v>0.53</v>
@@ -10311,7 +10308,7 @@
     </row>
     <row r="502" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A502" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B502" s="54">
         <v>0.53</v>
@@ -10325,7 +10322,7 @@
     </row>
     <row r="503" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B503" s="54">
         <v>4</v>
@@ -10339,7 +10336,7 @@
     </row>
     <row r="504" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B504" s="54">
         <v>0.08</v>
@@ -10353,7 +10350,7 @@
     </row>
     <row r="505" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B505" s="54">
         <v>0.56499999999999995</v>
@@ -10367,7 +10364,7 @@
     </row>
     <row r="506" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B506" s="54">
         <v>0.84</v>
@@ -10381,7 +10378,7 @@
     </row>
     <row r="507" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B507" s="54">
         <v>0.29599999999999999</v>
@@ -10395,7 +10392,7 @@
     </row>
     <row r="508" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B508" s="54">
         <v>1.02</v>
@@ -10409,7 +10406,7 @@
     </row>
     <row r="509" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B509" s="54">
         <v>6.8000000000000005E-2</v>
@@ -10423,7 +10420,7 @@
     </row>
     <row r="510" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B510" s="54">
         <v>0.24</v>
@@ -10437,7 +10434,7 @@
     </row>
     <row r="511" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B511" s="54">
         <v>35</v>
@@ -10451,7 +10448,7 @@
     </row>
     <row r="512" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B512" s="54">
         <v>0.5</v>
@@ -10465,7 +10462,7 @@
     </row>
     <row r="513" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B513" s="54">
         <v>1.7789999999999999</v>
@@ -10479,7 +10476,7 @@
     </row>
     <row r="514" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B514" s="54">
         <v>0.13</v>
@@ -10493,7 +10490,7 @@
     </row>
     <row r="515" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A515" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B515" s="54">
         <v>1</v>
@@ -10507,7 +10504,7 @@
     </row>
     <row r="516" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B516" s="54">
         <v>0.04</v>
@@ -10521,7 +10518,7 @@
     </row>
     <row r="517" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A517" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B517" s="54">
         <v>5.5E-2</v>
@@ -10535,7 +10532,7 @@
     </row>
     <row r="518" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B518" s="54">
         <v>60</v>
@@ -10549,7 +10546,7 @@
     </row>
     <row r="519" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A519" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B519" s="54">
         <v>60</v>
@@ -10563,7 +10560,7 @@
     </row>
     <row r="520" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B520" s="54">
         <v>0.59</v>
@@ -10572,12 +10569,12 @@
         <v>4</v>
       </c>
       <c r="D520" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="521" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B521" s="54">
         <v>0.08</v>
@@ -10591,7 +10588,7 @@
     </row>
     <row r="522" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B522" s="54">
         <v>2.5000000000000001E-2</v>
@@ -10605,7 +10602,7 @@
     </row>
     <row r="523" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A523" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B523" s="54">
         <v>0.39</v>
@@ -10619,7 +10616,7 @@
     </row>
     <row r="524" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B524" s="54">
         <v>0.91</v>
@@ -10633,7 +10630,7 @@
     </row>
     <row r="525" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B525" s="54">
         <v>0.91</v>
@@ -10647,7 +10644,7 @@
     </row>
     <row r="526" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B526" s="54">
         <v>0.91</v>
@@ -10661,7 +10658,7 @@
     </row>
     <row r="527" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A527" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B527" s="54">
         <v>0.71</v>
@@ -10675,7 +10672,7 @@
     </row>
     <row r="528" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B528" s="54">
         <v>0.71</v>
@@ -10689,7 +10686,7 @@
     </row>
     <row r="529" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B529" s="54">
         <v>0.71</v>
@@ -10703,7 +10700,7 @@
     </row>
     <row r="530" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B530" s="54">
         <v>0.71</v>
@@ -10717,7 +10714,7 @@
     </row>
     <row r="531" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A531" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B531" s="54">
         <v>0.91</v>
@@ -10731,7 +10728,7 @@
     </row>
     <row r="532" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B532" s="54">
         <v>0.71</v>
@@ -10745,7 +10742,7 @@
     </row>
     <row r="533" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A533" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B533" s="54">
         <v>0.71</v>
@@ -10759,7 +10756,7 @@
     </row>
     <row r="534" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B534" s="54">
         <v>0.91</v>
@@ -10773,7 +10770,7 @@
     </row>
     <row r="535" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A535" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B535" s="54">
         <v>0.91</v>
@@ -10787,7 +10784,7 @@
     </row>
     <row r="536" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B536" s="54">
         <v>0.71</v>
@@ -10801,7 +10798,7 @@
     </row>
     <row r="537" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A537" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B537" s="54">
         <v>0.71</v>
@@ -10815,7 +10812,7 @@
     </row>
     <row r="538" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B538" s="54">
         <v>0.91</v>
@@ -10829,7 +10826,7 @@
     </row>
     <row r="539" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A539" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B539" s="54">
         <v>0.91</v>
@@ -10843,7 +10840,7 @@
     </row>
     <row r="540" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A540" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B540" s="54">
         <v>0.91</v>
@@ -10857,7 +10854,7 @@
     </row>
     <row r="541" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A541" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B541" s="54">
         <v>0.91</v>
@@ -10871,7 +10868,7 @@
     </row>
     <row r="542" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A542" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B542" s="54">
         <v>0.91</v>
@@ -10885,7 +10882,7 @@
     </row>
     <row r="543" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A543" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B543" s="54">
         <v>0.71</v>
@@ -10899,7 +10896,7 @@
     </row>
     <row r="544" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A544" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B544" s="54">
         <v>0.55000000000000004</v>
@@ -10913,7 +10910,7 @@
     </row>
     <row r="545" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A545" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B545" s="54">
         <v>0.48</v>
@@ -10927,7 +10924,7 @@
     </row>
     <row r="546" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A546" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B546" s="54">
         <v>0.76700000000000002</v>
@@ -10941,7 +10938,7 @@
     </row>
     <row r="547" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A547" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B547" s="54">
         <v>0.26700000000000002</v>
@@ -10955,7 +10952,7 @@
     </row>
     <row r="548" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A548" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B548" s="54">
         <v>7.0000000000000007E-2</v>
@@ -10969,7 +10966,7 @@
     </row>
     <row r="549" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A549" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B549" s="54">
         <v>0.79600000000000004</v>
@@ -10983,7 +10980,7 @@
     </row>
     <row r="550" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A550" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B550" s="54">
         <v>1.087</v>
@@ -10997,7 +10994,7 @@
     </row>
     <row r="551" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A551" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B551" s="54">
         <v>1.091</v>
@@ -11011,7 +11008,7 @@
     </row>
     <row r="552" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A552" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B552" s="54">
         <v>0.13</v>
@@ -11025,7 +11022,7 @@
     </row>
     <row r="553" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A553" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B553" s="54">
         <v>0.28000000000000003</v>
@@ -11039,7 +11036,7 @@
     </row>
     <row r="554" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A554" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B554" s="54">
         <v>1</v>
@@ -11053,7 +11050,7 @@
     </row>
     <row r="555" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A555" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B555" s="54">
         <v>0.46500000000000002</v>
@@ -11067,7 +11064,7 @@
     </row>
     <row r="556" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A556" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B556" s="54">
         <v>1.212</v>
@@ -11081,7 +11078,7 @@
     </row>
     <row r="557" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A557" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B557" s="54">
         <v>0.125</v>
@@ -11095,7 +11092,7 @@
     </row>
     <row r="558" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A558" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B558" s="54">
         <v>0.186</v>
@@ -11109,7 +11106,7 @@
     </row>
     <row r="559" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A559" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B559" s="54">
         <v>0.29199999999999998</v>
@@ -11123,7 +11120,7 @@
     </row>
     <row r="560" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A560" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B560" s="54">
         <v>0.105</v>
@@ -11137,7 +11134,7 @@
     </row>
     <row r="561" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A561" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B561" s="54">
         <v>0.13</v>
@@ -11151,7 +11148,7 @@
     </row>
     <row r="562" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A562" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B562" s="54">
         <v>0.67100000000000004</v>
@@ -11165,7 +11162,7 @@
     </row>
     <row r="563" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A563" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B563" s="54">
         <v>0.61</v>
@@ -11179,7 +11176,7 @@
     </row>
     <row r="564" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A564" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B564" s="54">
         <v>37</v>
@@ -11193,7 +11190,7 @@
     </row>
     <row r="565" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A565" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B565" s="54">
         <v>0.08</v>
@@ -11207,7 +11204,7 @@
     </row>
     <row r="566" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A566" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B566" s="54">
         <v>0.65500000000000003</v>
@@ -11221,7 +11218,7 @@
     </row>
     <row r="567" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A567" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B567" s="54">
         <v>1.79</v>
@@ -11235,7 +11232,7 @@
     </row>
     <row r="568" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A568" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B568" s="54">
         <v>0.36</v>
@@ -11249,7 +11246,7 @@
     </row>
     <row r="569" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A569" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B569" s="54">
         <v>0.5</v>
@@ -11263,7 +11260,7 @@
     </row>
     <row r="570" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A570" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B570" s="54">
         <v>1.07</v>
@@ -11277,7 +11274,7 @@
     </row>
     <row r="571" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A571" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B571" s="54">
         <v>0.11</v>
@@ -11291,7 +11288,7 @@
     </row>
     <row r="572" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A572" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B572" s="54">
         <v>0.505</v>
@@ -11305,7 +11302,7 @@
     </row>
     <row r="573" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A573" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B573" s="54">
         <v>0.13800000000000001</v>
@@ -11319,7 +11316,7 @@
     </row>
     <row r="574" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A574" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B574" s="54">
         <v>0.26100000000000001</v>
@@ -11333,7 +11330,7 @@
     </row>
     <row r="575" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A575" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B575" s="54">
         <v>0.38400000000000001</v>
@@ -11347,7 +11344,7 @@
     </row>
     <row r="576" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A576" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B576" s="54">
         <v>0.65</v>
@@ -11361,7 +11358,7 @@
     </row>
     <row r="577" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A577" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B577" s="54">
         <v>7.0000000000000007E-2</v>
@@ -11375,7 +11372,7 @@
     </row>
     <row r="578" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A578" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B578" s="54">
         <v>0.09</v>
@@ -11389,7 +11386,7 @@
     </row>
     <row r="579" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A579" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B579" s="54">
         <v>1.8859999999999999</v>
@@ -11403,7 +11400,7 @@
     </row>
     <row r="580" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A580" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B580" s="54">
         <v>0.33</v>
@@ -11417,7 +11414,7 @@
     </row>
     <row r="581" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A581" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B581" s="54">
         <v>0.24</v>
@@ -11431,7 +11428,7 @@
     </row>
     <row r="582" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A582" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B582" s="54">
         <v>0.95</v>
@@ -11445,7 +11442,7 @@
     </row>
     <row r="583" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A583" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B583" s="54">
         <v>0.25</v>
@@ -11459,7 +11456,7 @@
     </row>
     <row r="584" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A584" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B584" s="54">
         <v>0.15</v>
@@ -11473,7 +11470,7 @@
     </row>
     <row r="585" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A585" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B585" s="54">
         <v>0.31</v>
@@ -11487,7 +11484,7 @@
     </row>
     <row r="586" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A586" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B586" s="54">
         <v>1.1499999999999999</v>
@@ -11501,7 +11498,7 @@
     </row>
     <row r="587" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A587" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B587" s="54">
         <v>1.05</v>
@@ -11515,7 +11512,7 @@
     </row>
     <row r="588" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A588" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B588" s="54">
         <v>2.0499999999999998</v>
@@ -11529,7 +11526,7 @@
     </row>
     <row r="589" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A589" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B589" s="54">
         <v>0.27</v>
@@ -11543,7 +11540,7 @@
     </row>
     <row r="590" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A590" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B590" s="54">
         <v>1.5720000000000001</v>
@@ -11557,7 +11554,7 @@
     </row>
     <row r="591" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A591" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B591" s="54">
         <v>0.13500000000000001</v>
@@ -11571,7 +11568,7 @@
     </row>
     <row r="592" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A592" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B592" s="54">
         <v>0.19900000000000001</v>
@@ -11585,7 +11582,7 @@
     </row>
     <row r="593" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A593" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B593" s="54">
         <v>0.3</v>
@@ -11599,7 +11596,7 @@
     </row>
     <row r="594" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A594" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B594" s="54">
         <v>0.13</v>
@@ -11613,7 +11610,7 @@
     </row>
     <row r="595" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A595" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B595" s="54">
         <v>0.25</v>
@@ -11627,7 +11624,7 @@
     </row>
     <row r="596" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A596" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B596" s="54">
         <v>0.17699999999999999</v>
@@ -11641,7 +11638,7 @@
     </row>
     <row r="597" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A597" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B597" s="54">
         <v>0.12</v>
@@ -11655,7 +11652,7 @@
     </row>
     <row r="598" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B598" s="54">
         <v>1.347</v>
@@ -11669,7 +11666,7 @@
     </row>
     <row r="599" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A599" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B599" s="54">
         <v>45</v>
@@ -11683,7 +11680,7 @@
     </row>
     <row r="600" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A600" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B600" s="54">
         <v>0.84699999999999998</v>
@@ -11697,7 +11694,7 @@
     </row>
     <row r="601" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A601" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B601" s="54">
         <v>0.5</v>
@@ -11711,7 +11708,7 @@
     </row>
     <row r="602" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B602" s="54">
         <v>0.5</v>
@@ -11725,7 +11722,7 @@
     </row>
     <row r="603" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A603" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B603" s="54">
         <v>0.35</v>
@@ -11739,7 +11736,7 @@
     </row>
     <row r="604" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A604" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B604" s="54">
         <v>0.23499999999999999</v>
@@ -11753,7 +11750,7 @@
     </row>
     <row r="605" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A605" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B605" s="54">
         <v>0.65</v>
@@ -11767,13 +11764,13 @@
     </row>
     <row r="606" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A606" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B606" s="54">
         <v>220</v>
       </c>
       <c r="C606" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D606" s="6" t="s">
         <v>28</v>
@@ -11781,7 +11778,7 @@
     </row>
     <row r="607" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A607" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B607" s="54">
         <v>1.7230000000000001</v>
@@ -11795,7 +11792,7 @@
     </row>
     <row r="608" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A608" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B608" s="54">
         <v>0.45</v>
@@ -11809,7 +11806,7 @@
     </row>
     <row r="609" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A609" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B609" s="54">
         <v>2.3119999999999998</v>
@@ -11823,7 +11820,7 @@
     </row>
     <row r="610" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A610" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B610" s="54">
         <v>1.0529999999999999</v>
@@ -11837,7 +11834,7 @@
     </row>
     <row r="611" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A611" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B611" s="54">
         <v>0.35499999999999998</v>
@@ -11851,7 +11848,7 @@
     </row>
     <row r="612" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A612" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B612" s="54">
         <v>0.25</v>
@@ -11865,7 +11862,7 @@
     </row>
     <row r="613" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A613" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B613" s="54">
         <v>0.52900000000000003</v>
@@ -11879,7 +11876,7 @@
     </row>
     <row r="614" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A614" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B614" s="54">
         <v>0.5</v>
@@ -11893,7 +11890,7 @@
     </row>
     <row r="615" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A615" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B615" s="54">
         <v>5.2999999999999999E-2</v>
@@ -11907,7 +11904,7 @@
     </row>
     <row r="616" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A616" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B616" s="54">
         <v>1.2</v>
@@ -11921,7 +11918,7 @@
     </row>
     <row r="617" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A617" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B617" s="54">
         <v>0.05</v>
@@ -11935,7 +11932,7 @@
     </row>
     <row r="618" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A618" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B618" s="54">
         <v>0.8</v>
@@ -11949,7 +11946,7 @@
     </row>
     <row r="619" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A619" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B619" s="54">
         <v>0.46</v>
@@ -11963,7 +11960,7 @@
     </row>
     <row r="620" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A620" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B620" s="54">
         <v>0.06</v>
@@ -11977,13 +11974,13 @@
     </row>
     <row r="621" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A621" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B621" s="54">
         <v>0.32</v>
       </c>
       <c r="C621" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D621" s="6" t="s">
         <v>7</v>
@@ -11991,7 +11988,7 @@
     </row>
     <row r="622" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A622" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B622" s="54">
         <v>0.25</v>
@@ -12005,7 +12002,7 @@
     </row>
     <row r="623" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A623" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B623" s="54">
         <v>0.52</v>
@@ -12019,7 +12016,7 @@
     </row>
     <row r="624" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A624" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B624" s="54">
         <v>3.3580000000000001</v>
@@ -12033,7 +12030,7 @@
     </row>
     <row r="625" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A625" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B625" s="54">
         <v>2.1</v>
@@ -12047,7 +12044,7 @@
     </row>
     <row r="626" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A626" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B626" s="54">
         <v>1.35</v>
@@ -12061,7 +12058,7 @@
     </row>
     <row r="627" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A627" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B627" s="54">
         <v>1.65</v>
@@ -12075,7 +12072,7 @@
     </row>
     <row r="628" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A628" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B628" s="54">
         <v>0.39</v>
@@ -12089,7 +12086,7 @@
     </row>
     <row r="629" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A629" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B629" s="54">
         <v>0.37</v>
@@ -12103,7 +12100,7 @@
     </row>
     <row r="630" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A630" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B630" s="54">
         <v>0.39</v>
@@ -12117,7 +12114,7 @@
     </row>
     <row r="631" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A631" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B631" s="54">
         <v>1.4390000000000001</v>
@@ -12131,7 +12128,7 @@
     </row>
     <row r="632" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A632" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B632" s="54">
         <v>2</v>
@@ -12145,7 +12142,7 @@
     </row>
     <row r="633" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A633" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B633" s="54">
         <v>0.74</v>
@@ -12159,7 +12156,7 @@
     </row>
     <row r="634" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A634" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B634" s="54">
         <v>0.74</v>
@@ -12173,7 +12170,7 @@
     </row>
     <row r="635" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A635" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B635" s="54">
         <v>0.9</v>
@@ -12187,7 +12184,7 @@
     </row>
     <row r="636" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A636" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B636" s="54">
         <v>450</v>
@@ -12201,7 +12198,7 @@
     </row>
     <row r="637" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A637" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B637" s="54">
         <v>0.3</v>
@@ -12215,7 +12212,7 @@
     </row>
     <row r="638" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A638" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B638" s="54">
         <v>0.25</v>
@@ -12224,32 +12221,32 @@
         <v>4</v>
       </c>
       <c r="D638" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="639" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A639" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B639" s="54">
         <v>0.38</v>
       </c>
       <c r="C639" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D639" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="640" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A640" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B640" s="54">
         <v>0.22</v>
       </c>
       <c r="C640" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D640" s="6" t="s">
         <v>10</v>
@@ -12257,7 +12254,7 @@
     </row>
     <row r="641" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A641" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B641" s="54">
         <v>1200</v>
@@ -12271,13 +12268,13 @@
     </row>
     <row r="642" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A642" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B642" s="54">
         <v>0.19</v>
       </c>
       <c r="C642" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D642" s="6" t="s">
         <v>10</v>
@@ -12285,13 +12282,13 @@
     </row>
     <row r="643" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A643" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B643" s="54">
         <v>0.82399999999999995</v>
       </c>
       <c r="C643" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D643" s="6" t="s">
         <v>7</v>
@@ -12299,13 +12296,13 @@
     </row>
     <row r="644" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A644" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B644" s="54">
         <v>170</v>
       </c>
       <c r="C644" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D644" s="6" t="s">
         <v>4</v>
@@ -12313,7 +12310,7 @@
     </row>
     <row r="645" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A645" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B645" s="54">
         <v>0.15</v>
@@ -12327,7 +12324,7 @@
     </row>
     <row r="646" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A646" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B646" s="54">
         <v>0.08</v>
@@ -12341,7 +12338,7 @@
     </row>
     <row r="647" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A647" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B647" s="54">
         <v>65</v>
@@ -12355,7 +12352,7 @@
     </row>
     <row r="648" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A648" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B648" s="54">
         <v>0.3</v>
@@ -12369,7 +12366,7 @@
     </row>
     <row r="649" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A649" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B649" s="54">
         <v>0.16</v>
@@ -12383,7 +12380,7 @@
     </row>
     <row r="650" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A650" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B650" s="54">
         <v>0.57199999999999995</v>
@@ -12397,7 +12394,7 @@
     </row>
     <row r="651" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A651" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B651" s="54">
         <v>0.28599999999999998</v>
@@ -12411,7 +12408,7 @@
     </row>
     <row r="652" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A652" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B652" s="54">
         <v>1.7</v>
@@ -12425,7 +12422,7 @@
     </row>
     <row r="653" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A653" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B653" s="54">
         <v>0.32</v>
@@ -12439,7 +12436,7 @@
     </row>
     <row r="654" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A654" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B654" s="54">
         <v>83</v>
@@ -12453,7 +12450,7 @@
     </row>
     <row r="655" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A655" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B655" s="54">
         <v>0.6</v>
@@ -12462,12 +12459,12 @@
         <v>4</v>
       </c>
       <c r="D655" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="656" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A656" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B656" s="54">
         <v>0.27500000000000002</v>
@@ -12481,7 +12478,7 @@
     </row>
     <row r="657" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A657" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B657" s="54">
         <v>0.27500000000000002</v>
@@ -12495,7 +12492,7 @@
     </row>
     <row r="658" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A658" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B658" s="54">
         <v>0.9</v>
@@ -12509,7 +12506,7 @@
     </row>
     <row r="659" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A659" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B659" s="55">
         <v>0.6</v>
@@ -12523,7 +12520,7 @@
     </row>
     <row r="660" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A660" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B660" s="54">
         <v>0.75</v>
@@ -12537,7 +12534,7 @@
     </row>
     <row r="661" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A661" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B661" s="54">
         <v>0.3</v>
@@ -12551,7 +12548,7 @@
     </row>
     <row r="662" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A662" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B662" s="56">
         <v>0.185</v>
@@ -12565,7 +12562,7 @@
     </row>
     <row r="663" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A663" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B663" s="56">
         <v>0.12</v>
@@ -12579,7 +12576,7 @@
     </row>
     <row r="664" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A664" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B664" s="56">
         <v>1.2649999999999999</v>
@@ -12593,7 +12590,7 @@
     </row>
     <row r="665" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A665" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B665" s="56">
         <v>1.84</v>
@@ -12607,7 +12604,7 @@
     </row>
     <row r="666" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A666" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B666" s="54">
         <v>0.74814814814814812</v>
@@ -12621,7 +12618,7 @@
     </row>
     <row r="667" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A667" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B667" s="56">
         <v>0.15</v>
@@ -12635,7 +12632,7 @@
     </row>
     <row r="668" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A668" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B668" s="56">
         <v>0.47199999999999998</v>
@@ -12649,7 +12646,7 @@
     </row>
     <row r="669" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A669" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B669" s="54">
         <v>1.6</v>
@@ -12663,7 +12660,7 @@
     </row>
     <row r="670" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A670" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B670" s="54">
         <v>1.6</v>
@@ -12677,7 +12674,7 @@
     </row>
     <row r="671" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A671" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B671" s="54">
         <v>1.6</v>
@@ -12691,7 +12688,7 @@
     </row>
     <row r="672" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A672" s="10" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B672" s="56">
         <v>2.8639999999999999</v>
@@ -12705,7 +12702,7 @@
     </row>
     <row r="673" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A673" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B673" s="56">
         <v>1.579</v>
@@ -12719,7 +12716,7 @@
     </row>
     <row r="674" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A674" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B674" s="54">
         <v>1.94</v>
@@ -12733,13 +12730,13 @@
     </row>
     <row r="675" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A675" s="50" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B675" s="55">
         <v>0.11700000000000001</v>
       </c>
       <c r="C675" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D675" s="13" t="s">
         <v>5</v>
@@ -12747,13 +12744,13 @@
     </row>
     <row r="676" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A676" s="50" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B676" s="55">
         <v>1.2</v>
       </c>
       <c r="C676" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D676" s="13" t="s">
         <v>5</v>
@@ -12761,7 +12758,7 @@
     </row>
     <row r="677" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A677" s="50" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B677" s="55">
         <v>0.27500000000000002</v>
@@ -12775,13 +12772,13 @@
     </row>
     <row r="678" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A678" s="50" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B678" s="55">
         <v>45</v>
       </c>
       <c r="C678" s="13" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D678" s="13" t="s">
         <v>10</v>
@@ -12789,7 +12786,7 @@
     </row>
     <row r="679" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A679" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B679" s="54">
         <v>3</v>
@@ -12803,7 +12800,7 @@
     </row>
     <row r="680" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A680" s="51" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B680" s="54">
         <v>0.22</v>
@@ -12817,7 +12814,7 @@
     </row>
     <row r="681" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A681" s="51" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B681" s="54">
         <v>0.17</v>
@@ -12831,7 +12828,7 @@
     </row>
     <row r="682" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A682" s="59" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B682" s="58">
         <v>0.91</v>
@@ -12845,7 +12842,7 @@
     </row>
     <row r="683" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A683" s="61" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B683" s="62">
         <v>0.38</v>
@@ -12854,26 +12851,26 @@
         <v>1</v>
       </c>
       <c r="D683" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="684" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A684" s="61" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B684" s="62">
         <v>0.22</v>
       </c>
       <c r="C684" s="63" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D684" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="685" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A685" s="61" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B685" s="62">
         <v>0.59</v>
@@ -12882,12 +12879,12 @@
         <v>32</v>
       </c>
       <c r="D685" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="686" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A686" s="61" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B686" s="62">
         <v>3.1</v>
@@ -12896,12 +12893,12 @@
         <v>32</v>
       </c>
       <c r="D686" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="687" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A687" s="61" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B687" s="62">
         <v>6.9</v>
@@ -12910,12 +12907,12 @@
         <v>32</v>
       </c>
       <c r="D687" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="688" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A688" s="61" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B688" s="62">
         <v>6.3</v>
@@ -12924,18 +12921,18 @@
         <v>32</v>
       </c>
       <c r="D688" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="689" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A689" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B689" s="64">
         <v>0.499</v>
       </c>
       <c r="C689" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D689" s="6" t="s">
         <v>10</v>
@@ -12943,7 +12940,7 @@
     </row>
     <row r="690" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A690" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B690" s="64">
         <v>0.4</v>
@@ -12957,7 +12954,7 @@
     </row>
     <row r="691" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A691" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B691" s="64">
         <v>0.36</v>
@@ -12971,7 +12968,7 @@
     </row>
     <row r="692" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A692" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B692" s="64">
         <v>0.2</v>
@@ -12985,7 +12982,7 @@
     </row>
     <row r="693" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A693" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B693" s="64">
         <v>0.25</v>
@@ -12999,7 +12996,7 @@
     </row>
     <row r="694" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A694" s="50" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B694" s="64">
         <v>0.64</v>
@@ -13013,7 +13010,7 @@
     </row>
     <row r="695" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A695" s="50" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B695" s="64">
         <v>0.85</v>
@@ -13027,7 +13024,7 @@
     </row>
     <row r="696" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="50" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B696" s="64">
         <v>0.15</v>
@@ -13041,7 +13038,7 @@
     </row>
     <row r="697" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A697" s="65" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B697" s="66">
         <v>1.3</v>
@@ -13050,26 +13047,26 @@
         <v>32</v>
       </c>
       <c r="D697" s="67" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="698" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A698" s="68" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B698" s="69">
         <v>0</v>
       </c>
       <c r="C698" s="63" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D698" s="63" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="699" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A699" s="68" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B699" s="69">
         <v>3</v>
@@ -13078,12 +13075,12 @@
         <v>32</v>
       </c>
       <c r="D699" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="700" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A700" s="68" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B700" s="69">
         <v>2</v>
@@ -13092,12 +13089,12 @@
         <v>32</v>
       </c>
       <c r="D700" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="701" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A701" s="68" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B701" s="69">
         <v>1.6</v>
@@ -13106,12 +13103,12 @@
         <v>32</v>
       </c>
       <c r="D701" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="702" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A702" s="68" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B702" s="69">
         <v>0.25</v>
@@ -13120,12 +13117,12 @@
         <v>32</v>
       </c>
       <c r="D702" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="703" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A703" s="68" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B703" s="69">
         <v>0.4</v>
@@ -13134,12 +13131,12 @@
         <v>32</v>
       </c>
       <c r="D703" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="704" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A704" s="68" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B704" s="69">
         <v>4</v>
@@ -13148,12 +13145,12 @@
         <v>32</v>
       </c>
       <c r="D704" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="705" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A705" s="70" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B705" s="71">
         <v>1</v>
@@ -13162,12 +13159,12 @@
         <v>32</v>
       </c>
       <c r="D705" s="72" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="706" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A706" s="68" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B706" s="69">
         <v>26</v>
@@ -13176,12 +13173,12 @@
         <v>32</v>
       </c>
       <c r="D706" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="707" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A707" s="68" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B707" s="69">
         <v>26</v>
@@ -13190,12 +13187,12 @@
         <v>32</v>
       </c>
       <c r="D707" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="708" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A708" s="68" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B708" s="69">
         <v>26</v>
@@ -13204,12 +13201,12 @@
         <v>32</v>
       </c>
       <c r="D708" s="63" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="709" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A709" s="68" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B709" s="69">
         <v>6.06</v>
@@ -13218,12 +13215,12 @@
         <v>32</v>
       </c>
       <c r="D709" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="710" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A710" s="68" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B710" s="69">
         <v>0.48</v>
@@ -13232,12 +13229,12 @@
         <v>4</v>
       </c>
       <c r="D710" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="711" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A711" s="68" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B711" s="69">
         <v>0.54</v>
@@ -13246,12 +13243,12 @@
         <v>4</v>
       </c>
       <c r="D711" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="712" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A712" s="68" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B712" s="69">
         <v>0.38</v>
@@ -13260,12 +13257,12 @@
         <v>4</v>
       </c>
       <c r="D712" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="713" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A713" s="68" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B713" s="69">
         <v>0.39</v>
@@ -13274,12 +13271,12 @@
         <v>4</v>
       </c>
       <c r="D713" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="714" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A714" s="50" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B714" s="64">
         <v>95</v>
@@ -13293,7 +13290,7 @@
     </row>
     <row r="715" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A715" s="50" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B715" s="64">
         <v>100</v>
@@ -13307,7 +13304,7 @@
     </row>
     <row r="716" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A716" s="50" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B716" s="64">
         <v>135</v>
@@ -13321,7 +13318,7 @@
     </row>
     <row r="717" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A717" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B717" s="64">
         <v>20</v>
@@ -13330,12 +13327,12 @@
         <v>32</v>
       </c>
       <c r="D717" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="718" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A718" s="50" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B718" s="64">
         <v>0.9</v>
@@ -13349,7 +13346,7 @@
     </row>
     <row r="719" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A719" s="50" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B719" s="64">
         <v>0.19</v>
@@ -13363,7 +13360,7 @@
     </row>
     <row r="720" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A720" s="50" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B720" s="64">
         <v>1.05</v>
@@ -13377,7 +13374,7 @@
     </row>
     <row r="721" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A721" s="50" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B721" s="64">
         <v>0.33</v>
@@ -13391,13 +13388,13 @@
     </row>
     <row r="722" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A722" s="50" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B722" s="64">
         <v>40</v>
       </c>
       <c r="C722" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D722" s="6" t="s">
         <v>28</v>
@@ -13405,13 +13402,13 @@
     </row>
     <row r="723" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A723" s="50" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B723" s="64">
         <v>40</v>
       </c>
       <c r="C723" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D723" s="6" t="s">
         <v>28</v>
@@ -13419,13 +13416,13 @@
     </row>
     <row r="724" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A724" s="74" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B724" s="73">
         <v>40</v>
       </c>
       <c r="C724" s="60" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D724" s="60" t="s">
         <v>28</v>
@@ -13433,7 +13430,7 @@
     </row>
     <row r="725" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A725" s="61" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B725" s="69">
         <v>0.35</v>
@@ -13442,12 +13439,12 @@
         <v>4</v>
       </c>
       <c r="D725" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="726" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A726" s="61" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B726" s="69">
         <v>14.91</v>
@@ -13456,12 +13453,12 @@
         <v>32</v>
       </c>
       <c r="D726" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="727" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A727" s="61" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B727" s="69">
         <v>1.62</v>
@@ -13475,7 +13472,7 @@
     </row>
     <row r="728" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A728" s="61" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B728" s="69">
         <v>0</v>
@@ -13484,12 +13481,12 @@
         <v>1</v>
       </c>
       <c r="D728" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="729" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A729" s="61" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B729" s="69">
         <v>0.24</v>
@@ -13498,40 +13495,40 @@
         <v>4</v>
       </c>
       <c r="D729" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="730" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A730" s="61" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B730" s="69">
         <v>94.5</v>
       </c>
       <c r="C730" s="63" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D730" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="731" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A731" s="61" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B731" s="69">
         <v>30</v>
       </c>
       <c r="C731" s="63" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D731" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="732" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A732" s="61" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B732" s="69">
         <v>0.18</v>
@@ -13540,12 +13537,12 @@
         <v>1</v>
       </c>
       <c r="D732" s="63" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="733" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A733" s="61" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B733" s="69">
         <v>0.74</v>
@@ -13559,7 +13556,7 @@
     </row>
     <row r="734" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A734" s="61" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B734" s="69">
         <v>1.6</v>
@@ -13573,7 +13570,7 @@
     </row>
     <row r="735" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A735" s="61" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B735" s="69">
         <v>1.55</v>
@@ -13587,7 +13584,7 @@
     </row>
     <row r="736" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A736" s="61" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B736" s="69">
         <v>1.1499999999999999</v>
@@ -13601,7 +13598,7 @@
     </row>
     <row r="737" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A737" s="61" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B737" s="69">
         <v>2.2000000000000002</v>
@@ -13615,7 +13612,7 @@
     </row>
     <row r="738" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A738" s="61" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B738" s="69">
         <v>0.82</v>
@@ -13629,7 +13626,7 @@
     </row>
     <row r="739" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A739" s="61" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B739" s="69">
         <v>1.5</v>
@@ -13643,7 +13640,7 @@
     </row>
     <row r="740" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A740" s="61" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B740" s="69">
         <v>1.05</v>
@@ -13657,7 +13654,7 @@
     </row>
     <row r="741" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A741" s="61" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B741" s="69">
         <v>1.3</v>
@@ -13671,7 +13668,7 @@
     </row>
     <row r="742" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A742" s="61" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B742" s="69">
         <v>0.12</v>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC841BC-E7A6-4237-917E-58853D97759A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3663F3C4-48A0-44AC-B5D1-F6157054484F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="771">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2340,6 +2340,9 @@
   </si>
   <si>
     <t>Dextrose Powder</t>
+  </si>
+  <si>
+    <t>Banana C - Gelato</t>
   </si>
 </sst>
 </file>
@@ -13681,10 +13684,18 @@
       </c>
     </row>
     <row r="743" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A743" s="61"/>
-      <c r="B743" s="69"/>
-      <c r="C743" s="63"/>
-      <c r="D743" s="63"/>
+      <c r="A743" s="61" t="s">
+        <v>770</v>
+      </c>
+      <c r="B743" s="69">
+        <v>1.07</v>
+      </c>
+      <c r="C743" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D743" s="63" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="744" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A744" s="61"/>

--- a/costs.xlsx
+++ b/costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markd\Desktop\Recipe-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3663F3C4-48A0-44AC-B5D1-F6157054484F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F68E73A-F6EE-4D56-9DC2-E2B402FEA658}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28800" windowHeight="11235" xr2:uid="{AB868D58-4637-4C24-A8D9-A3598505BA7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="772">
   <si>
     <t xml:space="preserve">Absolut Vodka Blue </t>
   </si>
@@ -2343,6 +2343,9 @@
   </si>
   <si>
     <t>Banana C - Gelato</t>
+  </si>
+  <si>
+    <t>Matcha Powder - Ceremonial</t>
   </si>
 </sst>
 </file>
@@ -3298,18 +3301,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9537A42C-F4AF-418F-A769-B84E72EA6B4B}">
   <dimension ref="A1:D806"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>457</v>
       </c>
@@ -3323,7 +3326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>464</v>
       </c>
@@ -3337,7 +3340,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>476</v>
       </c>
@@ -3351,7 +3354,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>465</v>
       </c>
@@ -3365,7 +3368,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>751</v>
       </c>
@@ -3379,7 +3382,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>477</v>
       </c>
@@ -3393,7 +3396,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>478</v>
       </c>
@@ -3407,7 +3410,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>479</v>
       </c>
@@ -3421,7 +3424,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>469</v>
       </c>
@@ -3435,7 +3438,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>470</v>
       </c>
@@ -3449,7 +3452,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>480</v>
       </c>
@@ -3463,7 +3466,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>481</v>
       </c>
@@ -3477,7 +3480,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="14"